--- a/Deliverables/Interface_Board/BOM/NEW-6 Prototypes_Interface_Board.xlsx
+++ b/Deliverables/Interface_Board/BOM/NEW-6 Prototypes_Interface_Board.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ChristianRaun-EthercatDesign\Deliverables\Interface_Board\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42F92E23-0475-4E30-B82A-075C8F0EE997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF979C34-0560-475B-8E10-1F732207B98C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="257">
   <si>
     <t>Bill of Material (BOM) for Interface_Board</t>
   </si>
@@ -673,10 +673,6 @@
     <t>0603WAF150LT5E</t>
   </si>
   <si>
-    <t xml:space="preserve"> Resistors 75V150mΩ 0603 Chip Resistor - Surface Mount ROHS
-</t>
-  </si>
-  <si>
     <t>C45879</t>
   </si>
   <si>
@@ -684,9 +680,6 @@
   </si>
   <si>
     <t>R#6,R#7</t>
-  </si>
-  <si>
-    <t>C#1,C#2,C#3,C#4</t>
   </si>
   <si>
     <t>CL10A475KA8NQNC</t>
@@ -826,6 +819,49 @@
   <si>
     <t>------</t>
   </si>
+  <si>
+    <t>C#1,C#2,C#3,C#4,C#12,C#13</t>
+  </si>
+  <si>
+    <t>GCM1885C2A471GA16D</t>
+  </si>
+  <si>
+    <t>C#14,C#15,C#16,C#17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">470 pF ±2% 100V Ceramic Capacitor C0G,0603
+</t>
+  </si>
+  <si>
+    <t>C437459</t>
+  </si>
+  <si>
+    <t>470pF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RC0603JR-0747KL
+</t>
+  </si>
+  <si>
+    <t>C127447</t>
+  </si>
+  <si>
+    <t>47K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RES 47K OHM 5% 1/10W 0603
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resistors 75V150mΩ 0603 Chip Resistor - Surface Mount ROHS
+</t>
+  </si>
+  <si>
+    <t>R01,R02</t>
+  </si>
+  <si>
+    <t>2x13</t>
+  </si>
 </sst>
 </file>
 
@@ -834,12 +870,19 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.0000"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1429,24 +1472,24 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="176">
+  <cellXfs count="180">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1455,19 +1498,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1476,19 +1519,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1500,25 +1543,22 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1529,7 +1569,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1541,10 +1581,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1553,7 +1593,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1565,16 +1605,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1595,19 +1635,19 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
@@ -1616,37 +1656,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="6" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="14" fillId="6" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1654,16 +1685,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
@@ -1675,89 +1706,86 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="22" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="1" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="22" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="22" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="22" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="22" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="22" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="22" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="21" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="21" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="28" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="28" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="27" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1766,13 +1794,13 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="15" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
@@ -1784,10 +1812,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="26" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="26" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1800,23 +1828,23 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="24" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="24" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1828,17 +1856,137 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="22" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="22" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="22" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="27" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="28" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="22" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="21" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="22" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="22" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1846,102 +1994,7 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="7" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="7" borderId="22" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="27" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="28" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="22" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="21" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2218,7 +2271,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AD59"/>
+  <dimension ref="A1:AD61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="2" customWidth="1"/>
@@ -2238,22 +2291,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="16.5" thickBot="1">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="168" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73"/>
-      <c r="J1" s="73"/>
-      <c r="K1" s="73"/>
-      <c r="L1" s="73"/>
-      <c r="M1" s="73"/>
-      <c r="N1" s="92"/>
+      <c r="B1" s="169"/>
+      <c r="C1" s="169"/>
+      <c r="D1" s="169"/>
+      <c r="E1" s="169"/>
+      <c r="F1" s="169"/>
+      <c r="G1" s="169"/>
+      <c r="H1" s="169"/>
+      <c r="I1" s="169"/>
+      <c r="J1" s="169"/>
+      <c r="K1" s="169"/>
+      <c r="L1" s="169"/>
+      <c r="M1" s="169"/>
+      <c r="N1" s="170"/>
     </row>
     <row r="2" spans="1:30" s="1" customFormat="1" ht="16.5" thickBot="1">
       <c r="A2" s="3" t="s">
@@ -2292,10 +2345,10 @@
       <c r="L2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="69" t="s">
+      <c r="M2" s="68" t="s">
         <v>181</v>
       </c>
-      <c r="N2" s="93" t="s">
+      <c r="N2" s="88" t="s">
         <v>180</v>
       </c>
       <c r="O2"/>
@@ -2322,41 +2375,41 @@
       <c r="B3" s="172" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="144" t="s">
+      <c r="C3" s="139" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="145" t="s">
-        <v>209</v>
-      </c>
-      <c r="E3" s="146" t="s">
+      <c r="D3" s="140" t="s">
+        <v>244</v>
+      </c>
+      <c r="E3" s="141" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="146" t="s">
+      <c r="F3" s="141" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="146" t="s">
+      <c r="G3" s="141" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="147" t="s">
+      <c r="H3" s="142" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="148" t="s">
+      <c r="I3" s="143" t="s">
         <v>19</v>
       </c>
-      <c r="J3" s="146" t="s">
+      <c r="J3" s="141" t="s">
         <v>20</v>
       </c>
-      <c r="K3" s="149">
+      <c r="K3" s="144">
         <v>50</v>
       </c>
-      <c r="L3" s="149">
-        <v>4</v>
-      </c>
-      <c r="M3" s="149">
+      <c r="L3" s="144">
+        <v>6</v>
+      </c>
+      <c r="M3" s="144">
         <f>L3*6</f>
-        <v>24</v>
-      </c>
-      <c r="N3" s="150" t="s">
+        <v>36</v>
+      </c>
+      <c r="N3" s="145" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2365,41 +2418,41 @@
         <v>2</v>
       </c>
       <c r="B4" s="173"/>
-      <c r="C4" s="151" t="s">
+      <c r="C4" s="146" t="s">
+        <v>209</v>
+      </c>
+      <c r="D4" s="147" t="s">
+        <v>210</v>
+      </c>
+      <c r="E4" s="132" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="133" t="s">
+        <v>208</v>
+      </c>
+      <c r="G4" s="133" t="s">
         <v>211</v>
       </c>
-      <c r="D4" s="152" t="s">
+      <c r="H4" s="148" t="s">
         <v>212</v>
       </c>
-      <c r="E4" s="137" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="138" t="s">
-        <v>210</v>
-      </c>
-      <c r="G4" s="138" t="s">
+      <c r="I4" s="149" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" s="133" t="s">
         <v>213</v>
       </c>
-      <c r="H4" s="153" t="s">
-        <v>214</v>
-      </c>
-      <c r="I4" s="154" t="s">
-        <v>19</v>
-      </c>
-      <c r="J4" s="138" t="s">
-        <v>215</v>
-      </c>
-      <c r="K4" s="139">
+      <c r="K4" s="134">
         <v>20</v>
       </c>
-      <c r="L4" s="139">
+      <c r="L4" s="134">
         <v>1</v>
       </c>
-      <c r="M4" s="139">
-        <f t="shared" ref="M4:M5" si="0">L4*6</f>
+      <c r="M4" s="134">
+        <f t="shared" ref="M4:M6" si="0">L4*6</f>
         <v>6</v>
       </c>
-      <c r="N4" s="155" t="s">
+      <c r="N4" s="150" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2408,41 +2461,41 @@
         <v>3</v>
       </c>
       <c r="B5" s="173"/>
-      <c r="C5" s="151" t="s">
-        <v>220</v>
-      </c>
-      <c r="D5" s="152" t="s">
-        <v>219</v>
-      </c>
-      <c r="E5" s="137" t="s">
+      <c r="C5" s="146" t="s">
+        <v>218</v>
+      </c>
+      <c r="D5" s="147" t="s">
+        <v>217</v>
+      </c>
+      <c r="E5" s="132" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="138" t="s">
+      <c r="F5" s="133" t="s">
+        <v>214</v>
+      </c>
+      <c r="G5" s="133" t="s">
+        <v>211</v>
+      </c>
+      <c r="H5" s="148" t="s">
+        <v>215</v>
+      </c>
+      <c r="I5" s="149" t="s">
+        <v>19</v>
+      </c>
+      <c r="J5" s="133" t="s">
         <v>216</v>
       </c>
-      <c r="G5" s="138" t="s">
-        <v>213</v>
-      </c>
-      <c r="H5" s="153" t="s">
-        <v>217</v>
-      </c>
-      <c r="I5" s="154" t="s">
-        <v>19</v>
-      </c>
-      <c r="J5" s="138" t="s">
-        <v>218</v>
-      </c>
-      <c r="K5" s="139">
+      <c r="K5" s="134">
         <v>50</v>
       </c>
-      <c r="L5" s="139">
+      <c r="L5" s="134">
         <v>2</v>
       </c>
-      <c r="M5" s="139">
+      <c r="M5" s="134">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="N5" s="155" t="s">
+      <c r="N5" s="150" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2451,41 +2504,41 @@
         <v>4</v>
       </c>
       <c r="B6" s="173"/>
-      <c r="C6" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="37" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="38" t="s">
+      <c r="C6" s="176" t="s">
+        <v>247</v>
+      </c>
+      <c r="D6" s="147" t="s">
+        <v>246</v>
+      </c>
+      <c r="E6" s="132" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="175" t="s">
+        <v>245</v>
+      </c>
+      <c r="G6" s="132" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="148" t="s">
+        <v>248</v>
+      </c>
+      <c r="I6" s="149" t="s">
+        <v>19</v>
+      </c>
+      <c r="J6" s="175" t="s">
+        <v>249</v>
+      </c>
+      <c r="K6" s="134">
+        <v>30</v>
+      </c>
+      <c r="L6" s="134">
+        <v>4</v>
+      </c>
+      <c r="M6" s="134">
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="F6" s="37" t="s">
-        <v>25</v>
-      </c>
-      <c r="G6" s="38" t="s">
-        <v>26</v>
-      </c>
-      <c r="H6" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="I6" s="39" t="s">
-        <v>19</v>
-      </c>
-      <c r="J6" s="38" t="s">
-        <v>28</v>
-      </c>
-      <c r="K6" s="11">
-        <v>10</v>
-      </c>
-      <c r="L6" s="8">
-        <v>1</v>
-      </c>
-      <c r="M6" s="11">
-        <f t="shared" ref="M6:M42" si="1">L6*6</f>
-        <v>6</v>
-      </c>
-      <c r="N6" s="87" t="s">
+      <c r="N6" s="150" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2494,41 +2547,41 @@
         <v>5</v>
       </c>
       <c r="B7" s="173"/>
-      <c r="C7" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="37" t="s">
-        <v>30</v>
-      </c>
-      <c r="E7" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="40" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="I7" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="J7" s="38" t="s">
-        <v>35</v>
+      <c r="C7" s="35" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="F7" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="I7" s="38" t="s">
+        <v>19</v>
+      </c>
+      <c r="J7" s="37" t="s">
+        <v>28</v>
       </c>
       <c r="K7" s="11">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="L7" s="8">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="M7" s="11">
-        <f t="shared" si="1"/>
-        <v>48</v>
-      </c>
-      <c r="N7" s="88" t="s">
+        <f t="shared" ref="M7:M44" si="1">L7*6</f>
+        <v>6</v>
+      </c>
+      <c r="N7" s="83" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2537,41 +2590,41 @@
         <v>6</v>
       </c>
       <c r="B8" s="173"/>
-      <c r="C8" s="156" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" s="138" t="s">
-        <v>235</v>
-      </c>
-      <c r="E8" s="137" t="s">
+      <c r="C8" s="35" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="167" t="s">
-        <v>37</v>
-      </c>
-      <c r="G8" s="154" t="s">
-        <v>38</v>
-      </c>
-      <c r="H8" s="81" t="s">
-        <v>39</v>
-      </c>
-      <c r="I8" s="137" t="s">
-        <v>40</v>
-      </c>
-      <c r="J8" s="137" t="s">
-        <v>41</v>
-      </c>
-      <c r="K8" s="139">
-        <v>50</v>
-      </c>
-      <c r="L8" s="81">
-        <v>3</v>
-      </c>
-      <c r="M8" s="139">
+      <c r="F8" s="39" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="J8" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="K8" s="11">
+        <v>100</v>
+      </c>
+      <c r="L8" s="8">
+        <v>8</v>
+      </c>
+      <c r="M8" s="11">
         <f t="shared" si="1"/>
-        <v>18</v>
-      </c>
-      <c r="N8" s="168" t="s">
+        <v>48</v>
+      </c>
+      <c r="N8" s="84" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2580,41 +2633,41 @@
         <v>7</v>
       </c>
       <c r="B9" s="173"/>
-      <c r="C9" s="41" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" s="37" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" s="42" t="s">
-        <v>44</v>
-      </c>
-      <c r="F9" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="G9" s="43" t="s">
-        <v>46</v>
-      </c>
-      <c r="H9" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="I9" s="39" t="s">
-        <v>19</v>
-      </c>
-      <c r="J9" s="42" t="s">
-        <v>48</v>
-      </c>
-      <c r="K9" s="11">
-        <v>10</v>
-      </c>
-      <c r="L9" s="29">
-        <v>1</v>
-      </c>
-      <c r="M9" s="11">
+      <c r="C9" s="151" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="133" t="s">
+        <v>233</v>
+      </c>
+      <c r="E9" s="132" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="162" t="s">
+        <v>37</v>
+      </c>
+      <c r="G9" s="149" t="s">
+        <v>38</v>
+      </c>
+      <c r="H9" s="77" t="s">
+        <v>39</v>
+      </c>
+      <c r="I9" s="132" t="s">
+        <v>40</v>
+      </c>
+      <c r="J9" s="132" t="s">
+        <v>41</v>
+      </c>
+      <c r="K9" s="134">
+        <v>50</v>
+      </c>
+      <c r="L9" s="77">
+        <v>3</v>
+      </c>
+      <c r="M9" s="134">
         <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="N9" s="89" t="s">
+        <v>18</v>
+      </c>
+      <c r="N9" s="163" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2623,120 +2676,119 @@
         <v>8</v>
       </c>
       <c r="B10" s="173"/>
-      <c r="C10" s="156" t="s">
-        <v>49</v>
-      </c>
-      <c r="D10" s="138" t="s">
-        <v>236</v>
-      </c>
-      <c r="E10" s="137" t="s">
+      <c r="C10" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" s="36" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="F10" s="137" t="s">
-        <v>50</v>
-      </c>
-      <c r="G10" s="154" t="s">
+      <c r="F10" s="36" t="s">
+        <v>45</v>
+      </c>
+      <c r="G10" s="42" t="s">
         <v>46</v>
       </c>
-      <c r="H10" s="81" t="s">
-        <v>51</v>
-      </c>
-      <c r="I10" s="154" t="s">
+      <c r="H10" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="I10" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="J10" s="137" t="s">
+      <c r="J10" s="41" t="s">
         <v>48</v>
       </c>
-      <c r="K10" s="139">
-        <v>12</v>
-      </c>
-      <c r="L10" s="81">
-        <v>3</v>
-      </c>
-      <c r="M10" s="139">
+      <c r="K10" s="11">
+        <v>10</v>
+      </c>
+      <c r="L10" s="28">
+        <v>1</v>
+      </c>
+      <c r="M10" s="11">
         <f t="shared" si="1"/>
-        <v>18</v>
-      </c>
-      <c r="N10" s="168" t="s">
+        <v>6</v>
+      </c>
+      <c r="N10" s="85" t="s">
         <v>21</v>
       </c>
-      <c r="O10" s="31"/>
     </row>
     <row r="11" spans="1:30" ht="15.75" thickBot="1">
       <c r="A11" s="6">
         <v>9</v>
       </c>
       <c r="B11" s="173"/>
-      <c r="C11" s="82" t="s">
-        <v>162</v>
-      </c>
-      <c r="D11" s="70" t="s">
-        <v>52</v>
-      </c>
-      <c r="E11" s="62" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" s="62" t="s">
-        <v>163</v>
-      </c>
-      <c r="G11" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="H11" s="80" t="s">
-        <v>243</v>
-      </c>
-      <c r="I11" s="39" t="s">
+      <c r="C11" s="151" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" s="133" t="s">
+        <v>234</v>
+      </c>
+      <c r="E11" s="132" t="s">
+        <v>44</v>
+      </c>
+      <c r="F11" s="132" t="s">
+        <v>50</v>
+      </c>
+      <c r="G11" s="149" t="s">
+        <v>46</v>
+      </c>
+      <c r="H11" s="77" t="s">
+        <v>51</v>
+      </c>
+      <c r="I11" s="149" t="s">
         <v>19</v>
       </c>
-      <c r="J11" s="42" t="s">
-        <v>53</v>
-      </c>
-      <c r="K11" s="11">
+      <c r="J11" s="132" t="s">
+        <v>48</v>
+      </c>
+      <c r="K11" s="134">
         <v>20</v>
       </c>
-      <c r="L11" s="12">
-        <v>1</v>
-      </c>
-      <c r="M11" s="11">
+      <c r="L11" s="77">
+        <v>3</v>
+      </c>
+      <c r="M11" s="134">
         <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="N11" s="90" t="s">
+        <v>18</v>
+      </c>
+      <c r="N11" s="163" t="s">
         <v>21</v>
       </c>
-      <c r="O11" s="31"/>
+      <c r="O11" s="30"/>
     </row>
     <row r="12" spans="1:30" ht="15.75" thickBot="1">
       <c r="A12" s="6">
         <v>10</v>
       </c>
       <c r="B12" s="173"/>
-      <c r="C12" s="41" t="s">
-        <v>164</v>
-      </c>
-      <c r="D12" s="37" t="s">
-        <v>54</v>
-      </c>
-      <c r="E12" s="42" t="s">
-        <v>24</v>
-      </c>
-      <c r="F12" s="37" t="s">
-        <v>165</v>
-      </c>
-      <c r="G12" s="43" t="s">
-        <v>17</v>
-      </c>
-      <c r="H12" s="80" t="s">
-        <v>244</v>
-      </c>
-      <c r="I12" s="39" t="s">
+      <c r="C12" s="78" t="s">
+        <v>162</v>
+      </c>
+      <c r="D12" s="69" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" s="61" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="61" t="s">
+        <v>163</v>
+      </c>
+      <c r="G12" s="42" t="s">
+        <v>26</v>
+      </c>
+      <c r="H12" s="76" t="s">
+        <v>241</v>
+      </c>
+      <c r="I12" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="J12" s="42" t="s">
-        <v>55</v>
+      <c r="J12" s="41" t="s">
+        <v>53</v>
       </c>
       <c r="K12" s="11">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L12" s="12">
         <v>1</v>
@@ -2745,51 +2797,51 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N12" s="90" t="s">
+      <c r="N12" s="86" t="s">
         <v>21</v>
       </c>
-      <c r="O12" s="32"/>
+      <c r="O12" s="30"/>
     </row>
     <row r="13" spans="1:30" ht="15.75" thickBot="1">
       <c r="A13" s="6">
         <v>11</v>
       </c>
-      <c r="B13" s="174"/>
-      <c r="C13" s="44" t="s">
-        <v>56</v>
-      </c>
-      <c r="D13" s="45" t="s">
-        <v>57</v>
-      </c>
-      <c r="E13" s="46" t="s">
-        <v>58</v>
-      </c>
-      <c r="F13" s="45" t="s">
-        <v>59</v>
-      </c>
-      <c r="G13" s="47" t="s">
-        <v>60</v>
-      </c>
-      <c r="H13" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="I13" s="48" t="s">
+      <c r="B13" s="173"/>
+      <c r="C13" s="40" t="s">
+        <v>164</v>
+      </c>
+      <c r="D13" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="F13" s="36" t="s">
+        <v>165</v>
+      </c>
+      <c r="G13" s="42" t="s">
+        <v>17</v>
+      </c>
+      <c r="H13" s="76" t="s">
+        <v>242</v>
+      </c>
+      <c r="I13" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="J13" s="46" t="s">
-        <v>62</v>
-      </c>
-      <c r="K13" s="15">
-        <v>50</v>
-      </c>
-      <c r="L13" s="16">
+      <c r="J13" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="K13" s="11">
+        <v>10</v>
+      </c>
+      <c r="L13" s="12">
         <v>1</v>
       </c>
-      <c r="M13" s="15">
+      <c r="M13" s="11">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N13" s="91" t="s">
+      <c r="N13" s="86" t="s">
         <v>21</v>
       </c>
       <c r="O13" s="31"/>
@@ -2798,91 +2850,91 @@
       <c r="A14" s="6">
         <v>12</v>
       </c>
-      <c r="B14" s="173" t="s">
-        <v>63</v>
-      </c>
-      <c r="C14" s="83" t="s">
-        <v>64</v>
-      </c>
-      <c r="D14" s="49" t="s">
-        <v>65</v>
-      </c>
-      <c r="E14" s="84" t="s">
-        <v>66</v>
-      </c>
-      <c r="F14" s="49" t="s">
-        <v>67</v>
-      </c>
-      <c r="G14" s="84" t="s">
-        <v>68</v>
-      </c>
-      <c r="H14" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="I14" s="50" t="s">
+      <c r="B14" s="174"/>
+      <c r="C14" s="43" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" s="44" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14" s="45" t="s">
+        <v>58</v>
+      </c>
+      <c r="F14" s="44" t="s">
+        <v>59</v>
+      </c>
+      <c r="G14" s="46" t="s">
+        <v>60</v>
+      </c>
+      <c r="H14" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="I14" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="J14" s="85" t="s">
-        <v>70</v>
-      </c>
-      <c r="K14" s="77">
-        <v>7</v>
-      </c>
-      <c r="L14" s="86">
+      <c r="J14" s="45" t="s">
+        <v>62</v>
+      </c>
+      <c r="K14" s="15">
+        <v>50</v>
+      </c>
+      <c r="L14" s="16">
         <v>1</v>
       </c>
-      <c r="M14" s="77">
+      <c r="M14" s="15">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N14" s="94" t="s">
+      <c r="N14" s="87" t="s">
         <v>21</v>
       </c>
-      <c r="O14" s="31"/>
+      <c r="O14" s="30"/>
     </row>
     <row r="15" spans="1:30" ht="15.75" thickBot="1">
       <c r="A15" s="6">
         <v>13</v>
       </c>
-      <c r="B15" s="173"/>
-      <c r="C15" s="156" t="s">
-        <v>224</v>
-      </c>
-      <c r="D15" s="157" t="s">
-        <v>223</v>
-      </c>
-      <c r="E15" s="138" t="s">
-        <v>222</v>
-      </c>
-      <c r="F15" s="138" t="s">
-        <v>221</v>
-      </c>
-      <c r="G15" s="138" t="s">
-        <v>225</v>
-      </c>
-      <c r="H15" s="158" t="s">
-        <v>226</v>
-      </c>
-      <c r="I15" s="159" t="s">
+      <c r="B15" s="173" t="s">
+        <v>63</v>
+      </c>
+      <c r="C15" s="79" t="s">
+        <v>64</v>
+      </c>
+      <c r="D15" s="48" t="s">
+        <v>65</v>
+      </c>
+      <c r="E15" s="80" t="s">
+        <v>66</v>
+      </c>
+      <c r="F15" s="48" t="s">
+        <v>67</v>
+      </c>
+      <c r="G15" s="80" t="s">
+        <v>68</v>
+      </c>
+      <c r="H15" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="I15" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="J15" s="159" t="s">
+      <c r="J15" s="81" t="s">
         <v>70</v>
       </c>
-      <c r="K15" s="139">
-        <v>50</v>
-      </c>
-      <c r="L15" s="81">
+      <c r="K15" s="73">
+        <v>8</v>
+      </c>
+      <c r="L15" s="82">
         <v>1</v>
       </c>
-      <c r="M15" s="139">
+      <c r="M15" s="73">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N15" s="141" t="s">
+      <c r="N15" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="O15" s="31"/>
+      <c r="O15" s="30"/>
     </row>
     <row r="16" spans="1:30" ht="15.75" thickBot="1">
       <c r="A16" s="6">
@@ -2890,692 +2942,692 @@
       </c>
       <c r="B16" s="173"/>
       <c r="C16" s="151" t="s">
-        <v>240</v>
-      </c>
-      <c r="D16" s="157" t="s">
-        <v>239</v>
-      </c>
-      <c r="E16" s="138" t="s">
-        <v>238</v>
-      </c>
-      <c r="F16" s="138" t="s">
-        <v>237</v>
-      </c>
-      <c r="G16" s="138" t="s">
-        <v>241</v>
-      </c>
-      <c r="H16" s="158" t="s">
-        <v>242</v>
-      </c>
-      <c r="I16" s="159" t="s">
+        <v>222</v>
+      </c>
+      <c r="D16" s="152" t="s">
+        <v>221</v>
+      </c>
+      <c r="E16" s="133" t="s">
+        <v>220</v>
+      </c>
+      <c r="F16" s="133" t="s">
+        <v>219</v>
+      </c>
+      <c r="G16" s="133" t="s">
+        <v>223</v>
+      </c>
+      <c r="H16" s="153" t="s">
+        <v>224</v>
+      </c>
+      <c r="I16" s="154" t="s">
         <v>19</v>
       </c>
-      <c r="J16" s="159" t="s">
+      <c r="J16" s="154" t="s">
         <v>70</v>
       </c>
-      <c r="K16" s="139">
-        <v>5</v>
-      </c>
-      <c r="L16" s="81">
+      <c r="K16" s="134">
+        <v>50</v>
+      </c>
+      <c r="L16" s="77">
         <v>1</v>
       </c>
-      <c r="M16" s="139">
+      <c r="M16" s="134">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N16" s="141" t="s">
+      <c r="N16" s="136" t="s">
         <v>21</v>
       </c>
-      <c r="O16" s="31"/>
+      <c r="O16" s="30"/>
     </row>
     <row r="17" spans="1:15" ht="15.75" thickBot="1">
       <c r="A17" s="6">
         <v>15</v>
       </c>
       <c r="B17" s="173"/>
-      <c r="C17" s="79" t="s">
-        <v>71</v>
-      </c>
-      <c r="D17" s="106" t="s">
-        <v>72</v>
-      </c>
-      <c r="E17" s="110" t="s">
-        <v>73</v>
-      </c>
-      <c r="F17" s="106" t="s">
-        <v>74</v>
-      </c>
-      <c r="G17" s="110" t="s">
-        <v>75</v>
-      </c>
-      <c r="H17" s="107" t="s">
-        <v>76</v>
-      </c>
-      <c r="I17" s="107" t="s">
+      <c r="C17" s="146" t="s">
+        <v>238</v>
+      </c>
+      <c r="D17" s="152" t="s">
+        <v>237</v>
+      </c>
+      <c r="E17" s="133" t="s">
+        <v>236</v>
+      </c>
+      <c r="F17" s="133" t="s">
+        <v>235</v>
+      </c>
+      <c r="G17" s="133" t="s">
+        <v>239</v>
+      </c>
+      <c r="H17" s="153" t="s">
+        <v>240</v>
+      </c>
+      <c r="I17" s="154" t="s">
         <v>19</v>
       </c>
-      <c r="J17" s="111" t="s">
+      <c r="J17" s="154" t="s">
         <v>70</v>
       </c>
-      <c r="K17" s="103">
-        <v>20</v>
-      </c>
-      <c r="L17" s="112">
+      <c r="K17" s="134">
+        <v>10</v>
+      </c>
+      <c r="L17" s="77">
         <v>1</v>
       </c>
-      <c r="M17" s="103">
+      <c r="M17" s="134">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N17" s="113" t="s">
+      <c r="N17" s="136" t="s">
         <v>21</v>
       </c>
-      <c r="O17" s="31"/>
-    </row>
-    <row r="18" spans="1:15" ht="16.5" thickBot="1">
+      <c r="O17" s="30"/>
+    </row>
+    <row r="18" spans="1:15" ht="15.75" thickBot="1">
       <c r="A18" s="6">
         <v>16</v>
       </c>
-      <c r="B18" s="175" t="s">
-        <v>77</v>
-      </c>
-      <c r="C18" s="114" t="s">
-        <v>78</v>
-      </c>
-      <c r="D18" s="115" t="s">
-        <v>79</v>
-      </c>
-      <c r="E18" s="115" t="s">
-        <v>80</v>
-      </c>
-      <c r="F18" s="115" t="s">
-        <v>81</v>
-      </c>
-      <c r="G18" s="116" t="s">
-        <v>82</v>
-      </c>
-      <c r="H18" s="116" t="s">
+      <c r="B18" s="173"/>
+      <c r="C18" s="75" t="s">
+        <v>71</v>
+      </c>
+      <c r="D18" s="101" t="s">
+        <v>72</v>
+      </c>
+      <c r="E18" s="105" t="s">
+        <v>73</v>
+      </c>
+      <c r="F18" s="101" t="s">
+        <v>74</v>
+      </c>
+      <c r="G18" s="105" t="s">
+        <v>75</v>
+      </c>
+      <c r="H18" s="102" t="s">
+        <v>76</v>
+      </c>
+      <c r="I18" s="102" t="s">
         <v>19</v>
       </c>
-      <c r="I18" s="115" t="s">
-        <v>19</v>
-      </c>
-      <c r="J18" s="116" t="s">
+      <c r="J18" s="106" t="s">
         <v>70</v>
       </c>
-      <c r="K18" s="108">
-        <v>7</v>
-      </c>
-      <c r="L18" s="108">
+      <c r="K18" s="98">
+        <v>20</v>
+      </c>
+      <c r="L18" s="107">
         <v>1</v>
       </c>
-      <c r="M18" s="67">
+      <c r="M18" s="98">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N18" s="109" t="s">
+      <c r="N18" s="108" t="s">
         <v>21</v>
       </c>
-      <c r="O18" s="31"/>
-    </row>
-    <row r="19" spans="1:15" ht="30.75" thickBot="1">
+      <c r="O18" s="30"/>
+    </row>
+    <row r="19" spans="1:15" ht="16.5" thickBot="1">
       <c r="A19" s="6">
         <v>17</v>
       </c>
-      <c r="B19" s="175" t="s">
-        <v>227</v>
-      </c>
-      <c r="C19" s="160" t="s">
-        <v>229</v>
-      </c>
-      <c r="D19" s="161" t="s">
-        <v>228</v>
-      </c>
-      <c r="E19" s="162" t="s">
-        <v>230</v>
-      </c>
-      <c r="F19" s="162" t="s">
-        <v>231</v>
-      </c>
-      <c r="G19" s="163" t="s">
-        <v>232</v>
-      </c>
-      <c r="H19" s="163" t="s">
-        <v>233</v>
-      </c>
-      <c r="I19" s="162" t="s">
-        <v>234</v>
-      </c>
-      <c r="J19" s="163" t="s">
+      <c r="B19" s="167" t="s">
+        <v>77</v>
+      </c>
+      <c r="C19" s="109" t="s">
+        <v>78</v>
+      </c>
+      <c r="D19" s="110" t="s">
+        <v>79</v>
+      </c>
+      <c r="E19" s="110" t="s">
+        <v>80</v>
+      </c>
+      <c r="F19" s="110" t="s">
+        <v>81</v>
+      </c>
+      <c r="G19" s="111" t="s">
+        <v>82</v>
+      </c>
+      <c r="H19" s="111" t="s">
+        <v>19</v>
+      </c>
+      <c r="I19" s="110" t="s">
+        <v>19</v>
+      </c>
+      <c r="J19" s="111" t="s">
         <v>70</v>
       </c>
-      <c r="K19" s="164">
-        <v>10</v>
-      </c>
-      <c r="L19" s="164">
+      <c r="K19" s="103">
+        <v>7</v>
+      </c>
+      <c r="L19" s="103">
         <v>1</v>
       </c>
-      <c r="M19" s="165">
+      <c r="M19" s="66">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N19" s="166" t="s">
+      <c r="N19" s="104" t="s">
         <v>21</v>
       </c>
-      <c r="O19" s="31"/>
-    </row>
-    <row r="20" spans="1:15" ht="15.75" thickBot="1">
+      <c r="O19" s="30"/>
+    </row>
+    <row r="20" spans="1:15" ht="30.75" thickBot="1">
       <c r="A20" s="6">
         <v>18</v>
       </c>
-      <c r="B20" s="172" t="s">
-        <v>83</v>
-      </c>
-      <c r="C20" s="104" t="s">
-        <v>174</v>
-      </c>
-      <c r="D20" s="63" t="s">
-        <v>175</v>
-      </c>
-      <c r="E20" s="63" t="s">
-        <v>176</v>
-      </c>
-      <c r="F20" s="63" t="s">
-        <v>176</v>
-      </c>
-      <c r="G20" s="35" t="s">
-        <v>177</v>
-      </c>
-      <c r="H20" s="35" t="s">
-        <v>178</v>
-      </c>
-      <c r="I20" s="34" t="s">
-        <v>19</v>
-      </c>
-      <c r="J20" s="35" t="s">
+      <c r="B20" s="167" t="s">
+        <v>225</v>
+      </c>
+      <c r="C20" s="155" t="s">
+        <v>227</v>
+      </c>
+      <c r="D20" s="156" t="s">
+        <v>226</v>
+      </c>
+      <c r="E20" s="157" t="s">
+        <v>228</v>
+      </c>
+      <c r="F20" s="157" t="s">
+        <v>229</v>
+      </c>
+      <c r="G20" s="158" t="s">
+        <v>230</v>
+      </c>
+      <c r="H20" s="158" t="s">
+        <v>231</v>
+      </c>
+      <c r="I20" s="157" t="s">
+        <v>232</v>
+      </c>
+      <c r="J20" s="158" t="s">
         <v>70</v>
       </c>
-      <c r="K20" s="19">
+      <c r="K20" s="159">
         <v>10</v>
       </c>
-      <c r="L20" s="19">
+      <c r="L20" s="159">
         <v>1</v>
       </c>
-      <c r="M20" s="18">
+      <c r="M20" s="160">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N20" s="105" t="s">
+      <c r="N20" s="161" t="s">
         <v>21</v>
       </c>
-      <c r="O20" s="31"/>
+      <c r="O20" s="30"/>
     </row>
     <row r="21" spans="1:15" ht="15.75" thickBot="1">
       <c r="A21" s="6">
         <v>19</v>
       </c>
-      <c r="B21" s="174"/>
-      <c r="C21" s="64" t="s">
-        <v>84</v>
-      </c>
-      <c r="D21" s="65" t="s">
-        <v>85</v>
-      </c>
-      <c r="E21" s="65" t="s">
-        <v>44</v>
-      </c>
-      <c r="F21" s="65" t="s">
-        <v>86</v>
-      </c>
-      <c r="G21" s="65" t="s">
-        <v>87</v>
-      </c>
-      <c r="H21" s="66"/>
-      <c r="I21" s="66"/>
-      <c r="J21" s="65" t="s">
+      <c r="B21" s="172" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" s="99" t="s">
+        <v>174</v>
+      </c>
+      <c r="D21" s="62" t="s">
+        <v>175</v>
+      </c>
+      <c r="E21" s="62" t="s">
+        <v>176</v>
+      </c>
+      <c r="F21" s="62" t="s">
+        <v>176</v>
+      </c>
+      <c r="G21" s="34" t="s">
+        <v>177</v>
+      </c>
+      <c r="H21" s="34" t="s">
+        <v>178</v>
+      </c>
+      <c r="I21" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="J21" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="K21" s="66">
-        <v>7</v>
-      </c>
-      <c r="L21" s="66">
+      <c r="K21" s="19">
+        <v>10</v>
+      </c>
+      <c r="L21" s="19">
         <v>1</v>
       </c>
-      <c r="M21" s="15">
+      <c r="M21" s="18">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N21" s="68" t="s">
-        <v>88</v>
-      </c>
-      <c r="O21" s="31"/>
+      <c r="N21" s="100" t="s">
+        <v>21</v>
+      </c>
+      <c r="O21" s="30"/>
     </row>
     <row r="22" spans="1:15" ht="15.75" thickBot="1">
       <c r="A22" s="6">
         <v>20</v>
       </c>
-      <c r="B22" s="172" t="s">
-        <v>89</v>
-      </c>
-      <c r="C22" s="144" t="s">
-        <v>90</v>
-      </c>
-      <c r="D22" s="169" t="s">
-        <v>187</v>
-      </c>
-      <c r="E22" s="146" t="s">
-        <v>91</v>
-      </c>
-      <c r="F22" s="146" t="s">
-        <v>92</v>
-      </c>
-      <c r="G22" s="148" t="s">
-        <v>60</v>
-      </c>
-      <c r="H22" s="170" t="s">
-        <v>93</v>
-      </c>
-      <c r="I22" s="146" t="s">
-        <v>19</v>
-      </c>
-      <c r="J22" s="146" t="s">
-        <v>94</v>
-      </c>
-      <c r="K22" s="149">
-        <v>100</v>
-      </c>
-      <c r="L22" s="149">
-        <v>3</v>
-      </c>
-      <c r="M22" s="149">
+      <c r="B22" s="174"/>
+      <c r="C22" s="63" t="s">
+        <v>84</v>
+      </c>
+      <c r="D22" s="64" t="s">
+        <v>85</v>
+      </c>
+      <c r="E22" s="64" t="s">
+        <v>44</v>
+      </c>
+      <c r="F22" s="64" t="s">
+        <v>86</v>
+      </c>
+      <c r="G22" s="64" t="s">
+        <v>87</v>
+      </c>
+      <c r="H22" s="65"/>
+      <c r="I22" s="65"/>
+      <c r="J22" s="64" t="s">
+        <v>70</v>
+      </c>
+      <c r="K22" s="65">
+        <v>7</v>
+      </c>
+      <c r="L22" s="65">
+        <v>1</v>
+      </c>
+      <c r="M22" s="15">
         <f t="shared" si="1"/>
-        <v>18</v>
-      </c>
-      <c r="N22" s="171" t="s">
-        <v>21</v>
-      </c>
-      <c r="O22" s="31"/>
+        <v>6</v>
+      </c>
+      <c r="N22" s="67" t="s">
+        <v>88</v>
+      </c>
+      <c r="O22" s="30"/>
     </row>
     <row r="23" spans="1:15" ht="15.75" thickBot="1">
       <c r="A23" s="6">
         <v>21</v>
       </c>
-      <c r="B23" s="173"/>
-      <c r="C23" s="76" t="s">
-        <v>166</v>
-      </c>
-      <c r="D23" s="62" t="s">
-        <v>167</v>
-      </c>
-      <c r="E23" s="62" t="s">
+      <c r="B23" s="172" t="s">
+        <v>89</v>
+      </c>
+      <c r="C23" s="139" t="s">
+        <v>90</v>
+      </c>
+      <c r="D23" s="164" t="s">
+        <v>187</v>
+      </c>
+      <c r="E23" s="141" t="s">
         <v>91</v>
       </c>
-      <c r="F23" s="62" t="s">
-        <v>168</v>
-      </c>
-      <c r="G23" s="39" t="s">
-        <v>156</v>
-      </c>
-      <c r="H23" s="80" t="s">
-        <v>245</v>
-      </c>
-      <c r="I23" s="37" t="s">
+      <c r="F23" s="141" t="s">
+        <v>92</v>
+      </c>
+      <c r="G23" s="143" t="s">
+        <v>60</v>
+      </c>
+      <c r="H23" s="165" t="s">
+        <v>93</v>
+      </c>
+      <c r="I23" s="141" t="s">
         <v>19</v>
       </c>
-      <c r="J23" s="78" t="s">
-        <v>169</v>
-      </c>
-      <c r="K23" s="7">
+      <c r="J23" s="141" t="s">
+        <v>94</v>
+      </c>
+      <c r="K23" s="144">
         <v>100</v>
       </c>
-      <c r="L23" s="7">
-        <v>1</v>
-      </c>
-      <c r="M23" s="11">
+      <c r="L23" s="144">
+        <v>3</v>
+      </c>
+      <c r="M23" s="144">
         <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="N23" s="95" t="s">
-        <v>179</v>
-      </c>
-      <c r="O23" s="31"/>
+        <v>18</v>
+      </c>
+      <c r="N23" s="166" t="s">
+        <v>21</v>
+      </c>
+      <c r="O23" s="30"/>
     </row>
     <row r="24" spans="1:15" ht="15.75" thickBot="1">
       <c r="A24" s="6">
         <v>22</v>
       </c>
       <c r="B24" s="173"/>
-      <c r="C24" s="133" t="s">
-        <v>195</v>
-      </c>
-      <c r="D24" s="134" t="s">
-        <v>188</v>
-      </c>
-      <c r="E24" s="75" t="s">
+      <c r="C24" s="72" t="s">
+        <v>166</v>
+      </c>
+      <c r="D24" s="61" t="s">
+        <v>167</v>
+      </c>
+      <c r="E24" s="61" t="s">
         <v>91</v>
       </c>
-      <c r="F24" s="135" t="s">
-        <v>189</v>
-      </c>
-      <c r="G24" s="135" t="s">
-        <v>190</v>
-      </c>
-      <c r="H24" s="136" t="s">
-        <v>191</v>
-      </c>
-      <c r="I24" s="137" t="s">
+      <c r="F24" s="61" t="s">
+        <v>168</v>
+      </c>
+      <c r="G24" s="38" t="s">
+        <v>156</v>
+      </c>
+      <c r="H24" s="76" t="s">
+        <v>243</v>
+      </c>
+      <c r="I24" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="J24" s="138" t="s">
-        <v>201</v>
-      </c>
-      <c r="K24" s="139">
-        <v>20</v>
-      </c>
-      <c r="L24" s="139">
+      <c r="J24" s="74" t="s">
+        <v>169</v>
+      </c>
+      <c r="K24" s="7">
+        <v>100</v>
+      </c>
+      <c r="L24" s="7">
         <v>1</v>
       </c>
-      <c r="M24" s="139">
+      <c r="M24" s="11">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N24" s="140" t="s">
-        <v>21</v>
-      </c>
-      <c r="O24" s="31"/>
+      <c r="N24" s="90" t="s">
+        <v>179</v>
+      </c>
+      <c r="O24" s="30"/>
     </row>
     <row r="25" spans="1:15" ht="15.75" thickBot="1">
       <c r="A25" s="6">
         <v>23</v>
       </c>
       <c r="B25" s="173"/>
-      <c r="C25" s="133" t="s">
-        <v>196</v>
-      </c>
-      <c r="D25" s="134" t="s">
-        <v>192</v>
-      </c>
-      <c r="E25" s="75" t="s">
+      <c r="C25" s="128" t="s">
+        <v>195</v>
+      </c>
+      <c r="D25" s="129" t="s">
+        <v>188</v>
+      </c>
+      <c r="E25" s="71" t="s">
         <v>91</v>
       </c>
-      <c r="F25" s="135" t="s">
-        <v>193</v>
-      </c>
-      <c r="G25" s="135" t="s">
+      <c r="F25" s="130" t="s">
+        <v>189</v>
+      </c>
+      <c r="G25" s="130" t="s">
         <v>190</v>
       </c>
-      <c r="H25" s="136" t="s">
-        <v>194</v>
-      </c>
-      <c r="I25" s="137" t="s">
+      <c r="H25" s="131" t="s">
+        <v>191</v>
+      </c>
+      <c r="I25" s="132" t="s">
         <v>19</v>
       </c>
-      <c r="J25" s="138" t="s">
-        <v>202</v>
-      </c>
-      <c r="K25" s="139">
-        <v>100</v>
-      </c>
-      <c r="L25" s="139">
+      <c r="J25" s="133" t="s">
+        <v>201</v>
+      </c>
+      <c r="K25" s="134">
+        <v>20</v>
+      </c>
+      <c r="L25" s="134">
         <v>1</v>
       </c>
-      <c r="M25" s="139">
+      <c r="M25" s="134">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N25" s="141" t="s">
+      <c r="N25" s="135" t="s">
         <v>21</v>
       </c>
-      <c r="O25" s="31"/>
+      <c r="O25" s="30"/>
     </row>
     <row r="26" spans="1:15" ht="15.75" thickBot="1">
       <c r="A26" s="6">
         <v>24</v>
       </c>
       <c r="B26" s="173"/>
-      <c r="C26" s="133" t="s">
-        <v>198</v>
-      </c>
-      <c r="D26" s="134" t="s">
-        <v>199</v>
-      </c>
-      <c r="E26" s="138" t="s">
+      <c r="C26" s="128" t="s">
+        <v>196</v>
+      </c>
+      <c r="D26" s="129" t="s">
+        <v>192</v>
+      </c>
+      <c r="E26" s="71" t="s">
         <v>91</v>
       </c>
-      <c r="F26" s="142" t="s">
-        <v>197</v>
-      </c>
-      <c r="G26" s="135" t="s">
+      <c r="F26" s="130" t="s">
+        <v>193</v>
+      </c>
+      <c r="G26" s="130" t="s">
         <v>190</v>
       </c>
-      <c r="H26" s="143" t="s">
-        <v>200</v>
-      </c>
-      <c r="I26" s="137" t="s">
+      <c r="H26" s="131" t="s">
+        <v>194</v>
+      </c>
+      <c r="I26" s="132" t="s">
         <v>19</v>
       </c>
-      <c r="J26" s="138" t="s">
-        <v>203</v>
-      </c>
-      <c r="K26" s="139">
+      <c r="J26" s="133" t="s">
+        <v>202</v>
+      </c>
+      <c r="K26" s="134">
         <v>100</v>
       </c>
-      <c r="L26" s="139">
+      <c r="L26" s="134">
         <v>1</v>
       </c>
-      <c r="M26" s="139">
+      <c r="M26" s="134">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N26" s="141" t="s">
+      <c r="N26" s="136" t="s">
         <v>21</v>
       </c>
-      <c r="O26" s="31"/>
+      <c r="O26" s="30"/>
     </row>
     <row r="27" spans="1:15" ht="15.75" thickBot="1">
       <c r="A27" s="6">
         <v>25</v>
       </c>
       <c r="B27" s="173"/>
-      <c r="C27" s="133" t="s">
-        <v>205</v>
-      </c>
-      <c r="D27" s="134" t="s">
-        <v>208</v>
-      </c>
-      <c r="E27" s="138" t="s">
+      <c r="C27" s="128" t="s">
+        <v>198</v>
+      </c>
+      <c r="D27" s="129" t="s">
+        <v>199</v>
+      </c>
+      <c r="E27" s="133" t="s">
         <v>91</v>
       </c>
-      <c r="F27" s="142" t="s">
-        <v>204</v>
-      </c>
-      <c r="G27" s="142" t="s">
-        <v>115</v>
-      </c>
-      <c r="H27" s="143" t="s">
-        <v>206</v>
-      </c>
-      <c r="I27" s="137" t="s">
+      <c r="F27" s="137" t="s">
+        <v>197</v>
+      </c>
+      <c r="G27" s="130" t="s">
+        <v>190</v>
+      </c>
+      <c r="H27" s="138" t="s">
+        <v>200</v>
+      </c>
+      <c r="I27" s="132" t="s">
         <v>19</v>
       </c>
-      <c r="J27" s="138" t="s">
-        <v>207</v>
-      </c>
-      <c r="K27" s="139">
-        <v>50</v>
-      </c>
-      <c r="L27" s="139">
-        <v>2</v>
-      </c>
-      <c r="M27" s="139">
+      <c r="J27" s="133" t="s">
+        <v>203</v>
+      </c>
+      <c r="K27" s="134">
+        <v>100</v>
+      </c>
+      <c r="L27" s="134">
+        <v>1</v>
+      </c>
+      <c r="M27" s="134">
         <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="N27" s="141" t="s">
+        <v>6</v>
+      </c>
+      <c r="N27" s="136" t="s">
         <v>21</v>
       </c>
-      <c r="O27" s="31"/>
+      <c r="O27" s="30"/>
     </row>
     <row r="28" spans="1:15" ht="15.75" thickBot="1">
       <c r="A28" s="6">
         <v>26</v>
       </c>
       <c r="B28" s="173"/>
-      <c r="C28" s="51" t="s">
-        <v>95</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="E28" s="37" t="s">
+      <c r="C28" s="179" t="s">
+        <v>254</v>
+      </c>
+      <c r="D28" s="129" t="s">
+        <v>207</v>
+      </c>
+      <c r="E28" s="133" t="s">
         <v>91</v>
       </c>
-      <c r="F28" s="37" t="s">
-        <v>97</v>
-      </c>
-      <c r="G28" s="39" t="s">
-        <v>60</v>
-      </c>
-      <c r="H28" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="I28" s="37" t="s">
+      <c r="F28" s="137" t="s">
+        <v>204</v>
+      </c>
+      <c r="G28" s="137" t="s">
+        <v>115</v>
+      </c>
+      <c r="H28" s="138" t="s">
+        <v>205</v>
+      </c>
+      <c r="I28" s="132" t="s">
         <v>19</v>
       </c>
-      <c r="J28" s="37" t="s">
-        <v>99</v>
-      </c>
-      <c r="K28" s="7">
-        <v>100</v>
-      </c>
-      <c r="L28" s="7">
+      <c r="J28" s="133" t="s">
+        <v>206</v>
+      </c>
+      <c r="K28" s="134">
+        <v>50</v>
+      </c>
+      <c r="L28" s="134">
         <v>2</v>
       </c>
-      <c r="M28" s="11">
+      <c r="M28" s="134">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="N28" s="96" t="s">
+      <c r="N28" s="136" t="s">
         <v>21</v>
       </c>
-      <c r="O28" s="31"/>
+      <c r="O28" s="30"/>
     </row>
     <row r="29" spans="1:15" ht="15.75" thickBot="1">
       <c r="A29" s="6">
         <v>27</v>
       </c>
       <c r="B29" s="173"/>
-      <c r="C29" s="51" t="s">
+      <c r="C29" s="179" t="s">
+        <v>253</v>
+      </c>
+      <c r="D29" s="129" t="s">
+        <v>255</v>
+      </c>
+      <c r="E29" s="133" t="s">
+        <v>91</v>
+      </c>
+      <c r="F29" s="177" t="s">
+        <v>250</v>
+      </c>
+      <c r="G29" s="177" t="s">
+        <v>190</v>
+      </c>
+      <c r="H29" s="178" t="s">
+        <v>251</v>
+      </c>
+      <c r="I29" s="132" t="s">
+        <v>19</v>
+      </c>
+      <c r="J29" s="175" t="s">
+        <v>252</v>
+      </c>
+      <c r="K29" s="134">
         <v>100</v>
       </c>
-      <c r="D29" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="E29" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="F29" s="37" t="s">
-        <v>101</v>
-      </c>
-      <c r="G29" s="39" t="s">
-        <v>60</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="I29" s="37" t="s">
-        <v>19</v>
-      </c>
-      <c r="J29" s="37" t="s">
-        <v>103</v>
-      </c>
-      <c r="K29" s="7">
-        <v>100</v>
-      </c>
-      <c r="L29" s="7">
-        <v>1</v>
-      </c>
-      <c r="M29" s="11">
+      <c r="L29" s="134">
+        <v>2</v>
+      </c>
+      <c r="M29" s="134">
         <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="N29" s="96" t="s">
+        <v>12</v>
+      </c>
+      <c r="N29" s="136" t="s">
         <v>21</v>
       </c>
-      <c r="O29" s="31"/>
+      <c r="O29" s="30"/>
     </row>
     <row r="30" spans="1:15" ht="15.75" thickBot="1">
       <c r="A30" s="6">
         <v>28</v>
       </c>
       <c r="B30" s="173"/>
-      <c r="C30" s="51" t="s">
-        <v>105</v>
-      </c>
-      <c r="D30" s="37" t="s">
-        <v>106</v>
-      </c>
-      <c r="E30" s="37" t="s">
-        <v>104</v>
-      </c>
-      <c r="F30" s="40" t="s">
-        <v>107</v>
-      </c>
-      <c r="G30" s="39" t="s">
-        <v>108</v>
+      <c r="C30" s="50" t="s">
+        <v>95</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="E30" s="36" t="s">
+        <v>91</v>
+      </c>
+      <c r="F30" s="36" t="s">
+        <v>97</v>
+      </c>
+      <c r="G30" s="38" t="s">
+        <v>60</v>
       </c>
       <c r="H30" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="I30" s="39" t="s">
-        <v>110</v>
-      </c>
-      <c r="J30" s="37" t="s">
-        <v>111</v>
+        <v>98</v>
+      </c>
+      <c r="I30" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="J30" s="36" t="s">
+        <v>99</v>
       </c>
       <c r="K30" s="7">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="L30" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M30" s="11">
         <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="N30" s="96" t="s">
+        <v>12</v>
+      </c>
+      <c r="N30" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="O30" s="31"/>
+      <c r="O30" s="30"/>
     </row>
     <row r="31" spans="1:15" ht="15.75" thickBot="1">
       <c r="A31" s="6">
         <v>29</v>
       </c>
       <c r="B31" s="173"/>
-      <c r="C31" s="51" t="s">
-        <v>112</v>
-      </c>
-      <c r="D31" s="37" t="s">
-        <v>113</v>
-      </c>
-      <c r="E31" s="37" t="s">
-        <v>24</v>
-      </c>
-      <c r="F31" s="37" t="s">
-        <v>114</v>
-      </c>
-      <c r="G31" s="39" t="s">
-        <v>115</v>
+      <c r="C31" s="50" t="s">
+        <v>100</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="E31" s="36" t="s">
+        <v>91</v>
+      </c>
+      <c r="F31" s="36" t="s">
+        <v>101</v>
+      </c>
+      <c r="G31" s="38" t="s">
+        <v>60</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="I31" s="37" t="s">
+        <v>102</v>
+      </c>
+      <c r="I31" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="J31" s="37" t="s">
-        <v>117</v>
+      <c r="J31" s="36" t="s">
+        <v>103</v>
       </c>
       <c r="K31" s="7">
         <v>100</v>
@@ -3587,574 +3639,662 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N31" s="96" t="s">
+      <c r="N31" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="O31" s="31"/>
-    </row>
-    <row r="32" spans="1:15" s="1" customFormat="1" ht="15.75" thickBot="1">
+      <c r="O31" s="30"/>
+    </row>
+    <row r="32" spans="1:15" ht="15.75" thickBot="1">
       <c r="A32" s="6">
         <v>30</v>
       </c>
-      <c r="B32" s="174"/>
-      <c r="C32" s="52" t="s">
-        <v>118</v>
-      </c>
-      <c r="D32" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="E32" s="45" t="s">
-        <v>91</v>
-      </c>
-      <c r="F32" s="45" t="s">
-        <v>120</v>
-      </c>
-      <c r="G32" s="48" t="s">
-        <v>60</v>
-      </c>
-      <c r="H32" s="17" t="s">
-        <v>121</v>
-      </c>
-      <c r="I32" s="45" t="s">
-        <v>19</v>
-      </c>
-      <c r="J32" s="45" t="s">
-        <v>122</v>
-      </c>
-      <c r="K32" s="14">
-        <v>100</v>
-      </c>
-      <c r="L32" s="17">
-        <v>8</v>
-      </c>
-      <c r="M32" s="15">
+      <c r="B32" s="173"/>
+      <c r="C32" s="50" t="s">
+        <v>105</v>
+      </c>
+      <c r="D32" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="E32" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="F32" s="39" t="s">
+        <v>107</v>
+      </c>
+      <c r="G32" s="38" t="s">
+        <v>108</v>
+      </c>
+      <c r="H32" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="I32" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="J32" s="36" t="s">
+        <v>111</v>
+      </c>
+      <c r="K32" s="7">
+        <v>10</v>
+      </c>
+      <c r="L32" s="7">
+        <v>1</v>
+      </c>
+      <c r="M32" s="11">
         <f t="shared" si="1"/>
-        <v>48</v>
-      </c>
-      <c r="N32" s="118" t="s">
+        <v>6</v>
+      </c>
+      <c r="N32" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="O32" s="33"/>
+      <c r="O32" s="30"/>
     </row>
     <row r="33" spans="1:15" ht="15.75" thickBot="1">
       <c r="A33" s="6">
         <v>31</v>
       </c>
-      <c r="B33" s="173" t="s">
-        <v>123</v>
-      </c>
-      <c r="C33" s="124" t="s">
-        <v>185</v>
-      </c>
-      <c r="D33" s="132" t="s">
-        <v>124</v>
-      </c>
-      <c r="E33" s="117" t="s">
-        <v>182</v>
-      </c>
-      <c r="F33" s="126" t="s">
-        <v>183</v>
-      </c>
-      <c r="G33" s="127" t="s">
-        <v>184</v>
-      </c>
-      <c r="H33" s="128" t="s">
+      <c r="B33" s="173"/>
+      <c r="C33" s="50" t="s">
+        <v>112</v>
+      </c>
+      <c r="D33" s="36" t="s">
+        <v>113</v>
+      </c>
+      <c r="E33" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="F33" s="36" t="s">
+        <v>114</v>
+      </c>
+      <c r="G33" s="38" t="s">
+        <v>115</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="I33" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="I33" s="125" t="s">
-        <v>19</v>
-      </c>
-      <c r="J33" s="128" t="s">
-        <v>70</v>
-      </c>
-      <c r="K33" s="129">
-        <v>7</v>
-      </c>
-      <c r="L33" s="129">
+      <c r="J33" s="36" t="s">
+        <v>117</v>
+      </c>
+      <c r="K33" s="7">
+        <v>100</v>
+      </c>
+      <c r="L33" s="7">
         <v>1</v>
       </c>
-      <c r="M33" s="130">
+      <c r="M33" s="11">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N33" s="131" t="s">
+      <c r="N33" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="O33" s="31"/>
-    </row>
-    <row r="34" spans="1:15" ht="15.75" thickBot="1">
+      <c r="O33" s="30"/>
+    </row>
+    <row r="34" spans="1:15" s="1" customFormat="1" ht="15.75" thickBot="1">
       <c r="A34" s="6">
         <v>32</v>
       </c>
-      <c r="B34" s="173"/>
+      <c r="B34" s="174"/>
       <c r="C34" s="51" t="s">
-        <v>125</v>
-      </c>
-      <c r="D34" s="37" t="s">
-        <v>126</v>
-      </c>
-      <c r="E34" s="37" t="s">
-        <v>127</v>
-      </c>
-      <c r="F34" s="37" t="s">
-        <v>128</v>
-      </c>
-      <c r="G34" s="39" t="s">
-        <v>129</v>
-      </c>
-      <c r="H34" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="I34" s="37" t="s">
+        <v>118</v>
+      </c>
+      <c r="D34" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="E34" s="44" t="s">
+        <v>91</v>
+      </c>
+      <c r="F34" s="44" t="s">
+        <v>120</v>
+      </c>
+      <c r="G34" s="47" t="s">
+        <v>60</v>
+      </c>
+      <c r="H34" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="I34" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="J34" s="39" t="s">
-        <v>70</v>
-      </c>
-      <c r="K34" s="13">
-        <v>6</v>
-      </c>
-      <c r="L34" s="13">
-        <v>1</v>
-      </c>
-      <c r="M34" s="11">
+      <c r="J34" s="44" t="s">
+        <v>122</v>
+      </c>
+      <c r="K34" s="14">
+        <v>100</v>
+      </c>
+      <c r="L34" s="17">
+        <v>8</v>
+      </c>
+      <c r="M34" s="15">
         <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="N34" s="96" t="s">
+        <v>48</v>
+      </c>
+      <c r="N34" s="113" t="s">
         <v>21</v>
       </c>
-      <c r="O34" s="31"/>
+      <c r="O34" s="32"/>
     </row>
     <row r="35" spans="1:15" ht="15.75" thickBot="1">
       <c r="A35" s="6">
         <v>33</v>
       </c>
-      <c r="B35" s="173"/>
+      <c r="B35" s="173" t="s">
+        <v>123</v>
+      </c>
       <c r="C35" s="119" t="s">
-        <v>170</v>
-      </c>
-      <c r="D35" s="120" t="s">
-        <v>131</v>
-      </c>
-      <c r="E35" s="120" t="s">
-        <v>171</v>
+        <v>185</v>
+      </c>
+      <c r="D35" s="127" t="s">
+        <v>124</v>
+      </c>
+      <c r="E35" s="112" t="s">
+        <v>182</v>
       </c>
       <c r="F35" s="121" t="s">
-        <v>173</v>
-      </c>
-      <c r="G35" s="106" t="s">
-        <v>172</v>
-      </c>
-      <c r="H35" s="102"/>
-      <c r="I35" s="106" t="s">
+        <v>183</v>
+      </c>
+      <c r="G35" s="122" t="s">
+        <v>184</v>
+      </c>
+      <c r="H35" s="123" t="s">
         <v>19</v>
       </c>
-      <c r="J35" s="107" t="s">
-        <v>132</v>
-      </c>
-      <c r="K35" s="102">
-        <v>6</v>
-      </c>
-      <c r="L35" s="102">
+      <c r="I35" s="120" t="s">
+        <v>19</v>
+      </c>
+      <c r="J35" s="123" t="s">
+        <v>70</v>
+      </c>
+      <c r="K35" s="124">
+        <v>7</v>
+      </c>
+      <c r="L35" s="124">
         <v>1</v>
       </c>
-      <c r="M35" s="103">
+      <c r="M35" s="125">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N35" s="122" t="s">
-        <v>88</v>
-      </c>
-      <c r="O35" s="31"/>
+      <c r="N35" s="126" t="s">
+        <v>21</v>
+      </c>
+      <c r="O35" s="30"/>
     </row>
     <row r="36" spans="1:15" ht="15.75" thickBot="1">
       <c r="A36" s="6">
         <v>34</v>
       </c>
-      <c r="B36" s="172" t="s">
-        <v>133</v>
-      </c>
-      <c r="C36" s="53" t="s">
-        <v>134</v>
-      </c>
-      <c r="D36" s="54" t="s">
-        <v>135</v>
-      </c>
-      <c r="E36" s="54" t="s">
-        <v>136</v>
-      </c>
-      <c r="F36" s="54" t="s">
-        <v>136</v>
-      </c>
-      <c r="G36" s="54" t="s">
-        <v>137</v>
-      </c>
-      <c r="H36" s="54" t="s">
+      <c r="B36" s="173"/>
+      <c r="C36" s="50" t="s">
+        <v>125</v>
+      </c>
+      <c r="D36" s="36" t="s">
+        <v>126</v>
+      </c>
+      <c r="E36" s="36" t="s">
+        <v>127</v>
+      </c>
+      <c r="F36" s="36" t="s">
+        <v>128</v>
+      </c>
+      <c r="G36" s="38" t="s">
+        <v>129</v>
+      </c>
+      <c r="H36" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="I36" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="I36" s="54" t="s">
-        <v>19</v>
-      </c>
-      <c r="J36" s="54" t="s">
+      <c r="J36" s="38" t="s">
         <v>70</v>
       </c>
-      <c r="K36" s="22">
-        <v>100</v>
-      </c>
-      <c r="L36" s="22">
+      <c r="K36" s="13">
+        <v>6</v>
+      </c>
+      <c r="L36" s="13">
         <v>1</v>
       </c>
-      <c r="M36" s="18">
+      <c r="M36" s="11">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N36" s="123" t="s">
-        <v>138</v>
-      </c>
-      <c r="O36" s="31"/>
+      <c r="N36" s="91" t="s">
+        <v>21</v>
+      </c>
+      <c r="O36" s="30"/>
     </row>
     <row r="37" spans="1:15" ht="15.75" thickBot="1">
       <c r="A37" s="6">
         <v>35</v>
       </c>
       <c r="B37" s="173"/>
-      <c r="C37" s="55" t="s">
-        <v>139</v>
-      </c>
-      <c r="D37" s="56" t="s">
-        <v>140</v>
-      </c>
-      <c r="E37" s="56" t="s">
-        <v>44</v>
-      </c>
-      <c r="F37" s="56" t="s">
-        <v>141</v>
-      </c>
-      <c r="G37" s="56" t="s">
-        <v>142</v>
-      </c>
-      <c r="H37" s="56" t="s">
+      <c r="C37" s="114" t="s">
+        <v>170</v>
+      </c>
+      <c r="D37" s="115" t="s">
+        <v>131</v>
+      </c>
+      <c r="E37" s="115" t="s">
+        <v>171</v>
+      </c>
+      <c r="F37" s="116" t="s">
+        <v>173</v>
+      </c>
+      <c r="G37" s="101" t="s">
+        <v>172</v>
+      </c>
+      <c r="H37" s="97"/>
+      <c r="I37" s="101" t="s">
         <v>19</v>
       </c>
-      <c r="I37" s="56" t="s">
-        <v>19</v>
-      </c>
-      <c r="J37" s="57" t="s">
-        <v>143</v>
-      </c>
-      <c r="K37" s="30">
-        <v>12</v>
-      </c>
-      <c r="L37" s="23">
-        <v>2</v>
-      </c>
-      <c r="M37" s="11">
+      <c r="J37" s="102" t="s">
+        <v>132</v>
+      </c>
+      <c r="K37" s="97">
+        <v>6</v>
+      </c>
+      <c r="L37" s="97">
+        <v>1</v>
+      </c>
+      <c r="M37" s="98">
         <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="N37" s="97" t="s">
-        <v>144</v>
-      </c>
-      <c r="O37" s="31"/>
+        <v>6</v>
+      </c>
+      <c r="N37" s="117" t="s">
+        <v>88</v>
+      </c>
+      <c r="O37" s="30"/>
     </row>
     <row r="38" spans="1:15" ht="15.75" thickBot="1">
       <c r="A38" s="6">
         <v>36</v>
       </c>
-      <c r="B38" s="173"/>
-      <c r="C38" s="55" t="s">
-        <v>145</v>
-      </c>
-      <c r="D38" s="56" t="s">
-        <v>146</v>
-      </c>
-      <c r="E38" s="56" t="s">
-        <v>44</v>
-      </c>
-      <c r="F38" s="56" t="s">
-        <v>147</v>
-      </c>
-      <c r="G38" s="56" t="s">
+      <c r="B38" s="172" t="s">
+        <v>133</v>
+      </c>
+      <c r="C38" s="52" t="s">
+        <v>134</v>
+      </c>
+      <c r="D38" s="53" t="s">
+        <v>135</v>
+      </c>
+      <c r="E38" s="53" t="s">
+        <v>256</v>
+      </c>
+      <c r="F38" s="53" t="s">
+        <v>136</v>
+      </c>
+      <c r="G38" s="53" t="s">
         <v>137</v>
       </c>
-      <c r="H38" s="56" t="s">
+      <c r="H38" s="53" t="s">
         <v>19</v>
       </c>
-      <c r="I38" s="56" t="s">
+      <c r="I38" s="53" t="s">
         <v>19</v>
       </c>
-      <c r="J38" s="57" t="s">
+      <c r="J38" s="53" t="s">
         <v>70</v>
       </c>
-      <c r="K38" s="30">
-        <v>10</v>
-      </c>
-      <c r="L38" s="23">
+      <c r="K38" s="22">
+        <v>100</v>
+      </c>
+      <c r="L38" s="22">
         <v>1</v>
       </c>
-      <c r="M38" s="11">
+      <c r="M38" s="18">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N38" s="97" t="s">
+      <c r="N38" s="118" t="s">
         <v>138</v>
       </c>
-      <c r="O38" s="31"/>
+      <c r="O38" s="30"/>
     </row>
     <row r="39" spans="1:15" ht="15.75" thickBot="1">
       <c r="A39" s="6">
         <v>37</v>
       </c>
       <c r="B39" s="173"/>
-      <c r="C39" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="D39" s="37" t="s">
-        <v>149</v>
-      </c>
-      <c r="E39" s="37" t="s">
+      <c r="C39" s="54" t="s">
+        <v>139</v>
+      </c>
+      <c r="D39" s="55" t="s">
+        <v>140</v>
+      </c>
+      <c r="E39" s="55" t="s">
         <v>44</v>
       </c>
-      <c r="F39" s="37" t="s">
-        <v>150</v>
-      </c>
-      <c r="G39" s="37" t="s">
-        <v>151</v>
-      </c>
-      <c r="H39" s="37" t="s">
-        <v>150</v>
-      </c>
-      <c r="I39" s="37" t="s">
+      <c r="F39" s="55" t="s">
+        <v>141</v>
+      </c>
+      <c r="G39" s="55" t="s">
+        <v>142</v>
+      </c>
+      <c r="H39" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="J39" s="39" t="s">
+      <c r="I39" s="55" t="s">
+        <v>19</v>
+      </c>
+      <c r="J39" s="56" t="s">
         <v>143</v>
       </c>
-      <c r="K39" s="13">
-        <v>20</v>
-      </c>
-      <c r="L39" s="7">
-        <v>1</v>
+      <c r="K39" s="29">
+        <v>12</v>
+      </c>
+      <c r="L39" s="23">
+        <v>2</v>
       </c>
       <c r="M39" s="11">
         <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="N39" s="98" t="s">
-        <v>21</v>
-      </c>
-      <c r="O39" s="31"/>
+        <v>12</v>
+      </c>
+      <c r="N39" s="92" t="s">
+        <v>144</v>
+      </c>
+      <c r="O39" s="30"/>
     </row>
     <row r="40" spans="1:15" ht="15.75" thickBot="1">
       <c r="A40" s="6">
         <v>38</v>
       </c>
       <c r="B40" s="173"/>
-      <c r="C40" s="51" t="s">
-        <v>152</v>
-      </c>
-      <c r="D40" s="37" t="s">
-        <v>153</v>
-      </c>
-      <c r="E40" s="37" t="s">
-        <v>154</v>
-      </c>
-      <c r="F40" s="37" t="s">
-        <v>155</v>
-      </c>
-      <c r="G40" s="37" t="s">
-        <v>156</v>
-      </c>
-      <c r="H40" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="I40" s="37" t="s">
+      <c r="C40" s="54" t="s">
+        <v>145</v>
+      </c>
+      <c r="D40" s="55" t="s">
+        <v>146</v>
+      </c>
+      <c r="E40" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="F40" s="55" t="s">
+        <v>147</v>
+      </c>
+      <c r="G40" s="55" t="s">
+        <v>137</v>
+      </c>
+      <c r="H40" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="J40" s="39" t="s">
+      <c r="I40" s="55" t="s">
+        <v>19</v>
+      </c>
+      <c r="J40" s="56" t="s">
         <v>70</v>
       </c>
-      <c r="K40" s="13">
-        <v>15</v>
-      </c>
-      <c r="L40" s="13">
-        <v>2</v>
+      <c r="K40" s="29">
+        <v>10</v>
+      </c>
+      <c r="L40" s="23">
+        <v>1</v>
       </c>
       <c r="M40" s="11">
         <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="N40" s="99" t="s">
-        <v>21</v>
-      </c>
-      <c r="O40" s="31"/>
+        <v>6</v>
+      </c>
+      <c r="N40" s="92" t="s">
+        <v>138</v>
+      </c>
+      <c r="O40" s="30"/>
     </row>
     <row r="41" spans="1:15" ht="15.75" thickBot="1">
       <c r="A41" s="6">
         <v>39</v>
       </c>
       <c r="B41" s="173"/>
-      <c r="C41" s="58" t="s">
-        <v>158</v>
-      </c>
-      <c r="D41" s="24"/>
-      <c r="E41" s="59" t="s">
-        <v>159</v>
-      </c>
-      <c r="F41" s="24" t="s">
-        <v>159</v>
-      </c>
-      <c r="G41" s="24"/>
-      <c r="H41" s="24"/>
-      <c r="I41" s="24"/>
-      <c r="J41" s="24"/>
-      <c r="K41" s="24"/>
-      <c r="L41" s="24">
-        <v>5</v>
+      <c r="C41" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="D41" s="36" t="s">
+        <v>149</v>
+      </c>
+      <c r="E41" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="F41" s="36" t="s">
+        <v>150</v>
+      </c>
+      <c r="G41" s="36" t="s">
+        <v>151</v>
+      </c>
+      <c r="H41" s="36" t="s">
+        <v>150</v>
+      </c>
+      <c r="I41" s="36" t="s">
+        <v>19</v>
+      </c>
+      <c r="J41" s="38" t="s">
+        <v>143</v>
+      </c>
+      <c r="K41" s="13">
+        <v>20</v>
+      </c>
+      <c r="L41" s="7">
+        <v>1</v>
       </c>
       <c r="M41" s="11">
         <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="N41" s="100" t="s">
+        <v>6</v>
+      </c>
+      <c r="N41" s="93" t="s">
+        <v>21</v>
+      </c>
+      <c r="O41" s="30"/>
+    </row>
+    <row r="42" spans="1:15" ht="15.75" thickBot="1">
+      <c r="A42" s="6">
+        <v>40</v>
+      </c>
+      <c r="B42" s="173"/>
+      <c r="C42" s="50" t="s">
+        <v>152</v>
+      </c>
+      <c r="D42" s="36" t="s">
+        <v>153</v>
+      </c>
+      <c r="E42" s="36" t="s">
+        <v>154</v>
+      </c>
+      <c r="F42" s="36" t="s">
+        <v>155</v>
+      </c>
+      <c r="G42" s="36" t="s">
+        <v>156</v>
+      </c>
+      <c r="H42" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="I42" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="O41" s="31"/>
-    </row>
-    <row r="42" spans="1:15" ht="15.75" thickBot="1">
-      <c r="A42" s="25">
-        <v>40</v>
-      </c>
-      <c r="B42" s="174"/>
-      <c r="C42" s="60" t="s">
-        <v>160</v>
-      </c>
-      <c r="D42" s="26"/>
-      <c r="E42" s="61" t="s">
-        <v>161</v>
-      </c>
-      <c r="F42" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="G42" s="26"/>
-      <c r="H42" s="26"/>
-      <c r="I42" s="26"/>
-      <c r="J42" s="26"/>
-      <c r="K42" s="26"/>
-      <c r="L42" s="26">
+      <c r="J42" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="K42" s="13">
+        <v>15</v>
+      </c>
+      <c r="L42" s="13">
+        <v>2</v>
+      </c>
+      <c r="M42" s="11">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="N42" s="94" t="s">
+        <v>21</v>
+      </c>
+      <c r="O42" s="30"/>
+    </row>
+    <row r="43" spans="1:15" ht="15.75" thickBot="1">
+      <c r="A43" s="6">
+        <v>41</v>
+      </c>
+      <c r="B43" s="173"/>
+      <c r="C43" s="57" t="s">
+        <v>158</v>
+      </c>
+      <c r="D43" s="24"/>
+      <c r="E43" s="58" t="s">
+        <v>159</v>
+      </c>
+      <c r="F43" s="24" t="s">
+        <v>159</v>
+      </c>
+      <c r="G43" s="24"/>
+      <c r="H43" s="24"/>
+      <c r="I43" s="24"/>
+      <c r="J43" s="24"/>
+      <c r="K43" s="24"/>
+      <c r="L43" s="24">
         <v>5</v>
       </c>
-      <c r="M42" s="15">
+      <c r="M43" s="11">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
-      <c r="N42" s="101" t="s">
+      <c r="N43" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="O42" s="31"/>
-    </row>
-    <row r="43" spans="1:15" ht="16.5" thickBot="1">
-      <c r="A43"/>
-      <c r="C43" s="27"/>
-      <c r="D43" s="27"/>
-      <c r="E43" s="27"/>
-      <c r="F43" s="27"/>
-      <c r="G43" s="27"/>
-      <c r="H43" s="27"/>
-      <c r="I43" s="27"/>
-      <c r="J43" s="27"/>
-      <c r="K43" s="27"/>
-      <c r="L43" s="74"/>
-      <c r="M43" s="74"/>
-      <c r="N43" s="74"/>
-      <c r="O43" s="31"/>
-    </row>
-    <row r="44" spans="1:15">
-      <c r="A44"/>
-      <c r="C44" s="27"/>
-      <c r="D44" s="27"/>
-      <c r="E44" s="27"/>
-      <c r="F44" s="27"/>
-      <c r="G44" s="27"/>
-      <c r="H44" s="27"/>
-      <c r="I44" s="27"/>
-      <c r="J44" s="27"/>
-      <c r="K44" s="27"/>
-      <c r="O44" s="31"/>
-    </row>
-    <row r="45" spans="1:15">
+      <c r="O43" s="30"/>
+    </row>
+    <row r="44" spans="1:15" ht="15.75" thickBot="1">
+      <c r="A44" s="6">
+        <v>42</v>
+      </c>
+      <c r="B44" s="174"/>
+      <c r="C44" s="59" t="s">
+        <v>160</v>
+      </c>
+      <c r="D44" s="25"/>
+      <c r="E44" s="60" t="s">
+        <v>161</v>
+      </c>
+      <c r="F44" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="G44" s="25"/>
+      <c r="H44" s="25"/>
+      <c r="I44" s="25"/>
+      <c r="J44" s="25"/>
+      <c r="K44" s="25"/>
+      <c r="L44" s="25">
+        <v>5</v>
+      </c>
+      <c r="M44" s="15">
+        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="N44" s="96" t="s">
+        <v>19</v>
+      </c>
+      <c r="O44" s="30"/>
+    </row>
+    <row r="45" spans="1:15" ht="16.5" thickBot="1">
       <c r="A45"/>
-      <c r="O45" s="31"/>
+      <c r="C45" s="26"/>
+      <c r="D45" s="26"/>
+      <c r="E45" s="26"/>
+      <c r="F45" s="26"/>
+      <c r="G45" s="26"/>
+      <c r="H45" s="26"/>
+      <c r="I45" s="26"/>
+      <c r="J45" s="26"/>
+      <c r="K45" s="26"/>
+      <c r="L45" s="171"/>
+      <c r="M45" s="171"/>
+      <c r="N45" s="171"/>
+      <c r="O45" s="30"/>
     </row>
     <row r="46" spans="1:15">
       <c r="A46"/>
-      <c r="O46" s="31"/>
+      <c r="C46" s="26"/>
+      <c r="D46" s="26"/>
+      <c r="E46" s="26"/>
+      <c r="F46" s="26"/>
+      <c r="G46" s="26"/>
+      <c r="H46" s="26"/>
+      <c r="I46" s="26"/>
+      <c r="J46" s="26"/>
+      <c r="K46" s="26"/>
+      <c r="O46" s="30"/>
     </row>
     <row r="47" spans="1:15">
       <c r="A47"/>
-      <c r="O47" s="31"/>
+      <c r="O47" s="30"/>
     </row>
     <row r="48" spans="1:15">
       <c r="A48"/>
-      <c r="O48" s="31"/>
+      <c r="O48" s="30"/>
     </row>
     <row r="49" spans="1:15">
       <c r="A49"/>
-      <c r="O49" s="31"/>
+      <c r="O49" s="30"/>
     </row>
     <row r="50" spans="1:15">
       <c r="A50"/>
-      <c r="O50" s="31"/>
+      <c r="O50" s="30"/>
     </row>
     <row r="51" spans="1:15">
       <c r="A51"/>
-      <c r="O51" s="31"/>
-    </row>
-    <row r="52" spans="1:15" ht="15.75" customHeight="1">
+      <c r="O51" s="30"/>
+    </row>
+    <row r="52" spans="1:15">
       <c r="A52"/>
-      <c r="N52" s="71"/>
-      <c r="O52" s="31"/>
+      <c r="O52" s="30"/>
     </row>
     <row r="53" spans="1:15">
       <c r="A53"/>
-      <c r="O53" s="31"/>
-    </row>
-    <row r="54" spans="1:15">
+      <c r="O53" s="30"/>
+    </row>
+    <row r="54" spans="1:15" ht="15.75" customHeight="1">
       <c r="A54"/>
-      <c r="O54" s="31"/>
+      <c r="N54" s="70"/>
+      <c r="O54" s="30"/>
     </row>
     <row r="55" spans="1:15">
       <c r="A55"/>
-      <c r="O55" s="31"/>
+      <c r="O55" s="30"/>
     </row>
     <row r="56" spans="1:15">
       <c r="A56"/>
-      <c r="O56" s="31"/>
+      <c r="O56" s="30"/>
     </row>
     <row r="57" spans="1:15">
       <c r="A57"/>
-      <c r="O57" s="31"/>
+      <c r="O57" s="30"/>
     </row>
     <row r="58" spans="1:15">
-      <c r="H58" s="28"/>
+      <c r="A58"/>
+      <c r="O58" s="30"/>
     </row>
     <row r="59" spans="1:15">
-      <c r="H59" s="28"/>
+      <c r="A59"/>
+      <c r="O59" s="30"/>
+    </row>
+    <row r="60" spans="1:15">
+      <c r="H60" s="27"/>
+    </row>
+    <row r="61" spans="1:15">
+      <c r="H61" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A1:N1"/>
-    <mergeCell ref="L43:N43"/>
-    <mergeCell ref="B3:B13"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="B22:B32"/>
-    <mergeCell ref="B33:B35"/>
-    <mergeCell ref="B36:B42"/>
-    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="L45:N45"/>
+    <mergeCell ref="B3:B14"/>
+    <mergeCell ref="B15:B18"/>
+    <mergeCell ref="B23:B34"/>
+    <mergeCell ref="B35:B37"/>
+    <mergeCell ref="B38:B44"/>
+    <mergeCell ref="B21:B22"/>
   </mergeCells>
-  <phoneticPr fontId="20" type="noConversion"/>
-  <conditionalFormatting sqref="N21">
+  <phoneticPr fontId="21" type="noConversion"/>
+  <conditionalFormatting sqref="N22">
     <cfRule type="dataBar" priority="38">
       <dataBar>
         <cfvo type="min"/>
@@ -4168,7 +4308,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L36:M36">
+  <conditionalFormatting sqref="L38:M38">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -4180,7 +4320,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L41">
+  <conditionalFormatting sqref="L43">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
@@ -4202,7 +4342,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L42">
+  <conditionalFormatting sqref="L44">
     <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
@@ -4224,7 +4364,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N3:N6">
+  <conditionalFormatting sqref="N3:N7">
     <cfRule type="dataBar" priority="40">
       <dataBar>
         <cfvo type="min"/>
@@ -4238,7 +4378,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N32">
+  <conditionalFormatting sqref="N34">
     <cfRule type="dataBar" priority="37">
       <dataBar>
         <cfvo type="min"/>
@@ -4252,7 +4392,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L12:L35 L40 M3:M42">
+  <conditionalFormatting sqref="L13:L37 L42 M3:M44">
     <cfRule type="colorScale" priority="50">
       <colorScale>
         <cfvo type="min"/>
@@ -4264,7 +4404,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L8:L11">
+  <conditionalFormatting sqref="L9:L12">
     <cfRule type="colorScale" priority="51">
       <colorScale>
         <cfvo type="min"/>
@@ -4276,7 +4416,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L3:M42">
+  <conditionalFormatting sqref="L3:M44">
     <cfRule type="colorScale" priority="61">
       <colorScale>
         <cfvo type="min"/>
@@ -4289,45 +4429,47 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="N9" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="N10" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="N13" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="N14" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="N17" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="N22" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="N28" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="N29" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="N31" r:id="rId9" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="N32" r:id="rId10" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="N34" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="N40" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="N8" r:id="rId13" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="N30" r:id="rId14" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="N10" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="N11" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="N14" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="N15" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="N18" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="N23" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="N30" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="N31" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="N33" r:id="rId9" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="N34" r:id="rId10" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="N36" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="N42" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="N9" r:id="rId13" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="N32" r:id="rId14" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
     <hyperlink ref="N3" r:id="rId15" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="N6" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="N7" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="N36" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="N38" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="N18" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="N39" r:id="rId21" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="N20" r:id="rId22" xr:uid="{5EAF2F70-555A-4B25-966F-95095861DC0E}"/>
-    <hyperlink ref="N23" r:id="rId23" xr:uid="{6B884554-8BB6-4BF7-8096-D834E9729A06}"/>
-    <hyperlink ref="N11" r:id="rId24" xr:uid="{44B658D6-BFFD-46B9-B230-29405BAF9534}"/>
-    <hyperlink ref="N12" r:id="rId25" xr:uid="{367FEFFE-61E8-47BB-BCCA-FD3358349566}"/>
-    <hyperlink ref="N33" r:id="rId26" xr:uid="{D1D06D79-D259-47BA-BC7F-8742EAB7848C}"/>
-    <hyperlink ref="N24" r:id="rId27" xr:uid="{5545F658-0692-42E9-BD6F-76E0A6B030B0}"/>
-    <hyperlink ref="N26" r:id="rId28" xr:uid="{168ECF43-5CE3-4702-A056-8FA8BBC47676}"/>
-    <hyperlink ref="N25" r:id="rId29" xr:uid="{EA5E5506-441F-4FE0-B453-D92044CD3CD6}"/>
-    <hyperlink ref="N27" r:id="rId30" xr:uid="{8D8C1B68-82FF-4307-AFCC-0412DDB5B0BE}"/>
+    <hyperlink ref="N7" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="N8" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="N38" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="N40" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="N19" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="N41" r:id="rId21" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="N21" r:id="rId22" xr:uid="{5EAF2F70-555A-4B25-966F-95095861DC0E}"/>
+    <hyperlink ref="N24" r:id="rId23" xr:uid="{6B884554-8BB6-4BF7-8096-D834E9729A06}"/>
+    <hyperlink ref="N12" r:id="rId24" xr:uid="{44B658D6-BFFD-46B9-B230-29405BAF9534}"/>
+    <hyperlink ref="N13" r:id="rId25" xr:uid="{367FEFFE-61E8-47BB-BCCA-FD3358349566}"/>
+    <hyperlink ref="N35" r:id="rId26" xr:uid="{D1D06D79-D259-47BA-BC7F-8742EAB7848C}"/>
+    <hyperlink ref="N25" r:id="rId27" xr:uid="{5545F658-0692-42E9-BD6F-76E0A6B030B0}"/>
+    <hyperlink ref="N27" r:id="rId28" xr:uid="{168ECF43-5CE3-4702-A056-8FA8BBC47676}"/>
+    <hyperlink ref="N26" r:id="rId29" xr:uid="{EA5E5506-441F-4FE0-B453-D92044CD3CD6}"/>
+    <hyperlink ref="N28" r:id="rId30" xr:uid="{8D8C1B68-82FF-4307-AFCC-0412DDB5B0BE}"/>
     <hyperlink ref="N4" r:id="rId31" xr:uid="{2EF0B57E-A4CF-4AC0-9358-948CDF39D8B4}"/>
     <hyperlink ref="N5" r:id="rId32" xr:uid="{ECCB4777-894F-4969-BB30-3BB1C2789276}"/>
-    <hyperlink ref="C15" r:id="rId33" xr:uid="{44A99C6C-4AC4-4D03-96BE-D592031C9536}"/>
-    <hyperlink ref="N15" r:id="rId34" xr:uid="{1A7B0E41-616E-45F1-BF6C-4CBB22A55EC6}"/>
-    <hyperlink ref="N19" r:id="rId35" xr:uid="{0E9DC705-3503-4FA0-87A9-DF2A5B60045D}"/>
-    <hyperlink ref="N16" r:id="rId36" xr:uid="{E7A9FE43-2492-4F96-944F-8153D9DD3BC5}"/>
+    <hyperlink ref="C16" r:id="rId33" xr:uid="{44A99C6C-4AC4-4D03-96BE-D592031C9536}"/>
+    <hyperlink ref="N16" r:id="rId34" xr:uid="{1A7B0E41-616E-45F1-BF6C-4CBB22A55EC6}"/>
+    <hyperlink ref="N20" r:id="rId35" xr:uid="{0E9DC705-3503-4FA0-87A9-DF2A5B60045D}"/>
+    <hyperlink ref="N17" r:id="rId36" xr:uid="{E7A9FE43-2492-4F96-944F-8153D9DD3BC5}"/>
+    <hyperlink ref="N6" r:id="rId37" xr:uid="{C6B216F8-5775-4357-B676-8FC9F8808265}"/>
+    <hyperlink ref="N29" r:id="rId38" xr:uid="{A2E7CF78-849E-4B20-A638-AA9D3B8EC8EE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId37"/>
+  <pageSetup orientation="portrait" r:id="rId39"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -4342,7 +4484,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>N21</xm:sqref>
+          <xm:sqref>N22</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{94E20060-874B-439F-8FDA-33B3DD39FFE6}">
@@ -4355,7 +4497,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>N3:N6</xm:sqref>
+          <xm:sqref>N3:N7</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{DBB933A5-5D45-42AE-8D8B-F05439EF033D}">
@@ -4368,7 +4510,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>N32</xm:sqref>
+          <xm:sqref>N34</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/Deliverables/Interface_Board/BOM/NEW-6 Prototypes_Interface_Board.xlsx
+++ b/Deliverables/Interface_Board/BOM/NEW-6 Prototypes_Interface_Board.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ChristianRaun-EthercatDesign\Deliverables\Interface_Board\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF979C34-0560-475B-8E10-1F732207B98C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D3A7ABD-CD90-4A4A-93AF-082A2F30B043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="256">
   <si>
     <t>Bill of Material (BOM) for Interface_Board</t>
   </si>
@@ -63,9 +63,6 @@
   </si>
   <si>
     <t>Value</t>
-  </si>
-  <si>
-    <t>LCSC/MOQ</t>
   </si>
   <si>
     <t>Quantity (Per Board)</t>
@@ -1474,7 +1471,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="180">
+  <cellXfs count="179">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1558,9 +1555,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1961,6 +1955,19 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1982,19 +1989,6 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2271,7 +2265,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AD61"/>
+  <dimension ref="A1:AC61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="2" customWidth="1"/>
@@ -2284,31 +2278,29 @@
     <col min="8" max="8" width="15.28515625" style="2" customWidth="1"/>
     <col min="9" max="9" width="21.5703125" customWidth="1"/>
     <col min="10" max="10" width="7" customWidth="1"/>
-    <col min="11" max="11" width="11.5703125" customWidth="1"/>
-    <col min="12" max="12" width="21.85546875" customWidth="1"/>
-    <col min="13" max="13" width="14.140625" customWidth="1"/>
-    <col min="14" max="14" width="16.28515625" customWidth="1"/>
+    <col min="11" max="11" width="21.85546875" customWidth="1"/>
+    <col min="12" max="12" width="14.140625" customWidth="1"/>
+    <col min="13" max="13" width="16.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="16.5" thickBot="1">
-      <c r="A1" s="168" t="s">
+    <row r="1" spans="1:29" ht="16.5" thickBot="1">
+      <c r="A1" s="172" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="169"/>
-      <c r="C1" s="169"/>
-      <c r="D1" s="169"/>
-      <c r="E1" s="169"/>
-      <c r="F1" s="169"/>
-      <c r="G1" s="169"/>
-      <c r="H1" s="169"/>
-      <c r="I1" s="169"/>
-      <c r="J1" s="169"/>
-      <c r="K1" s="169"/>
-      <c r="L1" s="169"/>
-      <c r="M1" s="169"/>
-      <c r="N1" s="170"/>
-    </row>
-    <row r="2" spans="1:30" s="1" customFormat="1" ht="16.5" thickBot="1">
+      <c r="B1" s="173"/>
+      <c r="C1" s="173"/>
+      <c r="D1" s="173"/>
+      <c r="E1" s="173"/>
+      <c r="F1" s="173"/>
+      <c r="G1" s="173"/>
+      <c r="H1" s="173"/>
+      <c r="I1" s="173"/>
+      <c r="J1" s="173"/>
+      <c r="K1" s="173"/>
+      <c r="L1" s="173"/>
+      <c r="M1" s="174"/>
+    </row>
+    <row r="2" spans="1:29" s="1" customFormat="1" ht="16.5" thickBot="1">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -2342,15 +2334,13 @@
       <c r="K2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="M2" s="68" t="s">
-        <v>181</v>
-      </c>
-      <c r="N2" s="88" t="s">
+      <c r="L2" s="67" t="s">
         <v>180</v>
       </c>
+      <c r="M2" s="87" t="s">
+        <v>179</v>
+      </c>
+      <c r="N2"/>
       <c r="O2"/>
       <c r="P2"/>
       <c r="Q2"/>
@@ -2366,1835 +2356,1712 @@
       <c r="AA2"/>
       <c r="AB2"/>
       <c r="AC2"/>
-      <c r="AD2"/>
-    </row>
-    <row r="3" spans="1:30" ht="15.75" thickBot="1">
+    </row>
+    <row r="3" spans="1:29" ht="15.75" thickBot="1">
       <c r="A3" s="6">
         <v>1</v>
       </c>
-      <c r="B3" s="172" t="s">
+      <c r="B3" s="176" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="138" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="139" t="s">
+      <c r="D3" s="139" t="s">
+        <v>243</v>
+      </c>
+      <c r="E3" s="140" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="140" t="s">
-        <v>244</v>
-      </c>
-      <c r="E3" s="141" t="s">
+      <c r="F3" s="140" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="141" t="s">
+      <c r="G3" s="140" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="141" t="s">
+      <c r="H3" s="141" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="142" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" s="143" t="s">
+      <c r="I3" s="142" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="140" t="s">
         <v>19</v>
       </c>
-      <c r="J3" s="141" t="s">
+      <c r="K3" s="143">
+        <v>6</v>
+      </c>
+      <c r="L3" s="143">
+        <f>K3*6</f>
+        <v>36</v>
+      </c>
+      <c r="M3" s="144" t="s">
         <v>20</v>
       </c>
-      <c r="K3" s="144">
-        <v>50</v>
-      </c>
-      <c r="L3" s="144">
-        <v>6</v>
-      </c>
-      <c r="M3" s="144">
-        <f>L3*6</f>
-        <v>36</v>
-      </c>
-      <c r="N3" s="145" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:30" ht="15.75" thickBot="1">
+    </row>
+    <row r="4" spans="1:29" ht="15.75" thickBot="1">
       <c r="A4" s="6">
         <v>2</v>
       </c>
-      <c r="B4" s="173"/>
-      <c r="C4" s="146" t="s">
+      <c r="B4" s="177"/>
+      <c r="C4" s="145" t="s">
+        <v>208</v>
+      </c>
+      <c r="D4" s="146" t="s">
         <v>209</v>
       </c>
-      <c r="D4" s="147" t="s">
+      <c r="E4" s="131" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="132" t="s">
+        <v>207</v>
+      </c>
+      <c r="G4" s="132" t="s">
         <v>210</v>
       </c>
-      <c r="E4" s="132" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="133" t="s">
-        <v>208</v>
-      </c>
-      <c r="G4" s="133" t="s">
+      <c r="H4" s="147" t="s">
         <v>211</v>
       </c>
-      <c r="H4" s="148" t="s">
+      <c r="I4" s="148" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" s="132" t="s">
         <v>212</v>
       </c>
-      <c r="I4" s="149" t="s">
-        <v>19</v>
-      </c>
-      <c r="J4" s="133" t="s">
-        <v>213</v>
-      </c>
-      <c r="K4" s="134">
+      <c r="K4" s="133">
+        <v>1</v>
+      </c>
+      <c r="L4" s="133">
+        <f t="shared" ref="L4:L6" si="0">K4*6</f>
+        <v>6</v>
+      </c>
+      <c r="M4" s="149" t="s">
         <v>20</v>
       </c>
-      <c r="L4" s="134">
-        <v>1</v>
-      </c>
-      <c r="M4" s="134">
-        <f t="shared" ref="M4:M6" si="0">L4*6</f>
-        <v>6</v>
-      </c>
-      <c r="N4" s="150" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:30" ht="15.75" thickBot="1">
+    </row>
+    <row r="5" spans="1:29" ht="15.75" thickBot="1">
       <c r="A5" s="6">
         <v>3</v>
       </c>
-      <c r="B5" s="173"/>
-      <c r="C5" s="146" t="s">
-        <v>218</v>
-      </c>
-      <c r="D5" s="147" t="s">
+      <c r="B5" s="177"/>
+      <c r="C5" s="145" t="s">
         <v>217</v>
       </c>
-      <c r="E5" s="132" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="133" t="s">
+      <c r="D5" s="146" t="s">
+        <v>216</v>
+      </c>
+      <c r="E5" s="131" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="132" t="s">
+        <v>213</v>
+      </c>
+      <c r="G5" s="132" t="s">
+        <v>210</v>
+      </c>
+      <c r="H5" s="147" t="s">
         <v>214</v>
       </c>
-      <c r="G5" s="133" t="s">
-        <v>211</v>
-      </c>
-      <c r="H5" s="148" t="s">
+      <c r="I5" s="148" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" s="132" t="s">
         <v>215</v>
       </c>
-      <c r="I5" s="149" t="s">
-        <v>19</v>
-      </c>
-      <c r="J5" s="133" t="s">
-        <v>216</v>
-      </c>
-      <c r="K5" s="134">
-        <v>50</v>
-      </c>
-      <c r="L5" s="134">
+      <c r="K5" s="133">
         <v>2</v>
       </c>
-      <c r="M5" s="134">
+      <c r="L5" s="133">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="N5" s="150" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:30" ht="15.75" thickBot="1">
+      <c r="M5" s="149" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29" ht="15.75" thickBot="1">
       <c r="A6" s="6">
         <v>4</v>
       </c>
-      <c r="B6" s="173"/>
-      <c r="C6" s="176" t="s">
+      <c r="B6" s="177"/>
+      <c r="C6" s="168" t="s">
+        <v>246</v>
+      </c>
+      <c r="D6" s="146" t="s">
+        <v>245</v>
+      </c>
+      <c r="E6" s="131" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="167" t="s">
+        <v>244</v>
+      </c>
+      <c r="G6" s="131" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" s="147" t="s">
         <v>247</v>
       </c>
-      <c r="D6" s="147" t="s">
-        <v>246</v>
-      </c>
-      <c r="E6" s="132" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="175" t="s">
-        <v>245</v>
-      </c>
-      <c r="G6" s="132" t="s">
-        <v>26</v>
-      </c>
-      <c r="H6" s="148" t="s">
+      <c r="I6" s="148" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6" s="167" t="s">
         <v>248</v>
       </c>
-      <c r="I6" s="149" t="s">
-        <v>19</v>
-      </c>
-      <c r="J6" s="175" t="s">
-        <v>249</v>
-      </c>
-      <c r="K6" s="134">
-        <v>30</v>
-      </c>
-      <c r="L6" s="134">
+      <c r="K6" s="133">
         <v>4</v>
       </c>
-      <c r="M6" s="134">
+      <c r="L6" s="133">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="N6" s="150" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:30" ht="15.75" thickBot="1">
+      <c r="M6" s="149" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29" ht="15.75" thickBot="1">
       <c r="A7" s="6">
         <v>5</v>
       </c>
-      <c r="B7" s="173"/>
-      <c r="C7" s="35" t="s">
+      <c r="B7" s="177"/>
+      <c r="C7" s="34" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="D7" s="36" t="s">
+      <c r="E7" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="37" t="s">
+      <c r="F7" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="F7" s="36" t="s">
+      <c r="G7" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="G7" s="37" t="s">
+      <c r="H7" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="I7" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7" s="36" t="s">
         <v>27</v>
       </c>
-      <c r="I7" s="38" t="s">
-        <v>19</v>
-      </c>
-      <c r="J7" s="37" t="s">
-        <v>28</v>
-      </c>
-      <c r="K7" s="11">
-        <v>10</v>
-      </c>
-      <c r="L7" s="8">
+      <c r="K7" s="8">
         <v>1</v>
       </c>
-      <c r="M7" s="11">
-        <f t="shared" ref="M7:M44" si="1">L7*6</f>
+      <c r="L7" s="11">
+        <f t="shared" ref="L7:L44" si="1">K7*6</f>
         <v>6</v>
       </c>
-      <c r="N7" s="83" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:30" ht="15.75" thickBot="1">
+      <c r="M7" s="82" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" ht="15.75" thickBot="1">
       <c r="A8" s="6">
         <v>6</v>
       </c>
-      <c r="B8" s="173"/>
-      <c r="C8" s="35" t="s">
+      <c r="B8" s="177"/>
+      <c r="C8" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="D8" s="36" t="s">
+      <c r="E8" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="37" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8" s="39" t="s">
+      <c r="G8" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="G8" s="37" t="s">
+      <c r="H8" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="H8" s="10" t="s">
+      <c r="I8" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="I8" s="10" t="s">
+      <c r="J8" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="J8" s="37" t="s">
-        <v>35</v>
-      </c>
-      <c r="K8" s="11">
-        <v>100</v>
-      </c>
-      <c r="L8" s="8">
+      <c r="K8" s="8">
         <v>8</v>
       </c>
-      <c r="M8" s="11">
+      <c r="L8" s="11">
         <f t="shared" si="1"/>
         <v>48</v>
       </c>
-      <c r="N8" s="84" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" spans="1:30" ht="15.75" thickBot="1">
+      <c r="M8" s="83" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" ht="15.75" thickBot="1">
       <c r="A9" s="6">
         <v>7</v>
       </c>
-      <c r="B9" s="173"/>
-      <c r="C9" s="151" t="s">
+      <c r="B9" s="177"/>
+      <c r="C9" s="150" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="132" t="s">
+        <v>232</v>
+      </c>
+      <c r="E9" s="131" t="s">
+        <v>14</v>
+      </c>
+      <c r="F9" s="161" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="133" t="s">
-        <v>233</v>
-      </c>
-      <c r="E9" s="132" t="s">
-        <v>15</v>
-      </c>
-      <c r="F9" s="162" t="s">
+      <c r="G9" s="148" t="s">
         <v>37</v>
       </c>
-      <c r="G9" s="149" t="s">
+      <c r="H9" s="76" t="s">
         <v>38</v>
       </c>
-      <c r="H9" s="77" t="s">
+      <c r="I9" s="131" t="s">
         <v>39</v>
       </c>
-      <c r="I9" s="132" t="s">
+      <c r="J9" s="131" t="s">
         <v>40</v>
       </c>
-      <c r="J9" s="132" t="s">
-        <v>41</v>
-      </c>
-      <c r="K9" s="134">
-        <v>50</v>
-      </c>
-      <c r="L9" s="77">
+      <c r="K9" s="76">
         <v>3</v>
       </c>
-      <c r="M9" s="134">
+      <c r="L9" s="133">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="N9" s="163" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:30" ht="15.75" thickBot="1">
+      <c r="M9" s="162" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" ht="15.75" thickBot="1">
       <c r="A10" s="6">
         <v>8</v>
       </c>
-      <c r="B10" s="173"/>
-      <c r="C10" s="40" t="s">
+      <c r="B10" s="177"/>
+      <c r="C10" s="39" t="s">
+        <v>41</v>
+      </c>
+      <c r="D10" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="36" t="s">
+      <c r="E10" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="41" t="s">
+      <c r="F10" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="F10" s="36" t="s">
+      <c r="G10" s="41" t="s">
         <v>45</v>
       </c>
-      <c r="G10" s="42" t="s">
+      <c r="H10" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="H10" s="13" t="s">
+      <c r="I10" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10" s="40" t="s">
         <v>47</v>
       </c>
-      <c r="I10" s="38" t="s">
-        <v>19</v>
-      </c>
-      <c r="J10" s="41" t="s">
-        <v>48</v>
-      </c>
-      <c r="K10" s="11">
-        <v>10</v>
-      </c>
-      <c r="L10" s="28">
+      <c r="K10" s="28">
         <v>1</v>
       </c>
-      <c r="M10" s="11">
+      <c r="L10" s="11">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N10" s="85" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:30" ht="15.75" thickBot="1">
+      <c r="M10" s="84" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" ht="15.75" thickBot="1">
       <c r="A11" s="6">
         <v>9</v>
       </c>
-      <c r="B11" s="173"/>
-      <c r="C11" s="151" t="s">
+      <c r="B11" s="177"/>
+      <c r="C11" s="150" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" s="132" t="s">
+        <v>233</v>
+      </c>
+      <c r="E11" s="131" t="s">
+        <v>43</v>
+      </c>
+      <c r="F11" s="131" t="s">
         <v>49</v>
       </c>
-      <c r="D11" s="133" t="s">
-        <v>234</v>
-      </c>
-      <c r="E11" s="132" t="s">
-        <v>44</v>
-      </c>
-      <c r="F11" s="132" t="s">
+      <c r="G11" s="148" t="s">
+        <v>45</v>
+      </c>
+      <c r="H11" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="G11" s="149" t="s">
-        <v>46</v>
-      </c>
-      <c r="H11" s="77" t="s">
-        <v>51</v>
-      </c>
-      <c r="I11" s="149" t="s">
-        <v>19</v>
-      </c>
-      <c r="J11" s="132" t="s">
-        <v>48</v>
-      </c>
-      <c r="K11" s="134">
+      <c r="I11" s="148" t="s">
+        <v>18</v>
+      </c>
+      <c r="J11" s="131" t="s">
+        <v>47</v>
+      </c>
+      <c r="K11" s="76">
+        <v>3</v>
+      </c>
+      <c r="L11" s="133">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="M11" s="162" t="s">
         <v>20</v>
       </c>
-      <c r="L11" s="77">
-        <v>3</v>
-      </c>
-      <c r="M11" s="134">
-        <f t="shared" si="1"/>
-        <v>18</v>
-      </c>
-      <c r="N11" s="163" t="s">
-        <v>21</v>
-      </c>
-      <c r="O11" s="30"/>
-    </row>
-    <row r="12" spans="1:30" ht="15.75" thickBot="1">
+      <c r="N11" s="29"/>
+    </row>
+    <row r="12" spans="1:29" ht="15.75" thickBot="1">
       <c r="A12" s="6">
         <v>10</v>
       </c>
-      <c r="B12" s="173"/>
-      <c r="C12" s="78" t="s">
+      <c r="B12" s="177"/>
+      <c r="C12" s="77" t="s">
+        <v>161</v>
+      </c>
+      <c r="D12" s="68" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" s="60" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="60" t="s">
         <v>162</v>
       </c>
-      <c r="D12" s="69" t="s">
+      <c r="G12" s="41" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12" s="75" t="s">
+        <v>240</v>
+      </c>
+      <c r="I12" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J12" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="E12" s="61" t="s">
-        <v>15</v>
-      </c>
-      <c r="F12" s="61" t="s">
-        <v>163</v>
-      </c>
-      <c r="G12" s="42" t="s">
-        <v>26</v>
-      </c>
-      <c r="H12" s="76" t="s">
-        <v>241</v>
-      </c>
-      <c r="I12" s="38" t="s">
-        <v>19</v>
-      </c>
-      <c r="J12" s="41" t="s">
-        <v>53</v>
-      </c>
-      <c r="K12" s="11">
-        <v>20</v>
-      </c>
-      <c r="L12" s="12">
+      <c r="K12" s="12">
         <v>1</v>
       </c>
-      <c r="M12" s="11">
+      <c r="L12" s="11">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N12" s="86" t="s">
-        <v>21</v>
-      </c>
-      <c r="O12" s="30"/>
-    </row>
-    <row r="13" spans="1:30" ht="15.75" thickBot="1">
+      <c r="M12" s="85" t="s">
+        <v>20</v>
+      </c>
+      <c r="N12" s="29"/>
+    </row>
+    <row r="13" spans="1:29" ht="15.75" thickBot="1">
       <c r="A13" s="6">
         <v>11</v>
       </c>
-      <c r="B13" s="173"/>
-      <c r="C13" s="40" t="s">
+      <c r="B13" s="177"/>
+      <c r="C13" s="39" t="s">
+        <v>163</v>
+      </c>
+      <c r="D13" s="35" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13" s="35" t="s">
         <v>164</v>
       </c>
-      <c r="D13" s="36" t="s">
+      <c r="G13" s="41" t="s">
+        <v>16</v>
+      </c>
+      <c r="H13" s="75" t="s">
+        <v>241</v>
+      </c>
+      <c r="I13" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J13" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="E13" s="41" t="s">
-        <v>24</v>
-      </c>
-      <c r="F13" s="36" t="s">
-        <v>165</v>
-      </c>
-      <c r="G13" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="H13" s="76" t="s">
-        <v>242</v>
-      </c>
-      <c r="I13" s="38" t="s">
-        <v>19</v>
-      </c>
-      <c r="J13" s="41" t="s">
-        <v>55</v>
-      </c>
-      <c r="K13" s="11">
-        <v>10</v>
-      </c>
-      <c r="L13" s="12">
+      <c r="K13" s="12">
         <v>1</v>
       </c>
-      <c r="M13" s="11">
+      <c r="L13" s="11">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N13" s="86" t="s">
-        <v>21</v>
-      </c>
-      <c r="O13" s="31"/>
-    </row>
-    <row r="14" spans="1:30" ht="15.75" thickBot="1">
+      <c r="M13" s="85" t="s">
+        <v>20</v>
+      </c>
+      <c r="N13" s="30"/>
+    </row>
+    <row r="14" spans="1:29" ht="15.75" thickBot="1">
       <c r="A14" s="6">
         <v>12</v>
       </c>
-      <c r="B14" s="174"/>
-      <c r="C14" s="43" t="s">
+      <c r="B14" s="178"/>
+      <c r="C14" s="42" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="43" t="s">
         <v>56</v>
       </c>
-      <c r="D14" s="44" t="s">
+      <c r="E14" s="44" t="s">
         <v>57</v>
       </c>
-      <c r="E14" s="45" t="s">
+      <c r="F14" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="44" t="s">
+      <c r="G14" s="45" t="s">
         <v>59</v>
       </c>
-      <c r="G14" s="46" t="s">
+      <c r="H14" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="H14" s="17" t="s">
+      <c r="I14" s="46" t="s">
+        <v>18</v>
+      </c>
+      <c r="J14" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="I14" s="47" t="s">
-        <v>19</v>
-      </c>
-      <c r="J14" s="45" t="s">
-        <v>62</v>
-      </c>
-      <c r="K14" s="15">
-        <v>50</v>
-      </c>
-      <c r="L14" s="16">
+      <c r="K14" s="16">
         <v>1</v>
       </c>
-      <c r="M14" s="15">
+      <c r="L14" s="15">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N14" s="87" t="s">
-        <v>21</v>
-      </c>
-      <c r="O14" s="30"/>
-    </row>
-    <row r="15" spans="1:30" ht="15.75" thickBot="1">
+      <c r="M14" s="86" t="s">
+        <v>20</v>
+      </c>
+      <c r="N14" s="29"/>
+    </row>
+    <row r="15" spans="1:29" ht="15.75" thickBot="1">
       <c r="A15" s="6">
         <v>13</v>
       </c>
-      <c r="B15" s="173" t="s">
+      <c r="B15" s="177" t="s">
+        <v>62</v>
+      </c>
+      <c r="C15" s="78" t="s">
         <v>63</v>
       </c>
-      <c r="C15" s="79" t="s">
+      <c r="D15" s="47" t="s">
         <v>64</v>
       </c>
-      <c r="D15" s="48" t="s">
+      <c r="E15" s="79" t="s">
         <v>65</v>
       </c>
-      <c r="E15" s="80" t="s">
+      <c r="F15" s="47" t="s">
         <v>66</v>
       </c>
-      <c r="F15" s="48" t="s">
+      <c r="G15" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="G15" s="80" t="s">
+      <c r="H15" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="H15" s="20" t="s">
+      <c r="I15" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="J15" s="80" t="s">
         <v>69</v>
       </c>
-      <c r="I15" s="49" t="s">
-        <v>19</v>
-      </c>
-      <c r="J15" s="81" t="s">
-        <v>70</v>
-      </c>
-      <c r="K15" s="73">
-        <v>8</v>
-      </c>
-      <c r="L15" s="82">
+      <c r="K15" s="81">
         <v>1</v>
       </c>
-      <c r="M15" s="73">
+      <c r="L15" s="72">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N15" s="89" t="s">
-        <v>21</v>
-      </c>
-      <c r="O15" s="30"/>
-    </row>
-    <row r="16" spans="1:30" ht="15.75" thickBot="1">
+      <c r="M15" s="88" t="s">
+        <v>20</v>
+      </c>
+      <c r="N15" s="29"/>
+    </row>
+    <row r="16" spans="1:29" ht="15.75" thickBot="1">
       <c r="A16" s="6">
         <v>14</v>
       </c>
-      <c r="B16" s="173"/>
-      <c r="C16" s="151" t="s">
+      <c r="B16" s="177"/>
+      <c r="C16" s="150" t="s">
+        <v>221</v>
+      </c>
+      <c r="D16" s="151" t="s">
+        <v>220</v>
+      </c>
+      <c r="E16" s="132" t="s">
+        <v>219</v>
+      </c>
+      <c r="F16" s="132" t="s">
+        <v>218</v>
+      </c>
+      <c r="G16" s="132" t="s">
         <v>222</v>
       </c>
-      <c r="D16" s="152" t="s">
-        <v>221</v>
-      </c>
-      <c r="E16" s="133" t="s">
-        <v>220</v>
-      </c>
-      <c r="F16" s="133" t="s">
-        <v>219</v>
-      </c>
-      <c r="G16" s="133" t="s">
+      <c r="H16" s="152" t="s">
         <v>223</v>
       </c>
-      <c r="H16" s="153" t="s">
-        <v>224</v>
-      </c>
-      <c r="I16" s="154" t="s">
-        <v>19</v>
-      </c>
-      <c r="J16" s="154" t="s">
-        <v>70</v>
-      </c>
-      <c r="K16" s="134">
-        <v>50</v>
-      </c>
-      <c r="L16" s="77">
+      <c r="I16" s="153" t="s">
+        <v>18</v>
+      </c>
+      <c r="J16" s="153" t="s">
+        <v>69</v>
+      </c>
+      <c r="K16" s="76">
         <v>1</v>
       </c>
-      <c r="M16" s="134">
+      <c r="L16" s="133">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N16" s="136" t="s">
-        <v>21</v>
-      </c>
-      <c r="O16" s="30"/>
-    </row>
-    <row r="17" spans="1:15" ht="15.75" thickBot="1">
+      <c r="M16" s="135" t="s">
+        <v>20</v>
+      </c>
+      <c r="N16" s="29"/>
+    </row>
+    <row r="17" spans="1:14" ht="15.75" thickBot="1">
       <c r="A17" s="6">
         <v>15</v>
       </c>
-      <c r="B17" s="173"/>
-      <c r="C17" s="146" t="s">
+      <c r="B17" s="177"/>
+      <c r="C17" s="145" t="s">
+        <v>237</v>
+      </c>
+      <c r="D17" s="151" t="s">
+        <v>236</v>
+      </c>
+      <c r="E17" s="132" t="s">
+        <v>235</v>
+      </c>
+      <c r="F17" s="132" t="s">
+        <v>234</v>
+      </c>
+      <c r="G17" s="132" t="s">
         <v>238</v>
       </c>
-      <c r="D17" s="152" t="s">
-        <v>237</v>
-      </c>
-      <c r="E17" s="133" t="s">
-        <v>236</v>
-      </c>
-      <c r="F17" s="133" t="s">
-        <v>235</v>
-      </c>
-      <c r="G17" s="133" t="s">
+      <c r="H17" s="152" t="s">
         <v>239</v>
       </c>
-      <c r="H17" s="153" t="s">
-        <v>240</v>
-      </c>
-      <c r="I17" s="154" t="s">
-        <v>19</v>
-      </c>
-      <c r="J17" s="154" t="s">
-        <v>70</v>
-      </c>
-      <c r="K17" s="134">
-        <v>10</v>
-      </c>
-      <c r="L17" s="77">
+      <c r="I17" s="153" t="s">
+        <v>18</v>
+      </c>
+      <c r="J17" s="153" t="s">
+        <v>69</v>
+      </c>
+      <c r="K17" s="76">
         <v>1</v>
       </c>
-      <c r="M17" s="134">
+      <c r="L17" s="133">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N17" s="136" t="s">
-        <v>21</v>
-      </c>
-      <c r="O17" s="30"/>
-    </row>
-    <row r="18" spans="1:15" ht="15.75" thickBot="1">
+      <c r="M17" s="135" t="s">
+        <v>20</v>
+      </c>
+      <c r="N17" s="29"/>
+    </row>
+    <row r="18" spans="1:14" ht="15.75" thickBot="1">
       <c r="A18" s="6">
         <v>16</v>
       </c>
-      <c r="B18" s="173"/>
-      <c r="C18" s="75" t="s">
+      <c r="B18" s="177"/>
+      <c r="C18" s="74" t="s">
+        <v>70</v>
+      </c>
+      <c r="D18" s="100" t="s">
         <v>71</v>
       </c>
-      <c r="D18" s="101" t="s">
+      <c r="E18" s="104" t="s">
         <v>72</v>
       </c>
-      <c r="E18" s="105" t="s">
+      <c r="F18" s="100" t="s">
         <v>73</v>
       </c>
-      <c r="F18" s="101" t="s">
+      <c r="G18" s="104" t="s">
         <v>74</v>
       </c>
-      <c r="G18" s="105" t="s">
+      <c r="H18" s="101" t="s">
         <v>75</v>
       </c>
-      <c r="H18" s="102" t="s">
-        <v>76</v>
-      </c>
-      <c r="I18" s="102" t="s">
-        <v>19</v>
-      </c>
-      <c r="J18" s="106" t="s">
-        <v>70</v>
-      </c>
-      <c r="K18" s="98">
-        <v>20</v>
-      </c>
-      <c r="L18" s="107">
+      <c r="I18" s="101" t="s">
+        <v>18</v>
+      </c>
+      <c r="J18" s="105" t="s">
+        <v>69</v>
+      </c>
+      <c r="K18" s="106">
         <v>1</v>
       </c>
-      <c r="M18" s="98">
+      <c r="L18" s="97">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N18" s="108" t="s">
-        <v>21</v>
-      </c>
-      <c r="O18" s="30"/>
-    </row>
-    <row r="19" spans="1:15" ht="16.5" thickBot="1">
+      <c r="M18" s="107" t="s">
+        <v>20</v>
+      </c>
+      <c r="N18" s="29"/>
+    </row>
+    <row r="19" spans="1:14" ht="16.5" thickBot="1">
       <c r="A19" s="6">
         <v>17</v>
       </c>
-      <c r="B19" s="167" t="s">
+      <c r="B19" s="166" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19" s="108" t="s">
         <v>77</v>
       </c>
-      <c r="C19" s="109" t="s">
+      <c r="D19" s="109" t="s">
         <v>78</v>
       </c>
-      <c r="D19" s="110" t="s">
+      <c r="E19" s="109" t="s">
         <v>79</v>
       </c>
-      <c r="E19" s="110" t="s">
+      <c r="F19" s="109" t="s">
         <v>80</v>
       </c>
-      <c r="F19" s="110" t="s">
+      <c r="G19" s="110" t="s">
         <v>81</v>
       </c>
-      <c r="G19" s="111" t="s">
-        <v>82</v>
-      </c>
-      <c r="H19" s="111" t="s">
-        <v>19</v>
-      </c>
-      <c r="I19" s="110" t="s">
-        <v>19</v>
-      </c>
-      <c r="J19" s="111" t="s">
-        <v>70</v>
-      </c>
-      <c r="K19" s="103">
-        <v>7</v>
-      </c>
-      <c r="L19" s="103">
+      <c r="H19" s="110" t="s">
+        <v>18</v>
+      </c>
+      <c r="I19" s="109" t="s">
+        <v>18</v>
+      </c>
+      <c r="J19" s="110" t="s">
+        <v>69</v>
+      </c>
+      <c r="K19" s="102">
         <v>1</v>
       </c>
-      <c r="M19" s="66">
+      <c r="L19" s="65">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N19" s="104" t="s">
-        <v>21</v>
-      </c>
-      <c r="O19" s="30"/>
-    </row>
-    <row r="20" spans="1:15" ht="30.75" thickBot="1">
+      <c r="M19" s="103" t="s">
+        <v>20</v>
+      </c>
+      <c r="N19" s="29"/>
+    </row>
+    <row r="20" spans="1:14" ht="30.75" thickBot="1">
       <c r="A20" s="6">
         <v>18</v>
       </c>
-      <c r="B20" s="167" t="s">
+      <c r="B20" s="166" t="s">
+        <v>224</v>
+      </c>
+      <c r="C20" s="154" t="s">
+        <v>226</v>
+      </c>
+      <c r="D20" s="155" t="s">
         <v>225</v>
       </c>
-      <c r="C20" s="155" t="s">
+      <c r="E20" s="156" t="s">
         <v>227</v>
       </c>
-      <c r="D20" s="156" t="s">
-        <v>226</v>
-      </c>
-      <c r="E20" s="157" t="s">
+      <c r="F20" s="156" t="s">
         <v>228</v>
       </c>
-      <c r="F20" s="157" t="s">
+      <c r="G20" s="157" t="s">
         <v>229</v>
       </c>
-      <c r="G20" s="158" t="s">
+      <c r="H20" s="157" t="s">
         <v>230</v>
       </c>
-      <c r="H20" s="158" t="s">
+      <c r="I20" s="156" t="s">
         <v>231</v>
       </c>
-      <c r="I20" s="157" t="s">
-        <v>232</v>
-      </c>
-      <c r="J20" s="158" t="s">
-        <v>70</v>
-      </c>
-      <c r="K20" s="159">
-        <v>10</v>
+      <c r="J20" s="157" t="s">
+        <v>69</v>
+      </c>
+      <c r="K20" s="158">
+        <v>1</v>
       </c>
       <c r="L20" s="159">
-        <v>1</v>
-      </c>
-      <c r="M20" s="160">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N20" s="161" t="s">
-        <v>21</v>
-      </c>
-      <c r="O20" s="30"/>
-    </row>
-    <row r="21" spans="1:15" ht="15.75" thickBot="1">
+      <c r="M20" s="160" t="s">
+        <v>20</v>
+      </c>
+      <c r="N20" s="29"/>
+    </row>
+    <row r="21" spans="1:14" ht="15.75" thickBot="1">
       <c r="A21" s="6">
         <v>19</v>
       </c>
-      <c r="B21" s="172" t="s">
-        <v>83</v>
-      </c>
-      <c r="C21" s="99" t="s">
+      <c r="B21" s="176" t="s">
+        <v>82</v>
+      </c>
+      <c r="C21" s="98" t="s">
+        <v>173</v>
+      </c>
+      <c r="D21" s="61" t="s">
         <v>174</v>
       </c>
-      <c r="D21" s="62" t="s">
+      <c r="E21" s="61" t="s">
         <v>175</v>
       </c>
-      <c r="E21" s="62" t="s">
+      <c r="F21" s="61" t="s">
+        <v>175</v>
+      </c>
+      <c r="G21" s="33" t="s">
         <v>176</v>
       </c>
-      <c r="F21" s="62" t="s">
-        <v>176</v>
-      </c>
-      <c r="G21" s="34" t="s">
+      <c r="H21" s="33" t="s">
         <v>177</v>
       </c>
-      <c r="H21" s="34" t="s">
-        <v>178</v>
-      </c>
-      <c r="I21" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="J21" s="34" t="s">
-        <v>70</v>
+      <c r="I21" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="J21" s="33" t="s">
+        <v>69</v>
       </c>
       <c r="K21" s="19">
-        <v>10</v>
-      </c>
-      <c r="L21" s="19">
         <v>1</v>
       </c>
-      <c r="M21" s="18">
+      <c r="L21" s="18">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N21" s="100" t="s">
-        <v>21</v>
-      </c>
-      <c r="O21" s="30"/>
-    </row>
-    <row r="22" spans="1:15" ht="15.75" thickBot="1">
+      <c r="M21" s="99" t="s">
+        <v>20</v>
+      </c>
+      <c r="N21" s="29"/>
+    </row>
+    <row r="22" spans="1:14" ht="15.75" thickBot="1">
       <c r="A22" s="6">
         <v>20</v>
       </c>
-      <c r="B22" s="174"/>
-      <c r="C22" s="63" t="s">
+      <c r="B22" s="178"/>
+      <c r="C22" s="62" t="s">
+        <v>83</v>
+      </c>
+      <c r="D22" s="63" t="s">
         <v>84</v>
       </c>
-      <c r="D22" s="64" t="s">
+      <c r="E22" s="63" t="s">
+        <v>43</v>
+      </c>
+      <c r="F22" s="63" t="s">
         <v>85</v>
       </c>
-      <c r="E22" s="64" t="s">
-        <v>44</v>
-      </c>
-      <c r="F22" s="64" t="s">
+      <c r="G22" s="63" t="s">
         <v>86</v>
       </c>
-      <c r="G22" s="64" t="s">
-        <v>87</v>
-      </c>
-      <c r="H22" s="65"/>
-      <c r="I22" s="65"/>
-      <c r="J22" s="64" t="s">
-        <v>70</v>
-      </c>
-      <c r="K22" s="65">
-        <v>7</v>
-      </c>
-      <c r="L22" s="65">
+      <c r="H22" s="64"/>
+      <c r="I22" s="64"/>
+      <c r="J22" s="63" t="s">
+        <v>69</v>
+      </c>
+      <c r="K22" s="64">
         <v>1</v>
       </c>
-      <c r="M22" s="15">
+      <c r="L22" s="15">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N22" s="67" t="s">
-        <v>88</v>
-      </c>
-      <c r="O22" s="30"/>
-    </row>
-    <row r="23" spans="1:15" ht="15.75" thickBot="1">
+      <c r="M22" s="66" t="s">
+        <v>87</v>
+      </c>
+      <c r="N22" s="29"/>
+    </row>
+    <row r="23" spans="1:14" ht="15.75" thickBot="1">
       <c r="A23" s="6">
         <v>21</v>
       </c>
-      <c r="B23" s="172" t="s">
+      <c r="B23" s="176" t="s">
+        <v>88</v>
+      </c>
+      <c r="C23" s="138" t="s">
         <v>89</v>
       </c>
-      <c r="C23" s="139" t="s">
+      <c r="D23" s="163" t="s">
+        <v>186</v>
+      </c>
+      <c r="E23" s="140" t="s">
         <v>90</v>
       </c>
-      <c r="D23" s="164" t="s">
-        <v>187</v>
-      </c>
-      <c r="E23" s="141" t="s">
+      <c r="F23" s="140" t="s">
         <v>91</v>
       </c>
-      <c r="F23" s="141" t="s">
+      <c r="G23" s="142" t="s">
+        <v>59</v>
+      </c>
+      <c r="H23" s="164" t="s">
         <v>92</v>
       </c>
-      <c r="G23" s="143" t="s">
-        <v>60</v>
-      </c>
-      <c r="H23" s="165" t="s">
+      <c r="I23" s="140" t="s">
+        <v>18</v>
+      </c>
+      <c r="J23" s="140" t="s">
         <v>93</v>
       </c>
-      <c r="I23" s="141" t="s">
-        <v>19</v>
-      </c>
-      <c r="J23" s="141" t="s">
-        <v>94</v>
-      </c>
-      <c r="K23" s="144">
-        <v>100</v>
-      </c>
-      <c r="L23" s="144">
+      <c r="K23" s="143">
         <v>3</v>
       </c>
-      <c r="M23" s="144">
+      <c r="L23" s="143">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="N23" s="166" t="s">
-        <v>21</v>
-      </c>
-      <c r="O23" s="30"/>
-    </row>
-    <row r="24" spans="1:15" ht="15.75" thickBot="1">
+      <c r="M23" s="165" t="s">
+        <v>20</v>
+      </c>
+      <c r="N23" s="29"/>
+    </row>
+    <row r="24" spans="1:14" ht="15.75" thickBot="1">
       <c r="A24" s="6">
         <v>22</v>
       </c>
-      <c r="B24" s="173"/>
-      <c r="C24" s="72" t="s">
+      <c r="B24" s="177"/>
+      <c r="C24" s="71" t="s">
+        <v>165</v>
+      </c>
+      <c r="D24" s="60" t="s">
         <v>166</v>
       </c>
-      <c r="D24" s="61" t="s">
+      <c r="E24" s="60" t="s">
+        <v>90</v>
+      </c>
+      <c r="F24" s="60" t="s">
         <v>167</v>
       </c>
-      <c r="E24" s="61" t="s">
-        <v>91</v>
-      </c>
-      <c r="F24" s="61" t="s">
+      <c r="G24" s="37" t="s">
+        <v>155</v>
+      </c>
+      <c r="H24" s="75" t="s">
+        <v>242</v>
+      </c>
+      <c r="I24" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J24" s="73" t="s">
         <v>168</v>
       </c>
-      <c r="G24" s="38" t="s">
-        <v>156</v>
-      </c>
-      <c r="H24" s="76" t="s">
-        <v>243</v>
-      </c>
-      <c r="I24" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="J24" s="74" t="s">
-        <v>169</v>
-      </c>
       <c r="K24" s="7">
-        <v>100</v>
-      </c>
-      <c r="L24" s="7">
         <v>1</v>
       </c>
-      <c r="M24" s="11">
+      <c r="L24" s="11">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N24" s="90" t="s">
-        <v>179</v>
-      </c>
-      <c r="O24" s="30"/>
-    </row>
-    <row r="25" spans="1:15" ht="15.75" thickBot="1">
+      <c r="M24" s="89" t="s">
+        <v>178</v>
+      </c>
+      <c r="N24" s="29"/>
+    </row>
+    <row r="25" spans="1:14" ht="15.75" thickBot="1">
       <c r="A25" s="6">
         <v>23</v>
       </c>
-      <c r="B25" s="173"/>
-      <c r="C25" s="128" t="s">
-        <v>195</v>
-      </c>
-      <c r="D25" s="129" t="s">
+      <c r="B25" s="177"/>
+      <c r="C25" s="127" t="s">
+        <v>194</v>
+      </c>
+      <c r="D25" s="128" t="s">
+        <v>187</v>
+      </c>
+      <c r="E25" s="70" t="s">
+        <v>90</v>
+      </c>
+      <c r="F25" s="129" t="s">
         <v>188</v>
       </c>
-      <c r="E25" s="71" t="s">
-        <v>91</v>
-      </c>
-      <c r="F25" s="130" t="s">
+      <c r="G25" s="129" t="s">
         <v>189</v>
       </c>
-      <c r="G25" s="130" t="s">
+      <c r="H25" s="130" t="s">
         <v>190</v>
       </c>
-      <c r="H25" s="131" t="s">
-        <v>191</v>
-      </c>
-      <c r="I25" s="132" t="s">
-        <v>19</v>
-      </c>
-      <c r="J25" s="133" t="s">
-        <v>201</v>
-      </c>
-      <c r="K25" s="134">
-        <v>20</v>
-      </c>
-      <c r="L25" s="134">
+      <c r="I25" s="131" t="s">
+        <v>18</v>
+      </c>
+      <c r="J25" s="132" t="s">
+        <v>200</v>
+      </c>
+      <c r="K25" s="133">
         <v>1</v>
       </c>
-      <c r="M25" s="134">
+      <c r="L25" s="133">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N25" s="135" t="s">
-        <v>21</v>
-      </c>
-      <c r="O25" s="30"/>
-    </row>
-    <row r="26" spans="1:15" ht="15.75" thickBot="1">
+      <c r="M25" s="134" t="s">
+        <v>20</v>
+      </c>
+      <c r="N25" s="29"/>
+    </row>
+    <row r="26" spans="1:14" ht="15.75" thickBot="1">
       <c r="A26" s="6">
         <v>24</v>
       </c>
-      <c r="B26" s="173"/>
-      <c r="C26" s="128" t="s">
-        <v>196</v>
-      </c>
-      <c r="D26" s="129" t="s">
+      <c r="B26" s="177"/>
+      <c r="C26" s="127" t="s">
+        <v>195</v>
+      </c>
+      <c r="D26" s="128" t="s">
+        <v>191</v>
+      </c>
+      <c r="E26" s="70" t="s">
+        <v>90</v>
+      </c>
+      <c r="F26" s="129" t="s">
         <v>192</v>
       </c>
-      <c r="E26" s="71" t="s">
-        <v>91</v>
-      </c>
-      <c r="F26" s="130" t="s">
+      <c r="G26" s="129" t="s">
+        <v>189</v>
+      </c>
+      <c r="H26" s="130" t="s">
         <v>193</v>
       </c>
-      <c r="G26" s="130" t="s">
-        <v>190</v>
-      </c>
-      <c r="H26" s="131" t="s">
-        <v>194</v>
-      </c>
-      <c r="I26" s="132" t="s">
-        <v>19</v>
-      </c>
-      <c r="J26" s="133" t="s">
-        <v>202</v>
-      </c>
-      <c r="K26" s="134">
-        <v>100</v>
-      </c>
-      <c r="L26" s="134">
+      <c r="I26" s="131" t="s">
+        <v>18</v>
+      </c>
+      <c r="J26" s="132" t="s">
+        <v>201</v>
+      </c>
+      <c r="K26" s="133">
         <v>1</v>
       </c>
-      <c r="M26" s="134">
+      <c r="L26" s="133">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N26" s="136" t="s">
-        <v>21</v>
-      </c>
-      <c r="O26" s="30"/>
-    </row>
-    <row r="27" spans="1:15" ht="15.75" thickBot="1">
+      <c r="M26" s="135" t="s">
+        <v>20</v>
+      </c>
+      <c r="N26" s="29"/>
+    </row>
+    <row r="27" spans="1:14" ht="15.75" thickBot="1">
       <c r="A27" s="6">
         <v>25</v>
       </c>
-      <c r="B27" s="173"/>
-      <c r="C27" s="128" t="s">
+      <c r="B27" s="177"/>
+      <c r="C27" s="127" t="s">
+        <v>197</v>
+      </c>
+      <c r="D27" s="128" t="s">
         <v>198</v>
       </c>
-      <c r="D27" s="129" t="s">
+      <c r="E27" s="132" t="s">
+        <v>90</v>
+      </c>
+      <c r="F27" s="136" t="s">
+        <v>196</v>
+      </c>
+      <c r="G27" s="129" t="s">
+        <v>189</v>
+      </c>
+      <c r="H27" s="137" t="s">
         <v>199</v>
       </c>
-      <c r="E27" s="133" t="s">
-        <v>91</v>
-      </c>
-      <c r="F27" s="137" t="s">
-        <v>197</v>
-      </c>
-      <c r="G27" s="130" t="s">
-        <v>190</v>
-      </c>
-      <c r="H27" s="138" t="s">
-        <v>200</v>
-      </c>
-      <c r="I27" s="132" t="s">
-        <v>19</v>
-      </c>
-      <c r="J27" s="133" t="s">
-        <v>203</v>
-      </c>
-      <c r="K27" s="134">
-        <v>100</v>
-      </c>
-      <c r="L27" s="134">
+      <c r="I27" s="131" t="s">
+        <v>18</v>
+      </c>
+      <c r="J27" s="132" t="s">
+        <v>202</v>
+      </c>
+      <c r="K27" s="133">
         <v>1</v>
       </c>
-      <c r="M27" s="134">
+      <c r="L27" s="133">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N27" s="136" t="s">
-        <v>21</v>
-      </c>
-      <c r="O27" s="30"/>
-    </row>
-    <row r="28" spans="1:15" ht="15.75" thickBot="1">
+      <c r="M27" s="135" t="s">
+        <v>20</v>
+      </c>
+      <c r="N27" s="29"/>
+    </row>
+    <row r="28" spans="1:14" ht="15.75" thickBot="1">
       <c r="A28" s="6">
         <v>26</v>
       </c>
-      <c r="B28" s="173"/>
-      <c r="C28" s="179" t="s">
-        <v>254</v>
-      </c>
-      <c r="D28" s="129" t="s">
-        <v>207</v>
-      </c>
-      <c r="E28" s="133" t="s">
-        <v>91</v>
-      </c>
-      <c r="F28" s="137" t="s">
+      <c r="B28" s="177"/>
+      <c r="C28" s="171" t="s">
+        <v>253</v>
+      </c>
+      <c r="D28" s="128" t="s">
+        <v>206</v>
+      </c>
+      <c r="E28" s="132" t="s">
+        <v>90</v>
+      </c>
+      <c r="F28" s="136" t="s">
+        <v>203</v>
+      </c>
+      <c r="G28" s="136" t="s">
+        <v>114</v>
+      </c>
+      <c r="H28" s="137" t="s">
         <v>204</v>
       </c>
-      <c r="G28" s="137" t="s">
-        <v>115</v>
-      </c>
-      <c r="H28" s="138" t="s">
+      <c r="I28" s="131" t="s">
+        <v>18</v>
+      </c>
+      <c r="J28" s="132" t="s">
         <v>205</v>
       </c>
-      <c r="I28" s="132" t="s">
-        <v>19</v>
-      </c>
-      <c r="J28" s="133" t="s">
-        <v>206</v>
-      </c>
-      <c r="K28" s="134">
-        <v>50</v>
-      </c>
-      <c r="L28" s="134">
+      <c r="K28" s="133">
         <v>2</v>
       </c>
-      <c r="M28" s="134">
+      <c r="L28" s="133">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="N28" s="136" t="s">
-        <v>21</v>
-      </c>
-      <c r="O28" s="30"/>
-    </row>
-    <row r="29" spans="1:15" ht="15.75" thickBot="1">
+      <c r="M28" s="135" t="s">
+        <v>20</v>
+      </c>
+      <c r="N28" s="29"/>
+    </row>
+    <row r="29" spans="1:14" ht="15.75" thickBot="1">
       <c r="A29" s="6">
         <v>27</v>
       </c>
-      <c r="B29" s="173"/>
-      <c r="C29" s="179" t="s">
-        <v>253</v>
-      </c>
-      <c r="D29" s="129" t="s">
-        <v>255</v>
-      </c>
-      <c r="E29" s="133" t="s">
-        <v>91</v>
-      </c>
-      <c r="F29" s="177" t="s">
+      <c r="B29" s="177"/>
+      <c r="C29" s="171" t="s">
+        <v>252</v>
+      </c>
+      <c r="D29" s="128" t="s">
+        <v>254</v>
+      </c>
+      <c r="E29" s="132" t="s">
+        <v>90</v>
+      </c>
+      <c r="F29" s="169" t="s">
+        <v>249</v>
+      </c>
+      <c r="G29" s="169" t="s">
+        <v>189</v>
+      </c>
+      <c r="H29" s="170" t="s">
         <v>250</v>
       </c>
-      <c r="G29" s="177" t="s">
-        <v>190</v>
-      </c>
-      <c r="H29" s="178" t="s">
+      <c r="I29" s="131" t="s">
+        <v>18</v>
+      </c>
+      <c r="J29" s="167" t="s">
         <v>251</v>
       </c>
-      <c r="I29" s="132" t="s">
-        <v>19</v>
-      </c>
-      <c r="J29" s="175" t="s">
-        <v>252</v>
-      </c>
-      <c r="K29" s="134">
-        <v>100</v>
-      </c>
-      <c r="L29" s="134">
+      <c r="K29" s="133">
         <v>2</v>
       </c>
-      <c r="M29" s="134">
+      <c r="L29" s="133">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="N29" s="136" t="s">
-        <v>21</v>
-      </c>
-      <c r="O29" s="30"/>
-    </row>
-    <row r="30" spans="1:15" ht="15.75" thickBot="1">
+      <c r="M29" s="135" t="s">
+        <v>20</v>
+      </c>
+      <c r="N29" s="29"/>
+    </row>
+    <row r="30" spans="1:14" ht="15.75" thickBot="1">
       <c r="A30" s="6">
         <v>28</v>
       </c>
-      <c r="B30" s="173"/>
-      <c r="C30" s="50" t="s">
+      <c r="B30" s="177"/>
+      <c r="C30" s="49" t="s">
+        <v>94</v>
+      </c>
+      <c r="D30" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="D30" s="7" t="s">
+      <c r="E30" s="35" t="s">
+        <v>90</v>
+      </c>
+      <c r="F30" s="35" t="s">
         <v>96</v>
       </c>
-      <c r="E30" s="36" t="s">
-        <v>91</v>
-      </c>
-      <c r="F30" s="36" t="s">
+      <c r="G30" s="37" t="s">
+        <v>59</v>
+      </c>
+      <c r="H30" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="G30" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="H30" s="13" t="s">
+      <c r="I30" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J30" s="35" t="s">
         <v>98</v>
       </c>
-      <c r="I30" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="J30" s="36" t="s">
-        <v>99</v>
-      </c>
       <c r="K30" s="7">
-        <v>100</v>
-      </c>
-      <c r="L30" s="7">
         <v>2</v>
       </c>
-      <c r="M30" s="11">
+      <c r="L30" s="11">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="N30" s="91" t="s">
-        <v>21</v>
-      </c>
-      <c r="O30" s="30"/>
-    </row>
-    <row r="31" spans="1:15" ht="15.75" thickBot="1">
+      <c r="M30" s="90" t="s">
+        <v>20</v>
+      </c>
+      <c r="N30" s="29"/>
+    </row>
+    <row r="31" spans="1:14" ht="15.75" thickBot="1">
       <c r="A31" s="6">
         <v>29</v>
       </c>
-      <c r="B31" s="173"/>
-      <c r="C31" s="50" t="s">
+      <c r="B31" s="177"/>
+      <c r="C31" s="49" t="s">
+        <v>99</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="E31" s="35" t="s">
+        <v>90</v>
+      </c>
+      <c r="F31" s="35" t="s">
         <v>100</v>
       </c>
-      <c r="D31" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="E31" s="36" t="s">
-        <v>91</v>
-      </c>
-      <c r="F31" s="36" t="s">
+      <c r="G31" s="37" t="s">
+        <v>59</v>
+      </c>
+      <c r="H31" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="G31" s="38" t="s">
-        <v>60</v>
-      </c>
-      <c r="H31" s="13" t="s">
+      <c r="I31" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J31" s="35" t="s">
         <v>102</v>
       </c>
-      <c r="I31" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="J31" s="36" t="s">
-        <v>103</v>
-      </c>
       <c r="K31" s="7">
-        <v>100</v>
-      </c>
-      <c r="L31" s="7">
         <v>1</v>
       </c>
-      <c r="M31" s="11">
+      <c r="L31" s="11">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N31" s="91" t="s">
-        <v>21</v>
-      </c>
-      <c r="O31" s="30"/>
-    </row>
-    <row r="32" spans="1:15" ht="15.75" thickBot="1">
+      <c r="M31" s="90" t="s">
+        <v>20</v>
+      </c>
+      <c r="N31" s="29"/>
+    </row>
+    <row r="32" spans="1:14" ht="15.75" thickBot="1">
       <c r="A32" s="6">
         <v>30</v>
       </c>
-      <c r="B32" s="173"/>
-      <c r="C32" s="50" t="s">
+      <c r="B32" s="177"/>
+      <c r="C32" s="49" t="s">
+        <v>104</v>
+      </c>
+      <c r="D32" s="35" t="s">
         <v>105</v>
       </c>
-      <c r="D32" s="36" t="s">
+      <c r="E32" s="35" t="s">
+        <v>103</v>
+      </c>
+      <c r="F32" s="38" t="s">
         <v>106</v>
       </c>
-      <c r="E32" s="36" t="s">
-        <v>104</v>
-      </c>
-      <c r="F32" s="39" t="s">
+      <c r="G32" s="37" t="s">
         <v>107</v>
       </c>
-      <c r="G32" s="38" t="s">
+      <c r="H32" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="H32" s="13" t="s">
+      <c r="I32" s="37" t="s">
         <v>109</v>
       </c>
-      <c r="I32" s="38" t="s">
+      <c r="J32" s="35" t="s">
         <v>110</v>
       </c>
-      <c r="J32" s="36" t="s">
-        <v>111</v>
-      </c>
       <c r="K32" s="7">
-        <v>10</v>
-      </c>
-      <c r="L32" s="7">
         <v>1</v>
       </c>
-      <c r="M32" s="11">
+      <c r="L32" s="11">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N32" s="91" t="s">
-        <v>21</v>
-      </c>
-      <c r="O32" s="30"/>
-    </row>
-    <row r="33" spans="1:15" ht="15.75" thickBot="1">
+      <c r="M32" s="90" t="s">
+        <v>20</v>
+      </c>
+      <c r="N32" s="29"/>
+    </row>
+    <row r="33" spans="1:14" ht="15.75" thickBot="1">
       <c r="A33" s="6">
         <v>31</v>
       </c>
-      <c r="B33" s="173"/>
-      <c r="C33" s="50" t="s">
+      <c r="B33" s="177"/>
+      <c r="C33" s="49" t="s">
+        <v>111</v>
+      </c>
+      <c r="D33" s="35" t="s">
         <v>112</v>
       </c>
-      <c r="D33" s="36" t="s">
+      <c r="E33" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="F33" s="35" t="s">
         <v>113</v>
       </c>
-      <c r="E33" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="F33" s="36" t="s">
+      <c r="G33" s="37" t="s">
         <v>114</v>
       </c>
-      <c r="G33" s="38" t="s">
+      <c r="H33" s="13" t="s">
         <v>115</v>
       </c>
-      <c r="H33" s="13" t="s">
+      <c r="I33" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J33" s="35" t="s">
         <v>116</v>
       </c>
-      <c r="I33" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="J33" s="36" t="s">
-        <v>117</v>
-      </c>
       <c r="K33" s="7">
-        <v>100</v>
-      </c>
-      <c r="L33" s="7">
         <v>1</v>
       </c>
-      <c r="M33" s="11">
+      <c r="L33" s="11">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N33" s="91" t="s">
-        <v>21</v>
-      </c>
-      <c r="O33" s="30"/>
-    </row>
-    <row r="34" spans="1:15" s="1" customFormat="1" ht="15.75" thickBot="1">
+      <c r="M33" s="90" t="s">
+        <v>20</v>
+      </c>
+      <c r="N33" s="29"/>
+    </row>
+    <row r="34" spans="1:14" s="1" customFormat="1" ht="15.75" thickBot="1">
       <c r="A34" s="6">
         <v>32</v>
       </c>
-      <c r="B34" s="174"/>
-      <c r="C34" s="51" t="s">
+      <c r="B34" s="178"/>
+      <c r="C34" s="50" t="s">
+        <v>117</v>
+      </c>
+      <c r="D34" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="D34" s="14" t="s">
+      <c r="E34" s="43" t="s">
+        <v>90</v>
+      </c>
+      <c r="F34" s="43" t="s">
         <v>119</v>
       </c>
-      <c r="E34" s="44" t="s">
-        <v>91</v>
-      </c>
-      <c r="F34" s="44" t="s">
+      <c r="G34" s="46" t="s">
+        <v>59</v>
+      </c>
+      <c r="H34" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="G34" s="47" t="s">
-        <v>60</v>
-      </c>
-      <c r="H34" s="17" t="s">
+      <c r="I34" s="43" t="s">
+        <v>18</v>
+      </c>
+      <c r="J34" s="43" t="s">
         <v>121</v>
       </c>
-      <c r="I34" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="J34" s="44" t="s">
-        <v>122</v>
-      </c>
-      <c r="K34" s="14">
-        <v>100</v>
-      </c>
-      <c r="L34" s="17">
+      <c r="K34" s="17">
         <v>8</v>
       </c>
-      <c r="M34" s="15">
+      <c r="L34" s="15">
         <f t="shared" si="1"/>
         <v>48</v>
       </c>
-      <c r="N34" s="113" t="s">
-        <v>21</v>
-      </c>
-      <c r="O34" s="32"/>
-    </row>
-    <row r="35" spans="1:15" ht="15.75" thickBot="1">
+      <c r="M34" s="112" t="s">
+        <v>20</v>
+      </c>
+      <c r="N34" s="31"/>
+    </row>
+    <row r="35" spans="1:14" ht="15.75" thickBot="1">
       <c r="A35" s="6">
         <v>33</v>
       </c>
-      <c r="B35" s="173" t="s">
+      <c r="B35" s="177" t="s">
+        <v>122</v>
+      </c>
+      <c r="C35" s="118" t="s">
+        <v>184</v>
+      </c>
+      <c r="D35" s="126" t="s">
         <v>123</v>
       </c>
-      <c r="C35" s="119" t="s">
-        <v>185</v>
-      </c>
-      <c r="D35" s="127" t="s">
-        <v>124</v>
-      </c>
-      <c r="E35" s="112" t="s">
+      <c r="E35" s="111" t="s">
+        <v>181</v>
+      </c>
+      <c r="F35" s="120" t="s">
         <v>182</v>
       </c>
-      <c r="F35" s="121" t="s">
+      <c r="G35" s="121" t="s">
         <v>183</v>
       </c>
-      <c r="G35" s="122" t="s">
-        <v>184</v>
-      </c>
-      <c r="H35" s="123" t="s">
-        <v>19</v>
-      </c>
-      <c r="I35" s="120" t="s">
-        <v>19</v>
-      </c>
-      <c r="J35" s="123" t="s">
-        <v>70</v>
-      </c>
-      <c r="K35" s="124">
-        <v>7</v>
+      <c r="H35" s="122" t="s">
+        <v>18</v>
+      </c>
+      <c r="I35" s="119" t="s">
+        <v>18</v>
+      </c>
+      <c r="J35" s="122" t="s">
+        <v>69</v>
+      </c>
+      <c r="K35" s="123">
+        <v>1</v>
       </c>
       <c r="L35" s="124">
-        <v>1</v>
-      </c>
-      <c r="M35" s="125">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N35" s="126" t="s">
-        <v>21</v>
-      </c>
-      <c r="O35" s="30"/>
-    </row>
-    <row r="36" spans="1:15" ht="15.75" thickBot="1">
+      <c r="M35" s="125" t="s">
+        <v>20</v>
+      </c>
+      <c r="N35" s="29"/>
+    </row>
+    <row r="36" spans="1:14" ht="15.75" thickBot="1">
       <c r="A36" s="6">
         <v>34</v>
       </c>
-      <c r="B36" s="173"/>
-      <c r="C36" s="50" t="s">
+      <c r="B36" s="177"/>
+      <c r="C36" s="49" t="s">
+        <v>124</v>
+      </c>
+      <c r="D36" s="35" t="s">
         <v>125</v>
       </c>
-      <c r="D36" s="36" t="s">
+      <c r="E36" s="35" t="s">
         <v>126</v>
       </c>
-      <c r="E36" s="36" t="s">
+      <c r="F36" s="35" t="s">
         <v>127</v>
       </c>
-      <c r="F36" s="36" t="s">
+      <c r="G36" s="37" t="s">
         <v>128</v>
       </c>
-      <c r="G36" s="38" t="s">
+      <c r="H36" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="H36" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="I36" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="J36" s="38" t="s">
-        <v>70</v>
+      <c r="I36" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J36" s="37" t="s">
+        <v>69</v>
       </c>
       <c r="K36" s="13">
-        <v>6</v>
-      </c>
-      <c r="L36" s="13">
         <v>1</v>
       </c>
-      <c r="M36" s="11">
+      <c r="L36" s="11">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N36" s="91" t="s">
-        <v>21</v>
-      </c>
-      <c r="O36" s="30"/>
-    </row>
-    <row r="37" spans="1:15" ht="15.75" thickBot="1">
+      <c r="M36" s="90" t="s">
+        <v>20</v>
+      </c>
+      <c r="N36" s="29"/>
+    </row>
+    <row r="37" spans="1:14" ht="15.75" thickBot="1">
       <c r="A37" s="6">
         <v>35</v>
       </c>
-      <c r="B37" s="173"/>
-      <c r="C37" s="114" t="s">
+      <c r="B37" s="177"/>
+      <c r="C37" s="113" t="s">
+        <v>169</v>
+      </c>
+      <c r="D37" s="114" t="s">
+        <v>130</v>
+      </c>
+      <c r="E37" s="114" t="s">
         <v>170</v>
       </c>
-      <c r="D37" s="115" t="s">
+      <c r="F37" s="115" t="s">
+        <v>172</v>
+      </c>
+      <c r="G37" s="100" t="s">
+        <v>171</v>
+      </c>
+      <c r="H37" s="96"/>
+      <c r="I37" s="100" t="s">
+        <v>18</v>
+      </c>
+      <c r="J37" s="101" t="s">
         <v>131</v>
       </c>
-      <c r="E37" s="115" t="s">
-        <v>171</v>
-      </c>
-      <c r="F37" s="116" t="s">
-        <v>173</v>
-      </c>
-      <c r="G37" s="101" t="s">
-        <v>172</v>
-      </c>
-      <c r="H37" s="97"/>
-      <c r="I37" s="101" t="s">
-        <v>19</v>
-      </c>
-      <c r="J37" s="102" t="s">
-        <v>132</v>
-      </c>
-      <c r="K37" s="97">
-        <v>6</v>
+      <c r="K37" s="96">
+        <v>1</v>
       </c>
       <c r="L37" s="97">
-        <v>1</v>
-      </c>
-      <c r="M37" s="98">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N37" s="117" t="s">
-        <v>88</v>
-      </c>
-      <c r="O37" s="30"/>
-    </row>
-    <row r="38" spans="1:15" ht="15.75" thickBot="1">
+      <c r="M37" s="116" t="s">
+        <v>87</v>
+      </c>
+      <c r="N37" s="29"/>
+    </row>
+    <row r="38" spans="1:14" ht="15.75" thickBot="1">
       <c r="A38" s="6">
         <v>36</v>
       </c>
-      <c r="B38" s="172" t="s">
+      <c r="B38" s="176" t="s">
+        <v>132</v>
+      </c>
+      <c r="C38" s="51" t="s">
         <v>133</v>
       </c>
-      <c r="C38" s="52" t="s">
+      <c r="D38" s="52" t="s">
         <v>134</v>
       </c>
-      <c r="D38" s="53" t="s">
+      <c r="E38" s="52" t="s">
+        <v>255</v>
+      </c>
+      <c r="F38" s="52" t="s">
         <v>135</v>
       </c>
-      <c r="E38" s="53" t="s">
-        <v>256</v>
-      </c>
-      <c r="F38" s="53" t="s">
+      <c r="G38" s="52" t="s">
         <v>136</v>
       </c>
-      <c r="G38" s="53" t="s">
-        <v>137</v>
-      </c>
-      <c r="H38" s="53" t="s">
-        <v>19</v>
-      </c>
-      <c r="I38" s="53" t="s">
-        <v>19</v>
-      </c>
-      <c r="J38" s="53" t="s">
-        <v>70</v>
+      <c r="H38" s="52" t="s">
+        <v>18</v>
+      </c>
+      <c r="I38" s="52" t="s">
+        <v>18</v>
+      </c>
+      <c r="J38" s="52" t="s">
+        <v>69</v>
       </c>
       <c r="K38" s="22">
-        <v>100</v>
-      </c>
-      <c r="L38" s="22">
         <v>1</v>
       </c>
-      <c r="M38" s="18">
+      <c r="L38" s="18">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N38" s="118" t="s">
-        <v>138</v>
-      </c>
-      <c r="O38" s="30"/>
-    </row>
-    <row r="39" spans="1:15" ht="15.75" thickBot="1">
+      <c r="M38" s="117" t="s">
+        <v>137</v>
+      </c>
+      <c r="N38" s="29"/>
+    </row>
+    <row r="39" spans="1:14" ht="15.75" thickBot="1">
       <c r="A39" s="6">
         <v>37</v>
       </c>
-      <c r="B39" s="173"/>
-      <c r="C39" s="54" t="s">
+      <c r="B39" s="177"/>
+      <c r="C39" s="53" t="s">
+        <v>138</v>
+      </c>
+      <c r="D39" s="54" t="s">
         <v>139</v>
       </c>
-      <c r="D39" s="55" t="s">
+      <c r="E39" s="54" t="s">
+        <v>43</v>
+      </c>
+      <c r="F39" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="E39" s="55" t="s">
-        <v>44</v>
-      </c>
-      <c r="F39" s="55" t="s">
+      <c r="G39" s="54" t="s">
         <v>141</v>
       </c>
-      <c r="G39" s="55" t="s">
+      <c r="H39" s="54" t="s">
+        <v>18</v>
+      </c>
+      <c r="I39" s="54" t="s">
+        <v>18</v>
+      </c>
+      <c r="J39" s="55" t="s">
         <v>142</v>
       </c>
-      <c r="H39" s="55" t="s">
-        <v>19</v>
-      </c>
-      <c r="I39" s="55" t="s">
-        <v>19</v>
-      </c>
-      <c r="J39" s="56" t="s">
-        <v>143</v>
-      </c>
-      <c r="K39" s="29">
-        <v>12</v>
-      </c>
-      <c r="L39" s="23">
+      <c r="K39" s="23">
         <v>2</v>
       </c>
-      <c r="M39" s="11">
+      <c r="L39" s="11">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="N39" s="92" t="s">
-        <v>144</v>
-      </c>
-      <c r="O39" s="30"/>
-    </row>
-    <row r="40" spans="1:15" ht="15.75" thickBot="1">
+      <c r="M39" s="91" t="s">
+        <v>143</v>
+      </c>
+      <c r="N39" s="29"/>
+    </row>
+    <row r="40" spans="1:14" ht="15.75" thickBot="1">
       <c r="A40" s="6">
         <v>38</v>
       </c>
-      <c r="B40" s="173"/>
-      <c r="C40" s="54" t="s">
+      <c r="B40" s="177"/>
+      <c r="C40" s="53" t="s">
+        <v>144</v>
+      </c>
+      <c r="D40" s="54" t="s">
         <v>145</v>
       </c>
-      <c r="D40" s="55" t="s">
+      <c r="E40" s="54" t="s">
+        <v>43</v>
+      </c>
+      <c r="F40" s="54" t="s">
         <v>146</v>
       </c>
-      <c r="E40" s="55" t="s">
-        <v>44</v>
-      </c>
-      <c r="F40" s="55" t="s">
-        <v>147</v>
-      </c>
-      <c r="G40" s="55" t="s">
-        <v>137</v>
-      </c>
-      <c r="H40" s="55" t="s">
-        <v>19</v>
-      </c>
-      <c r="I40" s="55" t="s">
-        <v>19</v>
-      </c>
-      <c r="J40" s="56" t="s">
-        <v>70</v>
-      </c>
-      <c r="K40" s="29">
-        <v>10</v>
-      </c>
-      <c r="L40" s="23">
+      <c r="G40" s="54" t="s">
+        <v>136</v>
+      </c>
+      <c r="H40" s="54" t="s">
+        <v>18</v>
+      </c>
+      <c r="I40" s="54" t="s">
+        <v>18</v>
+      </c>
+      <c r="J40" s="55" t="s">
+        <v>69</v>
+      </c>
+      <c r="K40" s="23">
         <v>1</v>
       </c>
-      <c r="M40" s="11">
+      <c r="L40" s="11">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N40" s="92" t="s">
-        <v>138</v>
-      </c>
-      <c r="O40" s="30"/>
-    </row>
-    <row r="41" spans="1:15" ht="15.75" thickBot="1">
+      <c r="M40" s="91" t="s">
+        <v>137</v>
+      </c>
+      <c r="N40" s="29"/>
+    </row>
+    <row r="41" spans="1:14" ht="15.75" thickBot="1">
       <c r="A41" s="6">
         <v>39</v>
       </c>
-      <c r="B41" s="173"/>
+      <c r="B41" s="177"/>
       <c r="C41" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="D41" s="35" t="s">
         <v>148</v>
       </c>
-      <c r="D41" s="36" t="s">
+      <c r="E41" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="F41" s="35" t="s">
         <v>149</v>
       </c>
-      <c r="E41" s="36" t="s">
-        <v>44</v>
-      </c>
-      <c r="F41" s="36" t="s">
+      <c r="G41" s="35" t="s">
         <v>150</v>
       </c>
-      <c r="G41" s="36" t="s">
-        <v>151</v>
-      </c>
-      <c r="H41" s="36" t="s">
-        <v>150</v>
-      </c>
-      <c r="I41" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="J41" s="38" t="s">
-        <v>143</v>
-      </c>
-      <c r="K41" s="13">
-        <v>20</v>
-      </c>
-      <c r="L41" s="7">
+      <c r="H41" s="35" t="s">
+        <v>149</v>
+      </c>
+      <c r="I41" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J41" s="37" t="s">
+        <v>142</v>
+      </c>
+      <c r="K41" s="7">
         <v>1</v>
       </c>
-      <c r="M41" s="11">
+      <c r="L41" s="11">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N41" s="93" t="s">
-        <v>21</v>
-      </c>
-      <c r="O41" s="30"/>
-    </row>
-    <row r="42" spans="1:15" ht="15.75" thickBot="1">
+      <c r="M41" s="92" t="s">
+        <v>20</v>
+      </c>
+      <c r="N41" s="29"/>
+    </row>
+    <row r="42" spans="1:14" ht="15.75" thickBot="1">
       <c r="A42" s="6">
         <v>40</v>
       </c>
-      <c r="B42" s="173"/>
-      <c r="C42" s="50" t="s">
+      <c r="B42" s="177"/>
+      <c r="C42" s="49" t="s">
+        <v>151</v>
+      </c>
+      <c r="D42" s="35" t="s">
         <v>152</v>
       </c>
-      <c r="D42" s="36" t="s">
+      <c r="E42" s="35" t="s">
         <v>153</v>
       </c>
-      <c r="E42" s="36" t="s">
+      <c r="F42" s="35" t="s">
         <v>154</v>
       </c>
-      <c r="F42" s="36" t="s">
+      <c r="G42" s="35" t="s">
         <v>155</v>
       </c>
-      <c r="G42" s="36" t="s">
+      <c r="H42" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="H42" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="I42" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="J42" s="38" t="s">
-        <v>70</v>
+      <c r="I42" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="J42" s="37" t="s">
+        <v>69</v>
       </c>
       <c r="K42" s="13">
-        <v>15</v>
-      </c>
-      <c r="L42" s="13">
         <v>2</v>
       </c>
-      <c r="M42" s="11">
+      <c r="L42" s="11">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="N42" s="94" t="s">
-        <v>21</v>
-      </c>
-      <c r="O42" s="30"/>
-    </row>
-    <row r="43" spans="1:15" ht="15.75" thickBot="1">
+      <c r="M42" s="93" t="s">
+        <v>20</v>
+      </c>
+      <c r="N42" s="29"/>
+    </row>
+    <row r="43" spans="1:14" ht="15.75" thickBot="1">
       <c r="A43" s="6">
         <v>41</v>
       </c>
-      <c r="B43" s="173"/>
-      <c r="C43" s="57" t="s">
+      <c r="B43" s="177"/>
+      <c r="C43" s="56" t="s">
+        <v>157</v>
+      </c>
+      <c r="D43" s="24"/>
+      <c r="E43" s="57" t="s">
         <v>158</v>
       </c>
-      <c r="D43" s="24"/>
-      <c r="E43" s="58" t="s">
-        <v>159</v>
-      </c>
       <c r="F43" s="24" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G43" s="24"/>
       <c r="H43" s="24"/>
       <c r="I43" s="24"/>
       <c r="J43" s="24"/>
-      <c r="K43" s="24"/>
-      <c r="L43" s="24">
+      <c r="K43" s="24">
         <v>5</v>
       </c>
-      <c r="M43" s="11">
+      <c r="L43" s="11">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
-      <c r="N43" s="95" t="s">
-        <v>19</v>
-      </c>
-      <c r="O43" s="30"/>
-    </row>
-    <row r="44" spans="1:15" ht="15.75" thickBot="1">
+      <c r="M43" s="94" t="s">
+        <v>18</v>
+      </c>
+      <c r="N43" s="29"/>
+    </row>
+    <row r="44" spans="1:14" ht="15.75" thickBot="1">
       <c r="A44" s="6">
         <v>42</v>
       </c>
-      <c r="B44" s="174"/>
-      <c r="C44" s="59" t="s">
+      <c r="B44" s="178"/>
+      <c r="C44" s="58" t="s">
+        <v>159</v>
+      </c>
+      <c r="D44" s="25"/>
+      <c r="E44" s="59" t="s">
         <v>160</v>
       </c>
-      <c r="D44" s="25"/>
-      <c r="E44" s="60" t="s">
-        <v>161</v>
-      </c>
       <c r="F44" s="25" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G44" s="25"/>
       <c r="H44" s="25"/>
       <c r="I44" s="25"/>
       <c r="J44" s="25"/>
-      <c r="K44" s="25"/>
-      <c r="L44" s="25">
+      <c r="K44" s="25">
         <v>5</v>
       </c>
-      <c r="M44" s="15">
+      <c r="L44" s="15">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
-      <c r="N44" s="96" t="s">
-        <v>19</v>
-      </c>
-      <c r="O44" s="30"/>
-    </row>
-    <row r="45" spans="1:15" ht="16.5" thickBot="1">
+      <c r="M44" s="95" t="s">
+        <v>18</v>
+      </c>
+      <c r="N44" s="29"/>
+    </row>
+    <row r="45" spans="1:14" ht="16.5" thickBot="1">
       <c r="A45"/>
       <c r="C45" s="26"/>
       <c r="D45" s="26"/>
@@ -4204,13 +4071,12 @@
       <c r="H45" s="26"/>
       <c r="I45" s="26"/>
       <c r="J45" s="26"/>
-      <c r="K45" s="26"/>
-      <c r="L45" s="171"/>
-      <c r="M45" s="171"/>
-      <c r="N45" s="171"/>
-      <c r="O45" s="30"/>
-    </row>
-    <row r="46" spans="1:15">
+      <c r="K45" s="175"/>
+      <c r="L45" s="175"/>
+      <c r="M45" s="175"/>
+      <c r="N45" s="29"/>
+    </row>
+    <row r="46" spans="1:14">
       <c r="A46"/>
       <c r="C46" s="26"/>
       <c r="D46" s="26"/>
@@ -4220,72 +4086,71 @@
       <c r="H46" s="26"/>
       <c r="I46" s="26"/>
       <c r="J46" s="26"/>
-      <c r="K46" s="26"/>
-      <c r="O46" s="30"/>
-    </row>
-    <row r="47" spans="1:15">
+      <c r="N46" s="29"/>
+    </row>
+    <row r="47" spans="1:14">
       <c r="A47"/>
-      <c r="O47" s="30"/>
-    </row>
-    <row r="48" spans="1:15">
+      <c r="N47" s="29"/>
+    </row>
+    <row r="48" spans="1:14">
       <c r="A48"/>
-      <c r="O48" s="30"/>
-    </row>
-    <row r="49" spans="1:15">
+      <c r="N48" s="29"/>
+    </row>
+    <row r="49" spans="1:14">
       <c r="A49"/>
-      <c r="O49" s="30"/>
-    </row>
-    <row r="50" spans="1:15">
+      <c r="N49" s="29"/>
+    </row>
+    <row r="50" spans="1:14">
       <c r="A50"/>
-      <c r="O50" s="30"/>
-    </row>
-    <row r="51" spans="1:15">
+      <c r="N50" s="29"/>
+    </row>
+    <row r="51" spans="1:14">
       <c r="A51"/>
-      <c r="O51" s="30"/>
-    </row>
-    <row r="52" spans="1:15">
+      <c r="N51" s="29"/>
+    </row>
+    <row r="52" spans="1:14">
       <c r="A52"/>
-      <c r="O52" s="30"/>
-    </row>
-    <row r="53" spans="1:15">
+      <c r="N52" s="29"/>
+    </row>
+    <row r="53" spans="1:14">
       <c r="A53"/>
-      <c r="O53" s="30"/>
-    </row>
-    <row r="54" spans="1:15" ht="15.75" customHeight="1">
+      <c r="N53" s="29"/>
+    </row>
+    <row r="54" spans="1:14" ht="15.75" customHeight="1">
       <c r="A54"/>
-      <c r="N54" s="70"/>
-      <c r="O54" s="30"/>
-    </row>
-    <row r="55" spans="1:15">
+      <c r="M54" s="69"/>
+      <c r="N54" s="29"/>
+    </row>
+    <row r="55" spans="1:14">
       <c r="A55"/>
-      <c r="O55" s="30"/>
-    </row>
-    <row r="56" spans="1:15">
+      <c r="N55" s="29"/>
+    </row>
+    <row r="56" spans="1:14">
       <c r="A56"/>
-      <c r="O56" s="30"/>
-    </row>
-    <row r="57" spans="1:15">
+      <c r="N56" s="29"/>
+    </row>
+    <row r="57" spans="1:14">
       <c r="A57"/>
-      <c r="O57" s="30"/>
-    </row>
-    <row r="58" spans="1:15">
+      <c r="N57" s="29"/>
+    </row>
+    <row r="58" spans="1:14">
       <c r="A58"/>
-      <c r="O58" s="30"/>
-    </row>
-    <row r="59" spans="1:15">
+      <c r="N58" s="29"/>
+    </row>
+    <row r="59" spans="1:14">
       <c r="A59"/>
-      <c r="O59" s="30"/>
-    </row>
-    <row r="60" spans="1:15">
+      <c r="N59" s="29"/>
+    </row>
+    <row r="60" spans="1:14">
       <c r="H60" s="27"/>
     </row>
-    <row r="61" spans="1:15">
+    <row r="61" spans="1:14">
       <c r="H61" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="L45:N45"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="K45:M45"/>
     <mergeCell ref="B3:B14"/>
     <mergeCell ref="B15:B18"/>
     <mergeCell ref="B23:B34"/>
@@ -4294,7 +4159,7 @@
     <mergeCell ref="B21:B22"/>
   </mergeCells>
   <phoneticPr fontId="21" type="noConversion"/>
-  <conditionalFormatting sqref="N22">
+  <conditionalFormatting sqref="M22">
     <cfRule type="dataBar" priority="38">
       <dataBar>
         <cfvo type="min"/>
@@ -4308,7 +4173,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L38:M38">
+  <conditionalFormatting sqref="K38:L38">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -4320,7 +4185,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L43">
+  <conditionalFormatting sqref="K43">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
@@ -4342,7 +4207,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L44">
+  <conditionalFormatting sqref="K44">
     <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
@@ -4364,7 +4229,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N3:N7">
+  <conditionalFormatting sqref="M3:M7">
     <cfRule type="dataBar" priority="40">
       <dataBar>
         <cfvo type="min"/>
@@ -4378,7 +4243,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N34">
+  <conditionalFormatting sqref="M34">
     <cfRule type="dataBar" priority="37">
       <dataBar>
         <cfvo type="min"/>
@@ -4392,7 +4257,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L13:L37 L42 M3:M44">
+  <conditionalFormatting sqref="K13:K37 K42 L3:L44">
     <cfRule type="colorScale" priority="50">
       <colorScale>
         <cfvo type="min"/>
@@ -4404,7 +4269,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L9:L12">
+  <conditionalFormatting sqref="K9:K12">
     <cfRule type="colorScale" priority="51">
       <colorScale>
         <cfvo type="min"/>
@@ -4416,7 +4281,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L3:M44">
+  <conditionalFormatting sqref="K3:L44">
     <cfRule type="colorScale" priority="61">
       <colorScale>
         <cfvo type="min"/>
@@ -4429,44 +4294,44 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="N10" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="N11" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="N14" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="N15" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="N18" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="N23" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="N30" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="N31" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="N33" r:id="rId9" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="N34" r:id="rId10" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="N36" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="N42" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="N9" r:id="rId13" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="N32" r:id="rId14" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="N3" r:id="rId15" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="N7" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="N8" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="N38" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="N40" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="N19" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="N41" r:id="rId21" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="N21" r:id="rId22" xr:uid="{5EAF2F70-555A-4B25-966F-95095861DC0E}"/>
-    <hyperlink ref="N24" r:id="rId23" xr:uid="{6B884554-8BB6-4BF7-8096-D834E9729A06}"/>
-    <hyperlink ref="N12" r:id="rId24" xr:uid="{44B658D6-BFFD-46B9-B230-29405BAF9534}"/>
-    <hyperlink ref="N13" r:id="rId25" xr:uid="{367FEFFE-61E8-47BB-BCCA-FD3358349566}"/>
-    <hyperlink ref="N35" r:id="rId26" xr:uid="{D1D06D79-D259-47BA-BC7F-8742EAB7848C}"/>
-    <hyperlink ref="N25" r:id="rId27" xr:uid="{5545F658-0692-42E9-BD6F-76E0A6B030B0}"/>
-    <hyperlink ref="N27" r:id="rId28" xr:uid="{168ECF43-5CE3-4702-A056-8FA8BBC47676}"/>
-    <hyperlink ref="N26" r:id="rId29" xr:uid="{EA5E5506-441F-4FE0-B453-D92044CD3CD6}"/>
-    <hyperlink ref="N28" r:id="rId30" xr:uid="{8D8C1B68-82FF-4307-AFCC-0412DDB5B0BE}"/>
-    <hyperlink ref="N4" r:id="rId31" xr:uid="{2EF0B57E-A4CF-4AC0-9358-948CDF39D8B4}"/>
-    <hyperlink ref="N5" r:id="rId32" xr:uid="{ECCB4777-894F-4969-BB30-3BB1C2789276}"/>
+    <hyperlink ref="M10" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="M11" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="M14" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="M15" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="M18" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="M23" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="M30" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="M31" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="M33" r:id="rId9" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="M34" r:id="rId10" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="M36" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="M42" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="M9" r:id="rId13" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="M32" r:id="rId14" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="M3" r:id="rId15" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="M7" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="M8" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="M38" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="M40" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="M19" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="M41" r:id="rId21" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="M21" r:id="rId22" xr:uid="{5EAF2F70-555A-4B25-966F-95095861DC0E}"/>
+    <hyperlink ref="M24" r:id="rId23" xr:uid="{6B884554-8BB6-4BF7-8096-D834E9729A06}"/>
+    <hyperlink ref="M12" r:id="rId24" xr:uid="{44B658D6-BFFD-46B9-B230-29405BAF9534}"/>
+    <hyperlink ref="M13" r:id="rId25" xr:uid="{367FEFFE-61E8-47BB-BCCA-FD3358349566}"/>
+    <hyperlink ref="M35" r:id="rId26" xr:uid="{D1D06D79-D259-47BA-BC7F-8742EAB7848C}"/>
+    <hyperlink ref="M25" r:id="rId27" xr:uid="{5545F658-0692-42E9-BD6F-76E0A6B030B0}"/>
+    <hyperlink ref="M27" r:id="rId28" xr:uid="{168ECF43-5CE3-4702-A056-8FA8BBC47676}"/>
+    <hyperlink ref="M26" r:id="rId29" xr:uid="{EA5E5506-441F-4FE0-B453-D92044CD3CD6}"/>
+    <hyperlink ref="M28" r:id="rId30" xr:uid="{8D8C1B68-82FF-4307-AFCC-0412DDB5B0BE}"/>
+    <hyperlink ref="M4" r:id="rId31" xr:uid="{2EF0B57E-A4CF-4AC0-9358-948CDF39D8B4}"/>
+    <hyperlink ref="M5" r:id="rId32" xr:uid="{ECCB4777-894F-4969-BB30-3BB1C2789276}"/>
     <hyperlink ref="C16" r:id="rId33" xr:uid="{44A99C6C-4AC4-4D03-96BE-D592031C9536}"/>
-    <hyperlink ref="N16" r:id="rId34" xr:uid="{1A7B0E41-616E-45F1-BF6C-4CBB22A55EC6}"/>
-    <hyperlink ref="N20" r:id="rId35" xr:uid="{0E9DC705-3503-4FA0-87A9-DF2A5B60045D}"/>
-    <hyperlink ref="N17" r:id="rId36" xr:uid="{E7A9FE43-2492-4F96-944F-8153D9DD3BC5}"/>
-    <hyperlink ref="N6" r:id="rId37" xr:uid="{C6B216F8-5775-4357-B676-8FC9F8808265}"/>
-    <hyperlink ref="N29" r:id="rId38" xr:uid="{A2E7CF78-849E-4B20-A638-AA9D3B8EC8EE}"/>
+    <hyperlink ref="M16" r:id="rId34" xr:uid="{1A7B0E41-616E-45F1-BF6C-4CBB22A55EC6}"/>
+    <hyperlink ref="M20" r:id="rId35" xr:uid="{0E9DC705-3503-4FA0-87A9-DF2A5B60045D}"/>
+    <hyperlink ref="M17" r:id="rId36" xr:uid="{E7A9FE43-2492-4F96-944F-8153D9DD3BC5}"/>
+    <hyperlink ref="M6" r:id="rId37" xr:uid="{C6B216F8-5775-4357-B676-8FC9F8808265}"/>
+    <hyperlink ref="M29" r:id="rId38" xr:uid="{A2E7CF78-849E-4B20-A638-AA9D3B8EC8EE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId39"/>
@@ -4484,7 +4349,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>N22</xm:sqref>
+          <xm:sqref>M22</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{94E20060-874B-439F-8FDA-33B3DD39FFE6}">
@@ -4497,7 +4362,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>N3:N7</xm:sqref>
+          <xm:sqref>M3:M7</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{DBB933A5-5D45-42AE-8D8B-F05439EF033D}">
@@ -4510,7 +4375,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>N34</xm:sqref>
+          <xm:sqref>M34</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/Deliverables/Interface_Board/BOM/NEW-6 Prototypes_Interface_Board.xlsx
+++ b/Deliverables/Interface_Board/BOM/NEW-6 Prototypes_Interface_Board.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ChristianRaun-EthercatDesign\Deliverables\Interface_Board\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D3A7ABD-CD90-4A4A-93AF-082A2F30B043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42F92E23-0475-4E30-B82A-075C8F0EE997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="246">
   <si>
     <t>Bill of Material (BOM) for Interface_Board</t>
   </si>
@@ -63,6 +63,9 @@
   </si>
   <si>
     <t>Value</t>
+  </si>
+  <si>
+    <t>LCSC/MOQ</t>
   </si>
   <si>
     <t>Quantity (Per Board)</t>
@@ -670,6 +673,10 @@
     <t>0603WAF150LT5E</t>
   </si>
   <si>
+    <t xml:space="preserve"> Resistors 75V150mΩ 0603 Chip Resistor - Surface Mount ROHS
+</t>
+  </si>
+  <si>
     <t>C45879</t>
   </si>
   <si>
@@ -677,6 +684,9 @@
   </si>
   <si>
     <t>R#6,R#7</t>
+  </si>
+  <si>
+    <t>C#1,C#2,C#3,C#4</t>
   </si>
   <si>
     <t>CL10A475KA8NQNC</t>
@@ -816,49 +826,6 @@
   <si>
     <t>------</t>
   </si>
-  <si>
-    <t>C#1,C#2,C#3,C#4,C#12,C#13</t>
-  </si>
-  <si>
-    <t>GCM1885C2A471GA16D</t>
-  </si>
-  <si>
-    <t>C#14,C#15,C#16,C#17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">470 pF ±2% 100V Ceramic Capacitor C0G,0603
-</t>
-  </si>
-  <si>
-    <t>C437459</t>
-  </si>
-  <si>
-    <t>470pF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RC0603JR-0747KL
-</t>
-  </si>
-  <si>
-    <t>C127447</t>
-  </si>
-  <si>
-    <t>47K</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RES 47K OHM 5% 1/10W 0603
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resistors 75V150mΩ 0603 Chip Resistor - Surface Mount ROHS
-</t>
-  </si>
-  <si>
-    <t>R01,R02</t>
-  </si>
-  <si>
-    <t>2x13</t>
-  </si>
 </sst>
 </file>
 
@@ -867,19 +834,12 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.0000"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1469,24 +1429,24 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="179">
+  <cellXfs count="176">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1495,19 +1455,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1516,19 +1476,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1540,19 +1500,25 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1563,7 +1529,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1575,10 +1541,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1587,7 +1553,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1599,16 +1565,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1629,19 +1595,19 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
@@ -1650,28 +1616,37 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="6" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1679,16 +1654,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
@@ -1700,86 +1675,89 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="1" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="22" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="22" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="22" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="22" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="22" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="22" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="22" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="21" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="21" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="28" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="28" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="27" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1788,13 +1766,13 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="15" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="4" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
@@ -1806,10 +1784,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="26" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="26" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1822,23 +1800,23 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="24" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="24" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1850,143 +1828,118 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="22" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="22" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="22" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="22" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="7" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="7" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="7" borderId="22" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="7" borderId="22" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="7" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="27" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="27" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="7" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="28" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="22" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="21" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="28" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="22" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="21" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2265,7 +2218,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC61"/>
+  <dimension ref="A1:AD59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="2" customWidth="1"/>
@@ -2278,29 +2231,31 @@
     <col min="8" max="8" width="15.28515625" style="2" customWidth="1"/>
     <col min="9" max="9" width="21.5703125" customWidth="1"/>
     <col min="10" max="10" width="7" customWidth="1"/>
-    <col min="11" max="11" width="21.85546875" customWidth="1"/>
-    <col min="12" max="12" width="14.140625" customWidth="1"/>
-    <col min="13" max="13" width="16.28515625" customWidth="1"/>
+    <col min="11" max="11" width="11.5703125" customWidth="1"/>
+    <col min="12" max="12" width="21.85546875" customWidth="1"/>
+    <col min="13" max="13" width="14.140625" customWidth="1"/>
+    <col min="14" max="14" width="16.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="16.5" thickBot="1">
-      <c r="A1" s="172" t="s">
+    <row r="1" spans="1:30" ht="16.5" thickBot="1">
+      <c r="A1" s="72" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="173"/>
-      <c r="C1" s="173"/>
-      <c r="D1" s="173"/>
-      <c r="E1" s="173"/>
-      <c r="F1" s="173"/>
-      <c r="G1" s="173"/>
-      <c r="H1" s="173"/>
-      <c r="I1" s="173"/>
-      <c r="J1" s="173"/>
-      <c r="K1" s="173"/>
-      <c r="L1" s="173"/>
-      <c r="M1" s="174"/>
-    </row>
-    <row r="2" spans="1:29" s="1" customFormat="1" ht="16.5" thickBot="1">
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="73"/>
+      <c r="K1" s="73"/>
+      <c r="L1" s="73"/>
+      <c r="M1" s="73"/>
+      <c r="N1" s="92"/>
+    </row>
+    <row r="2" spans="1:30" s="1" customFormat="1" ht="16.5" thickBot="1">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -2334,13 +2289,15 @@
       <c r="K2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="67" t="s">
+      <c r="L2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="M2" s="69" t="s">
+        <v>181</v>
+      </c>
+      <c r="N2" s="93" t="s">
         <v>180</v>
       </c>
-      <c r="M2" s="87" t="s">
-        <v>179</v>
-      </c>
-      <c r="N2"/>
       <c r="O2"/>
       <c r="P2"/>
       <c r="Q2"/>
@@ -2356,1810 +2313,1848 @@
       <c r="AA2"/>
       <c r="AB2"/>
       <c r="AC2"/>
-    </row>
-    <row r="3" spans="1:29" ht="15.75" thickBot="1">
+      <c r="AD2"/>
+    </row>
+    <row r="3" spans="1:30" ht="15.75" thickBot="1">
       <c r="A3" s="6">
         <v>1</v>
       </c>
-      <c r="B3" s="176" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="138" t="s">
+      <c r="B3" s="172" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="139" t="s">
-        <v>243</v>
-      </c>
-      <c r="E3" s="140" t="s">
+      <c r="C3" s="144" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="140" t="s">
+      <c r="D3" s="145" t="s">
+        <v>209</v>
+      </c>
+      <c r="E3" s="146" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="140" t="s">
+      <c r="F3" s="146" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="141" t="s">
+      <c r="G3" s="146" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="142" t="s">
+      <c r="H3" s="147" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="140" t="s">
+      <c r="I3" s="148" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="143">
-        <v>6</v>
-      </c>
-      <c r="L3" s="143">
-        <f>K3*6</f>
-        <v>36</v>
-      </c>
-      <c r="M3" s="144" t="s">
+      <c r="J3" s="146" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="4" spans="1:29" ht="15.75" thickBot="1">
+      <c r="K3" s="149">
+        <v>50</v>
+      </c>
+      <c r="L3" s="149">
+        <v>4</v>
+      </c>
+      <c r="M3" s="149">
+        <f>L3*6</f>
+        <v>24</v>
+      </c>
+      <c r="N3" s="150" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:30" ht="15.75" thickBot="1">
       <c r="A4" s="6">
         <v>2</v>
       </c>
-      <c r="B4" s="177"/>
-      <c r="C4" s="145" t="s">
-        <v>208</v>
-      </c>
-      <c r="D4" s="146" t="s">
-        <v>209</v>
-      </c>
-      <c r="E4" s="131" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="132" t="s">
-        <v>207</v>
-      </c>
-      <c r="G4" s="132" t="s">
+      <c r="B4" s="173"/>
+      <c r="C4" s="151" t="s">
+        <v>211</v>
+      </c>
+      <c r="D4" s="152" t="s">
+        <v>212</v>
+      </c>
+      <c r="E4" s="137" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="138" t="s">
         <v>210</v>
       </c>
-      <c r="H4" s="147" t="s">
-        <v>211</v>
-      </c>
-      <c r="I4" s="148" t="s">
-        <v>18</v>
-      </c>
-      <c r="J4" s="132" t="s">
-        <v>212</v>
-      </c>
-      <c r="K4" s="133">
+      <c r="G4" s="138" t="s">
+        <v>213</v>
+      </c>
+      <c r="H4" s="153" t="s">
+        <v>214</v>
+      </c>
+      <c r="I4" s="154" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" s="138" t="s">
+        <v>215</v>
+      </c>
+      <c r="K4" s="139">
+        <v>20</v>
+      </c>
+      <c r="L4" s="139">
         <v>1</v>
       </c>
-      <c r="L4" s="133">
-        <f t="shared" ref="L4:L6" si="0">K4*6</f>
+      <c r="M4" s="139">
+        <f t="shared" ref="M4:M5" si="0">L4*6</f>
         <v>6</v>
       </c>
-      <c r="M4" s="149" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:29" ht="15.75" thickBot="1">
+      <c r="N4" s="155" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30" ht="15.75" thickBot="1">
       <c r="A5" s="6">
         <v>3</v>
       </c>
-      <c r="B5" s="177"/>
-      <c r="C5" s="145" t="s">
+      <c r="B5" s="173"/>
+      <c r="C5" s="151" t="s">
+        <v>220</v>
+      </c>
+      <c r="D5" s="152" t="s">
+        <v>219</v>
+      </c>
+      <c r="E5" s="137" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="138" t="s">
+        <v>216</v>
+      </c>
+      <c r="G5" s="138" t="s">
+        <v>213</v>
+      </c>
+      <c r="H5" s="153" t="s">
         <v>217</v>
       </c>
-      <c r="D5" s="146" t="s">
-        <v>216</v>
-      </c>
-      <c r="E5" s="131" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="132" t="s">
-        <v>213</v>
-      </c>
-      <c r="G5" s="132" t="s">
-        <v>210</v>
-      </c>
-      <c r="H5" s="147" t="s">
-        <v>214</v>
-      </c>
-      <c r="I5" s="148" t="s">
-        <v>18</v>
-      </c>
-      <c r="J5" s="132" t="s">
-        <v>215</v>
-      </c>
-      <c r="K5" s="133">
+      <c r="I5" s="154" t="s">
+        <v>19</v>
+      </c>
+      <c r="J5" s="138" t="s">
+        <v>218</v>
+      </c>
+      <c r="K5" s="139">
+        <v>50</v>
+      </c>
+      <c r="L5" s="139">
         <v>2</v>
       </c>
-      <c r="L5" s="133">
+      <c r="M5" s="139">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="M5" s="149" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:29" ht="15.75" thickBot="1">
+      <c r="N5" s="155" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" ht="15.75" thickBot="1">
       <c r="A6" s="6">
         <v>4</v>
       </c>
-      <c r="B6" s="177"/>
-      <c r="C6" s="168" t="s">
-        <v>246</v>
-      </c>
-      <c r="D6" s="146" t="s">
-        <v>245</v>
-      </c>
-      <c r="E6" s="131" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="167" t="s">
-        <v>244</v>
-      </c>
-      <c r="G6" s="131" t="s">
+      <c r="B6" s="173"/>
+      <c r="C6" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="37" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="147" t="s">
-        <v>247</v>
-      </c>
-      <c r="I6" s="148" t="s">
-        <v>18</v>
-      </c>
-      <c r="J6" s="167" t="s">
-        <v>248</v>
-      </c>
-      <c r="K6" s="133">
-        <v>4</v>
-      </c>
-      <c r="L6" s="133">
-        <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="M6" s="149" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:29" ht="15.75" thickBot="1">
+      <c r="G6" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="I6" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="J6" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="K6" s="11">
+        <v>10</v>
+      </c>
+      <c r="L6" s="8">
+        <v>1</v>
+      </c>
+      <c r="M6" s="11">
+        <f t="shared" ref="M6:M42" si="1">L6*6</f>
+        <v>6</v>
+      </c>
+      <c r="N6" s="87" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30" ht="15.75" thickBot="1">
       <c r="A7" s="6">
         <v>5</v>
       </c>
-      <c r="B7" s="177"/>
-      <c r="C7" s="34" t="s">
+      <c r="B7" s="173"/>
+      <c r="C7" s="36" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="38" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="J7" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="K7" s="11">
+        <v>100</v>
+      </c>
+      <c r="L7" s="8">
+        <v>8</v>
+      </c>
+      <c r="M7" s="11">
+        <f t="shared" si="1"/>
+        <v>48</v>
+      </c>
+      <c r="N7" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="35" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="36" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="35" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" s="36" t="s">
-        <v>25</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="I7" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J7" s="36" t="s">
-        <v>27</v>
-      </c>
-      <c r="K7" s="8">
-        <v>1</v>
-      </c>
-      <c r="L7" s="11">
-        <f t="shared" ref="L7:L44" si="1">K7*6</f>
-        <v>6</v>
-      </c>
-      <c r="M7" s="82" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:29" ht="15.75" thickBot="1">
+    </row>
+    <row r="8" spans="1:30" ht="15.75" thickBot="1">
       <c r="A8" s="6">
         <v>6</v>
       </c>
-      <c r="B8" s="177"/>
-      <c r="C8" s="34" t="s">
+      <c r="B8" s="173"/>
+      <c r="C8" s="156" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="138" t="s">
+        <v>235</v>
+      </c>
+      <c r="E8" s="137" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="167" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="154" t="s">
+        <v>38</v>
+      </c>
+      <c r="H8" s="81" t="s">
+        <v>39</v>
+      </c>
+      <c r="I8" s="137" t="s">
+        <v>40</v>
+      </c>
+      <c r="J8" s="137" t="s">
+        <v>41</v>
+      </c>
+      <c r="K8" s="139">
+        <v>50</v>
+      </c>
+      <c r="L8" s="81">
+        <v>3</v>
+      </c>
+      <c r="M8" s="139">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="N8" s="168" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" ht="15.75" thickBot="1">
+      <c r="A9" s="6">
+        <v>7</v>
+      </c>
+      <c r="B9" s="173"/>
+      <c r="C9" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" s="37" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" s="42" t="s">
+        <v>44</v>
+      </c>
+      <c r="F9" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="G9" s="43" t="s">
+        <v>46</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="I9" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="J9" s="42" t="s">
+        <v>48</v>
+      </c>
+      <c r="K9" s="11">
+        <v>10</v>
+      </c>
+      <c r="L9" s="29">
+        <v>1</v>
+      </c>
+      <c r="M9" s="11">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="N9" s="89" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" ht="15.75" thickBot="1">
+      <c r="A10" s="6">
+        <v>8</v>
+      </c>
+      <c r="B10" s="173"/>
+      <c r="C10" s="156" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" s="138" t="s">
+        <v>236</v>
+      </c>
+      <c r="E10" s="137" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10" s="137" t="s">
+        <v>50</v>
+      </c>
+      <c r="G10" s="154" t="s">
+        <v>46</v>
+      </c>
+      <c r="H10" s="81" t="s">
+        <v>51</v>
+      </c>
+      <c r="I10" s="154" t="s">
+        <v>19</v>
+      </c>
+      <c r="J10" s="137" t="s">
+        <v>48</v>
+      </c>
+      <c r="K10" s="139">
+        <v>12</v>
+      </c>
+      <c r="L10" s="81">
+        <v>3</v>
+      </c>
+      <c r="M10" s="139">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="N10" s="168" t="s">
+        <v>21</v>
+      </c>
+      <c r="O10" s="31"/>
+    </row>
+    <row r="11" spans="1:30" ht="15.75" thickBot="1">
+      <c r="A11" s="6">
+        <v>9</v>
+      </c>
+      <c r="B11" s="173"/>
+      <c r="C11" s="82" t="s">
+        <v>162</v>
+      </c>
+      <c r="D11" s="70" t="s">
+        <v>52</v>
+      </c>
+      <c r="E11" s="62" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="62" t="s">
+        <v>163</v>
+      </c>
+      <c r="G11" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="H11" s="80" t="s">
+        <v>243</v>
+      </c>
+      <c r="I11" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="J11" s="42" t="s">
+        <v>53</v>
+      </c>
+      <c r="K11" s="11">
+        <v>20</v>
+      </c>
+      <c r="L11" s="12">
+        <v>1</v>
+      </c>
+      <c r="M11" s="11">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="N11" s="90" t="s">
+        <v>21</v>
+      </c>
+      <c r="O11" s="31"/>
+    </row>
+    <row r="12" spans="1:30" ht="15.75" thickBot="1">
+      <c r="A12" s="6">
+        <v>10</v>
+      </c>
+      <c r="B12" s="173"/>
+      <c r="C12" s="41" t="s">
+        <v>164</v>
+      </c>
+      <c r="D12" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="E12" s="42" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" s="37" t="s">
+        <v>165</v>
+      </c>
+      <c r="G12" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="H12" s="80" t="s">
+        <v>244</v>
+      </c>
+      <c r="I12" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="J12" s="42" t="s">
+        <v>55</v>
+      </c>
+      <c r="K12" s="11">
+        <v>10</v>
+      </c>
+      <c r="L12" s="12">
+        <v>1</v>
+      </c>
+      <c r="M12" s="11">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="N12" s="90" t="s">
+        <v>21</v>
+      </c>
+      <c r="O12" s="32"/>
+    </row>
+    <row r="13" spans="1:30" ht="15.75" thickBot="1">
+      <c r="A13" s="6">
+        <v>11</v>
+      </c>
+      <c r="B13" s="174"/>
+      <c r="C13" s="44" t="s">
+        <v>56</v>
+      </c>
+      <c r="D13" s="45" t="s">
+        <v>57</v>
+      </c>
+      <c r="E13" s="46" t="s">
+        <v>58</v>
+      </c>
+      <c r="F13" s="45" t="s">
+        <v>59</v>
+      </c>
+      <c r="G13" s="47" t="s">
+        <v>60</v>
+      </c>
+      <c r="H13" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="I13" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="J13" s="46" t="s">
+        <v>62</v>
+      </c>
+      <c r="K13" s="15">
+        <v>50</v>
+      </c>
+      <c r="L13" s="16">
+        <v>1</v>
+      </c>
+      <c r="M13" s="15">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="N13" s="91" t="s">
+        <v>21</v>
+      </c>
+      <c r="O13" s="31"/>
+    </row>
+    <row r="14" spans="1:30" ht="15.75" thickBot="1">
+      <c r="A14" s="6">
+        <v>12</v>
+      </c>
+      <c r="B14" s="173" t="s">
+        <v>63</v>
+      </c>
+      <c r="C14" s="83" t="s">
+        <v>64</v>
+      </c>
+      <c r="D14" s="49" t="s">
+        <v>65</v>
+      </c>
+      <c r="E14" s="84" t="s">
+        <v>66</v>
+      </c>
+      <c r="F14" s="49" t="s">
+        <v>67</v>
+      </c>
+      <c r="G14" s="84" t="s">
+        <v>68</v>
+      </c>
+      <c r="H14" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="I14" s="50" t="s">
+        <v>19</v>
+      </c>
+      <c r="J14" s="85" t="s">
+        <v>70</v>
+      </c>
+      <c r="K14" s="77">
+        <v>7</v>
+      </c>
+      <c r="L14" s="86">
+        <v>1</v>
+      </c>
+      <c r="M14" s="77">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="N14" s="94" t="s">
+        <v>21</v>
+      </c>
+      <c r="O14" s="31"/>
+    </row>
+    <row r="15" spans="1:30" ht="15.75" thickBot="1">
+      <c r="A15" s="6">
+        <v>13</v>
+      </c>
+      <c r="B15" s="173"/>
+      <c r="C15" s="156" t="s">
+        <v>224</v>
+      </c>
+      <c r="D15" s="157" t="s">
+        <v>223</v>
+      </c>
+      <c r="E15" s="138" t="s">
+        <v>222</v>
+      </c>
+      <c r="F15" s="138" t="s">
+        <v>221</v>
+      </c>
+      <c r="G15" s="138" t="s">
+        <v>225</v>
+      </c>
+      <c r="H15" s="158" t="s">
+        <v>226</v>
+      </c>
+      <c r="I15" s="159" t="s">
+        <v>19</v>
+      </c>
+      <c r="J15" s="159" t="s">
+        <v>70</v>
+      </c>
+      <c r="K15" s="139">
+        <v>50</v>
+      </c>
+      <c r="L15" s="81">
+        <v>1</v>
+      </c>
+      <c r="M15" s="139">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="N15" s="141" t="s">
+        <v>21</v>
+      </c>
+      <c r="O15" s="31"/>
+    </row>
+    <row r="16" spans="1:30" ht="15.75" thickBot="1">
+      <c r="A16" s="6">
+        <v>14</v>
+      </c>
+      <c r="B16" s="173"/>
+      <c r="C16" s="151" t="s">
+        <v>240</v>
+      </c>
+      <c r="D16" s="157" t="s">
+        <v>239</v>
+      </c>
+      <c r="E16" s="138" t="s">
+        <v>238</v>
+      </c>
+      <c r="F16" s="138" t="s">
+        <v>237</v>
+      </c>
+      <c r="G16" s="138" t="s">
+        <v>241</v>
+      </c>
+      <c r="H16" s="158" t="s">
+        <v>242</v>
+      </c>
+      <c r="I16" s="159" t="s">
+        <v>19</v>
+      </c>
+      <c r="J16" s="159" t="s">
+        <v>70</v>
+      </c>
+      <c r="K16" s="139">
+        <v>5</v>
+      </c>
+      <c r="L16" s="81">
+        <v>1</v>
+      </c>
+      <c r="M16" s="139">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="N16" s="141" t="s">
+        <v>21</v>
+      </c>
+      <c r="O16" s="31"/>
+    </row>
+    <row r="17" spans="1:15" ht="15.75" thickBot="1">
+      <c r="A17" s="6">
+        <v>15</v>
+      </c>
+      <c r="B17" s="173"/>
+      <c r="C17" s="79" t="s">
+        <v>71</v>
+      </c>
+      <c r="D17" s="106" t="s">
+        <v>72</v>
+      </c>
+      <c r="E17" s="110" t="s">
+        <v>73</v>
+      </c>
+      <c r="F17" s="106" t="s">
+        <v>74</v>
+      </c>
+      <c r="G17" s="110" t="s">
+        <v>75</v>
+      </c>
+      <c r="H17" s="107" t="s">
+        <v>76</v>
+      </c>
+      <c r="I17" s="107" t="s">
+        <v>19</v>
+      </c>
+      <c r="J17" s="111" t="s">
+        <v>70</v>
+      </c>
+      <c r="K17" s="103">
+        <v>20</v>
+      </c>
+      <c r="L17" s="112">
+        <v>1</v>
+      </c>
+      <c r="M17" s="103">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="N17" s="113" t="s">
+        <v>21</v>
+      </c>
+      <c r="O17" s="31"/>
+    </row>
+    <row r="18" spans="1:15" ht="16.5" thickBot="1">
+      <c r="A18" s="6">
+        <v>16</v>
+      </c>
+      <c r="B18" s="175" t="s">
+        <v>77</v>
+      </c>
+      <c r="C18" s="114" t="s">
+        <v>78</v>
+      </c>
+      <c r="D18" s="115" t="s">
+        <v>79</v>
+      </c>
+      <c r="E18" s="115" t="s">
+        <v>80</v>
+      </c>
+      <c r="F18" s="115" t="s">
+        <v>81</v>
+      </c>
+      <c r="G18" s="116" t="s">
+        <v>82</v>
+      </c>
+      <c r="H18" s="116" t="s">
+        <v>19</v>
+      </c>
+      <c r="I18" s="115" t="s">
+        <v>19</v>
+      </c>
+      <c r="J18" s="116" t="s">
+        <v>70</v>
+      </c>
+      <c r="K18" s="108">
+        <v>7</v>
+      </c>
+      <c r="L18" s="108">
+        <v>1</v>
+      </c>
+      <c r="M18" s="67">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="N18" s="109" t="s">
+        <v>21</v>
+      </c>
+      <c r="O18" s="31"/>
+    </row>
+    <row r="19" spans="1:15" ht="30.75" thickBot="1">
+      <c r="A19" s="6">
+        <v>17</v>
+      </c>
+      <c r="B19" s="175" t="s">
+        <v>227</v>
+      </c>
+      <c r="C19" s="160" t="s">
+        <v>229</v>
+      </c>
+      <c r="D19" s="161" t="s">
+        <v>228</v>
+      </c>
+      <c r="E19" s="162" t="s">
+        <v>230</v>
+      </c>
+      <c r="F19" s="162" t="s">
+        <v>231</v>
+      </c>
+      <c r="G19" s="163" t="s">
+        <v>232</v>
+      </c>
+      <c r="H19" s="163" t="s">
+        <v>233</v>
+      </c>
+      <c r="I19" s="162" t="s">
+        <v>234</v>
+      </c>
+      <c r="J19" s="163" t="s">
+        <v>70</v>
+      </c>
+      <c r="K19" s="164">
+        <v>10</v>
+      </c>
+      <c r="L19" s="164">
+        <v>1</v>
+      </c>
+      <c r="M19" s="165">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="N19" s="166" t="s">
+        <v>21</v>
+      </c>
+      <c r="O19" s="31"/>
+    </row>
+    <row r="20" spans="1:15" ht="15.75" thickBot="1">
+      <c r="A20" s="6">
+        <v>18</v>
+      </c>
+      <c r="B20" s="172" t="s">
+        <v>83</v>
+      </c>
+      <c r="C20" s="104" t="s">
+        <v>174</v>
+      </c>
+      <c r="D20" s="63" t="s">
+        <v>175</v>
+      </c>
+      <c r="E20" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="F20" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="G20" s="35" t="s">
+        <v>177</v>
+      </c>
+      <c r="H20" s="35" t="s">
+        <v>178</v>
+      </c>
+      <c r="I20" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="J20" s="35" t="s">
+        <v>70</v>
+      </c>
+      <c r="K20" s="19">
+        <v>10</v>
+      </c>
+      <c r="L20" s="19">
+        <v>1</v>
+      </c>
+      <c r="M20" s="18">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="N20" s="105" t="s">
+        <v>21</v>
+      </c>
+      <c r="O20" s="31"/>
+    </row>
+    <row r="21" spans="1:15" ht="15.75" thickBot="1">
+      <c r="A21" s="6">
+        <v>19</v>
+      </c>
+      <c r="B21" s="174"/>
+      <c r="C21" s="64" t="s">
+        <v>84</v>
+      </c>
+      <c r="D21" s="65" t="s">
+        <v>85</v>
+      </c>
+      <c r="E21" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="F21" s="65" t="s">
+        <v>86</v>
+      </c>
+      <c r="G21" s="65" t="s">
+        <v>87</v>
+      </c>
+      <c r="H21" s="66"/>
+      <c r="I21" s="66"/>
+      <c r="J21" s="65" t="s">
+        <v>70</v>
+      </c>
+      <c r="K21" s="66">
+        <v>7</v>
+      </c>
+      <c r="L21" s="66">
+        <v>1</v>
+      </c>
+      <c r="M21" s="15">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="N21" s="68" t="s">
+        <v>88</v>
+      </c>
+      <c r="O21" s="31"/>
+    </row>
+    <row r="22" spans="1:15" ht="15.75" thickBot="1">
+      <c r="A22" s="6">
+        <v>20</v>
+      </c>
+      <c r="B22" s="172" t="s">
+        <v>89</v>
+      </c>
+      <c r="C22" s="144" t="s">
+        <v>90</v>
+      </c>
+      <c r="D22" s="169" t="s">
+        <v>187</v>
+      </c>
+      <c r="E22" s="146" t="s">
+        <v>91</v>
+      </c>
+      <c r="F22" s="146" t="s">
+        <v>92</v>
+      </c>
+      <c r="G22" s="148" t="s">
+        <v>60</v>
+      </c>
+      <c r="H22" s="170" t="s">
+        <v>93</v>
+      </c>
+      <c r="I22" s="146" t="s">
+        <v>19</v>
+      </c>
+      <c r="J22" s="146" t="s">
+        <v>94</v>
+      </c>
+      <c r="K22" s="149">
+        <v>100</v>
+      </c>
+      <c r="L22" s="149">
+        <v>3</v>
+      </c>
+      <c r="M22" s="149">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="N22" s="171" t="s">
+        <v>21</v>
+      </c>
+      <c r="O22" s="31"/>
+    </row>
+    <row r="23" spans="1:15" ht="15.75" thickBot="1">
+      <c r="A23" s="6">
+        <v>21</v>
+      </c>
+      <c r="B23" s="173"/>
+      <c r="C23" s="76" t="s">
+        <v>166</v>
+      </c>
+      <c r="D23" s="62" t="s">
+        <v>167</v>
+      </c>
+      <c r="E23" s="62" t="s">
+        <v>91</v>
+      </c>
+      <c r="F23" s="62" t="s">
+        <v>168</v>
+      </c>
+      <c r="G23" s="39" t="s">
+        <v>156</v>
+      </c>
+      <c r="H23" s="80" t="s">
+        <v>245</v>
+      </c>
+      <c r="I23" s="37" t="s">
+        <v>19</v>
+      </c>
+      <c r="J23" s="78" t="s">
+        <v>169</v>
+      </c>
+      <c r="K23" s="7">
+        <v>100</v>
+      </c>
+      <c r="L23" s="7">
+        <v>1</v>
+      </c>
+      <c r="M23" s="11">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="N23" s="95" t="s">
+        <v>179</v>
+      </c>
+      <c r="O23" s="31"/>
+    </row>
+    <row r="24" spans="1:15" ht="15.75" thickBot="1">
+      <c r="A24" s="6">
+        <v>22</v>
+      </c>
+      <c r="B24" s="173"/>
+      <c r="C24" s="133" t="s">
+        <v>195</v>
+      </c>
+      <c r="D24" s="134" t="s">
+        <v>188</v>
+      </c>
+      <c r="E24" s="75" t="s">
+        <v>91</v>
+      </c>
+      <c r="F24" s="135" t="s">
+        <v>189</v>
+      </c>
+      <c r="G24" s="135" t="s">
+        <v>190</v>
+      </c>
+      <c r="H24" s="136" t="s">
+        <v>191</v>
+      </c>
+      <c r="I24" s="137" t="s">
+        <v>19</v>
+      </c>
+      <c r="J24" s="138" t="s">
+        <v>201</v>
+      </c>
+      <c r="K24" s="139">
+        <v>20</v>
+      </c>
+      <c r="L24" s="139">
+        <v>1</v>
+      </c>
+      <c r="M24" s="139">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="N24" s="140" t="s">
+        <v>21</v>
+      </c>
+      <c r="O24" s="31"/>
+    </row>
+    <row r="25" spans="1:15" ht="15.75" thickBot="1">
+      <c r="A25" s="6">
+        <v>23</v>
+      </c>
+      <c r="B25" s="173"/>
+      <c r="C25" s="133" t="s">
+        <v>196</v>
+      </c>
+      <c r="D25" s="134" t="s">
+        <v>192</v>
+      </c>
+      <c r="E25" s="75" t="s">
+        <v>91</v>
+      </c>
+      <c r="F25" s="135" t="s">
+        <v>193</v>
+      </c>
+      <c r="G25" s="135" t="s">
+        <v>190</v>
+      </c>
+      <c r="H25" s="136" t="s">
+        <v>194</v>
+      </c>
+      <c r="I25" s="137" t="s">
+        <v>19</v>
+      </c>
+      <c r="J25" s="138" t="s">
+        <v>202</v>
+      </c>
+      <c r="K25" s="139">
+        <v>100</v>
+      </c>
+      <c r="L25" s="139">
+        <v>1</v>
+      </c>
+      <c r="M25" s="139">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="N25" s="141" t="s">
+        <v>21</v>
+      </c>
+      <c r="O25" s="31"/>
+    </row>
+    <row r="26" spans="1:15" ht="15.75" thickBot="1">
+      <c r="A26" s="6">
+        <v>24</v>
+      </c>
+      <c r="B26" s="173"/>
+      <c r="C26" s="133" t="s">
+        <v>198</v>
+      </c>
+      <c r="D26" s="134" t="s">
+        <v>199</v>
+      </c>
+      <c r="E26" s="138" t="s">
+        <v>91</v>
+      </c>
+      <c r="F26" s="142" t="s">
+        <v>197</v>
+      </c>
+      <c r="G26" s="135" t="s">
+        <v>190</v>
+      </c>
+      <c r="H26" s="143" t="s">
+        <v>200</v>
+      </c>
+      <c r="I26" s="137" t="s">
+        <v>19</v>
+      </c>
+      <c r="J26" s="138" t="s">
+        <v>203</v>
+      </c>
+      <c r="K26" s="139">
+        <v>100</v>
+      </c>
+      <c r="L26" s="139">
+        <v>1</v>
+      </c>
+      <c r="M26" s="139">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="N26" s="141" t="s">
+        <v>21</v>
+      </c>
+      <c r="O26" s="31"/>
+    </row>
+    <row r="27" spans="1:15" ht="15.75" thickBot="1">
+      <c r="A27" s="6">
+        <v>25</v>
+      </c>
+      <c r="B27" s="173"/>
+      <c r="C27" s="133" t="s">
+        <v>205</v>
+      </c>
+      <c r="D27" s="134" t="s">
+        <v>208</v>
+      </c>
+      <c r="E27" s="138" t="s">
+        <v>91</v>
+      </c>
+      <c r="F27" s="142" t="s">
+        <v>204</v>
+      </c>
+      <c r="G27" s="142" t="s">
+        <v>115</v>
+      </c>
+      <c r="H27" s="143" t="s">
+        <v>206</v>
+      </c>
+      <c r="I27" s="137" t="s">
+        <v>19</v>
+      </c>
+      <c r="J27" s="138" t="s">
+        <v>207</v>
+      </c>
+      <c r="K27" s="139">
+        <v>50</v>
+      </c>
+      <c r="L27" s="139">
+        <v>2</v>
+      </c>
+      <c r="M27" s="139">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="N27" s="141" t="s">
+        <v>21</v>
+      </c>
+      <c r="O27" s="31"/>
+    </row>
+    <row r="28" spans="1:15" ht="15.75" thickBot="1">
+      <c r="A28" s="6">
+        <v>26</v>
+      </c>
+      <c r="B28" s="173"/>
+      <c r="C28" s="51" t="s">
+        <v>95</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="E28" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="F28" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="G28" s="39" t="s">
+        <v>60</v>
+      </c>
+      <c r="H28" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="I28" s="37" t="s">
+        <v>19</v>
+      </c>
+      <c r="J28" s="37" t="s">
+        <v>99</v>
+      </c>
+      <c r="K28" s="7">
+        <v>100</v>
+      </c>
+      <c r="L28" s="7">
+        <v>2</v>
+      </c>
+      <c r="M28" s="11">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="N28" s="96" t="s">
+        <v>21</v>
+      </c>
+      <c r="O28" s="31"/>
+    </row>
+    <row r="29" spans="1:15" ht="15.75" thickBot="1">
+      <c r="A29" s="6">
+        <v>27</v>
+      </c>
+      <c r="B29" s="173"/>
+      <c r="C29" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="E29" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="F29" s="37" t="s">
+        <v>101</v>
+      </c>
+      <c r="G29" s="39" t="s">
+        <v>60</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="I29" s="37" t="s">
+        <v>19</v>
+      </c>
+      <c r="J29" s="37" t="s">
+        <v>103</v>
+      </c>
+      <c r="K29" s="7">
+        <v>100</v>
+      </c>
+      <c r="L29" s="7">
+        <v>1</v>
+      </c>
+      <c r="M29" s="11">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="N29" s="96" t="s">
+        <v>21</v>
+      </c>
+      <c r="O29" s="31"/>
+    </row>
+    <row r="30" spans="1:15" ht="15.75" thickBot="1">
+      <c r="A30" s="6">
         <v>28</v>
       </c>
-      <c r="D8" s="35" t="s">
+      <c r="B30" s="173"/>
+      <c r="C30" s="51" t="s">
+        <v>105</v>
+      </c>
+      <c r="D30" s="37" t="s">
+        <v>106</v>
+      </c>
+      <c r="E30" s="37" t="s">
+        <v>104</v>
+      </c>
+      <c r="F30" s="40" t="s">
+        <v>107</v>
+      </c>
+      <c r="G30" s="39" t="s">
+        <v>108</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="I30" s="39" t="s">
+        <v>110</v>
+      </c>
+      <c r="J30" s="37" t="s">
+        <v>111</v>
+      </c>
+      <c r="K30" s="7">
+        <v>10</v>
+      </c>
+      <c r="L30" s="7">
+        <v>1</v>
+      </c>
+      <c r="M30" s="11">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="N30" s="96" t="s">
+        <v>21</v>
+      </c>
+      <c r="O30" s="31"/>
+    </row>
+    <row r="31" spans="1:15" ht="15.75" thickBot="1">
+      <c r="A31" s="6">
         <v>29</v>
       </c>
-      <c r="E8" s="36" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" s="38" t="s">
+      <c r="B31" s="173"/>
+      <c r="C31" s="51" t="s">
+        <v>112</v>
+      </c>
+      <c r="D31" s="37" t="s">
+        <v>113</v>
+      </c>
+      <c r="E31" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="F31" s="37" t="s">
+        <v>114</v>
+      </c>
+      <c r="G31" s="39" t="s">
+        <v>115</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="I31" s="37" t="s">
+        <v>19</v>
+      </c>
+      <c r="J31" s="37" t="s">
+        <v>117</v>
+      </c>
+      <c r="K31" s="7">
+        <v>100</v>
+      </c>
+      <c r="L31" s="7">
+        <v>1</v>
+      </c>
+      <c r="M31" s="11">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="N31" s="96" t="s">
+        <v>21</v>
+      </c>
+      <c r="O31" s="31"/>
+    </row>
+    <row r="32" spans="1:15" s="1" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A32" s="6">
         <v>30</v>
       </c>
-      <c r="G8" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="H8" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="I8" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="J8" s="36" t="s">
-        <v>34</v>
-      </c>
-      <c r="K8" s="8">
+      <c r="B32" s="174"/>
+      <c r="C32" s="52" t="s">
+        <v>118</v>
+      </c>
+      <c r="D32" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="E32" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="F32" s="45" t="s">
+        <v>120</v>
+      </c>
+      <c r="G32" s="48" t="s">
+        <v>60</v>
+      </c>
+      <c r="H32" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="I32" s="45" t="s">
+        <v>19</v>
+      </c>
+      <c r="J32" s="45" t="s">
+        <v>122</v>
+      </c>
+      <c r="K32" s="14">
+        <v>100</v>
+      </c>
+      <c r="L32" s="17">
         <v>8</v>
       </c>
-      <c r="L8" s="11">
+      <c r="M32" s="15">
         <f t="shared" si="1"/>
         <v>48</v>
       </c>
-      <c r="M8" s="83" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:29" ht="15.75" thickBot="1">
-      <c r="A9" s="6">
+      <c r="N32" s="118" t="s">
+        <v>21</v>
+      </c>
+      <c r="O32" s="33"/>
+    </row>
+    <row r="33" spans="1:15" ht="15.75" thickBot="1">
+      <c r="A33" s="6">
+        <v>31</v>
+      </c>
+      <c r="B33" s="173" t="s">
+        <v>123</v>
+      </c>
+      <c r="C33" s="124" t="s">
+        <v>185</v>
+      </c>
+      <c r="D33" s="132" t="s">
+        <v>124</v>
+      </c>
+      <c r="E33" s="117" t="s">
+        <v>182</v>
+      </c>
+      <c r="F33" s="126" t="s">
+        <v>183</v>
+      </c>
+      <c r="G33" s="127" t="s">
+        <v>184</v>
+      </c>
+      <c r="H33" s="128" t="s">
+        <v>19</v>
+      </c>
+      <c r="I33" s="125" t="s">
+        <v>19</v>
+      </c>
+      <c r="J33" s="128" t="s">
+        <v>70</v>
+      </c>
+      <c r="K33" s="129">
         <v>7</v>
       </c>
-      <c r="B9" s="177"/>
-      <c r="C9" s="150" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" s="132" t="s">
-        <v>232</v>
-      </c>
-      <c r="E9" s="131" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" s="161" t="s">
-        <v>36</v>
-      </c>
-      <c r="G9" s="148" t="s">
-        <v>37</v>
-      </c>
-      <c r="H9" s="76" t="s">
-        <v>38</v>
-      </c>
-      <c r="I9" s="131" t="s">
-        <v>39</v>
-      </c>
-      <c r="J9" s="131" t="s">
-        <v>40</v>
-      </c>
-      <c r="K9" s="76">
-        <v>3</v>
-      </c>
-      <c r="L9" s="133">
-        <f t="shared" si="1"/>
-        <v>18</v>
-      </c>
-      <c r="M9" s="162" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:29" ht="15.75" thickBot="1">
-      <c r="A10" s="6">
-        <v>8</v>
-      </c>
-      <c r="B10" s="177"/>
-      <c r="C10" s="39" t="s">
-        <v>41</v>
-      </c>
-      <c r="D10" s="35" t="s">
-        <v>42</v>
-      </c>
-      <c r="E10" s="40" t="s">
-        <v>43</v>
-      </c>
-      <c r="F10" s="35" t="s">
-        <v>44</v>
-      </c>
-      <c r="G10" s="41" t="s">
-        <v>45</v>
-      </c>
-      <c r="H10" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="I10" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J10" s="40" t="s">
-        <v>47</v>
-      </c>
-      <c r="K10" s="28">
+      <c r="L33" s="129">
         <v>1</v>
       </c>
-      <c r="L10" s="11">
+      <c r="M33" s="130">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M10" s="84" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:29" ht="15.75" thickBot="1">
-      <c r="A11" s="6">
-        <v>9</v>
-      </c>
-      <c r="B11" s="177"/>
-      <c r="C11" s="150" t="s">
-        <v>48</v>
-      </c>
-      <c r="D11" s="132" t="s">
-        <v>233</v>
-      </c>
-      <c r="E11" s="131" t="s">
-        <v>43</v>
-      </c>
-      <c r="F11" s="131" t="s">
-        <v>49</v>
-      </c>
-      <c r="G11" s="148" t="s">
-        <v>45</v>
-      </c>
-      <c r="H11" s="76" t="s">
-        <v>50</v>
-      </c>
-      <c r="I11" s="148" t="s">
-        <v>18</v>
-      </c>
-      <c r="J11" s="131" t="s">
-        <v>47</v>
-      </c>
-      <c r="K11" s="76">
-        <v>3</v>
-      </c>
-      <c r="L11" s="133">
-        <f t="shared" si="1"/>
-        <v>18</v>
-      </c>
-      <c r="M11" s="162" t="s">
-        <v>20</v>
-      </c>
-      <c r="N11" s="29"/>
-    </row>
-    <row r="12" spans="1:29" ht="15.75" thickBot="1">
-      <c r="A12" s="6">
-        <v>10</v>
-      </c>
-      <c r="B12" s="177"/>
-      <c r="C12" s="77" t="s">
-        <v>161</v>
-      </c>
-      <c r="D12" s="68" t="s">
-        <v>51</v>
-      </c>
-      <c r="E12" s="60" t="s">
-        <v>14</v>
-      </c>
-      <c r="F12" s="60" t="s">
-        <v>162</v>
-      </c>
-      <c r="G12" s="41" t="s">
-        <v>25</v>
-      </c>
-      <c r="H12" s="75" t="s">
-        <v>240</v>
-      </c>
-      <c r="I12" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J12" s="40" t="s">
-        <v>52</v>
-      </c>
-      <c r="K12" s="12">
+      <c r="N33" s="131" t="s">
+        <v>21</v>
+      </c>
+      <c r="O33" s="31"/>
+    </row>
+    <row r="34" spans="1:15" ht="15.75" thickBot="1">
+      <c r="A34" s="6">
+        <v>32</v>
+      </c>
+      <c r="B34" s="173"/>
+      <c r="C34" s="51" t="s">
+        <v>125</v>
+      </c>
+      <c r="D34" s="37" t="s">
+        <v>126</v>
+      </c>
+      <c r="E34" s="37" t="s">
+        <v>127</v>
+      </c>
+      <c r="F34" s="37" t="s">
+        <v>128</v>
+      </c>
+      <c r="G34" s="39" t="s">
+        <v>129</v>
+      </c>
+      <c r="H34" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="I34" s="37" t="s">
+        <v>19</v>
+      </c>
+      <c r="J34" s="39" t="s">
+        <v>70</v>
+      </c>
+      <c r="K34" s="13">
+        <v>6</v>
+      </c>
+      <c r="L34" s="13">
         <v>1</v>
       </c>
-      <c r="L12" s="11">
+      <c r="M34" s="11">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M12" s="85" t="s">
-        <v>20</v>
-      </c>
-      <c r="N12" s="29"/>
-    </row>
-    <row r="13" spans="1:29" ht="15.75" thickBot="1">
-      <c r="A13" s="6">
-        <v>11</v>
-      </c>
-      <c r="B13" s="177"/>
-      <c r="C13" s="39" t="s">
-        <v>163</v>
-      </c>
-      <c r="D13" s="35" t="s">
-        <v>53</v>
-      </c>
-      <c r="E13" s="40" t="s">
-        <v>23</v>
-      </c>
-      <c r="F13" s="35" t="s">
-        <v>164</v>
-      </c>
-      <c r="G13" s="41" t="s">
-        <v>16</v>
-      </c>
-      <c r="H13" s="75" t="s">
-        <v>241</v>
-      </c>
-      <c r="I13" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J13" s="40" t="s">
-        <v>54</v>
-      </c>
-      <c r="K13" s="12">
+      <c r="N34" s="96" t="s">
+        <v>21</v>
+      </c>
+      <c r="O34" s="31"/>
+    </row>
+    <row r="35" spans="1:15" ht="15.75" thickBot="1">
+      <c r="A35" s="6">
+        <v>33</v>
+      </c>
+      <c r="B35" s="173"/>
+      <c r="C35" s="119" t="s">
+        <v>170</v>
+      </c>
+      <c r="D35" s="120" t="s">
+        <v>131</v>
+      </c>
+      <c r="E35" s="120" t="s">
+        <v>171</v>
+      </c>
+      <c r="F35" s="121" t="s">
+        <v>173</v>
+      </c>
+      <c r="G35" s="106" t="s">
+        <v>172</v>
+      </c>
+      <c r="H35" s="102"/>
+      <c r="I35" s="106" t="s">
+        <v>19</v>
+      </c>
+      <c r="J35" s="107" t="s">
+        <v>132</v>
+      </c>
+      <c r="K35" s="102">
+        <v>6</v>
+      </c>
+      <c r="L35" s="102">
         <v>1</v>
       </c>
-      <c r="L13" s="11">
+      <c r="M35" s="103">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M13" s="85" t="s">
-        <v>20</v>
-      </c>
-      <c r="N13" s="30"/>
-    </row>
-    <row r="14" spans="1:29" ht="15.75" thickBot="1">
-      <c r="A14" s="6">
-        <v>12</v>
-      </c>
-      <c r="B14" s="178"/>
-      <c r="C14" s="42" t="s">
-        <v>55</v>
-      </c>
-      <c r="D14" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="E14" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="F14" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="G14" s="45" t="s">
-        <v>59</v>
-      </c>
-      <c r="H14" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="I14" s="46" t="s">
-        <v>18</v>
-      </c>
-      <c r="J14" s="44" t="s">
-        <v>61</v>
-      </c>
-      <c r="K14" s="16">
+      <c r="N35" s="122" t="s">
+        <v>88</v>
+      </c>
+      <c r="O35" s="31"/>
+    </row>
+    <row r="36" spans="1:15" ht="15.75" thickBot="1">
+      <c r="A36" s="6">
+        <v>34</v>
+      </c>
+      <c r="B36" s="172" t="s">
+        <v>133</v>
+      </c>
+      <c r="C36" s="53" t="s">
+        <v>134</v>
+      </c>
+      <c r="D36" s="54" t="s">
+        <v>135</v>
+      </c>
+      <c r="E36" s="54" t="s">
+        <v>136</v>
+      </c>
+      <c r="F36" s="54" t="s">
+        <v>136</v>
+      </c>
+      <c r="G36" s="54" t="s">
+        <v>137</v>
+      </c>
+      <c r="H36" s="54" t="s">
+        <v>19</v>
+      </c>
+      <c r="I36" s="54" t="s">
+        <v>19</v>
+      </c>
+      <c r="J36" s="54" t="s">
+        <v>70</v>
+      </c>
+      <c r="K36" s="22">
+        <v>100</v>
+      </c>
+      <c r="L36" s="22">
         <v>1</v>
       </c>
-      <c r="L14" s="15">
+      <c r="M36" s="18">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M14" s="86" t="s">
-        <v>20</v>
-      </c>
-      <c r="N14" s="29"/>
-    </row>
-    <row r="15" spans="1:29" ht="15.75" thickBot="1">
-      <c r="A15" s="6">
-        <v>13</v>
-      </c>
-      <c r="B15" s="177" t="s">
-        <v>62</v>
-      </c>
-      <c r="C15" s="78" t="s">
-        <v>63</v>
-      </c>
-      <c r="D15" s="47" t="s">
-        <v>64</v>
-      </c>
-      <c r="E15" s="79" t="s">
-        <v>65</v>
-      </c>
-      <c r="F15" s="47" t="s">
-        <v>66</v>
-      </c>
-      <c r="G15" s="79" t="s">
-        <v>67</v>
-      </c>
-      <c r="H15" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="I15" s="48" t="s">
-        <v>18</v>
-      </c>
-      <c r="J15" s="80" t="s">
-        <v>69</v>
-      </c>
-      <c r="K15" s="81">
+      <c r="N36" s="123" t="s">
+        <v>138</v>
+      </c>
+      <c r="O36" s="31"/>
+    </row>
+    <row r="37" spans="1:15" ht="15.75" thickBot="1">
+      <c r="A37" s="6">
+        <v>35</v>
+      </c>
+      <c r="B37" s="173"/>
+      <c r="C37" s="55" t="s">
+        <v>139</v>
+      </c>
+      <c r="D37" s="56" t="s">
+        <v>140</v>
+      </c>
+      <c r="E37" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="F37" s="56" t="s">
+        <v>141</v>
+      </c>
+      <c r="G37" s="56" t="s">
+        <v>142</v>
+      </c>
+      <c r="H37" s="56" t="s">
+        <v>19</v>
+      </c>
+      <c r="I37" s="56" t="s">
+        <v>19</v>
+      </c>
+      <c r="J37" s="57" t="s">
+        <v>143</v>
+      </c>
+      <c r="K37" s="30">
+        <v>12</v>
+      </c>
+      <c r="L37" s="23">
+        <v>2</v>
+      </c>
+      <c r="M37" s="11">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="N37" s="97" t="s">
+        <v>144</v>
+      </c>
+      <c r="O37" s="31"/>
+    </row>
+    <row r="38" spans="1:15" ht="15.75" thickBot="1">
+      <c r="A38" s="6">
+        <v>36</v>
+      </c>
+      <c r="B38" s="173"/>
+      <c r="C38" s="55" t="s">
+        <v>145</v>
+      </c>
+      <c r="D38" s="56" t="s">
+        <v>146</v>
+      </c>
+      <c r="E38" s="56" t="s">
+        <v>44</v>
+      </c>
+      <c r="F38" s="56" t="s">
+        <v>147</v>
+      </c>
+      <c r="G38" s="56" t="s">
+        <v>137</v>
+      </c>
+      <c r="H38" s="56" t="s">
+        <v>19</v>
+      </c>
+      <c r="I38" s="56" t="s">
+        <v>19</v>
+      </c>
+      <c r="J38" s="57" t="s">
+        <v>70</v>
+      </c>
+      <c r="K38" s="30">
+        <v>10</v>
+      </c>
+      <c r="L38" s="23">
         <v>1</v>
       </c>
-      <c r="L15" s="72">
+      <c r="M38" s="11">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M15" s="88" t="s">
+      <c r="N38" s="97" t="s">
+        <v>138</v>
+      </c>
+      <c r="O38" s="31"/>
+    </row>
+    <row r="39" spans="1:15" ht="15.75" thickBot="1">
+      <c r="A39" s="6">
+        <v>37</v>
+      </c>
+      <c r="B39" s="173"/>
+      <c r="C39" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="D39" s="37" t="s">
+        <v>149</v>
+      </c>
+      <c r="E39" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="F39" s="37" t="s">
+        <v>150</v>
+      </c>
+      <c r="G39" s="37" t="s">
+        <v>151</v>
+      </c>
+      <c r="H39" s="37" t="s">
+        <v>150</v>
+      </c>
+      <c r="I39" s="37" t="s">
+        <v>19</v>
+      </c>
+      <c r="J39" s="39" t="s">
+        <v>143</v>
+      </c>
+      <c r="K39" s="13">
         <v>20</v>
       </c>
-      <c r="N15" s="29"/>
-    </row>
-    <row r="16" spans="1:29" ht="15.75" thickBot="1">
-      <c r="A16" s="6">
-        <v>14</v>
-      </c>
-      <c r="B16" s="177"/>
-      <c r="C16" s="150" t="s">
-        <v>221</v>
-      </c>
-      <c r="D16" s="151" t="s">
-        <v>220</v>
-      </c>
-      <c r="E16" s="132" t="s">
-        <v>219</v>
-      </c>
-      <c r="F16" s="132" t="s">
-        <v>218</v>
-      </c>
-      <c r="G16" s="132" t="s">
-        <v>222</v>
-      </c>
-      <c r="H16" s="152" t="s">
-        <v>223</v>
-      </c>
-      <c r="I16" s="153" t="s">
-        <v>18</v>
-      </c>
-      <c r="J16" s="153" t="s">
-        <v>69</v>
-      </c>
-      <c r="K16" s="76">
+      <c r="L39" s="7">
         <v>1</v>
       </c>
-      <c r="L16" s="133">
+      <c r="M39" s="11">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M16" s="135" t="s">
-        <v>20</v>
-      </c>
-      <c r="N16" s="29"/>
-    </row>
-    <row r="17" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A17" s="6">
+      <c r="N39" s="98" t="s">
+        <v>21</v>
+      </c>
+      <c r="O39" s="31"/>
+    </row>
+    <row r="40" spans="1:15" ht="15.75" thickBot="1">
+      <c r="A40" s="6">
+        <v>38</v>
+      </c>
+      <c r="B40" s="173"/>
+      <c r="C40" s="51" t="s">
+        <v>152</v>
+      </c>
+      <c r="D40" s="37" t="s">
+        <v>153</v>
+      </c>
+      <c r="E40" s="37" t="s">
+        <v>154</v>
+      </c>
+      <c r="F40" s="37" t="s">
+        <v>155</v>
+      </c>
+      <c r="G40" s="37" t="s">
+        <v>156</v>
+      </c>
+      <c r="H40" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="I40" s="37" t="s">
+        <v>19</v>
+      </c>
+      <c r="J40" s="39" t="s">
+        <v>70</v>
+      </c>
+      <c r="K40" s="13">
         <v>15</v>
       </c>
-      <c r="B17" s="177"/>
-      <c r="C17" s="145" t="s">
-        <v>237</v>
-      </c>
-      <c r="D17" s="151" t="s">
-        <v>236</v>
-      </c>
-      <c r="E17" s="132" t="s">
-        <v>235</v>
-      </c>
-      <c r="F17" s="132" t="s">
-        <v>234</v>
-      </c>
-      <c r="G17" s="132" t="s">
-        <v>238</v>
-      </c>
-      <c r="H17" s="152" t="s">
-        <v>239</v>
-      </c>
-      <c r="I17" s="153" t="s">
-        <v>18</v>
-      </c>
-      <c r="J17" s="153" t="s">
-        <v>69</v>
-      </c>
-      <c r="K17" s="76">
-        <v>1</v>
-      </c>
-      <c r="L17" s="133">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="M17" s="135" t="s">
-        <v>20</v>
-      </c>
-      <c r="N17" s="29"/>
-    </row>
-    <row r="18" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A18" s="6">
-        <v>16</v>
-      </c>
-      <c r="B18" s="177"/>
-      <c r="C18" s="74" t="s">
-        <v>70</v>
-      </c>
-      <c r="D18" s="100" t="s">
-        <v>71</v>
-      </c>
-      <c r="E18" s="104" t="s">
-        <v>72</v>
-      </c>
-      <c r="F18" s="100" t="s">
-        <v>73</v>
-      </c>
-      <c r="G18" s="104" t="s">
-        <v>74</v>
-      </c>
-      <c r="H18" s="101" t="s">
-        <v>75</v>
-      </c>
-      <c r="I18" s="101" t="s">
-        <v>18</v>
-      </c>
-      <c r="J18" s="105" t="s">
-        <v>69</v>
-      </c>
-      <c r="K18" s="106">
-        <v>1</v>
-      </c>
-      <c r="L18" s="97">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="M18" s="107" t="s">
-        <v>20</v>
-      </c>
-      <c r="N18" s="29"/>
-    </row>
-    <row r="19" spans="1:14" ht="16.5" thickBot="1">
-      <c r="A19" s="6">
-        <v>17</v>
-      </c>
-      <c r="B19" s="166" t="s">
-        <v>76</v>
-      </c>
-      <c r="C19" s="108" t="s">
-        <v>77</v>
-      </c>
-      <c r="D19" s="109" t="s">
-        <v>78</v>
-      </c>
-      <c r="E19" s="109" t="s">
-        <v>79</v>
-      </c>
-      <c r="F19" s="109" t="s">
-        <v>80</v>
-      </c>
-      <c r="G19" s="110" t="s">
-        <v>81</v>
-      </c>
-      <c r="H19" s="110" t="s">
-        <v>18</v>
-      </c>
-      <c r="I19" s="109" t="s">
-        <v>18</v>
-      </c>
-      <c r="J19" s="110" t="s">
-        <v>69</v>
-      </c>
-      <c r="K19" s="102">
-        <v>1</v>
-      </c>
-      <c r="L19" s="65">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="M19" s="103" t="s">
-        <v>20</v>
-      </c>
-      <c r="N19" s="29"/>
-    </row>
-    <row r="20" spans="1:14" ht="30.75" thickBot="1">
-      <c r="A20" s="6">
-        <v>18</v>
-      </c>
-      <c r="B20" s="166" t="s">
-        <v>224</v>
-      </c>
-      <c r="C20" s="154" t="s">
-        <v>226</v>
-      </c>
-      <c r="D20" s="155" t="s">
-        <v>225</v>
-      </c>
-      <c r="E20" s="156" t="s">
-        <v>227</v>
-      </c>
-      <c r="F20" s="156" t="s">
-        <v>228</v>
-      </c>
-      <c r="G20" s="157" t="s">
-        <v>229</v>
-      </c>
-      <c r="H20" s="157" t="s">
-        <v>230</v>
-      </c>
-      <c r="I20" s="156" t="s">
-        <v>231</v>
-      </c>
-      <c r="J20" s="157" t="s">
-        <v>69</v>
-      </c>
-      <c r="K20" s="158">
-        <v>1</v>
-      </c>
-      <c r="L20" s="159">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="M20" s="160" t="s">
-        <v>20</v>
-      </c>
-      <c r="N20" s="29"/>
-    </row>
-    <row r="21" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A21" s="6">
-        <v>19</v>
-      </c>
-      <c r="B21" s="176" t="s">
-        <v>82</v>
-      </c>
-      <c r="C21" s="98" t="s">
-        <v>173</v>
-      </c>
-      <c r="D21" s="61" t="s">
-        <v>174</v>
-      </c>
-      <c r="E21" s="61" t="s">
-        <v>175</v>
-      </c>
-      <c r="F21" s="61" t="s">
-        <v>175</v>
-      </c>
-      <c r="G21" s="33" t="s">
-        <v>176</v>
-      </c>
-      <c r="H21" s="33" t="s">
-        <v>177</v>
-      </c>
-      <c r="I21" s="32" t="s">
-        <v>18</v>
-      </c>
-      <c r="J21" s="33" t="s">
-        <v>69</v>
-      </c>
-      <c r="K21" s="19">
-        <v>1</v>
-      </c>
-      <c r="L21" s="18">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="M21" s="99" t="s">
-        <v>20</v>
-      </c>
-      <c r="N21" s="29"/>
-    </row>
-    <row r="22" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A22" s="6">
-        <v>20</v>
-      </c>
-      <c r="B22" s="178"/>
-      <c r="C22" s="62" t="s">
-        <v>83</v>
-      </c>
-      <c r="D22" s="63" t="s">
-        <v>84</v>
-      </c>
-      <c r="E22" s="63" t="s">
-        <v>43</v>
-      </c>
-      <c r="F22" s="63" t="s">
-        <v>85</v>
-      </c>
-      <c r="G22" s="63" t="s">
-        <v>86</v>
-      </c>
-      <c r="H22" s="64"/>
-      <c r="I22" s="64"/>
-      <c r="J22" s="63" t="s">
-        <v>69</v>
-      </c>
-      <c r="K22" s="64">
-        <v>1</v>
-      </c>
-      <c r="L22" s="15">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="M22" s="66" t="s">
-        <v>87</v>
-      </c>
-      <c r="N22" s="29"/>
-    </row>
-    <row r="23" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A23" s="6">
-        <v>21</v>
-      </c>
-      <c r="B23" s="176" t="s">
-        <v>88</v>
-      </c>
-      <c r="C23" s="138" t="s">
-        <v>89</v>
-      </c>
-      <c r="D23" s="163" t="s">
-        <v>186</v>
-      </c>
-      <c r="E23" s="140" t="s">
-        <v>90</v>
-      </c>
-      <c r="F23" s="140" t="s">
-        <v>91</v>
-      </c>
-      <c r="G23" s="142" t="s">
-        <v>59</v>
-      </c>
-      <c r="H23" s="164" t="s">
-        <v>92</v>
-      </c>
-      <c r="I23" s="140" t="s">
-        <v>18</v>
-      </c>
-      <c r="J23" s="140" t="s">
-        <v>93</v>
-      </c>
-      <c r="K23" s="143">
-        <v>3</v>
-      </c>
-      <c r="L23" s="143">
-        <f t="shared" si="1"/>
-        <v>18</v>
-      </c>
-      <c r="M23" s="165" t="s">
-        <v>20</v>
-      </c>
-      <c r="N23" s="29"/>
-    </row>
-    <row r="24" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A24" s="6">
-        <v>22</v>
-      </c>
-      <c r="B24" s="177"/>
-      <c r="C24" s="71" t="s">
-        <v>165</v>
-      </c>
-      <c r="D24" s="60" t="s">
-        <v>166</v>
-      </c>
-      <c r="E24" s="60" t="s">
-        <v>90</v>
-      </c>
-      <c r="F24" s="60" t="s">
-        <v>167</v>
-      </c>
-      <c r="G24" s="37" t="s">
-        <v>155</v>
-      </c>
-      <c r="H24" s="75" t="s">
-        <v>242</v>
-      </c>
-      <c r="I24" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J24" s="73" t="s">
-        <v>168</v>
-      </c>
-      <c r="K24" s="7">
-        <v>1</v>
-      </c>
-      <c r="L24" s="11">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="M24" s="89" t="s">
-        <v>178</v>
-      </c>
-      <c r="N24" s="29"/>
-    </row>
-    <row r="25" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A25" s="6">
-        <v>23</v>
-      </c>
-      <c r="B25" s="177"/>
-      <c r="C25" s="127" t="s">
-        <v>194</v>
-      </c>
-      <c r="D25" s="128" t="s">
-        <v>187</v>
-      </c>
-      <c r="E25" s="70" t="s">
-        <v>90</v>
-      </c>
-      <c r="F25" s="129" t="s">
-        <v>188</v>
-      </c>
-      <c r="G25" s="129" t="s">
-        <v>189</v>
-      </c>
-      <c r="H25" s="130" t="s">
-        <v>190</v>
-      </c>
-      <c r="I25" s="131" t="s">
-        <v>18</v>
-      </c>
-      <c r="J25" s="132" t="s">
-        <v>200</v>
-      </c>
-      <c r="K25" s="133">
-        <v>1</v>
-      </c>
-      <c r="L25" s="133">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="M25" s="134" t="s">
-        <v>20</v>
-      </c>
-      <c r="N25" s="29"/>
-    </row>
-    <row r="26" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A26" s="6">
-        <v>24</v>
-      </c>
-      <c r="B26" s="177"/>
-      <c r="C26" s="127" t="s">
-        <v>195</v>
-      </c>
-      <c r="D26" s="128" t="s">
-        <v>191</v>
-      </c>
-      <c r="E26" s="70" t="s">
-        <v>90</v>
-      </c>
-      <c r="F26" s="129" t="s">
-        <v>192</v>
-      </c>
-      <c r="G26" s="129" t="s">
-        <v>189</v>
-      </c>
-      <c r="H26" s="130" t="s">
-        <v>193</v>
-      </c>
-      <c r="I26" s="131" t="s">
-        <v>18</v>
-      </c>
-      <c r="J26" s="132" t="s">
-        <v>201</v>
-      </c>
-      <c r="K26" s="133">
-        <v>1</v>
-      </c>
-      <c r="L26" s="133">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="M26" s="135" t="s">
-        <v>20</v>
-      </c>
-      <c r="N26" s="29"/>
-    </row>
-    <row r="27" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A27" s="6">
-        <v>25</v>
-      </c>
-      <c r="B27" s="177"/>
-      <c r="C27" s="127" t="s">
-        <v>197</v>
-      </c>
-      <c r="D27" s="128" t="s">
-        <v>198</v>
-      </c>
-      <c r="E27" s="132" t="s">
-        <v>90</v>
-      </c>
-      <c r="F27" s="136" t="s">
-        <v>196</v>
-      </c>
-      <c r="G27" s="129" t="s">
-        <v>189</v>
-      </c>
-      <c r="H27" s="137" t="s">
-        <v>199</v>
-      </c>
-      <c r="I27" s="131" t="s">
-        <v>18</v>
-      </c>
-      <c r="J27" s="132" t="s">
-        <v>202</v>
-      </c>
-      <c r="K27" s="133">
-        <v>1</v>
-      </c>
-      <c r="L27" s="133">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="M27" s="135" t="s">
-        <v>20</v>
-      </c>
-      <c r="N27" s="29"/>
-    </row>
-    <row r="28" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A28" s="6">
-        <v>26</v>
-      </c>
-      <c r="B28" s="177"/>
-      <c r="C28" s="171" t="s">
-        <v>253</v>
-      </c>
-      <c r="D28" s="128" t="s">
-        <v>206</v>
-      </c>
-      <c r="E28" s="132" t="s">
-        <v>90</v>
-      </c>
-      <c r="F28" s="136" t="s">
-        <v>203</v>
-      </c>
-      <c r="G28" s="136" t="s">
-        <v>114</v>
-      </c>
-      <c r="H28" s="137" t="s">
-        <v>204</v>
-      </c>
-      <c r="I28" s="131" t="s">
-        <v>18</v>
-      </c>
-      <c r="J28" s="132" t="s">
-        <v>205</v>
-      </c>
-      <c r="K28" s="133">
+      <c r="L40" s="13">
         <v>2</v>
       </c>
-      <c r="L28" s="133">
+      <c r="M40" s="11">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="M28" s="135" t="s">
-        <v>20</v>
-      </c>
-      <c r="N28" s="29"/>
-    </row>
-    <row r="29" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A29" s="6">
-        <v>27</v>
-      </c>
-      <c r="B29" s="177"/>
-      <c r="C29" s="171" t="s">
-        <v>252</v>
-      </c>
-      <c r="D29" s="128" t="s">
-        <v>254</v>
-      </c>
-      <c r="E29" s="132" t="s">
-        <v>90</v>
-      </c>
-      <c r="F29" s="169" t="s">
-        <v>249</v>
-      </c>
-      <c r="G29" s="169" t="s">
-        <v>189</v>
-      </c>
-      <c r="H29" s="170" t="s">
-        <v>250</v>
-      </c>
-      <c r="I29" s="131" t="s">
-        <v>18</v>
-      </c>
-      <c r="J29" s="167" t="s">
-        <v>251</v>
-      </c>
-      <c r="K29" s="133">
-        <v>2</v>
-      </c>
-      <c r="L29" s="133">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="M29" s="135" t="s">
-        <v>20</v>
-      </c>
-      <c r="N29" s="29"/>
-    </row>
-    <row r="30" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A30" s="6">
-        <v>28</v>
-      </c>
-      <c r="B30" s="177"/>
-      <c r="C30" s="49" t="s">
-        <v>94</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="E30" s="35" t="s">
-        <v>90</v>
-      </c>
-      <c r="F30" s="35" t="s">
-        <v>96</v>
-      </c>
-      <c r="G30" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="I30" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J30" s="35" t="s">
-        <v>98</v>
-      </c>
-      <c r="K30" s="7">
-        <v>2</v>
-      </c>
-      <c r="L30" s="11">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="M30" s="90" t="s">
-        <v>20</v>
-      </c>
-      <c r="N30" s="29"/>
-    </row>
-    <row r="31" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A31" s="6">
-        <v>29</v>
-      </c>
-      <c r="B31" s="177"/>
-      <c r="C31" s="49" t="s">
-        <v>99</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="E31" s="35" t="s">
-        <v>90</v>
-      </c>
-      <c r="F31" s="35" t="s">
-        <v>100</v>
-      </c>
-      <c r="G31" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="I31" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J31" s="35" t="s">
-        <v>102</v>
-      </c>
-      <c r="K31" s="7">
-        <v>1</v>
-      </c>
-      <c r="L31" s="11">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="M31" s="90" t="s">
-        <v>20</v>
-      </c>
-      <c r="N31" s="29"/>
-    </row>
-    <row r="32" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A32" s="6">
-        <v>30</v>
-      </c>
-      <c r="B32" s="177"/>
-      <c r="C32" s="49" t="s">
-        <v>104</v>
-      </c>
-      <c r="D32" s="35" t="s">
-        <v>105</v>
-      </c>
-      <c r="E32" s="35" t="s">
-        <v>103</v>
-      </c>
-      <c r="F32" s="38" t="s">
-        <v>106</v>
-      </c>
-      <c r="G32" s="37" t="s">
-        <v>107</v>
-      </c>
-      <c r="H32" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="I32" s="37" t="s">
-        <v>109</v>
-      </c>
-      <c r="J32" s="35" t="s">
-        <v>110</v>
-      </c>
-      <c r="K32" s="7">
-        <v>1</v>
-      </c>
-      <c r="L32" s="11">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="M32" s="90" t="s">
-        <v>20</v>
-      </c>
-      <c r="N32" s="29"/>
-    </row>
-    <row r="33" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A33" s="6">
-        <v>31</v>
-      </c>
-      <c r="B33" s="177"/>
-      <c r="C33" s="49" t="s">
-        <v>111</v>
-      </c>
-      <c r="D33" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="E33" s="35" t="s">
-        <v>23</v>
-      </c>
-      <c r="F33" s="35" t="s">
-        <v>113</v>
-      </c>
-      <c r="G33" s="37" t="s">
-        <v>114</v>
-      </c>
-      <c r="H33" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="I33" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J33" s="35" t="s">
-        <v>116</v>
-      </c>
-      <c r="K33" s="7">
-        <v>1</v>
-      </c>
-      <c r="L33" s="11">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="M33" s="90" t="s">
-        <v>20</v>
-      </c>
-      <c r="N33" s="29"/>
-    </row>
-    <row r="34" spans="1:14" s="1" customFormat="1" ht="15.75" thickBot="1">
-      <c r="A34" s="6">
-        <v>32</v>
-      </c>
-      <c r="B34" s="178"/>
-      <c r="C34" s="50" t="s">
-        <v>117</v>
-      </c>
-      <c r="D34" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="E34" s="43" t="s">
-        <v>90</v>
-      </c>
-      <c r="F34" s="43" t="s">
-        <v>119</v>
-      </c>
-      <c r="G34" s="46" t="s">
-        <v>59</v>
-      </c>
-      <c r="H34" s="17" t="s">
-        <v>120</v>
-      </c>
-      <c r="I34" s="43" t="s">
-        <v>18</v>
-      </c>
-      <c r="J34" s="43" t="s">
-        <v>121</v>
-      </c>
-      <c r="K34" s="17">
-        <v>8</v>
-      </c>
-      <c r="L34" s="15">
-        <f t="shared" si="1"/>
-        <v>48</v>
-      </c>
-      <c r="M34" s="112" t="s">
-        <v>20</v>
-      </c>
-      <c r="N34" s="31"/>
-    </row>
-    <row r="35" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A35" s="6">
-        <v>33</v>
-      </c>
-      <c r="B35" s="177" t="s">
-        <v>122</v>
-      </c>
-      <c r="C35" s="118" t="s">
-        <v>184</v>
-      </c>
-      <c r="D35" s="126" t="s">
-        <v>123</v>
-      </c>
-      <c r="E35" s="111" t="s">
-        <v>181</v>
-      </c>
-      <c r="F35" s="120" t="s">
-        <v>182</v>
-      </c>
-      <c r="G35" s="121" t="s">
-        <v>183</v>
-      </c>
-      <c r="H35" s="122" t="s">
-        <v>18</v>
-      </c>
-      <c r="I35" s="119" t="s">
-        <v>18</v>
-      </c>
-      <c r="J35" s="122" t="s">
-        <v>69</v>
-      </c>
-      <c r="K35" s="123">
-        <v>1</v>
-      </c>
-      <c r="L35" s="124">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="M35" s="125" t="s">
-        <v>20</v>
-      </c>
-      <c r="N35" s="29"/>
-    </row>
-    <row r="36" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A36" s="6">
-        <v>34</v>
-      </c>
-      <c r="B36" s="177"/>
-      <c r="C36" s="49" t="s">
-        <v>124</v>
-      </c>
-      <c r="D36" s="35" t="s">
-        <v>125</v>
-      </c>
-      <c r="E36" s="35" t="s">
-        <v>126</v>
-      </c>
-      <c r="F36" s="35" t="s">
-        <v>127</v>
-      </c>
-      <c r="G36" s="37" t="s">
-        <v>128</v>
-      </c>
-      <c r="H36" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="I36" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J36" s="37" t="s">
-        <v>69</v>
-      </c>
-      <c r="K36" s="13">
-        <v>1</v>
-      </c>
-      <c r="L36" s="11">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="M36" s="90" t="s">
-        <v>20</v>
-      </c>
-      <c r="N36" s="29"/>
-    </row>
-    <row r="37" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A37" s="6">
-        <v>35</v>
-      </c>
-      <c r="B37" s="177"/>
-      <c r="C37" s="113" t="s">
-        <v>169</v>
-      </c>
-      <c r="D37" s="114" t="s">
-        <v>130</v>
-      </c>
-      <c r="E37" s="114" t="s">
-        <v>170</v>
-      </c>
-      <c r="F37" s="115" t="s">
-        <v>172</v>
-      </c>
-      <c r="G37" s="100" t="s">
-        <v>171</v>
-      </c>
-      <c r="H37" s="96"/>
-      <c r="I37" s="100" t="s">
-        <v>18</v>
-      </c>
-      <c r="J37" s="101" t="s">
-        <v>131</v>
-      </c>
-      <c r="K37" s="96">
-        <v>1</v>
-      </c>
-      <c r="L37" s="97">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="M37" s="116" t="s">
-        <v>87</v>
-      </c>
-      <c r="N37" s="29"/>
-    </row>
-    <row r="38" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A38" s="6">
-        <v>36</v>
-      </c>
-      <c r="B38" s="176" t="s">
-        <v>132</v>
-      </c>
-      <c r="C38" s="51" t="s">
-        <v>133</v>
-      </c>
-      <c r="D38" s="52" t="s">
-        <v>134</v>
-      </c>
-      <c r="E38" s="52" t="s">
-        <v>255</v>
-      </c>
-      <c r="F38" s="52" t="s">
-        <v>135</v>
-      </c>
-      <c r="G38" s="52" t="s">
-        <v>136</v>
-      </c>
-      <c r="H38" s="52" t="s">
-        <v>18</v>
-      </c>
-      <c r="I38" s="52" t="s">
-        <v>18</v>
-      </c>
-      <c r="J38" s="52" t="s">
-        <v>69</v>
-      </c>
-      <c r="K38" s="22">
-        <v>1</v>
-      </c>
-      <c r="L38" s="18">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="M38" s="117" t="s">
-        <v>137</v>
-      </c>
-      <c r="N38" s="29"/>
-    </row>
-    <row r="39" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A39" s="6">
-        <v>37</v>
-      </c>
-      <c r="B39" s="177"/>
-      <c r="C39" s="53" t="s">
-        <v>138</v>
-      </c>
-      <c r="D39" s="54" t="s">
-        <v>139</v>
-      </c>
-      <c r="E39" s="54" t="s">
-        <v>43</v>
-      </c>
-      <c r="F39" s="54" t="s">
-        <v>140</v>
-      </c>
-      <c r="G39" s="54" t="s">
-        <v>141</v>
-      </c>
-      <c r="H39" s="54" t="s">
-        <v>18</v>
-      </c>
-      <c r="I39" s="54" t="s">
-        <v>18</v>
-      </c>
-      <c r="J39" s="55" t="s">
-        <v>142</v>
-      </c>
-      <c r="K39" s="23">
-        <v>2</v>
-      </c>
-      <c r="L39" s="11">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="M39" s="91" t="s">
-        <v>143</v>
-      </c>
-      <c r="N39" s="29"/>
-    </row>
-    <row r="40" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A40" s="6">
-        <v>38</v>
-      </c>
-      <c r="B40" s="177"/>
-      <c r="C40" s="53" t="s">
-        <v>144</v>
-      </c>
-      <c r="D40" s="54" t="s">
-        <v>145</v>
-      </c>
-      <c r="E40" s="54" t="s">
-        <v>43</v>
-      </c>
-      <c r="F40" s="54" t="s">
-        <v>146</v>
-      </c>
-      <c r="G40" s="54" t="s">
-        <v>136</v>
-      </c>
-      <c r="H40" s="54" t="s">
-        <v>18</v>
-      </c>
-      <c r="I40" s="54" t="s">
-        <v>18</v>
-      </c>
-      <c r="J40" s="55" t="s">
-        <v>69</v>
-      </c>
-      <c r="K40" s="23">
-        <v>1</v>
-      </c>
-      <c r="L40" s="11">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="M40" s="91" t="s">
-        <v>137</v>
-      </c>
-      <c r="N40" s="29"/>
-    </row>
-    <row r="41" spans="1:14" ht="15.75" thickBot="1">
+      <c r="N40" s="99" t="s">
+        <v>21</v>
+      </c>
+      <c r="O40" s="31"/>
+    </row>
+    <row r="41" spans="1:15" ht="15.75" thickBot="1">
       <c r="A41" s="6">
         <v>39</v>
       </c>
-      <c r="B41" s="177"/>
-      <c r="C41" s="21" t="s">
-        <v>147</v>
-      </c>
-      <c r="D41" s="35" t="s">
-        <v>148</v>
-      </c>
-      <c r="E41" s="35" t="s">
-        <v>43</v>
-      </c>
-      <c r="F41" s="35" t="s">
-        <v>149</v>
-      </c>
-      <c r="G41" s="35" t="s">
-        <v>150</v>
-      </c>
-      <c r="H41" s="35" t="s">
-        <v>149</v>
-      </c>
-      <c r="I41" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J41" s="37" t="s">
-        <v>142</v>
-      </c>
-      <c r="K41" s="7">
-        <v>1</v>
-      </c>
-      <c r="L41" s="11">
-        <f t="shared" si="1"/>
-        <v>6</v>
-      </c>
-      <c r="M41" s="92" t="s">
-        <v>20</v>
-      </c>
-      <c r="N41" s="29"/>
-    </row>
-    <row r="42" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A42" s="6">
-        <v>40</v>
-      </c>
-      <c r="B42" s="177"/>
-      <c r="C42" s="49" t="s">
-        <v>151</v>
-      </c>
-      <c r="D42" s="35" t="s">
-        <v>152</v>
-      </c>
-      <c r="E42" s="35" t="s">
-        <v>153</v>
-      </c>
-      <c r="F42" s="35" t="s">
-        <v>154</v>
-      </c>
-      <c r="G42" s="35" t="s">
-        <v>155</v>
-      </c>
-      <c r="H42" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="I42" s="35" t="s">
-        <v>18</v>
-      </c>
-      <c r="J42" s="37" t="s">
-        <v>69</v>
-      </c>
-      <c r="K42" s="13">
-        <v>2</v>
-      </c>
-      <c r="L42" s="11">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="M42" s="93" t="s">
-        <v>20</v>
-      </c>
-      <c r="N42" s="29"/>
-    </row>
-    <row r="43" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A43" s="6">
-        <v>41</v>
-      </c>
-      <c r="B43" s="177"/>
-      <c r="C43" s="56" t="s">
-        <v>157</v>
-      </c>
-      <c r="D43" s="24"/>
-      <c r="E43" s="57" t="s">
+      <c r="B41" s="173"/>
+      <c r="C41" s="58" t="s">
         <v>158</v>
       </c>
-      <c r="F43" s="24" t="s">
-        <v>158</v>
-      </c>
-      <c r="G43" s="24"/>
-      <c r="H43" s="24"/>
-      <c r="I43" s="24"/>
-      <c r="J43" s="24"/>
-      <c r="K43" s="24">
+      <c r="D41" s="24"/>
+      <c r="E41" s="59" t="s">
+        <v>159</v>
+      </c>
+      <c r="F41" s="24" t="s">
+        <v>159</v>
+      </c>
+      <c r="G41" s="24"/>
+      <c r="H41" s="24"/>
+      <c r="I41" s="24"/>
+      <c r="J41" s="24"/>
+      <c r="K41" s="24"/>
+      <c r="L41" s="24">
         <v>5</v>
       </c>
-      <c r="L43" s="11">
+      <c r="M41" s="11">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
-      <c r="M43" s="94" t="s">
-        <v>18</v>
-      </c>
-      <c r="N43" s="29"/>
-    </row>
-    <row r="44" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A44" s="6">
-        <v>42</v>
-      </c>
-      <c r="B44" s="178"/>
-      <c r="C44" s="58" t="s">
-        <v>159</v>
-      </c>
-      <c r="D44" s="25"/>
-      <c r="E44" s="59" t="s">
+      <c r="N41" s="100" t="s">
+        <v>19</v>
+      </c>
+      <c r="O41" s="31"/>
+    </row>
+    <row r="42" spans="1:15" ht="15.75" thickBot="1">
+      <c r="A42" s="25">
+        <v>40</v>
+      </c>
+      <c r="B42" s="174"/>
+      <c r="C42" s="60" t="s">
         <v>160</v>
       </c>
-      <c r="F44" s="25" t="s">
-        <v>160</v>
-      </c>
-      <c r="G44" s="25"/>
-      <c r="H44" s="25"/>
-      <c r="I44" s="25"/>
-      <c r="J44" s="25"/>
-      <c r="K44" s="25">
+      <c r="D42" s="26"/>
+      <c r="E42" s="61" t="s">
+        <v>161</v>
+      </c>
+      <c r="F42" s="26" t="s">
+        <v>161</v>
+      </c>
+      <c r="G42" s="26"/>
+      <c r="H42" s="26"/>
+      <c r="I42" s="26"/>
+      <c r="J42" s="26"/>
+      <c r="K42" s="26"/>
+      <c r="L42" s="26">
         <v>5</v>
       </c>
-      <c r="L44" s="15">
+      <c r="M42" s="15">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
-      <c r="M44" s="95" t="s">
-        <v>18</v>
-      </c>
-      <c r="N44" s="29"/>
-    </row>
-    <row r="45" spans="1:14" ht="16.5" thickBot="1">
+      <c r="N42" s="101" t="s">
+        <v>19</v>
+      </c>
+      <c r="O42" s="31"/>
+    </row>
+    <row r="43" spans="1:15" ht="16.5" thickBot="1">
+      <c r="A43"/>
+      <c r="C43" s="27"/>
+      <c r="D43" s="27"/>
+      <c r="E43" s="27"/>
+      <c r="F43" s="27"/>
+      <c r="G43" s="27"/>
+      <c r="H43" s="27"/>
+      <c r="I43" s="27"/>
+      <c r="J43" s="27"/>
+      <c r="K43" s="27"/>
+      <c r="L43" s="74"/>
+      <c r="M43" s="74"/>
+      <c r="N43" s="74"/>
+      <c r="O43" s="31"/>
+    </row>
+    <row r="44" spans="1:15">
+      <c r="A44"/>
+      <c r="C44" s="27"/>
+      <c r="D44" s="27"/>
+      <c r="E44" s="27"/>
+      <c r="F44" s="27"/>
+      <c r="G44" s="27"/>
+      <c r="H44" s="27"/>
+      <c r="I44" s="27"/>
+      <c r="J44" s="27"/>
+      <c r="K44" s="27"/>
+      <c r="O44" s="31"/>
+    </row>
+    <row r="45" spans="1:15">
       <c r="A45"/>
-      <c r="C45" s="26"/>
-      <c r="D45" s="26"/>
-      <c r="E45" s="26"/>
-      <c r="F45" s="26"/>
-      <c r="G45" s="26"/>
-      <c r="H45" s="26"/>
-      <c r="I45" s="26"/>
-      <c r="J45" s="26"/>
-      <c r="K45" s="175"/>
-      <c r="L45" s="175"/>
-      <c r="M45" s="175"/>
-      <c r="N45" s="29"/>
-    </row>
-    <row r="46" spans="1:14">
+      <c r="O45" s="31"/>
+    </row>
+    <row r="46" spans="1:15">
       <c r="A46"/>
-      <c r="C46" s="26"/>
-      <c r="D46" s="26"/>
-      <c r="E46" s="26"/>
-      <c r="F46" s="26"/>
-      <c r="G46" s="26"/>
-      <c r="H46" s="26"/>
-      <c r="I46" s="26"/>
-      <c r="J46" s="26"/>
-      <c r="N46" s="29"/>
-    </row>
-    <row r="47" spans="1:14">
+      <c r="O46" s="31"/>
+    </row>
+    <row r="47" spans="1:15">
       <c r="A47"/>
-      <c r="N47" s="29"/>
-    </row>
-    <row r="48" spans="1:14">
+      <c r="O47" s="31"/>
+    </row>
+    <row r="48" spans="1:15">
       <c r="A48"/>
-      <c r="N48" s="29"/>
-    </row>
-    <row r="49" spans="1:14">
+      <c r="O48" s="31"/>
+    </row>
+    <row r="49" spans="1:15">
       <c r="A49"/>
-      <c r="N49" s="29"/>
-    </row>
-    <row r="50" spans="1:14">
+      <c r="O49" s="31"/>
+    </row>
+    <row r="50" spans="1:15">
       <c r="A50"/>
-      <c r="N50" s="29"/>
-    </row>
-    <row r="51" spans="1:14">
+      <c r="O50" s="31"/>
+    </row>
+    <row r="51" spans="1:15">
       <c r="A51"/>
-      <c r="N51" s="29"/>
-    </row>
-    <row r="52" spans="1:14">
+      <c r="O51" s="31"/>
+    </row>
+    <row r="52" spans="1:15" ht="15.75" customHeight="1">
       <c r="A52"/>
-      <c r="N52" s="29"/>
-    </row>
-    <row r="53" spans="1:14">
+      <c r="N52" s="71"/>
+      <c r="O52" s="31"/>
+    </row>
+    <row r="53" spans="1:15">
       <c r="A53"/>
-      <c r="N53" s="29"/>
-    </row>
-    <row r="54" spans="1:14" ht="15.75" customHeight="1">
+      <c r="O53" s="31"/>
+    </row>
+    <row r="54" spans="1:15">
       <c r="A54"/>
-      <c r="M54" s="69"/>
-      <c r="N54" s="29"/>
-    </row>
-    <row r="55" spans="1:14">
+      <c r="O54" s="31"/>
+    </row>
+    <row r="55" spans="1:15">
       <c r="A55"/>
-      <c r="N55" s="29"/>
-    </row>
-    <row r="56" spans="1:14">
+      <c r="O55" s="31"/>
+    </row>
+    <row r="56" spans="1:15">
       <c r="A56"/>
-      <c r="N56" s="29"/>
-    </row>
-    <row r="57" spans="1:14">
+      <c r="O56" s="31"/>
+    </row>
+    <row r="57" spans="1:15">
       <c r="A57"/>
-      <c r="N57" s="29"/>
-    </row>
-    <row r="58" spans="1:14">
-      <c r="A58"/>
-      <c r="N58" s="29"/>
-    </row>
-    <row r="59" spans="1:14">
-      <c r="A59"/>
-      <c r="N59" s="29"/>
-    </row>
-    <row r="60" spans="1:14">
-      <c r="H60" s="27"/>
-    </row>
-    <row r="61" spans="1:14">
-      <c r="H61" s="27"/>
+      <c r="O57" s="31"/>
+    </row>
+    <row r="58" spans="1:15">
+      <c r="H58" s="28"/>
+    </row>
+    <row r="59" spans="1:15">
+      <c r="H59" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="K45:M45"/>
-    <mergeCell ref="B3:B14"/>
-    <mergeCell ref="B15:B18"/>
-    <mergeCell ref="B23:B34"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="B38:B44"/>
-    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="L43:N43"/>
+    <mergeCell ref="B3:B13"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="B22:B32"/>
+    <mergeCell ref="B33:B35"/>
+    <mergeCell ref="B36:B42"/>
+    <mergeCell ref="B20:B21"/>
   </mergeCells>
-  <phoneticPr fontId="21" type="noConversion"/>
-  <conditionalFormatting sqref="M22">
+  <phoneticPr fontId="20" type="noConversion"/>
+  <conditionalFormatting sqref="N21">
     <cfRule type="dataBar" priority="38">
       <dataBar>
         <cfvo type="min"/>
@@ -4173,7 +4168,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K38:L38">
+  <conditionalFormatting sqref="L36:M36">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -4185,7 +4180,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K43">
+  <conditionalFormatting sqref="L41">
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
@@ -4207,7 +4202,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K44">
+  <conditionalFormatting sqref="L42">
     <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
@@ -4229,7 +4224,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M3:M7">
+  <conditionalFormatting sqref="N3:N6">
     <cfRule type="dataBar" priority="40">
       <dataBar>
         <cfvo type="min"/>
@@ -4243,7 +4238,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M34">
+  <conditionalFormatting sqref="N32">
     <cfRule type="dataBar" priority="37">
       <dataBar>
         <cfvo type="min"/>
@@ -4257,7 +4252,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K13:K37 K42 L3:L44">
+  <conditionalFormatting sqref="L12:L35 L40 M3:M42">
     <cfRule type="colorScale" priority="50">
       <colorScale>
         <cfvo type="min"/>
@@ -4269,7 +4264,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K9:K12">
+  <conditionalFormatting sqref="L8:L11">
     <cfRule type="colorScale" priority="51">
       <colorScale>
         <cfvo type="min"/>
@@ -4281,7 +4276,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K3:L44">
+  <conditionalFormatting sqref="L3:M42">
     <cfRule type="colorScale" priority="61">
       <colorScale>
         <cfvo type="min"/>
@@ -4294,47 +4289,45 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="M10" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="M11" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="M14" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="M15" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="M18" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="M23" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="M30" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="M31" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="M33" r:id="rId9" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="M34" r:id="rId10" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="M36" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="M42" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="M9" r:id="rId13" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="M32" r:id="rId14" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="M3" r:id="rId15" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="M7" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="M8" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="M38" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="M40" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="M19" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="M41" r:id="rId21" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="M21" r:id="rId22" xr:uid="{5EAF2F70-555A-4B25-966F-95095861DC0E}"/>
-    <hyperlink ref="M24" r:id="rId23" xr:uid="{6B884554-8BB6-4BF7-8096-D834E9729A06}"/>
-    <hyperlink ref="M12" r:id="rId24" xr:uid="{44B658D6-BFFD-46B9-B230-29405BAF9534}"/>
-    <hyperlink ref="M13" r:id="rId25" xr:uid="{367FEFFE-61E8-47BB-BCCA-FD3358349566}"/>
-    <hyperlink ref="M35" r:id="rId26" xr:uid="{D1D06D79-D259-47BA-BC7F-8742EAB7848C}"/>
-    <hyperlink ref="M25" r:id="rId27" xr:uid="{5545F658-0692-42E9-BD6F-76E0A6B030B0}"/>
-    <hyperlink ref="M27" r:id="rId28" xr:uid="{168ECF43-5CE3-4702-A056-8FA8BBC47676}"/>
-    <hyperlink ref="M26" r:id="rId29" xr:uid="{EA5E5506-441F-4FE0-B453-D92044CD3CD6}"/>
-    <hyperlink ref="M28" r:id="rId30" xr:uid="{8D8C1B68-82FF-4307-AFCC-0412DDB5B0BE}"/>
-    <hyperlink ref="M4" r:id="rId31" xr:uid="{2EF0B57E-A4CF-4AC0-9358-948CDF39D8B4}"/>
-    <hyperlink ref="M5" r:id="rId32" xr:uid="{ECCB4777-894F-4969-BB30-3BB1C2789276}"/>
-    <hyperlink ref="C16" r:id="rId33" xr:uid="{44A99C6C-4AC4-4D03-96BE-D592031C9536}"/>
-    <hyperlink ref="M16" r:id="rId34" xr:uid="{1A7B0E41-616E-45F1-BF6C-4CBB22A55EC6}"/>
-    <hyperlink ref="M20" r:id="rId35" xr:uid="{0E9DC705-3503-4FA0-87A9-DF2A5B60045D}"/>
-    <hyperlink ref="M17" r:id="rId36" xr:uid="{E7A9FE43-2492-4F96-944F-8153D9DD3BC5}"/>
-    <hyperlink ref="M6" r:id="rId37" xr:uid="{C6B216F8-5775-4357-B676-8FC9F8808265}"/>
-    <hyperlink ref="M29" r:id="rId38" xr:uid="{A2E7CF78-849E-4B20-A638-AA9D3B8EC8EE}"/>
+    <hyperlink ref="N9" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="N10" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="N13" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="N14" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="N17" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="N22" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="N28" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="N29" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="N31" r:id="rId9" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="N32" r:id="rId10" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="N34" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="N40" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="N8" r:id="rId13" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="N30" r:id="rId14" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="N3" r:id="rId15" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="N6" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="N7" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="N36" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="N38" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="N18" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="N39" r:id="rId21" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="N20" r:id="rId22" xr:uid="{5EAF2F70-555A-4B25-966F-95095861DC0E}"/>
+    <hyperlink ref="N23" r:id="rId23" xr:uid="{6B884554-8BB6-4BF7-8096-D834E9729A06}"/>
+    <hyperlink ref="N11" r:id="rId24" xr:uid="{44B658D6-BFFD-46B9-B230-29405BAF9534}"/>
+    <hyperlink ref="N12" r:id="rId25" xr:uid="{367FEFFE-61E8-47BB-BCCA-FD3358349566}"/>
+    <hyperlink ref="N33" r:id="rId26" xr:uid="{D1D06D79-D259-47BA-BC7F-8742EAB7848C}"/>
+    <hyperlink ref="N24" r:id="rId27" xr:uid="{5545F658-0692-42E9-BD6F-76E0A6B030B0}"/>
+    <hyperlink ref="N26" r:id="rId28" xr:uid="{168ECF43-5CE3-4702-A056-8FA8BBC47676}"/>
+    <hyperlink ref="N25" r:id="rId29" xr:uid="{EA5E5506-441F-4FE0-B453-D92044CD3CD6}"/>
+    <hyperlink ref="N27" r:id="rId30" xr:uid="{8D8C1B68-82FF-4307-AFCC-0412DDB5B0BE}"/>
+    <hyperlink ref="N4" r:id="rId31" xr:uid="{2EF0B57E-A4CF-4AC0-9358-948CDF39D8B4}"/>
+    <hyperlink ref="N5" r:id="rId32" xr:uid="{ECCB4777-894F-4969-BB30-3BB1C2789276}"/>
+    <hyperlink ref="C15" r:id="rId33" xr:uid="{44A99C6C-4AC4-4D03-96BE-D592031C9536}"/>
+    <hyperlink ref="N15" r:id="rId34" xr:uid="{1A7B0E41-616E-45F1-BF6C-4CBB22A55EC6}"/>
+    <hyperlink ref="N19" r:id="rId35" xr:uid="{0E9DC705-3503-4FA0-87A9-DF2A5B60045D}"/>
+    <hyperlink ref="N16" r:id="rId36" xr:uid="{E7A9FE43-2492-4F96-944F-8153D9DD3BC5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId39"/>
+  <pageSetup orientation="portrait" r:id="rId37"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -4349,7 +4342,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>M22</xm:sqref>
+          <xm:sqref>N21</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{94E20060-874B-439F-8FDA-33B3DD39FFE6}">
@@ -4362,7 +4355,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>M3:M7</xm:sqref>
+          <xm:sqref>N3:N6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{DBB933A5-5D45-42AE-8D8B-F05439EF033D}">
@@ -4375,7 +4368,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>M34</xm:sqref>
+          <xm:sqref>N32</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/Deliverables/Interface_Board/BOM/NEW-6 Prototypes_Interface_Board.xlsx
+++ b/Deliverables/Interface_Board/BOM/NEW-6 Prototypes_Interface_Board.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ChristianRaun-EthercatDesign\Deliverables\Interface_Board\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42F92E23-0475-4E30-B82A-075C8F0EE997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{790979A6-2E27-47B4-AC3E-43B85D4D8B31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="249">
   <si>
     <t>Bill of Material (BOM) for Interface_Board</t>
   </si>
@@ -602,8 +602,184 @@
     <t>R29</t>
   </si>
   <si>
+    <t>R#3</t>
+  </si>
+  <si>
+    <t>RT0603BRE0722KL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YAGEO </t>
+  </si>
+  <si>
+    <t>C705830</t>
+  </si>
+  <si>
+    <t>R#4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RC0603FR-072R2L
+</t>
+  </si>
+  <si>
+    <t>C112307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RES SMD 22K OHM 0.1% 1/10W 0603
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RES 2.2 OHM 1% 1/10W 0603
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RC0603JR-07100RL
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RES 100 OHM 5% 1/10W 0603
+</t>
+  </si>
+  <si>
+    <t>R#5</t>
+  </si>
+  <si>
+    <t>C110091</t>
+  </si>
+  <si>
+    <t>22K</t>
+  </si>
+  <si>
+    <t>2.2R</t>
+  </si>
+  <si>
+    <t>100R</t>
+  </si>
+  <si>
+    <t>0603WAF150LT5E</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Resistors 75V150mΩ 0603 Chip Resistor - Surface Mount ROHS
+</t>
+  </si>
+  <si>
+    <t>C45879</t>
+  </si>
+  <si>
+    <t>150mR</t>
+  </si>
+  <si>
+    <t>R#6,R#7</t>
+  </si>
+  <si>
+    <t>CL10A475KA8NQNC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAP CER 4.7UF 25V X5R 0603
+</t>
+  </si>
+  <si>
+    <t>C#5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Samsung </t>
+  </si>
+  <si>
+    <t>C69335</t>
+  </si>
+  <si>
+    <t>4.7uF</t>
+  </si>
+  <si>
+    <t>CL10B474KA8NNNC</t>
+  </si>
+  <si>
+    <t>470nF</t>
+  </si>
+  <si>
+    <t>C#6,C#7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MMSZ5V6CW
+</t>
+  </si>
+  <si>
+    <t>SOD123G</t>
+  </si>
+  <si>
+    <t>D4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1μA@2V 40Ω Single 5.2V~6V 500mW 5.6V SOD123G Zener Diodes ROHS
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yangzhou </t>
+  </si>
+  <si>
+    <t>C700475</t>
+  </si>
+  <si>
+    <t>Transistor</t>
+  </si>
+  <si>
+    <t>Q2</t>
+  </si>
+  <si>
+    <t>80V 500mW 1A 63@150mA,2V 130MHz 500mV@500mA,50mA NPN +150℃@(Tj) SOT-89(SOT-89-3) Bipolar Transistors - BJT ROHS</t>
+  </si>
+  <si>
+    <t>SOT-89</t>
+  </si>
+  <si>
+    <t>BCX56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Changjiang </t>
+  </si>
+  <si>
+    <t>-----------</t>
+  </si>
+  <si>
+    <t>----------</t>
+  </si>
+  <si>
+    <t>SMBJ43A</t>
+  </si>
+  <si>
+    <t>SMB</t>
+  </si>
+  <si>
+    <t>D5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6A 69.4V 47.8V 43V Unidirectional SMB(DO-214AA) TVS ROHS
+</t>
+  </si>
+  <si>
+    <t>RUILON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C10222
+</t>
+  </si>
+  <si>
+    <t>--------</t>
+  </si>
+  <si>
+    <t>-------</t>
+  </si>
+  <si>
+    <t>------</t>
+  </si>
+  <si>
+    <t>C44, C#9, C#10</t>
+  </si>
+  <si>
+    <t>C56, C57, C#8</t>
+  </si>
+  <si>
     <r>
-      <t>R1,</t>
+      <t>C#1,C#2,C#3,C#4,</t>
     </r>
     <r>
       <rPr>
@@ -613,163 +789,18 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>R#,R#1</t>
+      <t>C#11,C#12</t>
     </r>
   </si>
   <si>
-    <t>R#3</t>
-  </si>
-  <si>
-    <t>RT0603BRE0722KL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YAGEO </t>
-  </si>
-  <si>
-    <t>C705830</t>
-  </si>
-  <si>
-    <t>R#4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RC0603FR-072R2L
-</t>
-  </si>
-  <si>
-    <t>C112307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RES SMD 22K OHM 0.1% 1/10W 0603
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RES 2.2 OHM 1% 1/10W 0603
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RC0603JR-07100RL
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RES 100 OHM 5% 1/10W 0603
-</t>
-  </si>
-  <si>
-    <t>R#5</t>
-  </si>
-  <si>
-    <t>C110091</t>
-  </si>
-  <si>
-    <t>22K</t>
-  </si>
-  <si>
-    <t>2.2R</t>
-  </si>
-  <si>
-    <t>100R</t>
-  </si>
-  <si>
-    <t>0603WAF150LT5E</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Resistors 75V150mΩ 0603 Chip Resistor - Surface Mount ROHS
-</t>
-  </si>
-  <si>
-    <t>C45879</t>
-  </si>
-  <si>
-    <t>150mR</t>
-  </si>
-  <si>
-    <t>R#6,R#7</t>
-  </si>
-  <si>
-    <t>C#1,C#2,C#3,C#4</t>
-  </si>
-  <si>
-    <t>CL10A475KA8NQNC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAP CER 4.7UF 25V X5R 0603
-</t>
-  </si>
-  <si>
-    <t>C#5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samsung </t>
-  </si>
-  <si>
-    <t>C69335</t>
-  </si>
-  <si>
-    <t>4.7uF</t>
-  </si>
-  <si>
-    <t>CL10B474KA8NNNC</t>
-  </si>
-  <si>
-    <t>C1623</t>
-  </si>
-  <si>
-    <t>470nF</t>
-  </si>
-  <si>
-    <t>C#6,C#7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAP CER 0.47UF 25V X7R 0603
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MMSZ5V6CW
-</t>
-  </si>
-  <si>
-    <t>SOD123G</t>
-  </si>
-  <si>
-    <t>D4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1μA@2V 40Ω Single 5.2V~6V 500mW 5.6V SOD123G Zener Diodes ROHS
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yangzhou </t>
-  </si>
-  <si>
-    <t>C700475</t>
-  </si>
-  <si>
-    <t>Transistor</t>
-  </si>
-  <si>
-    <t>Q2</t>
-  </si>
-  <si>
-    <t>80V 500mW 1A 63@150mA,2V 130MHz 500mV@500mA,50mA NPN +150℃@(Tj) SOT-89(SOT-89-3) Bipolar Transistors - BJT ROHS</t>
-  </si>
-  <si>
-    <t>SOT-89</t>
-  </si>
-  <si>
-    <t>BCX56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Changjiang </t>
-  </si>
-  <si>
-    <t>-----------</t>
-  </si>
-  <si>
-    <t>----------</t>
+    <t>Remarks</t>
+  </si>
+  <si>
+    <t>Increase Quantity +2</t>
   </si>
   <si>
     <r>
-      <t xml:space="preserve">C56, C57, </t>
+      <t>R1,R#,R#1,</t>
     </r>
     <r>
       <rPr>
@@ -779,52 +810,18 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>C#8</t>
+      <t>R#8,R#9</t>
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">C44, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>C#9, C#10</t>
-    </r>
-  </si>
-  <si>
-    <t>SMBJ43A</t>
-  </si>
-  <si>
-    <t>SMB</t>
-  </si>
-  <si>
-    <t>D5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6A 69.4V 47.8V 43V Unidirectional SMB(DO-214AA) TVS ROHS
+    <t xml:space="preserve">CAP CER 0.47UF 100V X7S 0805
 </t>
   </si>
   <si>
-    <t>RUILON</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C10222
-</t>
-  </si>
-  <si>
-    <t>--------</t>
-  </si>
-  <si>
-    <t>-------</t>
-  </si>
-  <si>
-    <t>------</t>
+    <t>C342818</t>
+  </si>
+  <si>
+    <t>Voltage Rating and Package Change 0805</t>
   </si>
 </sst>
 </file>
@@ -834,12 +831,19 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.0000"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -949,14 +953,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -1007,8 +1003,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1035,12 +1045,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1052,7 +1056,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -1251,15 +1255,6 @@
       </right>
       <top/>
       <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
         <color auto="1"/>
       </bottom>
       <diagonal/>
@@ -1429,45 +1424,33 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="176">
+  <cellXfs count="146">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1476,105 +1459,71 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1583,351 +1532,186 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="5" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="21" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="21" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="21" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="21" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="20" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="27" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="26" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="25" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="6" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="1" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="22" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="22" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="22" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="22" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="21" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="28" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="27" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="15" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="26" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="24" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="22" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="22" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="6" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="6" borderId="21" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="20" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="7" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="7" borderId="22" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="27" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="28" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="22" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="21" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1939,7 +1723,130 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="16" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="23" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="25" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="26" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2235,25 +2142,27 @@
     <col min="12" max="12" width="21.85546875" customWidth="1"/>
     <col min="13" max="13" width="14.140625" customWidth="1"/>
     <col min="14" max="14" width="16.28515625" customWidth="1"/>
+    <col min="15" max="15" width="37.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="16.5" thickBot="1">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="96" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
-      <c r="E1" s="73"/>
-      <c r="F1" s="73"/>
-      <c r="G1" s="73"/>
-      <c r="H1" s="73"/>
-      <c r="I1" s="73"/>
-      <c r="J1" s="73"/>
-      <c r="K1" s="73"/>
-      <c r="L1" s="73"/>
-      <c r="M1" s="73"/>
-      <c r="N1" s="92"/>
+      <c r="B1" s="97"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="97"/>
+      <c r="G1" s="97"/>
+      <c r="H1" s="97"/>
+      <c r="I1" s="97"/>
+      <c r="J1" s="97"/>
+      <c r="K1" s="97"/>
+      <c r="L1" s="97"/>
+      <c r="M1" s="97"/>
+      <c r="N1" s="97"/>
+      <c r="O1" s="98"/>
     </row>
     <row r="2" spans="1:30" s="1" customFormat="1" ht="16.5" thickBot="1">
       <c r="A2" s="3" t="s">
@@ -2292,13 +2201,15 @@
       <c r="L2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="69" t="s">
+      <c r="M2" s="51" t="s">
         <v>181</v>
       </c>
-      <c r="N2" s="93" t="s">
+      <c r="N2" s="56" t="s">
         <v>180</v>
       </c>
-      <c r="O2"/>
+      <c r="O2" s="142" t="s">
+        <v>243</v>
+      </c>
       <c r="P2"/>
       <c r="Q2"/>
       <c r="R2"/>
@@ -2319,910 +2230,923 @@
       <c r="A3" s="6">
         <v>1</v>
       </c>
-      <c r="B3" s="172" t="s">
+      <c r="B3" s="99" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="144" t="s">
+      <c r="C3" s="84" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="145" t="s">
-        <v>209</v>
-      </c>
-      <c r="E3" s="146" t="s">
+      <c r="D3" s="138" t="s">
+        <v>242</v>
+      </c>
+      <c r="E3" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="146" t="s">
+      <c r="F3" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="146" t="s">
+      <c r="G3" s="85" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="147" t="s">
+      <c r="H3" s="86" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="148" t="s">
+      <c r="I3" s="87" t="s">
         <v>19</v>
       </c>
-      <c r="J3" s="146" t="s">
+      <c r="J3" s="85" t="s">
         <v>20</v>
       </c>
-      <c r="K3" s="149">
+      <c r="K3" s="88">
         <v>50</v>
       </c>
-      <c r="L3" s="149">
-        <v>4</v>
-      </c>
-      <c r="M3" s="149">
+      <c r="L3" s="88">
+        <v>6</v>
+      </c>
+      <c r="M3" s="88">
         <f>L3*6</f>
-        <v>24</v>
-      </c>
-      <c r="N3" s="150" t="s">
+        <v>36</v>
+      </c>
+      <c r="N3" s="89" t="s">
         <v>21</v>
+      </c>
+      <c r="O3" s="141" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="4" spans="1:30" ht="15.75" thickBot="1">
       <c r="A4" s="6">
         <v>2</v>
       </c>
-      <c r="B4" s="173"/>
-      <c r="C4" s="151" t="s">
+      <c r="B4" s="100"/>
+      <c r="C4" s="102" t="s">
+        <v>209</v>
+      </c>
+      <c r="D4" s="124" t="s">
+        <v>210</v>
+      </c>
+      <c r="E4" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="54" t="s">
+        <v>208</v>
+      </c>
+      <c r="G4" s="54" t="s">
         <v>211</v>
       </c>
-      <c r="D4" s="152" t="s">
+      <c r="H4" s="103" t="s">
         <v>212</v>
       </c>
-      <c r="E4" s="137" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="138" t="s">
-        <v>210</v>
-      </c>
-      <c r="G4" s="138" t="s">
+      <c r="I4" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" s="54" t="s">
         <v>213</v>
       </c>
-      <c r="H4" s="153" t="s">
-        <v>214</v>
-      </c>
-      <c r="I4" s="154" t="s">
-        <v>19</v>
-      </c>
-      <c r="J4" s="138" t="s">
-        <v>215</v>
-      </c>
-      <c r="K4" s="139">
+      <c r="K4" s="7">
         <v>20</v>
       </c>
-      <c r="L4" s="139">
+      <c r="L4" s="7">
         <v>1</v>
       </c>
-      <c r="M4" s="139">
+      <c r="M4" s="7">
         <f t="shared" ref="M4:M5" si="0">L4*6</f>
         <v>6</v>
       </c>
-      <c r="N4" s="155" t="s">
+      <c r="N4" s="104" t="s">
         <v>21</v>
       </c>
+      <c r="O4" s="104"/>
     </row>
     <row r="5" spans="1:30" ht="15.75" thickBot="1">
       <c r="A5" s="6">
         <v>3</v>
       </c>
-      <c r="B5" s="173"/>
-      <c r="C5" s="151" t="s">
-        <v>220</v>
-      </c>
-      <c r="D5" s="152" t="s">
-        <v>219</v>
-      </c>
-      <c r="E5" s="137" t="s">
+      <c r="B5" s="100"/>
+      <c r="C5" s="144" t="s">
+        <v>246</v>
+      </c>
+      <c r="D5" s="145" t="s">
+        <v>216</v>
+      </c>
+      <c r="E5" s="81" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="82" t="s">
+        <v>214</v>
+      </c>
+      <c r="G5" s="91" t="s">
+        <v>38</v>
+      </c>
+      <c r="H5" s="90" t="s">
+        <v>247</v>
+      </c>
+      <c r="I5" s="91" t="s">
+        <v>19</v>
+      </c>
+      <c r="J5" s="82" t="s">
+        <v>215</v>
+      </c>
+      <c r="K5" s="83">
         <v>15</v>
       </c>
-      <c r="F5" s="138" t="s">
-        <v>216</v>
-      </c>
-      <c r="G5" s="138" t="s">
-        <v>213</v>
-      </c>
-      <c r="H5" s="153" t="s">
-        <v>217</v>
-      </c>
-      <c r="I5" s="154" t="s">
-        <v>19</v>
-      </c>
-      <c r="J5" s="138" t="s">
-        <v>218</v>
-      </c>
-      <c r="K5" s="139">
-        <v>50</v>
-      </c>
-      <c r="L5" s="139">
+      <c r="L5" s="83">
         <v>2</v>
       </c>
-      <c r="M5" s="139">
+      <c r="M5" s="83">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="N5" s="155" t="s">
+      <c r="N5" s="92" t="s">
         <v>21</v>
+      </c>
+      <c r="O5" s="143" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="6" spans="1:30" ht="15.75" thickBot="1">
       <c r="A6" s="6">
         <v>4</v>
       </c>
-      <c r="B6" s="173"/>
-      <c r="C6" s="36" t="s">
+      <c r="B6" s="100"/>
+      <c r="C6" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="37" t="s">
+      <c r="D6" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="38" t="s">
+      <c r="E6" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="37" t="s">
+      <c r="F6" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="G6" s="38" t="s">
+      <c r="G6" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="H6" s="105" t="s">
         <v>27</v>
       </c>
-      <c r="I6" s="39" t="s">
+      <c r="I6" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="J6" s="38" t="s">
+      <c r="J6" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="K6" s="11">
+      <c r="K6" s="7">
         <v>10</v>
       </c>
-      <c r="L6" s="8">
+      <c r="L6" s="7">
         <v>1</v>
       </c>
-      <c r="M6" s="11">
+      <c r="M6" s="7">
         <f t="shared" ref="M6:M42" si="1">L6*6</f>
         <v>6</v>
       </c>
-      <c r="N6" s="87" t="s">
+      <c r="N6" s="106" t="s">
         <v>21</v>
       </c>
+      <c r="O6" s="106"/>
     </row>
     <row r="7" spans="1:30" ht="15.75" thickBot="1">
       <c r="A7" s="6">
         <v>5</v>
       </c>
-      <c r="B7" s="173"/>
-      <c r="C7" s="36" t="s">
+      <c r="B7" s="100"/>
+      <c r="C7" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="37" t="s">
+      <c r="D7" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="38" t="s">
+      <c r="E7" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="40" t="s">
+      <c r="F7" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="G7" s="38" t="s">
+      <c r="G7" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="H7" s="10" t="s">
+      <c r="H7" s="105" t="s">
         <v>33</v>
       </c>
-      <c r="I7" s="10" t="s">
+      <c r="I7" s="105" t="s">
         <v>34</v>
       </c>
-      <c r="J7" s="38" t="s">
+      <c r="J7" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="K7" s="11">
+      <c r="K7" s="7">
         <v>100</v>
       </c>
-      <c r="L7" s="8">
+      <c r="L7" s="7">
         <v>8</v>
       </c>
-      <c r="M7" s="11">
+      <c r="M7" s="7">
         <f t="shared" si="1"/>
         <v>48</v>
       </c>
-      <c r="N7" s="88" t="s">
+      <c r="N7" s="107" t="s">
         <v>21</v>
       </c>
+      <c r="O7" s="107"/>
     </row>
     <row r="8" spans="1:30" ht="15.75" thickBot="1">
       <c r="A8" s="6">
         <v>6</v>
       </c>
-      <c r="B8" s="173"/>
-      <c r="C8" s="156" t="s">
+      <c r="B8" s="100"/>
+      <c r="C8" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="138" t="s">
-        <v>235</v>
-      </c>
-      <c r="E8" s="137" t="s">
+      <c r="D8" s="121" t="s">
+        <v>241</v>
+      </c>
+      <c r="E8" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="167" t="s">
+      <c r="F8" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="G8" s="154" t="s">
+      <c r="G8" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="H8" s="81" t="s">
+      <c r="H8" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="I8" s="137" t="s">
+      <c r="I8" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="J8" s="137" t="s">
+      <c r="J8" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="K8" s="139">
+      <c r="K8" s="7">
         <v>50</v>
       </c>
-      <c r="L8" s="81">
+      <c r="L8" s="9">
         <v>3</v>
       </c>
-      <c r="M8" s="139">
+      <c r="M8" s="7">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="N8" s="168" t="s">
+      <c r="N8" s="58" t="s">
         <v>21</v>
       </c>
+      <c r="O8" s="58"/>
     </row>
     <row r="9" spans="1:30" ht="15.75" thickBot="1">
       <c r="A9" s="6">
         <v>7</v>
       </c>
-      <c r="B9" s="173"/>
-      <c r="C9" s="41" t="s">
+      <c r="B9" s="100"/>
+      <c r="C9" s="35" t="s">
         <v>42</v>
       </c>
-      <c r="D9" s="37" t="s">
+      <c r="D9" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="E9" s="42" t="s">
+      <c r="E9" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="F9" s="37" t="s">
+      <c r="F9" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="43" t="s">
+      <c r="G9" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="H9" s="13" t="s">
+      <c r="H9" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="I9" s="39" t="s">
+      <c r="I9" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="J9" s="42" t="s">
+      <c r="J9" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="K9" s="11">
+      <c r="K9" s="7">
         <v>10</v>
       </c>
-      <c r="L9" s="29">
+      <c r="L9" s="9">
         <v>1</v>
       </c>
-      <c r="M9" s="11">
+      <c r="M9" s="7">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N9" s="89" t="s">
+      <c r="N9" s="58" t="s">
         <v>21</v>
       </c>
+      <c r="O9" s="58"/>
     </row>
     <row r="10" spans="1:30" ht="15.75" thickBot="1">
       <c r="A10" s="6">
         <v>8</v>
       </c>
-      <c r="B10" s="173"/>
-      <c r="C10" s="156" t="s">
+      <c r="B10" s="100"/>
+      <c r="C10" s="35" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="138" t="s">
-        <v>236</v>
-      </c>
-      <c r="E10" s="137" t="s">
+      <c r="D10" s="121" t="s">
+        <v>240</v>
+      </c>
+      <c r="E10" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="F10" s="137" t="s">
+      <c r="F10" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="G10" s="154" t="s">
+      <c r="G10" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="H10" s="81" t="s">
+      <c r="H10" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="I10" s="154" t="s">
+      <c r="I10" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="J10" s="137" t="s">
+      <c r="J10" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="K10" s="139">
+      <c r="K10" s="7">
         <v>12</v>
       </c>
-      <c r="L10" s="81">
+      <c r="L10" s="9">
         <v>3</v>
       </c>
-      <c r="M10" s="139">
+      <c r="M10" s="7">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="N10" s="168" t="s">
+      <c r="N10" s="58" t="s">
         <v>21</v>
       </c>
-      <c r="O10" s="31"/>
+      <c r="O10" s="58"/>
     </row>
     <row r="11" spans="1:30" ht="15.75" thickBot="1">
       <c r="A11" s="6">
         <v>9</v>
       </c>
-      <c r="B11" s="173"/>
-      <c r="C11" s="82" t="s">
+      <c r="B11" s="100"/>
+      <c r="C11" s="108" t="s">
         <v>162</v>
       </c>
-      <c r="D11" s="70" t="s">
+      <c r="D11" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="62" t="s">
+      <c r="E11" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="62" t="s">
+      <c r="F11" s="52" t="s">
         <v>163</v>
       </c>
-      <c r="G11" s="43" t="s">
+      <c r="G11" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="H11" s="80" t="s">
-        <v>243</v>
-      </c>
-      <c r="I11" s="39" t="s">
+      <c r="H11" s="55" t="s">
+        <v>237</v>
+      </c>
+      <c r="I11" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="J11" s="42" t="s">
+      <c r="J11" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="K11" s="11">
+      <c r="K11" s="7">
         <v>20</v>
       </c>
-      <c r="L11" s="12">
+      <c r="L11" s="9">
         <v>1</v>
       </c>
-      <c r="M11" s="11">
+      <c r="M11" s="7">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N11" s="90" t="s">
+      <c r="N11" s="57" t="s">
         <v>21</v>
       </c>
-      <c r="O11" s="31"/>
+      <c r="O11" s="57"/>
     </row>
     <row r="12" spans="1:30" ht="15.75" thickBot="1">
       <c r="A12" s="6">
         <v>10</v>
       </c>
-      <c r="B12" s="173"/>
-      <c r="C12" s="41" t="s">
+      <c r="B12" s="100"/>
+      <c r="C12" s="35" t="s">
         <v>164</v>
       </c>
-      <c r="D12" s="37" t="s">
+      <c r="D12" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="E12" s="42" t="s">
+      <c r="E12" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="F12" s="37" t="s">
+      <c r="F12" s="28" t="s">
         <v>165</v>
       </c>
-      <c r="G12" s="43" t="s">
+      <c r="G12" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="H12" s="80" t="s">
-        <v>244</v>
-      </c>
-      <c r="I12" s="39" t="s">
+      <c r="H12" s="55" t="s">
+        <v>238</v>
+      </c>
+      <c r="I12" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="J12" s="42" t="s">
+      <c r="J12" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="K12" s="11">
+      <c r="K12" s="7">
         <v>10</v>
       </c>
-      <c r="L12" s="12">
+      <c r="L12" s="9">
         <v>1</v>
       </c>
-      <c r="M12" s="11">
+      <c r="M12" s="7">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N12" s="90" t="s">
+      <c r="N12" s="57" t="s">
         <v>21</v>
       </c>
-      <c r="O12" s="32"/>
+      <c r="O12" s="57"/>
     </row>
     <row r="13" spans="1:30" ht="15.75" thickBot="1">
       <c r="A13" s="6">
         <v>11</v>
       </c>
-      <c r="B13" s="174"/>
-      <c r="C13" s="44" t="s">
+      <c r="B13" s="101"/>
+      <c r="C13" s="36" t="s">
         <v>56</v>
       </c>
-      <c r="D13" s="45" t="s">
+      <c r="D13" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="E13" s="46" t="s">
+      <c r="E13" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="F13" s="45" t="s">
+      <c r="F13" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="G13" s="47" t="s">
+      <c r="G13" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="H13" s="17" t="s">
+      <c r="H13" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="I13" s="48" t="s">
+      <c r="I13" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="J13" s="46" t="s">
+      <c r="J13" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="K13" s="15">
+      <c r="K13" s="10">
         <v>50</v>
       </c>
-      <c r="L13" s="16">
+      <c r="L13" s="12">
         <v>1</v>
       </c>
-      <c r="M13" s="15">
+      <c r="M13" s="10">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N13" s="91" t="s">
+      <c r="N13" s="109" t="s">
         <v>21</v>
       </c>
-      <c r="O13" s="31"/>
+      <c r="O13" s="109"/>
     </row>
     <row r="14" spans="1:30" ht="15.75" thickBot="1">
       <c r="A14" s="6">
         <v>12</v>
       </c>
-      <c r="B14" s="173" t="s">
+      <c r="B14" s="100" t="s">
         <v>63</v>
       </c>
-      <c r="C14" s="83" t="s">
+      <c r="C14" s="110" t="s">
         <v>64</v>
       </c>
-      <c r="D14" s="49" t="s">
+      <c r="D14" s="33" t="s">
         <v>65</v>
       </c>
-      <c r="E14" s="84" t="s">
+      <c r="E14" s="33" t="s">
         <v>66</v>
       </c>
-      <c r="F14" s="49" t="s">
+      <c r="F14" s="33" t="s">
         <v>67</v>
       </c>
-      <c r="G14" s="84" t="s">
+      <c r="G14" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="H14" s="20" t="s">
+      <c r="H14" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="I14" s="50" t="s">
+      <c r="I14" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="J14" s="85" t="s">
+      <c r="J14" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="K14" s="77">
+      <c r="K14" s="111">
         <v>7</v>
       </c>
-      <c r="L14" s="86">
+      <c r="L14" s="15">
         <v>1</v>
       </c>
-      <c r="M14" s="77">
+      <c r="M14" s="111">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N14" s="94" t="s">
+      <c r="N14" s="112" t="s">
         <v>21</v>
       </c>
-      <c r="O14" s="31"/>
+      <c r="O14" s="112"/>
     </row>
     <row r="15" spans="1:30" ht="15.75" thickBot="1">
       <c r="A15" s="6">
         <v>13</v>
       </c>
-      <c r="B15" s="173"/>
-      <c r="C15" s="156" t="s">
-        <v>224</v>
-      </c>
-      <c r="D15" s="157" t="s">
-        <v>223</v>
-      </c>
-      <c r="E15" s="138" t="s">
+      <c r="B15" s="100"/>
+      <c r="C15" s="35" t="s">
+        <v>220</v>
+      </c>
+      <c r="D15" s="121" t="s">
+        <v>219</v>
+      </c>
+      <c r="E15" s="54" t="s">
+        <v>218</v>
+      </c>
+      <c r="F15" s="54" t="s">
+        <v>217</v>
+      </c>
+      <c r="G15" s="54" t="s">
+        <v>221</v>
+      </c>
+      <c r="H15" s="113" t="s">
         <v>222</v>
       </c>
-      <c r="F15" s="138" t="s">
-        <v>221</v>
-      </c>
-      <c r="G15" s="138" t="s">
-        <v>225</v>
-      </c>
-      <c r="H15" s="158" t="s">
-        <v>226</v>
-      </c>
-      <c r="I15" s="159" t="s">
+      <c r="I15" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="J15" s="159" t="s">
+      <c r="J15" s="55" t="s">
         <v>70</v>
       </c>
-      <c r="K15" s="139">
+      <c r="K15" s="7">
         <v>50</v>
       </c>
-      <c r="L15" s="81">
+      <c r="L15" s="9">
         <v>1</v>
       </c>
-      <c r="M15" s="139">
+      <c r="M15" s="7">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N15" s="141" t="s">
+      <c r="N15" s="57" t="s">
         <v>21</v>
       </c>
-      <c r="O15" s="31"/>
+      <c r="O15" s="57"/>
     </row>
     <row r="16" spans="1:30" ht="15.75" thickBot="1">
       <c r="A16" s="6">
         <v>14</v>
       </c>
-      <c r="B16" s="173"/>
-      <c r="C16" s="151" t="s">
-        <v>240</v>
-      </c>
-      <c r="D16" s="157" t="s">
-        <v>239</v>
-      </c>
-      <c r="E16" s="138" t="s">
-        <v>238</v>
-      </c>
-      <c r="F16" s="138" t="s">
-        <v>237</v>
-      </c>
-      <c r="G16" s="138" t="s">
-        <v>241</v>
-      </c>
-      <c r="H16" s="158" t="s">
-        <v>242</v>
-      </c>
-      <c r="I16" s="159" t="s">
+      <c r="B16" s="100"/>
+      <c r="C16" s="102" t="s">
+        <v>234</v>
+      </c>
+      <c r="D16" s="121" t="s">
+        <v>233</v>
+      </c>
+      <c r="E16" s="54" t="s">
+        <v>232</v>
+      </c>
+      <c r="F16" s="54" t="s">
+        <v>231</v>
+      </c>
+      <c r="G16" s="54" t="s">
+        <v>235</v>
+      </c>
+      <c r="H16" s="113" t="s">
+        <v>236</v>
+      </c>
+      <c r="I16" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="J16" s="159" t="s">
+      <c r="J16" s="55" t="s">
         <v>70</v>
       </c>
-      <c r="K16" s="139">
+      <c r="K16" s="7">
         <v>5</v>
       </c>
-      <c r="L16" s="81">
+      <c r="L16" s="9">
         <v>1</v>
       </c>
-      <c r="M16" s="139">
+      <c r="M16" s="7">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N16" s="141" t="s">
+      <c r="N16" s="57" t="s">
         <v>21</v>
       </c>
-      <c r="O16" s="31"/>
+      <c r="O16" s="57"/>
     </row>
     <row r="17" spans="1:15" ht="15.75" thickBot="1">
       <c r="A17" s="6">
         <v>15</v>
       </c>
-      <c r="B17" s="173"/>
-      <c r="C17" s="79" t="s">
+      <c r="B17" s="100"/>
+      <c r="C17" s="114" t="s">
         <v>71</v>
       </c>
-      <c r="D17" s="106" t="s">
+      <c r="D17" s="122" t="s">
         <v>72</v>
       </c>
-      <c r="E17" s="110" t="s">
+      <c r="E17" s="68" t="s">
         <v>73</v>
       </c>
-      <c r="F17" s="106" t="s">
+      <c r="F17" s="68" t="s">
         <v>74</v>
       </c>
-      <c r="G17" s="110" t="s">
+      <c r="G17" s="68" t="s">
         <v>75</v>
       </c>
-      <c r="H17" s="107" t="s">
+      <c r="H17" s="69" t="s">
         <v>76</v>
       </c>
-      <c r="I17" s="107" t="s">
+      <c r="I17" s="69" t="s">
         <v>19</v>
       </c>
-      <c r="J17" s="111" t="s">
+      <c r="J17" s="69" t="s">
         <v>70</v>
       </c>
-      <c r="K17" s="103">
+      <c r="K17" s="115">
         <v>20</v>
       </c>
-      <c r="L17" s="112">
+      <c r="L17" s="64">
         <v>1</v>
       </c>
-      <c r="M17" s="103">
+      <c r="M17" s="115">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N17" s="113" t="s">
+      <c r="N17" s="116" t="s">
         <v>21</v>
       </c>
-      <c r="O17" s="31"/>
+      <c r="O17" s="116"/>
     </row>
     <row r="18" spans="1:15" ht="16.5" thickBot="1">
       <c r="A18" s="6">
         <v>16</v>
       </c>
-      <c r="B18" s="175" t="s">
+      <c r="B18" s="95" t="s">
         <v>77</v>
       </c>
-      <c r="C18" s="114" t="s">
+      <c r="C18" s="72" t="s">
         <v>78</v>
       </c>
-      <c r="D18" s="115" t="s">
+      <c r="D18" s="123" t="s">
         <v>79</v>
       </c>
-      <c r="E18" s="115" t="s">
+      <c r="E18" s="73" t="s">
         <v>80</v>
       </c>
-      <c r="F18" s="115" t="s">
+      <c r="F18" s="73" t="s">
         <v>81</v>
       </c>
-      <c r="G18" s="116" t="s">
+      <c r="G18" s="74" t="s">
         <v>82</v>
       </c>
-      <c r="H18" s="116" t="s">
+      <c r="H18" s="74" t="s">
         <v>19</v>
       </c>
-      <c r="I18" s="115" t="s">
+      <c r="I18" s="73" t="s">
         <v>19</v>
       </c>
-      <c r="J18" s="116" t="s">
+      <c r="J18" s="74" t="s">
         <v>70</v>
       </c>
-      <c r="K18" s="108">
+      <c r="K18" s="70">
         <v>7</v>
       </c>
-      <c r="L18" s="108">
+      <c r="L18" s="70">
         <v>1</v>
       </c>
-      <c r="M18" s="67">
+      <c r="M18" s="117">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N18" s="109" t="s">
+      <c r="N18" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="O18" s="31"/>
+      <c r="O18" s="71"/>
     </row>
     <row r="19" spans="1:15" ht="30.75" thickBot="1">
       <c r="A19" s="6">
         <v>17</v>
       </c>
-      <c r="B19" s="175" t="s">
+      <c r="B19" s="95" t="s">
+        <v>223</v>
+      </c>
+      <c r="C19" s="118" t="s">
+        <v>225</v>
+      </c>
+      <c r="D19" s="123" t="s">
+        <v>224</v>
+      </c>
+      <c r="E19" s="119" t="s">
+        <v>226</v>
+      </c>
+      <c r="F19" s="119" t="s">
         <v>227</v>
       </c>
-      <c r="C19" s="160" t="s">
+      <c r="G19" s="120" t="s">
+        <v>228</v>
+      </c>
+      <c r="H19" s="120" t="s">
         <v>229</v>
       </c>
-      <c r="D19" s="161" t="s">
-        <v>228</v>
-      </c>
-      <c r="E19" s="162" t="s">
+      <c r="I19" s="119" t="s">
         <v>230</v>
       </c>
-      <c r="F19" s="162" t="s">
-        <v>231</v>
-      </c>
-      <c r="G19" s="163" t="s">
-        <v>232</v>
-      </c>
-      <c r="H19" s="163" t="s">
-        <v>233</v>
-      </c>
-      <c r="I19" s="162" t="s">
-        <v>234</v>
-      </c>
-      <c r="J19" s="163" t="s">
+      <c r="J19" s="120" t="s">
         <v>70</v>
       </c>
-      <c r="K19" s="164">
+      <c r="K19" s="70">
         <v>10</v>
       </c>
-      <c r="L19" s="164">
+      <c r="L19" s="70">
         <v>1</v>
       </c>
-      <c r="M19" s="165">
+      <c r="M19" s="117">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N19" s="166" t="s">
+      <c r="N19" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="O19" s="31"/>
+      <c r="O19" s="71"/>
     </row>
     <row r="20" spans="1:15" ht="15.75" thickBot="1">
       <c r="A20" s="6">
         <v>18</v>
       </c>
-      <c r="B20" s="172" t="s">
+      <c r="B20" s="99" t="s">
         <v>83</v>
       </c>
-      <c r="C20" s="104" t="s">
+      <c r="C20" s="66" t="s">
         <v>174</v>
       </c>
-      <c r="D20" s="63" t="s">
+      <c r="D20" s="46" t="s">
         <v>175</v>
       </c>
-      <c r="E20" s="63" t="s">
+      <c r="E20" s="46" t="s">
         <v>176</v>
       </c>
-      <c r="F20" s="63" t="s">
+      <c r="F20" s="46" t="s">
         <v>176</v>
       </c>
-      <c r="G20" s="35" t="s">
+      <c r="G20" s="27" t="s">
         <v>177</v>
       </c>
-      <c r="H20" s="35" t="s">
+      <c r="H20" s="27" t="s">
         <v>178</v>
       </c>
-      <c r="I20" s="34" t="s">
+      <c r="I20" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="J20" s="35" t="s">
+      <c r="J20" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="K20" s="19">
+      <c r="K20" s="14">
         <v>10</v>
       </c>
-      <c r="L20" s="19">
+      <c r="L20" s="14">
         <v>1</v>
       </c>
-      <c r="M20" s="18">
+      <c r="M20" s="13">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N20" s="105" t="s">
+      <c r="N20" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="O20" s="31"/>
+      <c r="O20" s="67"/>
     </row>
     <row r="21" spans="1:15" ht="15.75" thickBot="1">
       <c r="A21" s="6">
         <v>19</v>
       </c>
-      <c r="B21" s="174"/>
-      <c r="C21" s="64" t="s">
+      <c r="B21" s="101"/>
+      <c r="C21" s="47" t="s">
         <v>84</v>
       </c>
-      <c r="D21" s="65" t="s">
+      <c r="D21" s="48" t="s">
         <v>85</v>
       </c>
-      <c r="E21" s="65" t="s">
+      <c r="E21" s="48" t="s">
         <v>44</v>
       </c>
-      <c r="F21" s="65" t="s">
+      <c r="F21" s="48" t="s">
         <v>86</v>
       </c>
-      <c r="G21" s="65" t="s">
+      <c r="G21" s="48" t="s">
         <v>87</v>
       </c>
-      <c r="H21" s="66"/>
-      <c r="I21" s="66"/>
-      <c r="J21" s="65" t="s">
+      <c r="H21" s="49"/>
+      <c r="I21" s="49"/>
+      <c r="J21" s="48" t="s">
         <v>70</v>
       </c>
-      <c r="K21" s="66">
+      <c r="K21" s="49">
         <v>7</v>
       </c>
-      <c r="L21" s="66">
+      <c r="L21" s="49">
         <v>1</v>
       </c>
-      <c r="M21" s="15">
+      <c r="M21" s="11">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N21" s="68" t="s">
+      <c r="N21" s="50" t="s">
         <v>88</v>
       </c>
-      <c r="O21" s="31"/>
+      <c r="O21" s="50"/>
     </row>
     <row r="22" spans="1:15" ht="15.75" thickBot="1">
       <c r="A22" s="6">
         <v>20</v>
       </c>
-      <c r="B22" s="172" t="s">
+      <c r="B22" s="99" t="s">
         <v>89</v>
       </c>
-      <c r="C22" s="144" t="s">
+      <c r="C22" s="84" t="s">
         <v>90</v>
       </c>
-      <c r="D22" s="169" t="s">
-        <v>187</v>
-      </c>
-      <c r="E22" s="146" t="s">
+      <c r="D22" s="140" t="s">
+        <v>245</v>
+      </c>
+      <c r="E22" s="85" t="s">
         <v>91</v>
       </c>
-      <c r="F22" s="146" t="s">
+      <c r="F22" s="85" t="s">
         <v>92</v>
       </c>
-      <c r="G22" s="148" t="s">
+      <c r="G22" s="87" t="s">
         <v>60</v>
       </c>
-      <c r="H22" s="170" t="s">
+      <c r="H22" s="93" t="s">
         <v>93</v>
       </c>
-      <c r="I22" s="146" t="s">
+      <c r="I22" s="85" t="s">
         <v>19</v>
       </c>
-      <c r="J22" s="146" t="s">
+      <c r="J22" s="85" t="s">
         <v>94</v>
       </c>
-      <c r="K22" s="149">
+      <c r="K22" s="88">
         <v>100</v>
       </c>
-      <c r="L22" s="149">
-        <v>3</v>
-      </c>
-      <c r="M22" s="149">
+      <c r="L22" s="88">
+        <v>5</v>
+      </c>
+      <c r="M22" s="88">
         <f t="shared" si="1"/>
-        <v>18</v>
-      </c>
-      <c r="N22" s="171" t="s">
+        <v>30</v>
+      </c>
+      <c r="N22" s="94" t="s">
         <v>21</v>
       </c>
-      <c r="O22" s="31"/>
+      <c r="O22" s="139" t="s">
+        <v>244</v>
+      </c>
     </row>
     <row r="23" spans="1:15" ht="15.75" thickBot="1">
       <c r="A23" s="6">
         <v>21</v>
       </c>
-      <c r="B23" s="173"/>
-      <c r="C23" s="76" t="s">
+      <c r="B23" s="100"/>
+      <c r="C23" s="125" t="s">
         <v>166</v>
       </c>
-      <c r="D23" s="62" t="s">
+      <c r="D23" s="131" t="s">
         <v>167</v>
       </c>
-      <c r="E23" s="62" t="s">
+      <c r="E23" s="52" t="s">
         <v>91</v>
       </c>
-      <c r="F23" s="62" t="s">
+      <c r="F23" s="52" t="s">
         <v>168</v>
       </c>
-      <c r="G23" s="39" t="s">
+      <c r="G23" s="29" t="s">
         <v>156</v>
       </c>
-      <c r="H23" s="80" t="s">
-        <v>245</v>
-      </c>
-      <c r="I23" s="37" t="s">
+      <c r="H23" s="55" t="s">
+        <v>239</v>
+      </c>
+      <c r="I23" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="J23" s="78" t="s">
+      <c r="J23" s="54" t="s">
         <v>169</v>
       </c>
       <c r="K23" s="7">
@@ -3231,218 +3155,218 @@
       <c r="L23" s="7">
         <v>1</v>
       </c>
-      <c r="M23" s="11">
+      <c r="M23" s="7">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N23" s="95" t="s">
+      <c r="N23" s="57" t="s">
         <v>179</v>
       </c>
-      <c r="O23" s="31"/>
+      <c r="O23" s="57"/>
     </row>
     <row r="24" spans="1:15" ht="15.75" thickBot="1">
       <c r="A24" s="6">
         <v>22</v>
       </c>
-      <c r="B24" s="173"/>
-      <c r="C24" s="133" t="s">
-        <v>195</v>
-      </c>
-      <c r="D24" s="134" t="s">
+      <c r="B24" s="100"/>
+      <c r="C24" s="126" t="s">
+        <v>194</v>
+      </c>
+      <c r="D24" s="132" t="s">
+        <v>187</v>
+      </c>
+      <c r="E24" s="52" t="s">
+        <v>91</v>
+      </c>
+      <c r="F24" s="127" t="s">
         <v>188</v>
       </c>
-      <c r="E24" s="75" t="s">
-        <v>91</v>
-      </c>
-      <c r="F24" s="135" t="s">
+      <c r="G24" s="127" t="s">
         <v>189</v>
       </c>
-      <c r="G24" s="135" t="s">
+      <c r="H24" s="128" t="s">
         <v>190</v>
       </c>
-      <c r="H24" s="136" t="s">
-        <v>191</v>
-      </c>
-      <c r="I24" s="137" t="s">
+      <c r="I24" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="J24" s="138" t="s">
-        <v>201</v>
-      </c>
-      <c r="K24" s="139">
+      <c r="J24" s="54" t="s">
+        <v>200</v>
+      </c>
+      <c r="K24" s="7">
         <v>20</v>
       </c>
-      <c r="L24" s="139">
+      <c r="L24" s="7">
         <v>1</v>
       </c>
-      <c r="M24" s="139">
+      <c r="M24" s="7">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N24" s="140" t="s">
+      <c r="N24" s="60" t="s">
         <v>21</v>
       </c>
-      <c r="O24" s="31"/>
+      <c r="O24" s="60"/>
     </row>
     <row r="25" spans="1:15" ht="15.75" thickBot="1">
       <c r="A25" s="6">
         <v>23</v>
       </c>
-      <c r="B25" s="173"/>
-      <c r="C25" s="133" t="s">
-        <v>196</v>
-      </c>
-      <c r="D25" s="134" t="s">
+      <c r="B25" s="100"/>
+      <c r="C25" s="126" t="s">
+        <v>195</v>
+      </c>
+      <c r="D25" s="132" t="s">
+        <v>191</v>
+      </c>
+      <c r="E25" s="52" t="s">
+        <v>91</v>
+      </c>
+      <c r="F25" s="127" t="s">
         <v>192</v>
       </c>
-      <c r="E25" s="75" t="s">
-        <v>91</v>
-      </c>
-      <c r="F25" s="135" t="s">
+      <c r="G25" s="127" t="s">
+        <v>189</v>
+      </c>
+      <c r="H25" s="128" t="s">
         <v>193</v>
       </c>
-      <c r="G25" s="135" t="s">
-        <v>190</v>
-      </c>
-      <c r="H25" s="136" t="s">
-        <v>194</v>
-      </c>
-      <c r="I25" s="137" t="s">
+      <c r="I25" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="J25" s="138" t="s">
-        <v>202</v>
-      </c>
-      <c r="K25" s="139">
+      <c r="J25" s="54" t="s">
+        <v>201</v>
+      </c>
+      <c r="K25" s="7">
         <v>100</v>
       </c>
-      <c r="L25" s="139">
+      <c r="L25" s="7">
         <v>1</v>
       </c>
-      <c r="M25" s="139">
+      <c r="M25" s="7">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N25" s="141" t="s">
+      <c r="N25" s="57" t="s">
         <v>21</v>
       </c>
-      <c r="O25" s="31"/>
+      <c r="O25" s="57"/>
     </row>
     <row r="26" spans="1:15" ht="15.75" thickBot="1">
       <c r="A26" s="6">
         <v>24</v>
       </c>
-      <c r="B26" s="173"/>
-      <c r="C26" s="133" t="s">
+      <c r="B26" s="100"/>
+      <c r="C26" s="126" t="s">
+        <v>197</v>
+      </c>
+      <c r="D26" s="132" t="s">
         <v>198</v>
       </c>
-      <c r="D26" s="134" t="s">
+      <c r="E26" s="54" t="s">
+        <v>91</v>
+      </c>
+      <c r="F26" s="129" t="s">
+        <v>196</v>
+      </c>
+      <c r="G26" s="127" t="s">
+        <v>189</v>
+      </c>
+      <c r="H26" s="130" t="s">
         <v>199</v>
       </c>
-      <c r="E26" s="138" t="s">
-        <v>91</v>
-      </c>
-      <c r="F26" s="142" t="s">
-        <v>197</v>
-      </c>
-      <c r="G26" s="135" t="s">
-        <v>190</v>
-      </c>
-      <c r="H26" s="143" t="s">
-        <v>200</v>
-      </c>
-      <c r="I26" s="137" t="s">
+      <c r="I26" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="J26" s="138" t="s">
-        <v>203</v>
-      </c>
-      <c r="K26" s="139">
+      <c r="J26" s="54" t="s">
+        <v>202</v>
+      </c>
+      <c r="K26" s="7">
         <v>100</v>
       </c>
-      <c r="L26" s="139">
+      <c r="L26" s="7">
         <v>1</v>
       </c>
-      <c r="M26" s="139">
+      <c r="M26" s="7">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N26" s="141" t="s">
+      <c r="N26" s="57" t="s">
         <v>21</v>
       </c>
-      <c r="O26" s="31"/>
+      <c r="O26" s="57"/>
     </row>
     <row r="27" spans="1:15" ht="15.75" thickBot="1">
       <c r="A27" s="6">
         <v>25</v>
       </c>
-      <c r="B27" s="173"/>
-      <c r="C27" s="133" t="s">
+      <c r="B27" s="100"/>
+      <c r="C27" s="126" t="s">
+        <v>204</v>
+      </c>
+      <c r="D27" s="132" t="s">
+        <v>207</v>
+      </c>
+      <c r="E27" s="54" t="s">
+        <v>91</v>
+      </c>
+      <c r="F27" s="129" t="s">
+        <v>203</v>
+      </c>
+      <c r="G27" s="129" t="s">
+        <v>115</v>
+      </c>
+      <c r="H27" s="130" t="s">
         <v>205</v>
       </c>
-      <c r="D27" s="134" t="s">
-        <v>208</v>
-      </c>
-      <c r="E27" s="138" t="s">
-        <v>91</v>
-      </c>
-      <c r="F27" s="142" t="s">
-        <v>204</v>
-      </c>
-      <c r="G27" s="142" t="s">
-        <v>115</v>
-      </c>
-      <c r="H27" s="143" t="s">
+      <c r="I27" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="J27" s="54" t="s">
         <v>206</v>
       </c>
-      <c r="I27" s="137" t="s">
-        <v>19</v>
-      </c>
-      <c r="J27" s="138" t="s">
-        <v>207</v>
-      </c>
-      <c r="K27" s="139">
+      <c r="K27" s="7">
         <v>50</v>
       </c>
-      <c r="L27" s="139">
+      <c r="L27" s="7">
         <v>2</v>
       </c>
-      <c r="M27" s="139">
+      <c r="M27" s="7">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="N27" s="141" t="s">
+      <c r="N27" s="57" t="s">
         <v>21</v>
       </c>
-      <c r="O27" s="31"/>
+      <c r="O27" s="57"/>
     </row>
     <row r="28" spans="1:15" ht="15.75" thickBot="1">
       <c r="A28" s="6">
         <v>26</v>
       </c>
-      <c r="B28" s="173"/>
-      <c r="C28" s="51" t="s">
+      <c r="B28" s="100"/>
+      <c r="C28" s="35" t="s">
         <v>95</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="E28" s="37" t="s">
+      <c r="E28" s="28" t="s">
         <v>91</v>
       </c>
-      <c r="F28" s="37" t="s">
+      <c r="F28" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="G28" s="39" t="s">
+      <c r="G28" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="H28" s="13" t="s">
+      <c r="H28" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="I28" s="37" t="s">
+      <c r="I28" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="J28" s="37" t="s">
+      <c r="J28" s="28" t="s">
         <v>99</v>
       </c>
       <c r="K28" s="7">
@@ -3451,42 +3375,42 @@
       <c r="L28" s="7">
         <v>2</v>
       </c>
-      <c r="M28" s="11">
+      <c r="M28" s="8">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="N28" s="96" t="s">
+      <c r="N28" s="58" t="s">
         <v>21</v>
       </c>
-      <c r="O28" s="31"/>
+      <c r="O28" s="58"/>
     </row>
     <row r="29" spans="1:15" ht="15.75" thickBot="1">
       <c r="A29" s="6">
         <v>27</v>
       </c>
-      <c r="B29" s="173"/>
-      <c r="C29" s="51" t="s">
+      <c r="B29" s="100"/>
+      <c r="C29" s="35" t="s">
         <v>100</v>
       </c>
       <c r="D29" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="E29" s="37" t="s">
+      <c r="E29" s="28" t="s">
         <v>91</v>
       </c>
-      <c r="F29" s="37" t="s">
+      <c r="F29" s="28" t="s">
         <v>101</v>
       </c>
-      <c r="G29" s="39" t="s">
+      <c r="G29" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="H29" s="13" t="s">
+      <c r="H29" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="I29" s="37" t="s">
+      <c r="I29" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="J29" s="37" t="s">
+      <c r="J29" s="28" t="s">
         <v>103</v>
       </c>
       <c r="K29" s="7">
@@ -3495,42 +3419,42 @@
       <c r="L29" s="7">
         <v>1</v>
       </c>
-      <c r="M29" s="11">
+      <c r="M29" s="8">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N29" s="96" t="s">
+      <c r="N29" s="58" t="s">
         <v>21</v>
       </c>
-      <c r="O29" s="31"/>
+      <c r="O29" s="58"/>
     </row>
     <row r="30" spans="1:15" ht="15.75" thickBot="1">
       <c r="A30" s="6">
         <v>28</v>
       </c>
-      <c r="B30" s="173"/>
-      <c r="C30" s="51" t="s">
+      <c r="B30" s="100"/>
+      <c r="C30" s="35" t="s">
         <v>105</v>
       </c>
-      <c r="D30" s="37" t="s">
+      <c r="D30" s="28" t="s">
         <v>106</v>
       </c>
-      <c r="E30" s="37" t="s">
+      <c r="E30" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="F30" s="40" t="s">
+      <c r="F30" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="G30" s="39" t="s">
+      <c r="G30" s="29" t="s">
         <v>108</v>
       </c>
-      <c r="H30" s="13" t="s">
+      <c r="H30" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="I30" s="39" t="s">
+      <c r="I30" s="29" t="s">
         <v>110</v>
       </c>
-      <c r="J30" s="37" t="s">
+      <c r="J30" s="28" t="s">
         <v>111</v>
       </c>
       <c r="K30" s="7">
@@ -3539,42 +3463,42 @@
       <c r="L30" s="7">
         <v>1</v>
       </c>
-      <c r="M30" s="11">
+      <c r="M30" s="8">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N30" s="96" t="s">
+      <c r="N30" s="58" t="s">
         <v>21</v>
       </c>
-      <c r="O30" s="31"/>
+      <c r="O30" s="58"/>
     </row>
     <row r="31" spans="1:15" ht="15.75" thickBot="1">
       <c r="A31" s="6">
         <v>29</v>
       </c>
-      <c r="B31" s="173"/>
-      <c r="C31" s="51" t="s">
+      <c r="B31" s="100"/>
+      <c r="C31" s="35" t="s">
         <v>112</v>
       </c>
-      <c r="D31" s="37" t="s">
+      <c r="D31" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="E31" s="37" t="s">
+      <c r="E31" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="F31" s="37" t="s">
+      <c r="F31" s="28" t="s">
         <v>114</v>
       </c>
-      <c r="G31" s="39" t="s">
+      <c r="G31" s="29" t="s">
         <v>115</v>
       </c>
-      <c r="H31" s="13" t="s">
+      <c r="H31" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="I31" s="37" t="s">
+      <c r="I31" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="J31" s="37" t="s">
+      <c r="J31" s="28" t="s">
         <v>117</v>
       </c>
       <c r="K31" s="7">
@@ -3583,579 +3507,562 @@
       <c r="L31" s="7">
         <v>1</v>
       </c>
-      <c r="M31" s="11">
+      <c r="M31" s="8">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N31" s="96" t="s">
+      <c r="N31" s="58" t="s">
         <v>21</v>
       </c>
-      <c r="O31" s="31"/>
+      <c r="O31" s="58"/>
     </row>
     <row r="32" spans="1:15" s="1" customFormat="1" ht="15.75" thickBot="1">
       <c r="A32" s="6">
         <v>30</v>
       </c>
-      <c r="B32" s="174"/>
-      <c r="C32" s="52" t="s">
+      <c r="B32" s="101"/>
+      <c r="C32" s="36" t="s">
         <v>118</v>
       </c>
-      <c r="D32" s="14" t="s">
+      <c r="D32" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="E32" s="45" t="s">
+      <c r="E32" s="31" t="s">
         <v>91</v>
       </c>
-      <c r="F32" s="45" t="s">
+      <c r="F32" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="G32" s="48" t="s">
+      <c r="G32" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="H32" s="17" t="s">
+      <c r="H32" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="I32" s="45" t="s">
+      <c r="I32" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="J32" s="45" t="s">
+      <c r="J32" s="31" t="s">
         <v>122</v>
       </c>
-      <c r="K32" s="14">
+      <c r="K32" s="10">
         <v>100</v>
       </c>
-      <c r="L32" s="17">
+      <c r="L32" s="12">
         <v>8</v>
       </c>
-      <c r="M32" s="15">
+      <c r="M32" s="11">
         <f t="shared" si="1"/>
         <v>48</v>
       </c>
-      <c r="N32" s="118" t="s">
+      <c r="N32" s="75" t="s">
         <v>21</v>
       </c>
-      <c r="O32" s="33"/>
+      <c r="O32" s="75"/>
     </row>
     <row r="33" spans="1:15" ht="15.75" thickBot="1">
       <c r="A33" s="6">
         <v>31</v>
       </c>
-      <c r="B33" s="173" t="s">
+      <c r="B33" s="100" t="s">
         <v>123</v>
       </c>
-      <c r="C33" s="124" t="s">
+      <c r="C33" s="133" t="s">
         <v>185</v>
       </c>
-      <c r="D33" s="132" t="s">
+      <c r="D33" s="137" t="s">
         <v>124</v>
       </c>
-      <c r="E33" s="117" t="s">
+      <c r="E33" s="134" t="s">
         <v>182</v>
       </c>
-      <c r="F33" s="126" t="s">
+      <c r="F33" s="135" t="s">
         <v>183</v>
       </c>
-      <c r="G33" s="127" t="s">
+      <c r="G33" s="136" t="s">
         <v>184</v>
       </c>
-      <c r="H33" s="128" t="s">
+      <c r="H33" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="I33" s="125" t="s">
+      <c r="I33" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="J33" s="128" t="s">
+      <c r="J33" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="K33" s="129">
+      <c r="K33" s="15">
         <v>7</v>
       </c>
-      <c r="L33" s="129">
+      <c r="L33" s="15">
         <v>1</v>
       </c>
-      <c r="M33" s="130">
+      <c r="M33" s="111">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N33" s="131" t="s">
+      <c r="N33" s="112" t="s">
         <v>21</v>
       </c>
-      <c r="O33" s="31"/>
+      <c r="O33" s="112"/>
     </row>
     <row r="34" spans="1:15" ht="15.75" thickBot="1">
       <c r="A34" s="6">
         <v>32</v>
       </c>
-      <c r="B34" s="173"/>
-      <c r="C34" s="51" t="s">
+      <c r="B34" s="100"/>
+      <c r="C34" s="35" t="s">
         <v>125</v>
       </c>
-      <c r="D34" s="37" t="s">
+      <c r="D34" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="E34" s="37" t="s">
+      <c r="E34" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="F34" s="37" t="s">
+      <c r="F34" s="28" t="s">
         <v>128</v>
       </c>
-      <c r="G34" s="39" t="s">
+      <c r="G34" s="29" t="s">
         <v>129</v>
       </c>
-      <c r="H34" s="13" t="s">
+      <c r="H34" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="I34" s="37" t="s">
+      <c r="I34" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="J34" s="39" t="s">
+      <c r="J34" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="K34" s="13">
+      <c r="K34" s="9">
         <v>6</v>
       </c>
-      <c r="L34" s="13">
+      <c r="L34" s="9">
         <v>1</v>
       </c>
-      <c r="M34" s="11">
+      <c r="M34" s="8">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N34" s="96" t="s">
+      <c r="N34" s="58" t="s">
         <v>21</v>
       </c>
-      <c r="O34" s="31"/>
+      <c r="O34" s="58"/>
     </row>
     <row r="35" spans="1:15" ht="15.75" thickBot="1">
       <c r="A35" s="6">
         <v>33</v>
       </c>
-      <c r="B35" s="173"/>
-      <c r="C35" s="119" t="s">
+      <c r="B35" s="100"/>
+      <c r="C35" s="76" t="s">
         <v>170</v>
       </c>
-      <c r="D35" s="120" t="s">
+      <c r="D35" s="77" t="s">
         <v>131</v>
       </c>
-      <c r="E35" s="120" t="s">
+      <c r="E35" s="77" t="s">
         <v>171</v>
       </c>
-      <c r="F35" s="121" t="s">
+      <c r="F35" s="78" t="s">
         <v>173</v>
       </c>
-      <c r="G35" s="106" t="s">
+      <c r="G35" s="68" t="s">
         <v>172</v>
       </c>
-      <c r="H35" s="102"/>
-      <c r="I35" s="106" t="s">
+      <c r="H35" s="64"/>
+      <c r="I35" s="68" t="s">
         <v>19</v>
       </c>
-      <c r="J35" s="107" t="s">
+      <c r="J35" s="69" t="s">
         <v>132</v>
       </c>
-      <c r="K35" s="102">
+      <c r="K35" s="64">
         <v>6</v>
       </c>
-      <c r="L35" s="102">
+      <c r="L35" s="64">
         <v>1</v>
       </c>
-      <c r="M35" s="103">
+      <c r="M35" s="65">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N35" s="122" t="s">
+      <c r="N35" s="79" t="s">
         <v>88</v>
       </c>
-      <c r="O35" s="31"/>
+      <c r="O35" s="79"/>
     </row>
     <row r="36" spans="1:15" ht="15.75" thickBot="1">
       <c r="A36" s="6">
         <v>34</v>
       </c>
-      <c r="B36" s="172" t="s">
+      <c r="B36" s="99" t="s">
         <v>133</v>
       </c>
-      <c r="C36" s="53" t="s">
+      <c r="C36" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="D36" s="54" t="s">
+      <c r="D36" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="E36" s="54" t="s">
+      <c r="E36" s="38" t="s">
         <v>136</v>
       </c>
-      <c r="F36" s="54" t="s">
+      <c r="F36" s="38" t="s">
         <v>136</v>
       </c>
-      <c r="G36" s="54" t="s">
+      <c r="G36" s="38" t="s">
         <v>137</v>
       </c>
-      <c r="H36" s="54" t="s">
+      <c r="H36" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="I36" s="54" t="s">
+      <c r="I36" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="J36" s="54" t="s">
+      <c r="J36" s="38" t="s">
         <v>70</v>
       </c>
-      <c r="K36" s="22">
+      <c r="K36" s="17">
         <v>100</v>
       </c>
-      <c r="L36" s="22">
+      <c r="L36" s="17">
         <v>1</v>
       </c>
-      <c r="M36" s="18">
+      <c r="M36" s="13">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N36" s="123" t="s">
+      <c r="N36" s="80" t="s">
         <v>138</v>
       </c>
-      <c r="O36" s="31"/>
+      <c r="O36" s="80"/>
     </row>
     <row r="37" spans="1:15" ht="15.75" thickBot="1">
       <c r="A37" s="6">
         <v>35</v>
       </c>
-      <c r="B37" s="173"/>
-      <c r="C37" s="55" t="s">
+      <c r="B37" s="100"/>
+      <c r="C37" s="39" t="s">
         <v>139</v>
       </c>
-      <c r="D37" s="56" t="s">
+      <c r="D37" s="40" t="s">
         <v>140</v>
       </c>
-      <c r="E37" s="56" t="s">
+      <c r="E37" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="F37" s="56" t="s">
+      <c r="F37" s="40" t="s">
         <v>141</v>
       </c>
-      <c r="G37" s="56" t="s">
+      <c r="G37" s="40" t="s">
         <v>142</v>
       </c>
-      <c r="H37" s="56" t="s">
+      <c r="H37" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="I37" s="56" t="s">
+      <c r="I37" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="J37" s="57" t="s">
+      <c r="J37" s="41" t="s">
         <v>143</v>
       </c>
-      <c r="K37" s="30">
+      <c r="K37" s="24">
         <v>12</v>
       </c>
-      <c r="L37" s="23">
+      <c r="L37" s="18">
         <v>2</v>
       </c>
-      <c r="M37" s="11">
+      <c r="M37" s="8">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="N37" s="97" t="s">
+      <c r="N37" s="59" t="s">
         <v>144</v>
       </c>
-      <c r="O37" s="31"/>
+      <c r="O37" s="59"/>
     </row>
     <row r="38" spans="1:15" ht="15.75" thickBot="1">
       <c r="A38" s="6">
         <v>36</v>
       </c>
-      <c r="B38" s="173"/>
-      <c r="C38" s="55" t="s">
+      <c r="B38" s="100"/>
+      <c r="C38" s="39" t="s">
         <v>145</v>
       </c>
-      <c r="D38" s="56" t="s">
+      <c r="D38" s="40" t="s">
         <v>146</v>
       </c>
-      <c r="E38" s="56" t="s">
+      <c r="E38" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="F38" s="56" t="s">
+      <c r="F38" s="40" t="s">
         <v>147</v>
       </c>
-      <c r="G38" s="56" t="s">
+      <c r="G38" s="40" t="s">
         <v>137</v>
       </c>
-      <c r="H38" s="56" t="s">
+      <c r="H38" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="I38" s="56" t="s">
+      <c r="I38" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="J38" s="57" t="s">
+      <c r="J38" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="K38" s="30">
+      <c r="K38" s="24">
         <v>10</v>
       </c>
-      <c r="L38" s="23">
+      <c r="L38" s="18">
         <v>1</v>
       </c>
-      <c r="M38" s="11">
+      <c r="M38" s="8">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N38" s="97" t="s">
+      <c r="N38" s="59" t="s">
         <v>138</v>
       </c>
-      <c r="O38" s="31"/>
+      <c r="O38" s="59"/>
     </row>
     <row r="39" spans="1:15" ht="15.75" thickBot="1">
       <c r="A39" s="6">
         <v>37</v>
       </c>
-      <c r="B39" s="173"/>
-      <c r="C39" s="21" t="s">
+      <c r="B39" s="100"/>
+      <c r="C39" s="16" t="s">
         <v>148</v>
       </c>
-      <c r="D39" s="37" t="s">
+      <c r="D39" s="28" t="s">
         <v>149</v>
       </c>
-      <c r="E39" s="37" t="s">
+      <c r="E39" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="F39" s="37" t="s">
+      <c r="F39" s="28" t="s">
         <v>150</v>
       </c>
-      <c r="G39" s="37" t="s">
+      <c r="G39" s="28" t="s">
         <v>151</v>
       </c>
-      <c r="H39" s="37" t="s">
+      <c r="H39" s="28" t="s">
         <v>150</v>
       </c>
-      <c r="I39" s="37" t="s">
+      <c r="I39" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="J39" s="39" t="s">
+      <c r="J39" s="29" t="s">
         <v>143</v>
       </c>
-      <c r="K39" s="13">
+      <c r="K39" s="9">
         <v>20</v>
       </c>
       <c r="L39" s="7">
         <v>1</v>
       </c>
-      <c r="M39" s="11">
+      <c r="M39" s="8">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N39" s="98" t="s">
+      <c r="N39" s="60" t="s">
         <v>21</v>
       </c>
-      <c r="O39" s="31"/>
+      <c r="O39" s="60"/>
     </row>
     <row r="40" spans="1:15" ht="15.75" thickBot="1">
       <c r="A40" s="6">
         <v>38</v>
       </c>
-      <c r="B40" s="173"/>
-      <c r="C40" s="51" t="s">
+      <c r="B40" s="100"/>
+      <c r="C40" s="35" t="s">
         <v>152</v>
       </c>
-      <c r="D40" s="37" t="s">
+      <c r="D40" s="28" t="s">
         <v>153</v>
       </c>
-      <c r="E40" s="37" t="s">
+      <c r="E40" s="28" t="s">
         <v>154</v>
       </c>
-      <c r="F40" s="37" t="s">
+      <c r="F40" s="28" t="s">
         <v>155</v>
       </c>
-      <c r="G40" s="37" t="s">
+      <c r="G40" s="28" t="s">
         <v>156</v>
       </c>
-      <c r="H40" s="13" t="s">
+      <c r="H40" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="I40" s="37" t="s">
+      <c r="I40" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="J40" s="39" t="s">
+      <c r="J40" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="K40" s="13">
+      <c r="K40" s="9">
         <v>15</v>
       </c>
-      <c r="L40" s="13">
+      <c r="L40" s="9">
         <v>2</v>
       </c>
-      <c r="M40" s="11">
+      <c r="M40" s="8">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="N40" s="99" t="s">
+      <c r="N40" s="61" t="s">
         <v>21</v>
       </c>
-      <c r="O40" s="31"/>
+      <c r="O40" s="61"/>
     </row>
     <row r="41" spans="1:15" ht="15.75" thickBot="1">
       <c r="A41" s="6">
         <v>39</v>
       </c>
-      <c r="B41" s="173"/>
-      <c r="C41" s="58" t="s">
+      <c r="B41" s="100"/>
+      <c r="C41" s="42" t="s">
         <v>158</v>
       </c>
-      <c r="D41" s="24"/>
-      <c r="E41" s="59" t="s">
+      <c r="D41" s="19"/>
+      <c r="E41" s="43" t="s">
         <v>159</v>
       </c>
-      <c r="F41" s="24" t="s">
+      <c r="F41" s="19" t="s">
         <v>159</v>
       </c>
-      <c r="G41" s="24"/>
-      <c r="H41" s="24"/>
-      <c r="I41" s="24"/>
-      <c r="J41" s="24"/>
-      <c r="K41" s="24"/>
-      <c r="L41" s="24">
+      <c r="G41" s="19"/>
+      <c r="H41" s="19"/>
+      <c r="I41" s="19"/>
+      <c r="J41" s="19"/>
+      <c r="K41" s="19"/>
+      <c r="L41" s="19">
         <v>5</v>
       </c>
-      <c r="M41" s="11">
+      <c r="M41" s="8">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
-      <c r="N41" s="100" t="s">
+      <c r="N41" s="62" t="s">
         <v>19</v>
       </c>
-      <c r="O41" s="31"/>
+      <c r="O41" s="62"/>
     </row>
     <row r="42" spans="1:15" ht="15.75" thickBot="1">
-      <c r="A42" s="25">
+      <c r="A42" s="20">
         <v>40</v>
       </c>
-      <c r="B42" s="174"/>
-      <c r="C42" s="60" t="s">
+      <c r="B42" s="101"/>
+      <c r="C42" s="44" t="s">
         <v>160</v>
       </c>
-      <c r="D42" s="26"/>
-      <c r="E42" s="61" t="s">
+      <c r="D42" s="21"/>
+      <c r="E42" s="45" t="s">
         <v>161</v>
       </c>
-      <c r="F42" s="26" t="s">
+      <c r="F42" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="G42" s="26"/>
-      <c r="H42" s="26"/>
-      <c r="I42" s="26"/>
-      <c r="J42" s="26"/>
-      <c r="K42" s="26"/>
-      <c r="L42" s="26">
+      <c r="G42" s="21"/>
+      <c r="H42" s="21"/>
+      <c r="I42" s="21"/>
+      <c r="J42" s="21"/>
+      <c r="K42" s="21"/>
+      <c r="L42" s="21">
         <v>5</v>
       </c>
-      <c r="M42" s="15">
+      <c r="M42" s="11">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
-      <c r="N42" s="101" t="s">
+      <c r="N42" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="O42" s="31"/>
-    </row>
-    <row r="43" spans="1:15" ht="16.5" thickBot="1">
+      <c r="O42" s="63"/>
+    </row>
+    <row r="43" spans="1:15">
       <c r="A43"/>
-      <c r="C43" s="27"/>
-      <c r="D43" s="27"/>
-      <c r="E43" s="27"/>
-      <c r="F43" s="27"/>
-      <c r="G43" s="27"/>
-      <c r="H43" s="27"/>
-      <c r="I43" s="27"/>
-      <c r="J43" s="27"/>
-      <c r="K43" s="27"/>
-      <c r="L43" s="74"/>
-      <c r="M43" s="74"/>
-      <c r="N43" s="74"/>
-      <c r="O43" s="31"/>
+      <c r="C43" s="22"/>
+      <c r="D43" s="22"/>
+      <c r="E43" s="22"/>
+      <c r="F43" s="22"/>
+      <c r="G43" s="22"/>
+      <c r="H43" s="22"/>
+      <c r="I43" s="22"/>
+      <c r="J43" s="22"/>
+      <c r="K43" s="22"/>
+      <c r="O43" s="25"/>
     </row>
     <row r="44" spans="1:15">
       <c r="A44"/>
-      <c r="C44" s="27"/>
-      <c r="D44" s="27"/>
-      <c r="E44" s="27"/>
-      <c r="F44" s="27"/>
-      <c r="G44" s="27"/>
-      <c r="H44" s="27"/>
-      <c r="I44" s="27"/>
-      <c r="J44" s="27"/>
-      <c r="K44" s="27"/>
-      <c r="O44" s="31"/>
+      <c r="C44" s="22"/>
+      <c r="D44" s="22"/>
+      <c r="E44" s="22"/>
+      <c r="F44" s="22"/>
+      <c r="G44" s="22"/>
+      <c r="H44" s="22"/>
+      <c r="I44" s="22"/>
+      <c r="J44" s="22"/>
+      <c r="K44" s="22"/>
     </row>
     <row r="45" spans="1:15">
       <c r="A45"/>
-      <c r="O45" s="31"/>
     </row>
     <row r="46" spans="1:15">
       <c r="A46"/>
-      <c r="O46" s="31"/>
     </row>
     <row r="47" spans="1:15">
       <c r="A47"/>
-      <c r="O47" s="31"/>
     </row>
     <row r="48" spans="1:15">
       <c r="A48"/>
-      <c r="O48" s="31"/>
     </row>
     <row r="49" spans="1:15">
       <c r="A49"/>
-      <c r="O49" s="31"/>
     </row>
     <row r="50" spans="1:15">
       <c r="A50"/>
-      <c r="O50" s="31"/>
     </row>
     <row r="51" spans="1:15">
       <c r="A51"/>
-      <c r="O51" s="31"/>
     </row>
     <row r="52" spans="1:15" ht="15.75" customHeight="1">
       <c r="A52"/>
-      <c r="N52" s="71"/>
-      <c r="O52" s="31"/>
+      <c r="N52" s="53"/>
+      <c r="O52" s="53"/>
     </row>
     <row r="53" spans="1:15">
       <c r="A53"/>
-      <c r="O53" s="31"/>
     </row>
     <row r="54" spans="1:15">
       <c r="A54"/>
-      <c r="O54" s="31"/>
     </row>
     <row r="55" spans="1:15">
       <c r="A55"/>
-      <c r="O55" s="31"/>
     </row>
     <row r="56" spans="1:15">
       <c r="A56"/>
-      <c r="O56" s="31"/>
     </row>
     <row r="57" spans="1:15">
       <c r="A57"/>
-      <c r="O57" s="31"/>
     </row>
     <row r="58" spans="1:15">
-      <c r="H58" s="28"/>
+      <c r="H58" s="23"/>
     </row>
     <row r="59" spans="1:15">
-      <c r="H59" s="28"/>
+      <c r="H59" s="23"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="A1:N1"/>
-    <mergeCell ref="L43:N43"/>
+  <mergeCells count="7">
     <mergeCell ref="B3:B13"/>
     <mergeCell ref="B14:B17"/>
     <mergeCell ref="B22:B32"/>
     <mergeCell ref="B33:B35"/>
     <mergeCell ref="B36:B42"/>
     <mergeCell ref="B20:B21"/>
+    <mergeCell ref="A1:O1"/>
   </mergeCells>
   <phoneticPr fontId="20" type="noConversion"/>
-  <conditionalFormatting sqref="N21">
-    <cfRule type="dataBar" priority="38">
+  <conditionalFormatting sqref="N21:O21">
+    <cfRule type="dataBar" priority="39">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4169,7 +4076,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L36:M36">
-    <cfRule type="colorScale" priority="4">
+    <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4181,7 +4088,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L41">
-    <cfRule type="colorScale" priority="10">
+    <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4191,7 +4098,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="11">
+    <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4203,7 +4110,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L42">
-    <cfRule type="colorScale" priority="13">
+    <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4213,7 +4120,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="14">
+    <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4225,7 +4132,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N3:N6">
-    <cfRule type="dataBar" priority="40">
+    <cfRule type="dataBar" priority="41">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4238,8 +4145,8 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N32">
-    <cfRule type="dataBar" priority="37">
+  <conditionalFormatting sqref="N32:O32">
+    <cfRule type="dataBar" priority="38">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -4253,7 +4160,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L12:L35 L40 M3:M42">
-    <cfRule type="colorScale" priority="50">
+    <cfRule type="colorScale" priority="51">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4265,7 +4172,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L8:L11">
-    <cfRule type="colorScale" priority="51">
+    <cfRule type="colorScale" priority="52">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4277,7 +4184,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L3:M42">
-    <cfRule type="colorScale" priority="61">
+    <cfRule type="colorScale" priority="62">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4286,6 +4193,20 @@
         <color rgb="FFFFEB84"/>
         <color rgb="FFF8696B"/>
       </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O4 O6">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{C3E05EE2-5FD9-4A95-BA99-400BB7B88162}</x14:id>
+        </ext>
+      </extLst>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
@@ -4320,11 +4241,11 @@
     <hyperlink ref="N25" r:id="rId29" xr:uid="{EA5E5506-441F-4FE0-B453-D92044CD3CD6}"/>
     <hyperlink ref="N27" r:id="rId30" xr:uid="{8D8C1B68-82FF-4307-AFCC-0412DDB5B0BE}"/>
     <hyperlink ref="N4" r:id="rId31" xr:uid="{2EF0B57E-A4CF-4AC0-9358-948CDF39D8B4}"/>
-    <hyperlink ref="N5" r:id="rId32" xr:uid="{ECCB4777-894F-4969-BB30-3BB1C2789276}"/>
-    <hyperlink ref="C15" r:id="rId33" xr:uid="{44A99C6C-4AC4-4D03-96BE-D592031C9536}"/>
-    <hyperlink ref="N15" r:id="rId34" xr:uid="{1A7B0E41-616E-45F1-BF6C-4CBB22A55EC6}"/>
-    <hyperlink ref="N19" r:id="rId35" xr:uid="{0E9DC705-3503-4FA0-87A9-DF2A5B60045D}"/>
-    <hyperlink ref="N16" r:id="rId36" xr:uid="{E7A9FE43-2492-4F96-944F-8153D9DD3BC5}"/>
+    <hyperlink ref="C15" r:id="rId32" xr:uid="{44A99C6C-4AC4-4D03-96BE-D592031C9536}"/>
+    <hyperlink ref="N15" r:id="rId33" xr:uid="{1A7B0E41-616E-45F1-BF6C-4CBB22A55EC6}"/>
+    <hyperlink ref="N19" r:id="rId34" xr:uid="{0E9DC705-3503-4FA0-87A9-DF2A5B60045D}"/>
+    <hyperlink ref="N16" r:id="rId35" xr:uid="{E7A9FE43-2492-4F96-944F-8153D9DD3BC5}"/>
+    <hyperlink ref="N5" r:id="rId36" xr:uid="{307763C7-77E9-4298-8365-93694DC5AA9D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId37"/>
@@ -4342,7 +4263,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>N21</xm:sqref>
+          <xm:sqref>N21:O21</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{94E20060-874B-439F-8FDA-33B3DD39FFE6}">
@@ -4368,7 +4289,20 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>N32</xm:sqref>
+          <xm:sqref>N32:O32</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{C3E05EE2-5FD9-4A95-BA99-400BB7B88162}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>O4 O6</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/Deliverables/Interface_Board/BOM/NEW-6 Prototypes_Interface_Board.xlsx
+++ b/Deliverables/Interface_Board/BOM/NEW-6 Prototypes_Interface_Board.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ChristianRaun-EthercatDesign\Deliverables\Interface_Board\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{790979A6-2E27-47B4-AC3E-43B85D4D8B31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4AC0271-9438-4137-BC8F-87A3C52BEC57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="250">
   <si>
     <t>Bill of Material (BOM) for Interface_Board</t>
   </si>
@@ -63,9 +63,6 @@
   </si>
   <si>
     <t>Value</t>
-  </si>
-  <si>
-    <t>LCSC/MOQ</t>
   </si>
   <si>
     <t>Quantity (Per Board)</t>
@@ -653,16 +650,6 @@
   </si>
   <si>
     <t>100R</t>
-  </si>
-  <si>
-    <t>0603WAF150LT5E</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Resistors 75V150mΩ 0603 Chip Resistor - Surface Mount ROHS
-</t>
-  </si>
-  <si>
-    <t>C45879</t>
   </si>
   <si>
     <t>150mR</t>
@@ -799,21 +786,6 @@
     <t>Increase Quantity +2</t>
   </si>
   <si>
-    <r>
-      <t>R1,R#,R#1,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>R#8,R#9</t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">CAP CER 0.47UF 100V X7S 0805
 </t>
   </si>
@@ -822,6 +794,25 @@
   </si>
   <si>
     <t>Voltage Rating and Package Change 0805</t>
+  </si>
+  <si>
+    <t>R1,R#,R#1</t>
+  </si>
+  <si>
+    <t>C37936</t>
+  </si>
+  <si>
+    <t>1206W4F150LT5E</t>
+  </si>
+  <si>
+    <t>Res1206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">±1% 1/4W Thick Film Resistors 200V ±800ppm/℃ -55℃~+155℃ 150mΩ 1206 Chip Resistor - Surface Mount ROHS
+</t>
+  </si>
+  <si>
+    <t>Wattage Rating and Package Change 1206</t>
   </si>
 </sst>
 </file>
@@ -831,12 +822,19 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.0000"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1424,24 +1422,24 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="146">
+  <cellXfs count="152">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1450,7 +1448,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1459,16 +1457,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1480,50 +1478,47 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1544,93 +1539,93 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="5" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="5" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="21" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="21" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="21" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="21" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="21" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="21" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="21" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="20" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="20" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="27" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="27" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="26" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1639,10 +1634,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="4" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
@@ -1654,16 +1649,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="25" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="25" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1675,76 +1670,52 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="6" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="6" borderId="21" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="20" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="21" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="16" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="16" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1753,10 +1724,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="23" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="23" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1765,51 +1736,51 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="25" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="25" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="26" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="26" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1822,32 +1793,75 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="20" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="21" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2125,12 +2139,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AD59"/>
+  <dimension ref="A1:AC59"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="14.42578125" customWidth="1"/>
-    <col min="3" max="3" width="77.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="103.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="34.7109375" customWidth="1"/>
     <col min="5" max="5" width="21" customWidth="1"/>
     <col min="6" max="6" width="29" customWidth="1"/>
@@ -2138,33 +2152,31 @@
     <col min="8" max="8" width="15.28515625" style="2" customWidth="1"/>
     <col min="9" max="9" width="21.5703125" customWidth="1"/>
     <col min="10" max="10" width="7" customWidth="1"/>
-    <col min="11" max="11" width="11.5703125" customWidth="1"/>
-    <col min="12" max="12" width="21.85546875" customWidth="1"/>
-    <col min="13" max="13" width="14.140625" customWidth="1"/>
-    <col min="14" max="14" width="16.28515625" customWidth="1"/>
-    <col min="15" max="15" width="37.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.85546875" customWidth="1"/>
+    <col min="12" max="12" width="14.140625" customWidth="1"/>
+    <col min="13" max="13" width="16.28515625" customWidth="1"/>
+    <col min="14" max="14" width="37.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" ht="16.5" thickBot="1">
-      <c r="A1" s="96" t="s">
+    <row r="1" spans="1:29" ht="16.5" thickBot="1">
+      <c r="A1" s="138" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="97"/>
-      <c r="H1" s="97"/>
-      <c r="I1" s="97"/>
-      <c r="J1" s="97"/>
-      <c r="K1" s="97"/>
-      <c r="L1" s="97"/>
-      <c r="M1" s="97"/>
-      <c r="N1" s="97"/>
-      <c r="O1" s="98"/>
-    </row>
-    <row r="2" spans="1:30" s="1" customFormat="1" ht="16.5" thickBot="1">
+      <c r="B1" s="139"/>
+      <c r="C1" s="139"/>
+      <c r="D1" s="139"/>
+      <c r="E1" s="139"/>
+      <c r="F1" s="139"/>
+      <c r="G1" s="139"/>
+      <c r="H1" s="139"/>
+      <c r="I1" s="139"/>
+      <c r="J1" s="139"/>
+      <c r="K1" s="139"/>
+      <c r="L1" s="139"/>
+      <c r="M1" s="139"/>
+      <c r="N1" s="140"/>
+    </row>
+    <row r="2" spans="1:29" s="1" customFormat="1" ht="16.5" thickBot="1">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -2198,18 +2210,16 @@
       <c r="K2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="M2" s="51" t="s">
-        <v>181</v>
-      </c>
-      <c r="N2" s="56" t="s">
+      <c r="L2" s="50" t="s">
         <v>180</v>
       </c>
-      <c r="O2" s="142" t="s">
-        <v>243</v>
-      </c>
+      <c r="M2" s="55" t="s">
+        <v>179</v>
+      </c>
+      <c r="N2" s="131" t="s">
+        <v>239</v>
+      </c>
+      <c r="O2"/>
       <c r="P2"/>
       <c r="Q2"/>
       <c r="R2"/>
@@ -2224,1761 +2234,1644 @@
       <c r="AA2"/>
       <c r="AB2"/>
       <c r="AC2"/>
-      <c r="AD2"/>
-    </row>
-    <row r="3" spans="1:30" ht="15.75" thickBot="1">
+    </row>
+    <row r="3" spans="1:29" ht="15.75" thickBot="1">
       <c r="A3" s="6">
         <v>1</v>
       </c>
-      <c r="B3" s="99" t="s">
+      <c r="B3" s="135" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="83" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="84" t="s">
+      <c r="D3" s="129" t="s">
+        <v>238</v>
+      </c>
+      <c r="E3" s="84" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="138" t="s">
-        <v>242</v>
-      </c>
-      <c r="E3" s="85" t="s">
+      <c r="F3" s="84" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="85" t="s">
+      <c r="G3" s="84" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="85" t="s">
+      <c r="H3" s="85" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="86" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" s="87" t="s">
+      <c r="I3" s="86" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="84" t="s">
         <v>19</v>
       </c>
-      <c r="J3" s="85" t="s">
+      <c r="K3" s="87">
+        <v>6</v>
+      </c>
+      <c r="L3" s="87">
+        <f>K3*6</f>
+        <v>36</v>
+      </c>
+      <c r="M3" s="88" t="s">
         <v>20</v>
       </c>
-      <c r="K3" s="88">
-        <v>50</v>
-      </c>
-      <c r="L3" s="88">
-        <v>6</v>
-      </c>
-      <c r="M3" s="88">
-        <f>L3*6</f>
-        <v>36</v>
-      </c>
-      <c r="N3" s="89" t="s">
-        <v>21</v>
-      </c>
-      <c r="O3" s="141" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="4" spans="1:30" ht="15.75" thickBot="1">
+      <c r="N3" s="130" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" ht="15.75" thickBot="1">
       <c r="A4" s="6">
         <v>2</v>
       </c>
-      <c r="B4" s="100"/>
-      <c r="C4" s="102" t="s">
+      <c r="B4" s="136"/>
+      <c r="C4" s="93" t="s">
+        <v>205</v>
+      </c>
+      <c r="D4" s="115" t="s">
+        <v>206</v>
+      </c>
+      <c r="E4" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="53" t="s">
+        <v>204</v>
+      </c>
+      <c r="G4" s="53" t="s">
+        <v>207</v>
+      </c>
+      <c r="H4" s="94" t="s">
+        <v>208</v>
+      </c>
+      <c r="I4" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" s="53" t="s">
         <v>209</v>
       </c>
-      <c r="D4" s="124" t="s">
-        <v>210</v>
-      </c>
-      <c r="E4" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="54" t="s">
-        <v>208</v>
-      </c>
-      <c r="G4" s="54" t="s">
-        <v>211</v>
-      </c>
-      <c r="H4" s="103" t="s">
-        <v>212</v>
-      </c>
-      <c r="I4" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="J4" s="54" t="s">
-        <v>213</v>
-      </c>
       <c r="K4" s="7">
+        <v>1</v>
+      </c>
+      <c r="L4" s="7">
+        <f t="shared" ref="L4:L5" si="0">K4*6</f>
+        <v>6</v>
+      </c>
+      <c r="M4" s="95" t="s">
         <v>20</v>
       </c>
-      <c r="L4" s="7">
-        <v>1</v>
-      </c>
-      <c r="M4" s="7">
-        <f t="shared" ref="M4:M5" si="0">L4*6</f>
-        <v>6</v>
-      </c>
-      <c r="N4" s="104" t="s">
-        <v>21</v>
-      </c>
-      <c r="O4" s="104"/>
-    </row>
-    <row r="5" spans="1:30" ht="15.75" thickBot="1">
+      <c r="N4" s="95"/>
+    </row>
+    <row r="5" spans="1:29" ht="15.75" thickBot="1">
       <c r="A5" s="6">
         <v>3</v>
       </c>
-      <c r="B5" s="100"/>
-      <c r="C5" s="144" t="s">
-        <v>246</v>
-      </c>
-      <c r="D5" s="145" t="s">
-        <v>216</v>
-      </c>
-      <c r="E5" s="81" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="82" t="s">
-        <v>214</v>
-      </c>
-      <c r="G5" s="91" t="s">
-        <v>38</v>
-      </c>
-      <c r="H5" s="90" t="s">
-        <v>247</v>
-      </c>
-      <c r="I5" s="91" t="s">
-        <v>19</v>
-      </c>
-      <c r="J5" s="82" t="s">
-        <v>215</v>
-      </c>
-      <c r="K5" s="83">
-        <v>15</v>
-      </c>
-      <c r="L5" s="83">
+      <c r="B5" s="136"/>
+      <c r="C5" s="133" t="s">
+        <v>241</v>
+      </c>
+      <c r="D5" s="134" t="s">
+        <v>212</v>
+      </c>
+      <c r="E5" s="80" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="81" t="s">
+        <v>210</v>
+      </c>
+      <c r="G5" s="90" t="s">
+        <v>37</v>
+      </c>
+      <c r="H5" s="89" t="s">
+        <v>242</v>
+      </c>
+      <c r="I5" s="90" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" s="81" t="s">
+        <v>211</v>
+      </c>
+      <c r="K5" s="82">
         <v>2</v>
       </c>
-      <c r="M5" s="83">
+      <c r="L5" s="82">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="N5" s="92" t="s">
-        <v>21</v>
-      </c>
-      <c r="O5" s="143" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="6" spans="1:30" ht="15.75" thickBot="1">
+      <c r="M5" s="91" t="s">
+        <v>20</v>
+      </c>
+      <c r="N5" s="132" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29" ht="15.75" thickBot="1">
       <c r="A6" s="6">
         <v>4</v>
       </c>
-      <c r="B6" s="100"/>
-      <c r="C6" s="35" t="s">
+      <c r="B6" s="136"/>
+      <c r="C6" s="34" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="28" t="s">
+      <c r="E6" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="28" t="s">
+      <c r="F6" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="28" t="s">
+      <c r="G6" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="G6" s="28" t="s">
+      <c r="H6" s="96" t="s">
         <v>26</v>
       </c>
-      <c r="H6" s="105" t="s">
+      <c r="I6" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="I6" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="J6" s="28" t="s">
-        <v>28</v>
-      </c>
       <c r="K6" s="7">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L6" s="7">
-        <v>1</v>
-      </c>
-      <c r="M6" s="7">
-        <f t="shared" ref="M6:M42" si="1">L6*6</f>
+        <f t="shared" ref="L6:L42" si="1">K6*6</f>
         <v>6</v>
       </c>
-      <c r="N6" s="106" t="s">
-        <v>21</v>
-      </c>
-      <c r="O6" s="106"/>
-    </row>
-    <row r="7" spans="1:30" ht="15.75" thickBot="1">
+      <c r="M6" s="97" t="s">
+        <v>20</v>
+      </c>
+      <c r="N6" s="97"/>
+    </row>
+    <row r="7" spans="1:29" ht="15.75" thickBot="1">
       <c r="A7" s="6">
         <v>5</v>
       </c>
-      <c r="B7" s="100"/>
-      <c r="C7" s="35" t="s">
+      <c r="B7" s="136"/>
+      <c r="C7" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="28" t="s">
+      <c r="E7" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="F7" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="30" t="s">
+      <c r="G7" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="G7" s="28" t="s">
+      <c r="H7" s="96" t="s">
         <v>32</v>
       </c>
-      <c r="H7" s="105" t="s">
+      <c r="I7" s="96" t="s">
         <v>33</v>
       </c>
-      <c r="I7" s="105" t="s">
+      <c r="J7" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="J7" s="28" t="s">
-        <v>35</v>
-      </c>
       <c r="K7" s="7">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="L7" s="7">
-        <v>8</v>
-      </c>
-      <c r="M7" s="7">
         <f t="shared" si="1"/>
         <v>48</v>
       </c>
-      <c r="N7" s="107" t="s">
-        <v>21</v>
-      </c>
-      <c r="O7" s="107"/>
-    </row>
-    <row r="8" spans="1:30" ht="15.75" thickBot="1">
+      <c r="M7" s="98" t="s">
+        <v>20</v>
+      </c>
+      <c r="N7" s="98"/>
+    </row>
+    <row r="8" spans="1:29" ht="15.75" thickBot="1">
       <c r="A8" s="6">
         <v>6</v>
       </c>
-      <c r="B8" s="100"/>
-      <c r="C8" s="35" t="s">
+      <c r="B8" s="136"/>
+      <c r="C8" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="112" t="s">
+        <v>237</v>
+      </c>
+      <c r="E8" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="121" t="s">
-        <v>241</v>
-      </c>
-      <c r="E8" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8" s="30" t="s">
+      <c r="G8" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="G8" s="29" t="s">
+      <c r="H8" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="I8" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="I8" s="28" t="s">
+      <c r="J8" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="J8" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="K8" s="7">
-        <v>50</v>
-      </c>
-      <c r="L8" s="9">
+      <c r="K8" s="9">
         <v>3</v>
       </c>
-      <c r="M8" s="7">
+      <c r="L8" s="7">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="N8" s="58" t="s">
-        <v>21</v>
-      </c>
-      <c r="O8" s="58"/>
-    </row>
-    <row r="9" spans="1:30" ht="15.75" thickBot="1">
+      <c r="M8" s="57" t="s">
+        <v>20</v>
+      </c>
+      <c r="N8" s="57"/>
+    </row>
+    <row r="9" spans="1:29" ht="15.75" thickBot="1">
       <c r="A9" s="6">
         <v>7</v>
       </c>
-      <c r="B9" s="100"/>
-      <c r="C9" s="35" t="s">
+      <c r="B9" s="136"/>
+      <c r="C9" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="D9" s="28" t="s">
+      <c r="E9" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="E9" s="28" t="s">
+      <c r="F9" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="F9" s="28" t="s">
+      <c r="G9" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="29" t="s">
+      <c r="H9" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="I9" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="I9" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="J9" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="K9" s="7">
-        <v>10</v>
-      </c>
-      <c r="L9" s="9">
+      <c r="K9" s="9">
         <v>1</v>
       </c>
-      <c r="M9" s="7">
+      <c r="L9" s="7">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N9" s="58" t="s">
-        <v>21</v>
-      </c>
-      <c r="O9" s="58"/>
-    </row>
-    <row r="10" spans="1:30" ht="15.75" thickBot="1">
+      <c r="M9" s="57" t="s">
+        <v>20</v>
+      </c>
+      <c r="N9" s="57"/>
+    </row>
+    <row r="10" spans="1:29" ht="15.75" thickBot="1">
       <c r="A10" s="6">
         <v>8</v>
       </c>
-      <c r="B10" s="100"/>
-      <c r="C10" s="35" t="s">
+      <c r="B10" s="136"/>
+      <c r="C10" s="34" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="112" t="s">
+        <v>236</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="121" t="s">
-        <v>240</v>
-      </c>
-      <c r="E10" s="28" t="s">
-        <v>44</v>
-      </c>
-      <c r="F10" s="28" t="s">
+      <c r="G10" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="H10" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="G10" s="29" t="s">
-        <v>46</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="I10" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="J10" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="K10" s="7">
-        <v>12</v>
-      </c>
-      <c r="L10" s="9">
+      <c r="I10" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="K10" s="9">
         <v>3</v>
       </c>
-      <c r="M10" s="7">
+      <c r="L10" s="7">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="N10" s="58" t="s">
-        <v>21</v>
-      </c>
-      <c r="O10" s="58"/>
-    </row>
-    <row r="11" spans="1:30" ht="15.75" thickBot="1">
+      <c r="M10" s="57" t="s">
+        <v>20</v>
+      </c>
+      <c r="N10" s="57"/>
+    </row>
+    <row r="11" spans="1:29" ht="15.75" thickBot="1">
       <c r="A11" s="6">
         <v>9</v>
       </c>
-      <c r="B11" s="100"/>
-      <c r="C11" s="108" t="s">
+      <c r="B11" s="136"/>
+      <c r="C11" s="99" t="s">
+        <v>161</v>
+      </c>
+      <c r="D11" s="51" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" s="51" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="51" t="s">
         <v>162</v>
       </c>
-      <c r="D11" s="52" t="s">
+      <c r="G11" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="H11" s="54" t="s">
+        <v>233</v>
+      </c>
+      <c r="I11" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J11" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="52" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" s="52" t="s">
-        <v>163</v>
-      </c>
-      <c r="G11" s="29" t="s">
-        <v>26</v>
-      </c>
-      <c r="H11" s="55" t="s">
-        <v>237</v>
-      </c>
-      <c r="I11" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="J11" s="28" t="s">
-        <v>53</v>
-      </c>
-      <c r="K11" s="7">
-        <v>20</v>
-      </c>
-      <c r="L11" s="9">
+      <c r="K11" s="9">
         <v>1</v>
       </c>
-      <c r="M11" s="7">
+      <c r="L11" s="7">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N11" s="57" t="s">
-        <v>21</v>
-      </c>
-      <c r="O11" s="57"/>
-    </row>
-    <row r="12" spans="1:30" ht="15.75" thickBot="1">
+      <c r="M11" s="56" t="s">
+        <v>20</v>
+      </c>
+      <c r="N11" s="56"/>
+    </row>
+    <row r="12" spans="1:29" ht="15.75" thickBot="1">
       <c r="A12" s="6">
         <v>10</v>
       </c>
-      <c r="B12" s="100"/>
-      <c r="C12" s="35" t="s">
+      <c r="B12" s="136"/>
+      <c r="C12" s="34" t="s">
+        <v>163</v>
+      </c>
+      <c r="D12" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" s="27" t="s">
         <v>164</v>
       </c>
-      <c r="D12" s="28" t="s">
+      <c r="G12" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="H12" s="54" t="s">
+        <v>234</v>
+      </c>
+      <c r="I12" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J12" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="E12" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="F12" s="28" t="s">
-        <v>165</v>
-      </c>
-      <c r="G12" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="H12" s="55" t="s">
-        <v>238</v>
-      </c>
-      <c r="I12" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="J12" s="28" t="s">
-        <v>55</v>
-      </c>
-      <c r="K12" s="7">
-        <v>10</v>
-      </c>
-      <c r="L12" s="9">
+      <c r="K12" s="9">
         <v>1</v>
       </c>
-      <c r="M12" s="7">
+      <c r="L12" s="7">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N12" s="57" t="s">
-        <v>21</v>
-      </c>
-      <c r="O12" s="57"/>
-    </row>
-    <row r="13" spans="1:30" ht="15.75" thickBot="1">
+      <c r="M12" s="56" t="s">
+        <v>20</v>
+      </c>
+      <c r="N12" s="56"/>
+    </row>
+    <row r="13" spans="1:29" ht="15.75" thickBot="1">
       <c r="A13" s="6">
         <v>11</v>
       </c>
-      <c r="B13" s="101"/>
-      <c r="C13" s="36" t="s">
+      <c r="B13" s="137"/>
+      <c r="C13" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="D13" s="31" t="s">
+      <c r="E13" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="E13" s="31" t="s">
+      <c r="F13" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="F13" s="31" t="s">
+      <c r="G13" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="G13" s="32" t="s">
+      <c r="H13" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="H13" s="12" t="s">
+      <c r="I13" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="J13" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="I13" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="J13" s="31" t="s">
-        <v>62</v>
-      </c>
-      <c r="K13" s="10">
-        <v>50</v>
-      </c>
-      <c r="L13" s="12">
+      <c r="K13" s="12">
         <v>1</v>
       </c>
-      <c r="M13" s="10">
+      <c r="L13" s="10">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N13" s="109" t="s">
-        <v>21</v>
-      </c>
-      <c r="O13" s="109"/>
-    </row>
-    <row r="14" spans="1:30" ht="15.75" thickBot="1">
+      <c r="M13" s="100" t="s">
+        <v>20</v>
+      </c>
+      <c r="N13" s="100"/>
+    </row>
+    <row r="14" spans="1:29" ht="15.75" thickBot="1">
       <c r="A14" s="6">
         <v>12</v>
       </c>
-      <c r="B14" s="100" t="s">
+      <c r="B14" s="136" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" s="101" t="s">
         <v>63</v>
       </c>
-      <c r="C14" s="110" t="s">
+      <c r="D14" s="32" t="s">
         <v>64</v>
       </c>
-      <c r="D14" s="33" t="s">
+      <c r="E14" s="32" t="s">
         <v>65</v>
       </c>
-      <c r="E14" s="33" t="s">
+      <c r="F14" s="32" t="s">
         <v>66</v>
       </c>
-      <c r="F14" s="33" t="s">
+      <c r="G14" s="32" t="s">
         <v>67</v>
       </c>
-      <c r="G14" s="33" t="s">
+      <c r="H14" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="H14" s="15" t="s">
+      <c r="I14" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="J14" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="I14" s="34" t="s">
-        <v>19</v>
-      </c>
-      <c r="J14" s="34" t="s">
-        <v>70</v>
-      </c>
-      <c r="K14" s="111">
-        <v>7</v>
-      </c>
-      <c r="L14" s="15">
+      <c r="K14" s="15">
         <v>1</v>
       </c>
-      <c r="M14" s="111">
+      <c r="L14" s="102">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N14" s="112" t="s">
-        <v>21</v>
-      </c>
-      <c r="O14" s="112"/>
-    </row>
-    <row r="15" spans="1:30" ht="15.75" thickBot="1">
+      <c r="M14" s="103" t="s">
+        <v>20</v>
+      </c>
+      <c r="N14" s="103"/>
+    </row>
+    <row r="15" spans="1:29" ht="15.75" thickBot="1">
       <c r="A15" s="6">
         <v>13</v>
       </c>
-      <c r="B15" s="100"/>
-      <c r="C15" s="35" t="s">
-        <v>220</v>
-      </c>
-      <c r="D15" s="121" t="s">
-        <v>219</v>
-      </c>
-      <c r="E15" s="54" t="s">
+      <c r="B15" s="136"/>
+      <c r="C15" s="34" t="s">
+        <v>216</v>
+      </c>
+      <c r="D15" s="112" t="s">
+        <v>215</v>
+      </c>
+      <c r="E15" s="53" t="s">
+        <v>214</v>
+      </c>
+      <c r="F15" s="53" t="s">
+        <v>213</v>
+      </c>
+      <c r="G15" s="53" t="s">
+        <v>217</v>
+      </c>
+      <c r="H15" s="104" t="s">
         <v>218</v>
       </c>
-      <c r="F15" s="54" t="s">
-        <v>217</v>
-      </c>
-      <c r="G15" s="54" t="s">
-        <v>221</v>
-      </c>
-      <c r="H15" s="113" t="s">
-        <v>222</v>
-      </c>
-      <c r="I15" s="55" t="s">
-        <v>19</v>
-      </c>
-      <c r="J15" s="55" t="s">
-        <v>70</v>
-      </c>
-      <c r="K15" s="7">
-        <v>50</v>
-      </c>
-      <c r="L15" s="9">
+      <c r="I15" s="54" t="s">
+        <v>18</v>
+      </c>
+      <c r="J15" s="54" t="s">
+        <v>69</v>
+      </c>
+      <c r="K15" s="9">
         <v>1</v>
       </c>
-      <c r="M15" s="7">
+      <c r="L15" s="7">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N15" s="57" t="s">
-        <v>21</v>
-      </c>
-      <c r="O15" s="57"/>
-    </row>
-    <row r="16" spans="1:30" ht="15.75" thickBot="1">
+      <c r="M15" s="56" t="s">
+        <v>20</v>
+      </c>
+      <c r="N15" s="56"/>
+    </row>
+    <row r="16" spans="1:29" ht="15.75" thickBot="1">
       <c r="A16" s="6">
         <v>14</v>
       </c>
-      <c r="B16" s="100"/>
-      <c r="C16" s="102" t="s">
-        <v>234</v>
-      </c>
-      <c r="D16" s="121" t="s">
-        <v>233</v>
-      </c>
-      <c r="E16" s="54" t="s">
+      <c r="B16" s="136"/>
+      <c r="C16" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="D16" s="112" t="s">
+        <v>229</v>
+      </c>
+      <c r="E16" s="53" t="s">
+        <v>228</v>
+      </c>
+      <c r="F16" s="53" t="s">
+        <v>227</v>
+      </c>
+      <c r="G16" s="53" t="s">
+        <v>231</v>
+      </c>
+      <c r="H16" s="104" t="s">
         <v>232</v>
       </c>
-      <c r="F16" s="54" t="s">
-        <v>231</v>
-      </c>
-      <c r="G16" s="54" t="s">
-        <v>235</v>
-      </c>
-      <c r="H16" s="113" t="s">
-        <v>236</v>
-      </c>
-      <c r="I16" s="55" t="s">
-        <v>19</v>
-      </c>
-      <c r="J16" s="55" t="s">
-        <v>70</v>
-      </c>
-      <c r="K16" s="7">
-        <v>5</v>
-      </c>
-      <c r="L16" s="9">
+      <c r="I16" s="54" t="s">
+        <v>18</v>
+      </c>
+      <c r="J16" s="54" t="s">
+        <v>69</v>
+      </c>
+      <c r="K16" s="9">
         <v>1</v>
       </c>
-      <c r="M16" s="7">
+      <c r="L16" s="7">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N16" s="57" t="s">
-        <v>21</v>
-      </c>
-      <c r="O16" s="57"/>
-    </row>
-    <row r="17" spans="1:15" ht="15.75" thickBot="1">
+      <c r="M16" s="56" t="s">
+        <v>20</v>
+      </c>
+      <c r="N16" s="56"/>
+    </row>
+    <row r="17" spans="1:14" ht="15.75" thickBot="1">
       <c r="A17" s="6">
         <v>15</v>
       </c>
-      <c r="B17" s="100"/>
-      <c r="C17" s="114" t="s">
+      <c r="B17" s="136"/>
+      <c r="C17" s="105" t="s">
+        <v>70</v>
+      </c>
+      <c r="D17" s="113" t="s">
         <v>71</v>
       </c>
-      <c r="D17" s="122" t="s">
+      <c r="E17" s="67" t="s">
         <v>72</v>
       </c>
-      <c r="E17" s="68" t="s">
+      <c r="F17" s="67" t="s">
         <v>73</v>
       </c>
-      <c r="F17" s="68" t="s">
+      <c r="G17" s="67" t="s">
         <v>74</v>
       </c>
-      <c r="G17" s="68" t="s">
+      <c r="H17" s="68" t="s">
         <v>75</v>
       </c>
-      <c r="H17" s="69" t="s">
-        <v>76</v>
-      </c>
-      <c r="I17" s="69" t="s">
-        <v>19</v>
-      </c>
-      <c r="J17" s="69" t="s">
-        <v>70</v>
-      </c>
-      <c r="K17" s="115">
-        <v>20</v>
-      </c>
-      <c r="L17" s="64">
+      <c r="I17" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="J17" s="68" t="s">
+        <v>69</v>
+      </c>
+      <c r="K17" s="63">
         <v>1</v>
       </c>
-      <c r="M17" s="115">
+      <c r="L17" s="106">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N17" s="116" t="s">
-        <v>21</v>
-      </c>
-      <c r="O17" s="116"/>
-    </row>
-    <row r="18" spans="1:15" ht="16.5" thickBot="1">
+      <c r="M17" s="107" t="s">
+        <v>20</v>
+      </c>
+      <c r="N17" s="107"/>
+    </row>
+    <row r="18" spans="1:14" ht="16.5" thickBot="1">
       <c r="A18" s="6">
         <v>16</v>
       </c>
-      <c r="B18" s="95" t="s">
+      <c r="B18" s="92" t="s">
+        <v>76</v>
+      </c>
+      <c r="C18" s="71" t="s">
         <v>77</v>
       </c>
-      <c r="C18" s="72" t="s">
+      <c r="D18" s="114" t="s">
         <v>78</v>
       </c>
-      <c r="D18" s="123" t="s">
+      <c r="E18" s="72" t="s">
         <v>79</v>
       </c>
-      <c r="E18" s="73" t="s">
+      <c r="F18" s="72" t="s">
         <v>80</v>
       </c>
-      <c r="F18" s="73" t="s">
+      <c r="G18" s="73" t="s">
         <v>81</v>
       </c>
-      <c r="G18" s="74" t="s">
-        <v>82</v>
-      </c>
-      <c r="H18" s="74" t="s">
-        <v>19</v>
-      </c>
-      <c r="I18" s="73" t="s">
-        <v>19</v>
-      </c>
-      <c r="J18" s="74" t="s">
-        <v>70</v>
-      </c>
-      <c r="K18" s="70">
-        <v>7</v>
-      </c>
-      <c r="L18" s="70">
+      <c r="H18" s="73" t="s">
+        <v>18</v>
+      </c>
+      <c r="I18" s="72" t="s">
+        <v>18</v>
+      </c>
+      <c r="J18" s="73" t="s">
+        <v>69</v>
+      </c>
+      <c r="K18" s="69">
         <v>1</v>
       </c>
-      <c r="M18" s="117">
+      <c r="L18" s="108">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N18" s="71" t="s">
-        <v>21</v>
-      </c>
-      <c r="O18" s="71"/>
-    </row>
-    <row r="19" spans="1:15" ht="30.75" thickBot="1">
+      <c r="M18" s="70" t="s">
+        <v>20</v>
+      </c>
+      <c r="N18" s="70"/>
+    </row>
+    <row r="19" spans="1:14" ht="30.75" thickBot="1">
       <c r="A19" s="6">
         <v>17</v>
       </c>
-      <c r="B19" s="95" t="s">
+      <c r="B19" s="92" t="s">
+        <v>219</v>
+      </c>
+      <c r="C19" s="109" t="s">
+        <v>221</v>
+      </c>
+      <c r="D19" s="114" t="s">
+        <v>220</v>
+      </c>
+      <c r="E19" s="110" t="s">
+        <v>222</v>
+      </c>
+      <c r="F19" s="110" t="s">
         <v>223</v>
       </c>
-      <c r="C19" s="118" t="s">
+      <c r="G19" s="111" t="s">
+        <v>224</v>
+      </c>
+      <c r="H19" s="111" t="s">
         <v>225</v>
       </c>
-      <c r="D19" s="123" t="s">
-        <v>224</v>
-      </c>
-      <c r="E19" s="119" t="s">
+      <c r="I19" s="110" t="s">
         <v>226</v>
       </c>
-      <c r="F19" s="119" t="s">
-        <v>227</v>
-      </c>
-      <c r="G19" s="120" t="s">
-        <v>228</v>
-      </c>
-      <c r="H19" s="120" t="s">
-        <v>229</v>
-      </c>
-      <c r="I19" s="119" t="s">
-        <v>230</v>
-      </c>
-      <c r="J19" s="120" t="s">
-        <v>70</v>
-      </c>
-      <c r="K19" s="70">
-        <v>10</v>
-      </c>
-      <c r="L19" s="70">
+      <c r="J19" s="111" t="s">
+        <v>69</v>
+      </c>
+      <c r="K19" s="69">
         <v>1</v>
       </c>
-      <c r="M19" s="117">
+      <c r="L19" s="108">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N19" s="71" t="s">
-        <v>21</v>
-      </c>
-      <c r="O19" s="71"/>
-    </row>
-    <row r="20" spans="1:15" ht="15.75" thickBot="1">
+      <c r="M19" s="70" t="s">
+        <v>20</v>
+      </c>
+      <c r="N19" s="70"/>
+    </row>
+    <row r="20" spans="1:14" ht="15.75" thickBot="1">
       <c r="A20" s="6">
         <v>18</v>
       </c>
-      <c r="B20" s="99" t="s">
-        <v>83</v>
-      </c>
-      <c r="C20" s="66" t="s">
+      <c r="B20" s="135" t="s">
+        <v>82</v>
+      </c>
+      <c r="C20" s="65" t="s">
+        <v>173</v>
+      </c>
+      <c r="D20" s="45" t="s">
         <v>174</v>
       </c>
-      <c r="D20" s="46" t="s">
+      <c r="E20" s="45" t="s">
         <v>175</v>
       </c>
-      <c r="E20" s="46" t="s">
+      <c r="F20" s="45" t="s">
+        <v>175</v>
+      </c>
+      <c r="G20" s="26" t="s">
         <v>176</v>
       </c>
-      <c r="F20" s="46" t="s">
-        <v>176</v>
-      </c>
-      <c r="G20" s="27" t="s">
+      <c r="H20" s="26" t="s">
         <v>177</v>
       </c>
-      <c r="H20" s="27" t="s">
-        <v>178</v>
-      </c>
-      <c r="I20" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="J20" s="27" t="s">
-        <v>70</v>
+      <c r="I20" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="J20" s="26" t="s">
+        <v>69</v>
       </c>
       <c r="K20" s="14">
-        <v>10</v>
-      </c>
-      <c r="L20" s="14">
         <v>1</v>
       </c>
-      <c r="M20" s="13">
+      <c r="L20" s="13">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N20" s="67" t="s">
-        <v>21</v>
-      </c>
-      <c r="O20" s="67"/>
-    </row>
-    <row r="21" spans="1:15" ht="15.75" thickBot="1">
+      <c r="M20" s="66" t="s">
+        <v>20</v>
+      </c>
+      <c r="N20" s="66"/>
+    </row>
+    <row r="21" spans="1:14" ht="15.75" thickBot="1">
       <c r="A21" s="6">
         <v>19</v>
       </c>
-      <c r="B21" s="101"/>
-      <c r="C21" s="47" t="s">
+      <c r="B21" s="137"/>
+      <c r="C21" s="46" t="s">
+        <v>83</v>
+      </c>
+      <c r="D21" s="47" t="s">
         <v>84</v>
       </c>
-      <c r="D21" s="48" t="s">
+      <c r="E21" s="47" t="s">
+        <v>43</v>
+      </c>
+      <c r="F21" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="E21" s="48" t="s">
-        <v>44</v>
-      </c>
-      <c r="F21" s="48" t="s">
+      <c r="G21" s="47" t="s">
         <v>86</v>
       </c>
-      <c r="G21" s="48" t="s">
-        <v>87</v>
-      </c>
-      <c r="H21" s="49"/>
-      <c r="I21" s="49"/>
-      <c r="J21" s="48" t="s">
-        <v>70</v>
-      </c>
-      <c r="K21" s="49">
-        <v>7</v>
-      </c>
-      <c r="L21" s="49">
+      <c r="H21" s="48"/>
+      <c r="I21" s="48"/>
+      <c r="J21" s="47" t="s">
+        <v>69</v>
+      </c>
+      <c r="K21" s="48">
         <v>1</v>
       </c>
-      <c r="M21" s="11">
+      <c r="L21" s="11">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N21" s="50" t="s">
-        <v>88</v>
-      </c>
-      <c r="O21" s="50"/>
-    </row>
-    <row r="22" spans="1:15" ht="15.75" thickBot="1">
+      <c r="M21" s="49" t="s">
+        <v>87</v>
+      </c>
+      <c r="N21" s="49"/>
+    </row>
+    <row r="22" spans="1:14" ht="15.75" thickBot="1">
       <c r="A22" s="6">
         <v>20</v>
       </c>
-      <c r="B22" s="99" t="s">
+      <c r="B22" s="135" t="s">
+        <v>88</v>
+      </c>
+      <c r="C22" s="141" t="s">
         <v>89</v>
       </c>
-      <c r="C22" s="84" t="s">
+      <c r="D22" s="145" t="s">
+        <v>244</v>
+      </c>
+      <c r="E22" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="D22" s="140" t="s">
-        <v>245</v>
-      </c>
-      <c r="E22" s="85" t="s">
+      <c r="F22" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="F22" s="85" t="s">
+      <c r="G22" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="H22" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="G22" s="87" t="s">
-        <v>60</v>
-      </c>
-      <c r="H22" s="93" t="s">
+      <c r="I22" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="J22" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="I22" s="85" t="s">
-        <v>19</v>
-      </c>
-      <c r="J22" s="85" t="s">
-        <v>94</v>
-      </c>
-      <c r="K22" s="88">
-        <v>100</v>
-      </c>
-      <c r="L22" s="88">
-        <v>5</v>
-      </c>
-      <c r="M22" s="88">
+      <c r="K22" s="142">
+        <v>3</v>
+      </c>
+      <c r="L22" s="142">
         <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="N22" s="94" t="s">
-        <v>21</v>
-      </c>
-      <c r="O22" s="139" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" ht="15.75" thickBot="1">
+        <v>18</v>
+      </c>
+      <c r="M22" s="143" t="s">
+        <v>20</v>
+      </c>
+      <c r="N22" s="144"/>
+    </row>
+    <row r="23" spans="1:14" ht="15.75" thickBot="1">
       <c r="A23" s="6">
         <v>21</v>
       </c>
-      <c r="B23" s="100"/>
-      <c r="C23" s="125" t="s">
+      <c r="B23" s="136"/>
+      <c r="C23" s="116" t="s">
+        <v>165</v>
+      </c>
+      <c r="D23" s="122" t="s">
         <v>166</v>
       </c>
-      <c r="D23" s="131" t="s">
+      <c r="E23" s="51" t="s">
+        <v>90</v>
+      </c>
+      <c r="F23" s="51" t="s">
         <v>167</v>
       </c>
-      <c r="E23" s="52" t="s">
-        <v>91</v>
-      </c>
-      <c r="F23" s="52" t="s">
+      <c r="G23" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="H23" s="54" t="s">
+        <v>235</v>
+      </c>
+      <c r="I23" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="J23" s="53" t="s">
         <v>168</v>
       </c>
-      <c r="G23" s="29" t="s">
-        <v>156</v>
-      </c>
-      <c r="H23" s="55" t="s">
-        <v>239</v>
-      </c>
-      <c r="I23" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="J23" s="54" t="s">
-        <v>169</v>
-      </c>
       <c r="K23" s="7">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="L23" s="7">
-        <v>1</v>
-      </c>
-      <c r="M23" s="7">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N23" s="57" t="s">
-        <v>179</v>
-      </c>
-      <c r="O23" s="57"/>
-    </row>
-    <row r="24" spans="1:15" ht="15.75" thickBot="1">
+      <c r="M23" s="56" t="s">
+        <v>178</v>
+      </c>
+      <c r="N23" s="56"/>
+    </row>
+    <row r="24" spans="1:14" ht="15.75" thickBot="1">
       <c r="A24" s="6">
         <v>22</v>
       </c>
-      <c r="B24" s="100"/>
-      <c r="C24" s="126" t="s">
-        <v>194</v>
-      </c>
-      <c r="D24" s="132" t="s">
+      <c r="B24" s="136"/>
+      <c r="C24" s="117" t="s">
+        <v>193</v>
+      </c>
+      <c r="D24" s="123" t="s">
+        <v>186</v>
+      </c>
+      <c r="E24" s="51" t="s">
+        <v>90</v>
+      </c>
+      <c r="F24" s="118" t="s">
         <v>187</v>
       </c>
-      <c r="E24" s="52" t="s">
-        <v>91</v>
-      </c>
-      <c r="F24" s="127" t="s">
+      <c r="G24" s="118" t="s">
         <v>188</v>
       </c>
-      <c r="G24" s="127" t="s">
+      <c r="H24" s="119" t="s">
         <v>189</v>
       </c>
-      <c r="H24" s="128" t="s">
-        <v>190</v>
-      </c>
-      <c r="I24" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="J24" s="54" t="s">
-        <v>200</v>
+      <c r="I24" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="J24" s="53" t="s">
+        <v>199</v>
       </c>
       <c r="K24" s="7">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="L24" s="7">
-        <v>1</v>
-      </c>
-      <c r="M24" s="7">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N24" s="60" t="s">
-        <v>21</v>
-      </c>
-      <c r="O24" s="60"/>
-    </row>
-    <row r="25" spans="1:15" ht="15.75" thickBot="1">
+      <c r="M24" s="59" t="s">
+        <v>20</v>
+      </c>
+      <c r="N24" s="59"/>
+    </row>
+    <row r="25" spans="1:14" ht="15.75" thickBot="1">
       <c r="A25" s="6">
         <v>23</v>
       </c>
-      <c r="B25" s="100"/>
-      <c r="C25" s="126" t="s">
-        <v>195</v>
-      </c>
-      <c r="D25" s="132" t="s">
+      <c r="B25" s="136"/>
+      <c r="C25" s="117" t="s">
+        <v>194</v>
+      </c>
+      <c r="D25" s="123" t="s">
+        <v>190</v>
+      </c>
+      <c r="E25" s="51" t="s">
+        <v>90</v>
+      </c>
+      <c r="F25" s="118" t="s">
         <v>191</v>
       </c>
-      <c r="E25" s="52" t="s">
-        <v>91</v>
-      </c>
-      <c r="F25" s="127" t="s">
+      <c r="G25" s="118" t="s">
+        <v>188</v>
+      </c>
+      <c r="H25" s="119" t="s">
         <v>192</v>
       </c>
-      <c r="G25" s="127" t="s">
-        <v>189</v>
-      </c>
-      <c r="H25" s="128" t="s">
-        <v>193</v>
-      </c>
-      <c r="I25" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="J25" s="54" t="s">
-        <v>201</v>
+      <c r="I25" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="J25" s="53" t="s">
+        <v>200</v>
       </c>
       <c r="K25" s="7">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="L25" s="7">
-        <v>1</v>
-      </c>
-      <c r="M25" s="7">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N25" s="57" t="s">
-        <v>21</v>
-      </c>
-      <c r="O25" s="57"/>
-    </row>
-    <row r="26" spans="1:15" ht="15.75" thickBot="1">
+      <c r="M25" s="56" t="s">
+        <v>20</v>
+      </c>
+      <c r="N25" s="56"/>
+    </row>
+    <row r="26" spans="1:14" ht="15.75" thickBot="1">
       <c r="A26" s="6">
         <v>24</v>
       </c>
-      <c r="B26" s="100"/>
-      <c r="C26" s="126" t="s">
+      <c r="B26" s="136"/>
+      <c r="C26" s="117" t="s">
+        <v>196</v>
+      </c>
+      <c r="D26" s="123" t="s">
         <v>197</v>
       </c>
-      <c r="D26" s="132" t="s">
+      <c r="E26" s="53" t="s">
+        <v>90</v>
+      </c>
+      <c r="F26" s="120" t="s">
+        <v>195</v>
+      </c>
+      <c r="G26" s="118" t="s">
+        <v>188</v>
+      </c>
+      <c r="H26" s="121" t="s">
         <v>198</v>
       </c>
-      <c r="E26" s="54" t="s">
-        <v>91</v>
-      </c>
-      <c r="F26" s="129" t="s">
-        <v>196</v>
-      </c>
-      <c r="G26" s="127" t="s">
-        <v>189</v>
-      </c>
-      <c r="H26" s="130" t="s">
-        <v>199</v>
-      </c>
-      <c r="I26" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="J26" s="54" t="s">
-        <v>202</v>
+      <c r="I26" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="J26" s="53" t="s">
+        <v>201</v>
       </c>
       <c r="K26" s="7">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="L26" s="7">
-        <v>1</v>
-      </c>
-      <c r="M26" s="7">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N26" s="57" t="s">
-        <v>21</v>
-      </c>
-      <c r="O26" s="57"/>
-    </row>
-    <row r="27" spans="1:15" ht="15.75" thickBot="1">
+      <c r="M26" s="56" t="s">
+        <v>20</v>
+      </c>
+      <c r="N26" s="56"/>
+    </row>
+    <row r="27" spans="1:14" ht="15.75" thickBot="1">
       <c r="A27" s="6">
         <v>25</v>
       </c>
-      <c r="B27" s="100"/>
-      <c r="C27" s="126" t="s">
-        <v>204</v>
-      </c>
-      <c r="D27" s="132" t="s">
-        <v>207</v>
-      </c>
-      <c r="E27" s="54" t="s">
-        <v>91</v>
-      </c>
-      <c r="F27" s="129" t="s">
+      <c r="B27" s="136"/>
+      <c r="C27" s="146" t="s">
+        <v>248</v>
+      </c>
+      <c r="D27" s="147" t="s">
         <v>203</v>
       </c>
-      <c r="G27" s="129" t="s">
-        <v>115</v>
-      </c>
-      <c r="H27" s="130" t="s">
-        <v>205</v>
-      </c>
-      <c r="I27" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="J27" s="54" t="s">
-        <v>206</v>
-      </c>
-      <c r="K27" s="7">
-        <v>50</v>
-      </c>
-      <c r="L27" s="7">
+      <c r="E27" s="148" t="s">
+        <v>247</v>
+      </c>
+      <c r="F27" s="149" t="s">
+        <v>246</v>
+      </c>
+      <c r="G27" s="149" t="s">
+        <v>114</v>
+      </c>
+      <c r="H27" s="150" t="s">
+        <v>245</v>
+      </c>
+      <c r="I27" s="80" t="s">
+        <v>18</v>
+      </c>
+      <c r="J27" s="81" t="s">
+        <v>202</v>
+      </c>
+      <c r="K27" s="82">
         <v>2</v>
       </c>
-      <c r="M27" s="7">
+      <c r="L27" s="82">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="N27" s="57" t="s">
-        <v>21</v>
-      </c>
-      <c r="O27" s="57"/>
-    </row>
-    <row r="28" spans="1:15" ht="15.75" thickBot="1">
+      <c r="M27" s="151" t="s">
+        <v>20</v>
+      </c>
+      <c r="N27" s="132" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="15.75" thickBot="1">
       <c r="A28" s="6">
         <v>26</v>
       </c>
-      <c r="B28" s="100"/>
-      <c r="C28" s="35" t="s">
+      <c r="B28" s="136"/>
+      <c r="C28" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="D28" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="D28" s="7" t="s">
+      <c r="E28" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="F28" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="E28" s="28" t="s">
-        <v>91</v>
-      </c>
-      <c r="F28" s="28" t="s">
+      <c r="G28" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="H28" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="G28" s="29" t="s">
-        <v>60</v>
-      </c>
-      <c r="H28" s="9" t="s">
+      <c r="I28" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="J28" s="27" t="s">
         <v>98</v>
       </c>
-      <c r="I28" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="J28" s="28" t="s">
-        <v>99</v>
-      </c>
       <c r="K28" s="7">
-        <v>100</v>
-      </c>
-      <c r="L28" s="7">
         <v>2</v>
       </c>
-      <c r="M28" s="8">
+      <c r="L28" s="8">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="N28" s="58" t="s">
-        <v>21</v>
-      </c>
-      <c r="O28" s="58"/>
-    </row>
-    <row r="29" spans="1:15" ht="15.75" thickBot="1">
+      <c r="M28" s="57" t="s">
+        <v>20</v>
+      </c>
+      <c r="N28" s="57"/>
+    </row>
+    <row r="29" spans="1:14" ht="15.75" thickBot="1">
       <c r="A29" s="6">
         <v>27</v>
       </c>
-      <c r="B29" s="100"/>
-      <c r="C29" s="35" t="s">
+      <c r="B29" s="136"/>
+      <c r="C29" s="34" t="s">
+        <v>99</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="E29" s="27" t="s">
+        <v>90</v>
+      </c>
+      <c r="F29" s="27" t="s">
         <v>100</v>
       </c>
-      <c r="D29" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="E29" s="28" t="s">
-        <v>91</v>
-      </c>
-      <c r="F29" s="28" t="s">
+      <c r="G29" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="H29" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="G29" s="29" t="s">
-        <v>60</v>
-      </c>
-      <c r="H29" s="9" t="s">
+      <c r="I29" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="J29" s="27" t="s">
         <v>102</v>
       </c>
-      <c r="I29" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="J29" s="28" t="s">
-        <v>103</v>
-      </c>
       <c r="K29" s="7">
-        <v>100</v>
-      </c>
-      <c r="L29" s="7">
         <v>1</v>
       </c>
-      <c r="M29" s="8">
+      <c r="L29" s="8">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N29" s="58" t="s">
-        <v>21</v>
-      </c>
-      <c r="O29" s="58"/>
-    </row>
-    <row r="30" spans="1:15" ht="15.75" thickBot="1">
+      <c r="M29" s="57" t="s">
+        <v>20</v>
+      </c>
+      <c r="N29" s="57"/>
+    </row>
+    <row r="30" spans="1:14" ht="15.75" thickBot="1">
       <c r="A30" s="6">
         <v>28</v>
       </c>
-      <c r="B30" s="100"/>
-      <c r="C30" s="35" t="s">
+      <c r="B30" s="136"/>
+      <c r="C30" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="D30" s="27" t="s">
         <v>105</v>
       </c>
-      <c r="D30" s="28" t="s">
+      <c r="E30" s="27" t="s">
+        <v>103</v>
+      </c>
+      <c r="F30" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="E30" s="28" t="s">
-        <v>104</v>
-      </c>
-      <c r="F30" s="30" t="s">
+      <c r="G30" s="28" t="s">
         <v>107</v>
       </c>
-      <c r="G30" s="29" t="s">
+      <c r="H30" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="H30" s="9" t="s">
+      <c r="I30" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="I30" s="29" t="s">
+      <c r="J30" s="27" t="s">
         <v>110</v>
       </c>
-      <c r="J30" s="28" t="s">
-        <v>111</v>
-      </c>
       <c r="K30" s="7">
-        <v>10</v>
-      </c>
-      <c r="L30" s="7">
         <v>1</v>
       </c>
-      <c r="M30" s="8">
+      <c r="L30" s="8">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N30" s="58" t="s">
-        <v>21</v>
-      </c>
-      <c r="O30" s="58"/>
-    </row>
-    <row r="31" spans="1:15" ht="15.75" thickBot="1">
+      <c r="M30" s="57" t="s">
+        <v>20</v>
+      </c>
+      <c r="N30" s="57"/>
+    </row>
+    <row r="31" spans="1:14" ht="15.75" thickBot="1">
       <c r="A31" s="6">
         <v>29</v>
       </c>
-      <c r="B31" s="100"/>
-      <c r="C31" s="35" t="s">
+      <c r="B31" s="136"/>
+      <c r="C31" s="34" t="s">
+        <v>111</v>
+      </c>
+      <c r="D31" s="27" t="s">
         <v>112</v>
       </c>
-      <c r="D31" s="28" t="s">
+      <c r="E31" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="F31" s="27" t="s">
         <v>113</v>
       </c>
-      <c r="E31" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="F31" s="28" t="s">
+      <c r="G31" s="28" t="s">
         <v>114</v>
       </c>
-      <c r="G31" s="29" t="s">
+      <c r="H31" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="H31" s="9" t="s">
+      <c r="I31" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="J31" s="27" t="s">
         <v>116</v>
       </c>
-      <c r="I31" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="J31" s="28" t="s">
-        <v>117</v>
-      </c>
       <c r="K31" s="7">
-        <v>100</v>
-      </c>
-      <c r="L31" s="7">
         <v>1</v>
       </c>
-      <c r="M31" s="8">
+      <c r="L31" s="8">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N31" s="58" t="s">
-        <v>21</v>
-      </c>
-      <c r="O31" s="58"/>
-    </row>
-    <row r="32" spans="1:15" s="1" customFormat="1" ht="15.75" thickBot="1">
+      <c r="M31" s="57" t="s">
+        <v>20</v>
+      </c>
+      <c r="N31" s="57"/>
+    </row>
+    <row r="32" spans="1:14" s="1" customFormat="1" ht="15.75" thickBot="1">
       <c r="A32" s="6">
         <v>30</v>
       </c>
-      <c r="B32" s="101"/>
-      <c r="C32" s="36" t="s">
+      <c r="B32" s="137"/>
+      <c r="C32" s="35" t="s">
+        <v>117</v>
+      </c>
+      <c r="D32" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="D32" s="10" t="s">
+      <c r="E32" s="30" t="s">
+        <v>90</v>
+      </c>
+      <c r="F32" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="E32" s="31" t="s">
-        <v>91</v>
-      </c>
-      <c r="F32" s="31" t="s">
+      <c r="G32" s="31" t="s">
+        <v>59</v>
+      </c>
+      <c r="H32" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="G32" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="H32" s="12" t="s">
+      <c r="I32" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J32" s="30" t="s">
         <v>121</v>
       </c>
-      <c r="I32" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="J32" s="31" t="s">
-        <v>122</v>
-      </c>
-      <c r="K32" s="10">
-        <v>100</v>
-      </c>
-      <c r="L32" s="12">
+      <c r="K32" s="12">
         <v>8</v>
       </c>
-      <c r="M32" s="11">
+      <c r="L32" s="11">
         <f t="shared" si="1"/>
         <v>48</v>
       </c>
-      <c r="N32" s="75" t="s">
-        <v>21</v>
-      </c>
-      <c r="O32" s="75"/>
-    </row>
-    <row r="33" spans="1:15" ht="15.75" thickBot="1">
+      <c r="M32" s="74" t="s">
+        <v>20</v>
+      </c>
+      <c r="N32" s="74"/>
+    </row>
+    <row r="33" spans="1:14" ht="15.75" thickBot="1">
       <c r="A33" s="6">
         <v>31</v>
       </c>
-      <c r="B33" s="100" t="s">
+      <c r="B33" s="136" t="s">
+        <v>122</v>
+      </c>
+      <c r="C33" s="124" t="s">
+        <v>184</v>
+      </c>
+      <c r="D33" s="128" t="s">
         <v>123</v>
       </c>
-      <c r="C33" s="133" t="s">
-        <v>185</v>
-      </c>
-      <c r="D33" s="137" t="s">
-        <v>124</v>
-      </c>
-      <c r="E33" s="134" t="s">
+      <c r="E33" s="125" t="s">
+        <v>181</v>
+      </c>
+      <c r="F33" s="126" t="s">
         <v>182</v>
       </c>
-      <c r="F33" s="135" t="s">
+      <c r="G33" s="127" t="s">
         <v>183</v>
       </c>
-      <c r="G33" s="136" t="s">
-        <v>184</v>
-      </c>
-      <c r="H33" s="34" t="s">
-        <v>19</v>
-      </c>
-      <c r="I33" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="J33" s="34" t="s">
-        <v>70</v>
+      <c r="H33" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="I33" s="32" t="s">
+        <v>18</v>
+      </c>
+      <c r="J33" s="33" t="s">
+        <v>69</v>
       </c>
       <c r="K33" s="15">
-        <v>7</v>
-      </c>
-      <c r="L33" s="15">
         <v>1</v>
       </c>
-      <c r="M33" s="111">
+      <c r="L33" s="102">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N33" s="112" t="s">
-        <v>21</v>
-      </c>
-      <c r="O33" s="112"/>
-    </row>
-    <row r="34" spans="1:15" ht="15.75" thickBot="1">
+      <c r="M33" s="103" t="s">
+        <v>20</v>
+      </c>
+      <c r="N33" s="103"/>
+    </row>
+    <row r="34" spans="1:14" ht="15.75" thickBot="1">
       <c r="A34" s="6">
         <v>32</v>
       </c>
-      <c r="B34" s="100"/>
-      <c r="C34" s="35" t="s">
+      <c r="B34" s="136"/>
+      <c r="C34" s="34" t="s">
+        <v>124</v>
+      </c>
+      <c r="D34" s="27" t="s">
         <v>125</v>
       </c>
-      <c r="D34" s="28" t="s">
+      <c r="E34" s="27" t="s">
         <v>126</v>
       </c>
-      <c r="E34" s="28" t="s">
+      <c r="F34" s="27" t="s">
         <v>127</v>
       </c>
-      <c r="F34" s="28" t="s">
+      <c r="G34" s="28" t="s">
         <v>128</v>
       </c>
-      <c r="G34" s="29" t="s">
+      <c r="H34" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="H34" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="I34" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="J34" s="29" t="s">
-        <v>70</v>
+      <c r="I34" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="J34" s="28" t="s">
+        <v>69</v>
       </c>
       <c r="K34" s="9">
-        <v>6</v>
-      </c>
-      <c r="L34" s="9">
         <v>1</v>
       </c>
-      <c r="M34" s="8">
+      <c r="L34" s="8">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N34" s="58" t="s">
-        <v>21</v>
-      </c>
-      <c r="O34" s="58"/>
-    </row>
-    <row r="35" spans="1:15" ht="15.75" thickBot="1">
+      <c r="M34" s="57" t="s">
+        <v>20</v>
+      </c>
+      <c r="N34" s="57"/>
+    </row>
+    <row r="35" spans="1:14" ht="15.75" thickBot="1">
       <c r="A35" s="6">
         <v>33</v>
       </c>
-      <c r="B35" s="100"/>
-      <c r="C35" s="76" t="s">
+      <c r="B35" s="136"/>
+      <c r="C35" s="75" t="s">
+        <v>169</v>
+      </c>
+      <c r="D35" s="76" t="s">
+        <v>130</v>
+      </c>
+      <c r="E35" s="76" t="s">
         <v>170</v>
       </c>
-      <c r="D35" s="77" t="s">
+      <c r="F35" s="77" t="s">
+        <v>172</v>
+      </c>
+      <c r="G35" s="67" t="s">
+        <v>171</v>
+      </c>
+      <c r="H35" s="63"/>
+      <c r="I35" s="67" t="s">
+        <v>18</v>
+      </c>
+      <c r="J35" s="68" t="s">
         <v>131</v>
       </c>
-      <c r="E35" s="77" t="s">
-        <v>171</v>
-      </c>
-      <c r="F35" s="78" t="s">
-        <v>173</v>
-      </c>
-      <c r="G35" s="68" t="s">
-        <v>172</v>
-      </c>
-      <c r="H35" s="64"/>
-      <c r="I35" s="68" t="s">
-        <v>19</v>
-      </c>
-      <c r="J35" s="69" t="s">
-        <v>132</v>
-      </c>
-      <c r="K35" s="64">
-        <v>6</v>
+      <c r="K35" s="63">
+        <v>1</v>
       </c>
       <c r="L35" s="64">
-        <v>1</v>
-      </c>
-      <c r="M35" s="65">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N35" s="79" t="s">
-        <v>88</v>
-      </c>
-      <c r="O35" s="79"/>
-    </row>
-    <row r="36" spans="1:15" ht="15.75" thickBot="1">
+      <c r="M35" s="78" t="s">
+        <v>87</v>
+      </c>
+      <c r="N35" s="78"/>
+    </row>
+    <row r="36" spans="1:14" ht="15.75" thickBot="1">
       <c r="A36" s="6">
         <v>34</v>
       </c>
-      <c r="B36" s="99" t="s">
+      <c r="B36" s="135" t="s">
+        <v>132</v>
+      </c>
+      <c r="C36" s="36" t="s">
         <v>133</v>
       </c>
-      <c r="C36" s="37" t="s">
+      <c r="D36" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="D36" s="38" t="s">
+      <c r="E36" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="E36" s="38" t="s">
+      <c r="F36" s="37" t="s">
+        <v>135</v>
+      </c>
+      <c r="G36" s="37" t="s">
         <v>136</v>
       </c>
-      <c r="F36" s="38" t="s">
-        <v>136</v>
-      </c>
-      <c r="G36" s="38" t="s">
-        <v>137</v>
-      </c>
-      <c r="H36" s="38" t="s">
-        <v>19</v>
-      </c>
-      <c r="I36" s="38" t="s">
-        <v>19</v>
-      </c>
-      <c r="J36" s="38" t="s">
-        <v>70</v>
+      <c r="H36" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="I36" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="J36" s="37" t="s">
+        <v>69</v>
       </c>
       <c r="K36" s="17">
-        <v>100</v>
-      </c>
-      <c r="L36" s="17">
         <v>1</v>
       </c>
-      <c r="M36" s="13">
+      <c r="L36" s="13">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N36" s="80" t="s">
-        <v>138</v>
-      </c>
-      <c r="O36" s="80"/>
-    </row>
-    <row r="37" spans="1:15" ht="15.75" thickBot="1">
+      <c r="M36" s="79" t="s">
+        <v>137</v>
+      </c>
+      <c r="N36" s="79"/>
+    </row>
+    <row r="37" spans="1:14" ht="15.75" thickBot="1">
       <c r="A37" s="6">
         <v>35</v>
       </c>
-      <c r="B37" s="100"/>
-      <c r="C37" s="39" t="s">
+      <c r="B37" s="136"/>
+      <c r="C37" s="38" t="s">
+        <v>138</v>
+      </c>
+      <c r="D37" s="39" t="s">
         <v>139</v>
       </c>
-      <c r="D37" s="40" t="s">
+      <c r="E37" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="F37" s="39" t="s">
         <v>140</v>
       </c>
-      <c r="E37" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="F37" s="40" t="s">
+      <c r="G37" s="39" t="s">
         <v>141</v>
       </c>
-      <c r="G37" s="40" t="s">
+      <c r="H37" s="39" t="s">
+        <v>18</v>
+      </c>
+      <c r="I37" s="39" t="s">
+        <v>18</v>
+      </c>
+      <c r="J37" s="40" t="s">
         <v>142</v>
       </c>
-      <c r="H37" s="40" t="s">
-        <v>19</v>
-      </c>
-      <c r="I37" s="40" t="s">
-        <v>19</v>
-      </c>
-      <c r="J37" s="41" t="s">
-        <v>143</v>
-      </c>
-      <c r="K37" s="24">
-        <v>12</v>
-      </c>
-      <c r="L37" s="18">
+      <c r="K37" s="18">
         <v>2</v>
       </c>
-      <c r="M37" s="8">
+      <c r="L37" s="8">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="N37" s="59" t="s">
-        <v>144</v>
-      </c>
-      <c r="O37" s="59"/>
-    </row>
-    <row r="38" spans="1:15" ht="15.75" thickBot="1">
+      <c r="M37" s="58" t="s">
+        <v>143</v>
+      </c>
+      <c r="N37" s="58"/>
+    </row>
+    <row r="38" spans="1:14" ht="15.75" thickBot="1">
       <c r="A38" s="6">
         <v>36</v>
       </c>
-      <c r="B38" s="100"/>
-      <c r="C38" s="39" t="s">
+      <c r="B38" s="136"/>
+      <c r="C38" s="38" t="s">
+        <v>144</v>
+      </c>
+      <c r="D38" s="39" t="s">
         <v>145</v>
       </c>
-      <c r="D38" s="40" t="s">
+      <c r="E38" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="F38" s="39" t="s">
         <v>146</v>
       </c>
-      <c r="E38" s="40" t="s">
-        <v>44</v>
-      </c>
-      <c r="F38" s="40" t="s">
-        <v>147</v>
-      </c>
-      <c r="G38" s="40" t="s">
-        <v>137</v>
-      </c>
-      <c r="H38" s="40" t="s">
-        <v>19</v>
-      </c>
-      <c r="I38" s="40" t="s">
-        <v>19</v>
-      </c>
-      <c r="J38" s="41" t="s">
-        <v>70</v>
-      </c>
-      <c r="K38" s="24">
-        <v>10</v>
-      </c>
-      <c r="L38" s="18">
+      <c r="G38" s="39" t="s">
+        <v>136</v>
+      </c>
+      <c r="H38" s="39" t="s">
+        <v>18</v>
+      </c>
+      <c r="I38" s="39" t="s">
+        <v>18</v>
+      </c>
+      <c r="J38" s="40" t="s">
+        <v>69</v>
+      </c>
+      <c r="K38" s="18">
         <v>1</v>
       </c>
-      <c r="M38" s="8">
+      <c r="L38" s="8">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N38" s="59" t="s">
-        <v>138</v>
-      </c>
-      <c r="O38" s="59"/>
-    </row>
-    <row r="39" spans="1:15" ht="15.75" thickBot="1">
+      <c r="M38" s="58" t="s">
+        <v>137</v>
+      </c>
+      <c r="N38" s="58"/>
+    </row>
+    <row r="39" spans="1:14" ht="15.75" thickBot="1">
       <c r="A39" s="6">
         <v>37</v>
       </c>
-      <c r="B39" s="100"/>
+      <c r="B39" s="136"/>
       <c r="C39" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="D39" s="27" t="s">
         <v>148</v>
       </c>
-      <c r="D39" s="28" t="s">
+      <c r="E39" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="F39" s="27" t="s">
         <v>149</v>
       </c>
-      <c r="E39" s="28" t="s">
-        <v>44</v>
-      </c>
-      <c r="F39" s="28" t="s">
+      <c r="G39" s="27" t="s">
         <v>150</v>
       </c>
-      <c r="G39" s="28" t="s">
-        <v>151</v>
-      </c>
-      <c r="H39" s="28" t="s">
-        <v>150</v>
-      </c>
-      <c r="I39" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="J39" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="K39" s="9">
-        <v>20</v>
-      </c>
-      <c r="L39" s="7">
+      <c r="H39" s="27" t="s">
+        <v>149</v>
+      </c>
+      <c r="I39" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="J39" s="28" t="s">
+        <v>142</v>
+      </c>
+      <c r="K39" s="7">
         <v>1</v>
       </c>
-      <c r="M39" s="8">
+      <c r="L39" s="8">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="N39" s="60" t="s">
-        <v>21</v>
-      </c>
-      <c r="O39" s="60"/>
-    </row>
-    <row r="40" spans="1:15" ht="15.75" thickBot="1">
+      <c r="M39" s="59" t="s">
+        <v>20</v>
+      </c>
+      <c r="N39" s="59"/>
+    </row>
+    <row r="40" spans="1:14" ht="15.75" thickBot="1">
       <c r="A40" s="6">
         <v>38</v>
       </c>
-      <c r="B40" s="100"/>
-      <c r="C40" s="35" t="s">
+      <c r="B40" s="136"/>
+      <c r="C40" s="34" t="s">
+        <v>151</v>
+      </c>
+      <c r="D40" s="27" t="s">
         <v>152</v>
       </c>
-      <c r="D40" s="28" t="s">
+      <c r="E40" s="27" t="s">
         <v>153</v>
       </c>
-      <c r="E40" s="28" t="s">
+      <c r="F40" s="27" t="s">
         <v>154</v>
       </c>
-      <c r="F40" s="28" t="s">
+      <c r="G40" s="27" t="s">
         <v>155</v>
       </c>
-      <c r="G40" s="28" t="s">
+      <c r="H40" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="H40" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="I40" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="J40" s="29" t="s">
-        <v>70</v>
+      <c r="I40" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="J40" s="28" t="s">
+        <v>69</v>
       </c>
       <c r="K40" s="9">
-        <v>15</v>
-      </c>
-      <c r="L40" s="9">
         <v>2</v>
       </c>
-      <c r="M40" s="8">
+      <c r="L40" s="8">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="N40" s="61" t="s">
-        <v>21</v>
-      </c>
-      <c r="O40" s="61"/>
-    </row>
-    <row r="41" spans="1:15" ht="15.75" thickBot="1">
+      <c r="M40" s="60" t="s">
+        <v>20</v>
+      </c>
+      <c r="N40" s="60"/>
+    </row>
+    <row r="41" spans="1:14" ht="15.75" thickBot="1">
       <c r="A41" s="6">
         <v>39</v>
       </c>
-      <c r="B41" s="100"/>
-      <c r="C41" s="42" t="s">
+      <c r="B41" s="136"/>
+      <c r="C41" s="41" t="s">
+        <v>157</v>
+      </c>
+      <c r="D41" s="19"/>
+      <c r="E41" s="42" t="s">
         <v>158</v>
       </c>
-      <c r="D41" s="19"/>
-      <c r="E41" s="43" t="s">
-        <v>159</v>
-      </c>
       <c r="F41" s="19" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G41" s="19"/>
       <c r="H41" s="19"/>
       <c r="I41" s="19"/>
       <c r="J41" s="19"/>
-      <c r="K41" s="19"/>
-      <c r="L41" s="19">
+      <c r="K41" s="19">
         <v>5</v>
       </c>
-      <c r="M41" s="8">
+      <c r="L41" s="8">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
-      <c r="N41" s="62" t="s">
-        <v>19</v>
-      </c>
-      <c r="O41" s="62"/>
-    </row>
-    <row r="42" spans="1:15" ht="15.75" thickBot="1">
+      <c r="M41" s="61" t="s">
+        <v>18</v>
+      </c>
+      <c r="N41" s="61"/>
+    </row>
+    <row r="42" spans="1:14" ht="15.75" thickBot="1">
       <c r="A42" s="20">
         <v>40</v>
       </c>
-      <c r="B42" s="101"/>
-      <c r="C42" s="44" t="s">
+      <c r="B42" s="137"/>
+      <c r="C42" s="43" t="s">
+        <v>159</v>
+      </c>
+      <c r="D42" s="21"/>
+      <c r="E42" s="44" t="s">
         <v>160</v>
       </c>
-      <c r="D42" s="21"/>
-      <c r="E42" s="45" t="s">
-        <v>161</v>
-      </c>
       <c r="F42" s="21" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G42" s="21"/>
       <c r="H42" s="21"/>
       <c r="I42" s="21"/>
       <c r="J42" s="21"/>
-      <c r="K42" s="21"/>
-      <c r="L42" s="21">
+      <c r="K42" s="21">
         <v>5</v>
       </c>
-      <c r="M42" s="11">
+      <c r="L42" s="11">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
-      <c r="N42" s="63" t="s">
-        <v>19</v>
-      </c>
-      <c r="O42" s="63"/>
-    </row>
-    <row r="43" spans="1:15">
+      <c r="M42" s="62" t="s">
+        <v>18</v>
+      </c>
+      <c r="N42" s="62"/>
+    </row>
+    <row r="43" spans="1:14">
       <c r="A43"/>
       <c r="C43" s="22"/>
       <c r="D43" s="22"/>
@@ -3988,10 +3881,9 @@
       <c r="H43" s="22"/>
       <c r="I43" s="22"/>
       <c r="J43" s="22"/>
-      <c r="K43" s="22"/>
-      <c r="O43" s="25"/>
-    </row>
-    <row r="44" spans="1:15">
+      <c r="N43" s="24"/>
+    </row>
+    <row r="44" spans="1:14">
       <c r="A44"/>
       <c r="C44" s="22"/>
       <c r="D44" s="22"/>
@@ -4001,67 +3893,66 @@
       <c r="H44" s="22"/>
       <c r="I44" s="22"/>
       <c r="J44" s="22"/>
-      <c r="K44" s="22"/>
-    </row>
-    <row r="45" spans="1:15">
+    </row>
+    <row r="45" spans="1:14">
       <c r="A45"/>
     </row>
-    <row r="46" spans="1:15">
+    <row r="46" spans="1:14">
       <c r="A46"/>
     </row>
-    <row r="47" spans="1:15">
+    <row r="47" spans="1:14">
       <c r="A47"/>
     </row>
-    <row r="48" spans="1:15">
+    <row r="48" spans="1:14">
       <c r="A48"/>
     </row>
-    <row r="49" spans="1:15">
+    <row r="49" spans="1:14">
       <c r="A49"/>
     </row>
-    <row r="50" spans="1:15">
+    <row r="50" spans="1:14">
       <c r="A50"/>
     </row>
-    <row r="51" spans="1:15">
+    <row r="51" spans="1:14">
       <c r="A51"/>
     </row>
-    <row r="52" spans="1:15" ht="15.75" customHeight="1">
+    <row r="52" spans="1:14" ht="15.75" customHeight="1">
       <c r="A52"/>
-      <c r="N52" s="53"/>
-      <c r="O52" s="53"/>
-    </row>
-    <row r="53" spans="1:15">
+      <c r="M52" s="52"/>
+      <c r="N52" s="52"/>
+    </row>
+    <row r="53" spans="1:14">
       <c r="A53"/>
     </row>
-    <row r="54" spans="1:15">
+    <row r="54" spans="1:14">
       <c r="A54"/>
     </row>
-    <row r="55" spans="1:15">
+    <row r="55" spans="1:14">
       <c r="A55"/>
     </row>
-    <row r="56" spans="1:15">
+    <row r="56" spans="1:14">
       <c r="A56"/>
     </row>
-    <row r="57" spans="1:15">
+    <row r="57" spans="1:14">
       <c r="A57"/>
     </row>
-    <row r="58" spans="1:15">
+    <row r="58" spans="1:14">
       <c r="H58" s="23"/>
     </row>
-    <row r="59" spans="1:15">
+    <row r="59" spans="1:14">
       <c r="H59" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="A1:N1"/>
     <mergeCell ref="B3:B13"/>
     <mergeCell ref="B14:B17"/>
     <mergeCell ref="B22:B32"/>
     <mergeCell ref="B33:B35"/>
     <mergeCell ref="B36:B42"/>
     <mergeCell ref="B20:B21"/>
-    <mergeCell ref="A1:O1"/>
   </mergeCells>
-  <phoneticPr fontId="20" type="noConversion"/>
-  <conditionalFormatting sqref="N21:O21">
+  <phoneticPr fontId="21" type="noConversion"/>
+  <conditionalFormatting sqref="M21:N21">
     <cfRule type="dataBar" priority="39">
       <dataBar>
         <cfvo type="min"/>
@@ -4075,7 +3966,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L36:M36">
+  <conditionalFormatting sqref="K36:L36">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -4087,7 +3978,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L41">
+  <conditionalFormatting sqref="K41">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
@@ -4109,7 +4000,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L42">
+  <conditionalFormatting sqref="K42">
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
@@ -4131,7 +4022,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N3:N6">
+  <conditionalFormatting sqref="M3:M6">
     <cfRule type="dataBar" priority="41">
       <dataBar>
         <cfvo type="min"/>
@@ -4145,7 +4036,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N32:O32">
+  <conditionalFormatting sqref="M32:N32">
     <cfRule type="dataBar" priority="38">
       <dataBar>
         <cfvo type="min"/>
@@ -4159,7 +4050,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L12:L35 L40 M3:M42">
+  <conditionalFormatting sqref="K12:K35 K40 L3:L42">
     <cfRule type="colorScale" priority="51">
       <colorScale>
         <cfvo type="min"/>
@@ -4171,7 +4062,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L8:L11">
+  <conditionalFormatting sqref="K8:K11">
     <cfRule type="colorScale" priority="52">
       <colorScale>
         <cfvo type="min"/>
@@ -4183,7 +4074,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L3:M42">
+  <conditionalFormatting sqref="K3:L42">
     <cfRule type="colorScale" priority="62">
       <colorScale>
         <cfvo type="min"/>
@@ -4195,7 +4086,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O4 O6">
+  <conditionalFormatting sqref="N4 N6">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="min"/>
@@ -4210,42 +4101,42 @@
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="N9" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="N10" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="N13" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="N14" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="N17" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="N22" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="N28" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="N29" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="N31" r:id="rId9" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="N32" r:id="rId10" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="N34" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="N40" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="N8" r:id="rId13" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="N30" r:id="rId14" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="N3" r:id="rId15" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="N6" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="N7" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="N36" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="N38" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="N18" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="N39" r:id="rId21" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="N20" r:id="rId22" xr:uid="{5EAF2F70-555A-4B25-966F-95095861DC0E}"/>
-    <hyperlink ref="N23" r:id="rId23" xr:uid="{6B884554-8BB6-4BF7-8096-D834E9729A06}"/>
-    <hyperlink ref="N11" r:id="rId24" xr:uid="{44B658D6-BFFD-46B9-B230-29405BAF9534}"/>
-    <hyperlink ref="N12" r:id="rId25" xr:uid="{367FEFFE-61E8-47BB-BCCA-FD3358349566}"/>
-    <hyperlink ref="N33" r:id="rId26" xr:uid="{D1D06D79-D259-47BA-BC7F-8742EAB7848C}"/>
-    <hyperlink ref="N24" r:id="rId27" xr:uid="{5545F658-0692-42E9-BD6F-76E0A6B030B0}"/>
-    <hyperlink ref="N26" r:id="rId28" xr:uid="{168ECF43-5CE3-4702-A056-8FA8BBC47676}"/>
-    <hyperlink ref="N25" r:id="rId29" xr:uid="{EA5E5506-441F-4FE0-B453-D92044CD3CD6}"/>
-    <hyperlink ref="N27" r:id="rId30" xr:uid="{8D8C1B68-82FF-4307-AFCC-0412DDB5B0BE}"/>
-    <hyperlink ref="N4" r:id="rId31" xr:uid="{2EF0B57E-A4CF-4AC0-9358-948CDF39D8B4}"/>
-    <hyperlink ref="C15" r:id="rId32" xr:uid="{44A99C6C-4AC4-4D03-96BE-D592031C9536}"/>
-    <hyperlink ref="N15" r:id="rId33" xr:uid="{1A7B0E41-616E-45F1-BF6C-4CBB22A55EC6}"/>
-    <hyperlink ref="N19" r:id="rId34" xr:uid="{0E9DC705-3503-4FA0-87A9-DF2A5B60045D}"/>
-    <hyperlink ref="N16" r:id="rId35" xr:uid="{E7A9FE43-2492-4F96-944F-8153D9DD3BC5}"/>
-    <hyperlink ref="N5" r:id="rId36" xr:uid="{307763C7-77E9-4298-8365-93694DC5AA9D}"/>
+    <hyperlink ref="M9" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="M10" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="M13" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="M14" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="M17" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="M22" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="M28" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="M29" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="M31" r:id="rId9" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="M32" r:id="rId10" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="M34" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="M40" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="M8" r:id="rId13" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="M30" r:id="rId14" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="M3" r:id="rId15" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="M6" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="M7" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="M36" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="M38" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="M18" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="M39" r:id="rId21" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="M20" r:id="rId22" xr:uid="{5EAF2F70-555A-4B25-966F-95095861DC0E}"/>
+    <hyperlink ref="M23" r:id="rId23" xr:uid="{6B884554-8BB6-4BF7-8096-D834E9729A06}"/>
+    <hyperlink ref="M11" r:id="rId24" xr:uid="{44B658D6-BFFD-46B9-B230-29405BAF9534}"/>
+    <hyperlink ref="M12" r:id="rId25" xr:uid="{367FEFFE-61E8-47BB-BCCA-FD3358349566}"/>
+    <hyperlink ref="M33" r:id="rId26" xr:uid="{D1D06D79-D259-47BA-BC7F-8742EAB7848C}"/>
+    <hyperlink ref="M24" r:id="rId27" xr:uid="{5545F658-0692-42E9-BD6F-76E0A6B030B0}"/>
+    <hyperlink ref="M26" r:id="rId28" xr:uid="{168ECF43-5CE3-4702-A056-8FA8BBC47676}"/>
+    <hyperlink ref="M25" r:id="rId29" xr:uid="{EA5E5506-441F-4FE0-B453-D92044CD3CD6}"/>
+    <hyperlink ref="M4" r:id="rId30" xr:uid="{2EF0B57E-A4CF-4AC0-9358-948CDF39D8B4}"/>
+    <hyperlink ref="C15" r:id="rId31" xr:uid="{44A99C6C-4AC4-4D03-96BE-D592031C9536}"/>
+    <hyperlink ref="M15" r:id="rId32" xr:uid="{1A7B0E41-616E-45F1-BF6C-4CBB22A55EC6}"/>
+    <hyperlink ref="M19" r:id="rId33" xr:uid="{0E9DC705-3503-4FA0-87A9-DF2A5B60045D}"/>
+    <hyperlink ref="M16" r:id="rId34" xr:uid="{E7A9FE43-2492-4F96-944F-8153D9DD3BC5}"/>
+    <hyperlink ref="M5" r:id="rId35" xr:uid="{307763C7-77E9-4298-8365-93694DC5AA9D}"/>
+    <hyperlink ref="M27" r:id="rId36" xr:uid="{57DF62BF-599B-4CBE-A3A7-7AFF81EE4B99}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId37"/>
@@ -4263,7 +4154,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>N21:O21</xm:sqref>
+          <xm:sqref>M21:N21</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{94E20060-874B-439F-8FDA-33B3DD39FFE6}">
@@ -4276,7 +4167,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>N3:N6</xm:sqref>
+          <xm:sqref>M3:M6</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{DBB933A5-5D45-42AE-8D8B-F05439EF033D}">
@@ -4289,7 +4180,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>N32:O32</xm:sqref>
+          <xm:sqref>M32:N32</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{C3E05EE2-5FD9-4A95-BA99-400BB7B88162}">
@@ -4302,7 +4193,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>O4 O6</xm:sqref>
+          <xm:sqref>N4 N6</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>

--- a/Deliverables/Interface_Board/BOM/NEW-6 Prototypes_Interface_Board.xlsx
+++ b/Deliverables/Interface_Board/BOM/NEW-6 Prototypes_Interface_Board.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ChristianRaun-EthercatDesign\Deliverables\Interface_Board\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4AC0271-9438-4137-BC8F-87A3C52BEC57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E38A106E-3A42-44DC-A3F9-96698FEBA69F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-10695" yWindow="4170" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -677,9 +677,6 @@
     <t>4.7uF</t>
   </si>
   <si>
-    <t>CL10B474KA8NNNC</t>
-  </si>
-  <si>
     <t>470nF</t>
   </si>
   <si>
@@ -814,6 +811,9 @@
   <si>
     <t>Wattage Rating and Package Change 1206</t>
   </si>
+  <si>
+    <t>C2012X7S2A474KT000N</t>
+  </si>
 </sst>
 </file>
 
@@ -822,12 +822,19 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.0000"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1422,24 +1429,24 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="152">
+  <cellXfs count="153">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1448,7 +1455,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1457,16 +1464,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1478,47 +1485,47 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1539,93 +1546,93 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="5" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="5" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="21" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="21" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="21" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="21" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="21" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="21" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="21" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="20" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="20" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="27" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="27" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="26" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1634,10 +1641,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="4" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="4" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
@@ -1649,16 +1656,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="25" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="25" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1670,52 +1677,52 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="6" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="6" borderId="21" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="14" fillId="6" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="6" borderId="21" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="16" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="16" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1724,10 +1731,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="23" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="23" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1736,51 +1743,51 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="25" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="25" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="26" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="26" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1793,44 +1800,26 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1838,29 +1827,50 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="20" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="20" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="21" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="21" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2159,22 +2169,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" ht="16.5" thickBot="1">
-      <c r="A1" s="138" t="s">
+      <c r="A1" s="146" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="139"/>
-      <c r="G1" s="139"/>
-      <c r="H1" s="139"/>
-      <c r="I1" s="139"/>
-      <c r="J1" s="139"/>
-      <c r="K1" s="139"/>
-      <c r="L1" s="139"/>
-      <c r="M1" s="139"/>
-      <c r="N1" s="140"/>
+      <c r="B1" s="147"/>
+      <c r="C1" s="147"/>
+      <c r="D1" s="147"/>
+      <c r="E1" s="147"/>
+      <c r="F1" s="147"/>
+      <c r="G1" s="147"/>
+      <c r="H1" s="147"/>
+      <c r="I1" s="147"/>
+      <c r="J1" s="147"/>
+      <c r="K1" s="147"/>
+      <c r="L1" s="147"/>
+      <c r="M1" s="147"/>
+      <c r="N1" s="148"/>
     </row>
     <row r="2" spans="1:29" s="1" customFormat="1" ht="16.5" thickBot="1">
       <c r="A2" s="3" t="s">
@@ -2217,7 +2227,7 @@
         <v>179</v>
       </c>
       <c r="N2" s="131" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O2"/>
       <c r="P2"/>
@@ -2239,14 +2249,14 @@
       <c r="A3" s="6">
         <v>1</v>
       </c>
-      <c r="B3" s="135" t="s">
+      <c r="B3" s="149" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="83" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="129" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E3" s="84" t="s">
         <v>14</v>
@@ -2277,14 +2287,14 @@
         <v>20</v>
       </c>
       <c r="N3" s="130" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4" spans="1:29" ht="15.75" thickBot="1">
       <c r="A4" s="6">
         <v>2</v>
       </c>
-      <c r="B4" s="136"/>
+      <c r="B4" s="150"/>
       <c r="C4" s="93" t="s">
         <v>205</v>
       </c>
@@ -2325,30 +2335,30 @@
       <c r="A5" s="6">
         <v>3</v>
       </c>
-      <c r="B5" s="136"/>
+      <c r="B5" s="150"/>
       <c r="C5" s="133" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D5" s="134" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E5" s="80" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="81" t="s">
-        <v>210</v>
+      <c r="F5" s="152" t="s">
+        <v>249</v>
       </c>
       <c r="G5" s="90" t="s">
         <v>37</v>
       </c>
       <c r="H5" s="89" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I5" s="90" t="s">
         <v>18</v>
       </c>
       <c r="J5" s="81" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="K5" s="82">
         <v>2</v>
@@ -2361,14 +2371,14 @@
         <v>20</v>
       </c>
       <c r="N5" s="132" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6" spans="1:29" ht="15.75" thickBot="1">
       <c r="A6" s="6">
         <v>4</v>
       </c>
-      <c r="B6" s="136"/>
+      <c r="B6" s="150"/>
       <c r="C6" s="34" t="s">
         <v>21</v>
       </c>
@@ -2409,7 +2419,7 @@
       <c r="A7" s="6">
         <v>5</v>
       </c>
-      <c r="B7" s="136"/>
+      <c r="B7" s="150"/>
       <c r="C7" s="34" t="s">
         <v>28</v>
       </c>
@@ -2450,12 +2460,12 @@
       <c r="A8" s="6">
         <v>6</v>
       </c>
-      <c r="B8" s="136"/>
+      <c r="B8" s="150"/>
       <c r="C8" s="34" t="s">
         <v>35</v>
       </c>
       <c r="D8" s="112" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E8" s="27" t="s">
         <v>14</v>
@@ -2491,7 +2501,7 @@
       <c r="A9" s="6">
         <v>7</v>
       </c>
-      <c r="B9" s="136"/>
+      <c r="B9" s="150"/>
       <c r="C9" s="34" t="s">
         <v>41</v>
       </c>
@@ -2532,12 +2542,12 @@
       <c r="A10" s="6">
         <v>8</v>
       </c>
-      <c r="B10" s="136"/>
+      <c r="B10" s="150"/>
       <c r="C10" s="34" t="s">
         <v>48</v>
       </c>
       <c r="D10" s="112" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E10" s="27" t="s">
         <v>43</v>
@@ -2573,7 +2583,7 @@
       <c r="A11" s="6">
         <v>9</v>
       </c>
-      <c r="B11" s="136"/>
+      <c r="B11" s="150"/>
       <c r="C11" s="99" t="s">
         <v>161</v>
       </c>
@@ -2590,7 +2600,7 @@
         <v>25</v>
       </c>
       <c r="H11" s="54" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I11" s="28" t="s">
         <v>18</v>
@@ -2614,7 +2624,7 @@
       <c r="A12" s="6">
         <v>10</v>
       </c>
-      <c r="B12" s="136"/>
+      <c r="B12" s="150"/>
       <c r="C12" s="34" t="s">
         <v>163</v>
       </c>
@@ -2631,7 +2641,7 @@
         <v>16</v>
       </c>
       <c r="H12" s="54" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="I12" s="28" t="s">
         <v>18</v>
@@ -2655,7 +2665,7 @@
       <c r="A13" s="6">
         <v>11</v>
       </c>
-      <c r="B13" s="137"/>
+      <c r="B13" s="151"/>
       <c r="C13" s="35" t="s">
         <v>55</v>
       </c>
@@ -2696,7 +2706,7 @@
       <c r="A14" s="6">
         <v>12</v>
       </c>
-      <c r="B14" s="136" t="s">
+      <c r="B14" s="150" t="s">
         <v>62</v>
       </c>
       <c r="C14" s="101" t="s">
@@ -2739,24 +2749,24 @@
       <c r="A15" s="6">
         <v>13</v>
       </c>
-      <c r="B15" s="136"/>
+      <c r="B15" s="150"/>
       <c r="C15" s="34" t="s">
+        <v>215</v>
+      </c>
+      <c r="D15" s="112" t="s">
+        <v>214</v>
+      </c>
+      <c r="E15" s="53" t="s">
+        <v>213</v>
+      </c>
+      <c r="F15" s="53" t="s">
+        <v>212</v>
+      </c>
+      <c r="G15" s="53" t="s">
         <v>216</v>
       </c>
-      <c r="D15" s="112" t="s">
-        <v>215</v>
-      </c>
-      <c r="E15" s="53" t="s">
-        <v>214</v>
-      </c>
-      <c r="F15" s="53" t="s">
-        <v>213</v>
-      </c>
-      <c r="G15" s="53" t="s">
+      <c r="H15" s="104" t="s">
         <v>217</v>
-      </c>
-      <c r="H15" s="104" t="s">
-        <v>218</v>
       </c>
       <c r="I15" s="54" t="s">
         <v>18</v>
@@ -2780,24 +2790,24 @@
       <c r="A16" s="6">
         <v>14</v>
       </c>
-      <c r="B16" s="136"/>
+      <c r="B16" s="150"/>
       <c r="C16" s="93" t="s">
+        <v>229</v>
+      </c>
+      <c r="D16" s="112" t="s">
+        <v>228</v>
+      </c>
+      <c r="E16" s="53" t="s">
+        <v>227</v>
+      </c>
+      <c r="F16" s="53" t="s">
+        <v>226</v>
+      </c>
+      <c r="G16" s="53" t="s">
         <v>230</v>
       </c>
-      <c r="D16" s="112" t="s">
-        <v>229</v>
-      </c>
-      <c r="E16" s="53" t="s">
-        <v>228</v>
-      </c>
-      <c r="F16" s="53" t="s">
-        <v>227</v>
-      </c>
-      <c r="G16" s="53" t="s">
+      <c r="H16" s="104" t="s">
         <v>231</v>
-      </c>
-      <c r="H16" s="104" t="s">
-        <v>232</v>
       </c>
       <c r="I16" s="54" t="s">
         <v>18</v>
@@ -2821,7 +2831,7 @@
       <c r="A17" s="6">
         <v>15</v>
       </c>
-      <c r="B17" s="136"/>
+      <c r="B17" s="150"/>
       <c r="C17" s="105" t="s">
         <v>70</v>
       </c>
@@ -2906,28 +2916,28 @@
         <v>17</v>
       </c>
       <c r="B19" s="92" t="s">
+        <v>218</v>
+      </c>
+      <c r="C19" s="109" t="s">
+        <v>220</v>
+      </c>
+      <c r="D19" s="114" t="s">
         <v>219</v>
       </c>
-      <c r="C19" s="109" t="s">
+      <c r="E19" s="110" t="s">
         <v>221</v>
       </c>
-      <c r="D19" s="114" t="s">
-        <v>220</v>
-      </c>
-      <c r="E19" s="110" t="s">
+      <c r="F19" s="110" t="s">
         <v>222</v>
       </c>
-      <c r="F19" s="110" t="s">
+      <c r="G19" s="111" t="s">
         <v>223</v>
       </c>
-      <c r="G19" s="111" t="s">
+      <c r="H19" s="111" t="s">
         <v>224</v>
       </c>
-      <c r="H19" s="111" t="s">
+      <c r="I19" s="110" t="s">
         <v>225</v>
-      </c>
-      <c r="I19" s="110" t="s">
-        <v>226</v>
       </c>
       <c r="J19" s="111" t="s">
         <v>69</v>
@@ -2948,7 +2958,7 @@
       <c r="A20" s="6">
         <v>18</v>
       </c>
-      <c r="B20" s="135" t="s">
+      <c r="B20" s="149" t="s">
         <v>82</v>
       </c>
       <c r="C20" s="65" t="s">
@@ -2991,7 +3001,7 @@
       <c r="A21" s="6">
         <v>19</v>
       </c>
-      <c r="B21" s="137"/>
+      <c r="B21" s="151"/>
       <c r="C21" s="46" t="s">
         <v>83</v>
       </c>
@@ -3028,14 +3038,14 @@
       <c r="A22" s="6">
         <v>20</v>
       </c>
-      <c r="B22" s="135" t="s">
+      <c r="B22" s="149" t="s">
         <v>88</v>
       </c>
-      <c r="C22" s="141" t="s">
+      <c r="C22" s="135" t="s">
         <v>89</v>
       </c>
-      <c r="D22" s="145" t="s">
-        <v>244</v>
+      <c r="D22" s="139" t="s">
+        <v>243</v>
       </c>
       <c r="E22" s="25" t="s">
         <v>90</v>
@@ -3055,23 +3065,23 @@
       <c r="J22" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="K22" s="142">
+      <c r="K22" s="136">
         <v>3</v>
       </c>
-      <c r="L22" s="142">
+      <c r="L22" s="136">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="M22" s="143" t="s">
+      <c r="M22" s="137" t="s">
         <v>20</v>
       </c>
-      <c r="N22" s="144"/>
+      <c r="N22" s="138"/>
     </row>
     <row r="23" spans="1:14" ht="15.75" thickBot="1">
       <c r="A23" s="6">
         <v>21</v>
       </c>
-      <c r="B23" s="136"/>
+      <c r="B23" s="150"/>
       <c r="C23" s="116" t="s">
         <v>165</v>
       </c>
@@ -3088,7 +3098,7 @@
         <v>155</v>
       </c>
       <c r="H23" s="54" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="I23" s="27" t="s">
         <v>18</v>
@@ -3112,7 +3122,7 @@
       <c r="A24" s="6">
         <v>22</v>
       </c>
-      <c r="B24" s="136"/>
+      <c r="B24" s="150"/>
       <c r="C24" s="117" t="s">
         <v>193</v>
       </c>
@@ -3153,7 +3163,7 @@
       <c r="A25" s="6">
         <v>23</v>
       </c>
-      <c r="B25" s="136"/>
+      <c r="B25" s="150"/>
       <c r="C25" s="117" t="s">
         <v>194</v>
       </c>
@@ -3194,7 +3204,7 @@
       <c r="A26" s="6">
         <v>24</v>
       </c>
-      <c r="B26" s="136"/>
+      <c r="B26" s="150"/>
       <c r="C26" s="117" t="s">
         <v>196</v>
       </c>
@@ -3235,24 +3245,24 @@
       <c r="A27" s="6">
         <v>25</v>
       </c>
-      <c r="B27" s="136"/>
-      <c r="C27" s="146" t="s">
-        <v>248</v>
-      </c>
-      <c r="D27" s="147" t="s">
+      <c r="B27" s="150"/>
+      <c r="C27" s="140" t="s">
+        <v>247</v>
+      </c>
+      <c r="D27" s="141" t="s">
         <v>203</v>
       </c>
-      <c r="E27" s="148" t="s">
-        <v>247</v>
-      </c>
-      <c r="F27" s="149" t="s">
+      <c r="E27" s="142" t="s">
         <v>246</v>
       </c>
-      <c r="G27" s="149" t="s">
+      <c r="F27" s="143" t="s">
+        <v>245</v>
+      </c>
+      <c r="G27" s="143" t="s">
         <v>114</v>
       </c>
-      <c r="H27" s="150" t="s">
-        <v>245</v>
+      <c r="H27" s="144" t="s">
+        <v>244</v>
       </c>
       <c r="I27" s="80" t="s">
         <v>18</v>
@@ -3267,18 +3277,18 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="M27" s="151" t="s">
+      <c r="M27" s="145" t="s">
         <v>20</v>
       </c>
       <c r="N27" s="132" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="15.75" thickBot="1">
       <c r="A28" s="6">
         <v>26</v>
       </c>
-      <c r="B28" s="136"/>
+      <c r="B28" s="150"/>
       <c r="C28" s="34" t="s">
         <v>94</v>
       </c>
@@ -3319,7 +3329,7 @@
       <c r="A29" s="6">
         <v>27</v>
       </c>
-      <c r="B29" s="136"/>
+      <c r="B29" s="150"/>
       <c r="C29" s="34" t="s">
         <v>99</v>
       </c>
@@ -3360,7 +3370,7 @@
       <c r="A30" s="6">
         <v>28</v>
       </c>
-      <c r="B30" s="136"/>
+      <c r="B30" s="150"/>
       <c r="C30" s="34" t="s">
         <v>104</v>
       </c>
@@ -3401,7 +3411,7 @@
       <c r="A31" s="6">
         <v>29</v>
       </c>
-      <c r="B31" s="136"/>
+      <c r="B31" s="150"/>
       <c r="C31" s="34" t="s">
         <v>111</v>
       </c>
@@ -3442,7 +3452,7 @@
       <c r="A32" s="6">
         <v>30</v>
       </c>
-      <c r="B32" s="137"/>
+      <c r="B32" s="151"/>
       <c r="C32" s="35" t="s">
         <v>117</v>
       </c>
@@ -3483,7 +3493,7 @@
       <c r="A33" s="6">
         <v>31</v>
       </c>
-      <c r="B33" s="136" t="s">
+      <c r="B33" s="150" t="s">
         <v>122</v>
       </c>
       <c r="C33" s="124" t="s">
@@ -3526,7 +3536,7 @@
       <c r="A34" s="6">
         <v>32</v>
       </c>
-      <c r="B34" s="136"/>
+      <c r="B34" s="150"/>
       <c r="C34" s="34" t="s">
         <v>124</v>
       </c>
@@ -3567,7 +3577,7 @@
       <c r="A35" s="6">
         <v>33</v>
       </c>
-      <c r="B35" s="136"/>
+      <c r="B35" s="150"/>
       <c r="C35" s="75" t="s">
         <v>169</v>
       </c>
@@ -3606,7 +3616,7 @@
       <c r="A36" s="6">
         <v>34</v>
       </c>
-      <c r="B36" s="135" t="s">
+      <c r="B36" s="149" t="s">
         <v>132</v>
       </c>
       <c r="C36" s="36" t="s">
@@ -3649,7 +3659,7 @@
       <c r="A37" s="6">
         <v>35</v>
       </c>
-      <c r="B37" s="136"/>
+      <c r="B37" s="150"/>
       <c r="C37" s="38" t="s">
         <v>138</v>
       </c>
@@ -3690,7 +3700,7 @@
       <c r="A38" s="6">
         <v>36</v>
       </c>
-      <c r="B38" s="136"/>
+      <c r="B38" s="150"/>
       <c r="C38" s="38" t="s">
         <v>144</v>
       </c>
@@ -3731,7 +3741,7 @@
       <c r="A39" s="6">
         <v>37</v>
       </c>
-      <c r="B39" s="136"/>
+      <c r="B39" s="150"/>
       <c r="C39" s="16" t="s">
         <v>147</v>
       </c>
@@ -3772,7 +3782,7 @@
       <c r="A40" s="6">
         <v>38</v>
       </c>
-      <c r="B40" s="136"/>
+      <c r="B40" s="150"/>
       <c r="C40" s="34" t="s">
         <v>151</v>
       </c>
@@ -3813,7 +3823,7 @@
       <c r="A41" s="6">
         <v>39</v>
       </c>
-      <c r="B41" s="136"/>
+      <c r="B41" s="150"/>
       <c r="C41" s="41" t="s">
         <v>157</v>
       </c>
@@ -3844,7 +3854,7 @@
       <c r="A42" s="20">
         <v>40</v>
       </c>
-      <c r="B42" s="137"/>
+      <c r="B42" s="151"/>
       <c r="C42" s="43" t="s">
         <v>159</v>
       </c>
@@ -3943,15 +3953,15 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="B36:B42"/>
+    <mergeCell ref="B20:B21"/>
     <mergeCell ref="A1:N1"/>
     <mergeCell ref="B3:B13"/>
     <mergeCell ref="B14:B17"/>
     <mergeCell ref="B22:B32"/>
     <mergeCell ref="B33:B35"/>
-    <mergeCell ref="B36:B42"/>
-    <mergeCell ref="B20:B21"/>
   </mergeCells>
-  <phoneticPr fontId="21" type="noConversion"/>
+  <phoneticPr fontId="22" type="noConversion"/>
   <conditionalFormatting sqref="M21:N21">
     <cfRule type="dataBar" priority="39">
       <dataBar>

--- a/Deliverables/Interface_Board/BOM/NEW-6 Prototypes_Interface_Board.xlsx
+++ b/Deliverables/Interface_Board/BOM/NEW-6 Prototypes_Interface_Board.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25219"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ChristianRaun-EthercatDesign\Deliverables\Interface_Board\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\ChristianRaun-EthercatDesign\Deliverables\Interface_Board\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E38A106E-3A42-44DC-A3F9-96698FEBA69F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDF47179-0C58-4C13-A5D5-F912EB5D2053}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-10695" yWindow="4170" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="251">
   <si>
     <t>Bill of Material (BOM) for Interface_Board</t>
   </si>
@@ -435,9 +435,6 @@
   </si>
   <si>
     <t>Connector</t>
-  </si>
-  <si>
-    <t>P=2.54mm Female Headers,SMD,ROHS</t>
   </si>
   <si>
     <t>J1</t>
@@ -813,6 +810,12 @@
   </si>
   <si>
     <t>C2012X7S2A474KT000N</t>
+  </si>
+  <si>
+    <t>26-pin Dual Row (13 x 2), P=2.54mm Female Headers,SMD,ROHS</t>
+  </si>
+  <si>
+    <t>Description added for number of pins</t>
   </si>
 </sst>
 </file>
@@ -1061,7 +1064,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="28">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -1426,14 +1429,43 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="153">
+  <cellXfs count="142">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1449,25 +1481,25 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1476,13 +1508,10 @@
     <xf numFmtId="0" fontId="10" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1494,20 +1523,19 @@
     <xf numFmtId="0" fontId="12" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1516,34 +1544,28 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1579,9 +1601,6 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1598,15 +1617,12 @@
     <xf numFmtId="0" fontId="15" fillId="4" borderId="21" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="21" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="21" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="21" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1616,14 +1632,14 @@
     <xf numFmtId="0" fontId="10" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="20" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="24" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1635,10 +1651,10 @@
     <xf numFmtId="0" fontId="14" fillId="4" borderId="27" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="26" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="26" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1653,28 +1669,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="4" borderId="25" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1683,10 +1693,10 @@
     <xf numFmtId="0" fontId="10" fillId="6" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="6" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="6" borderId="20" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1713,40 +1723,31 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="16" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="16" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="23" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="23" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="25" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="26" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1771,10 +1772,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1791,12 +1789,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1821,10 +1813,10 @@
     <xf numFmtId="0" fontId="26" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="20" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1836,7 +1828,7 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1852,13 +1844,7 @@
     <xf numFmtId="0" fontId="14" fillId="6" borderId="21" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1870,7 +1856,25 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="28" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="29" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2149,1760 +2153,1746 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC59"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <dimension ref="A1:N59"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="6.140625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="14.42578125" customWidth="1"/>
-    <col min="3" max="3" width="103.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="34.7109375" customWidth="1"/>
+    <col min="1" max="1" width="6.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="14.44140625" customWidth="1"/>
+    <col min="3" max="3" width="103.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.6640625" customWidth="1"/>
     <col min="5" max="5" width="21" customWidth="1"/>
     <col min="6" max="6" width="29" customWidth="1"/>
-    <col min="7" max="7" width="26.28515625" customWidth="1"/>
-    <col min="8" max="8" width="15.28515625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="21.5703125" customWidth="1"/>
+    <col min="7" max="7" width="26.33203125" customWidth="1"/>
+    <col min="8" max="8" width="15.33203125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="21.5546875" customWidth="1"/>
     <col min="10" max="10" width="7" customWidth="1"/>
-    <col min="11" max="11" width="21.85546875" customWidth="1"/>
-    <col min="12" max="12" width="14.140625" customWidth="1"/>
-    <col min="13" max="13" width="16.28515625" customWidth="1"/>
-    <col min="14" max="14" width="37.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.88671875" customWidth="1"/>
+    <col min="12" max="12" width="14.109375" customWidth="1"/>
+    <col min="13" max="13" width="16.33203125" customWidth="1"/>
+    <col min="14" max="14" width="37.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="16.5" thickBot="1">
-      <c r="A1" s="146" t="s">
+    <row r="1" spans="1:14" ht="16.2" thickBot="1">
+      <c r="A1" s="135" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="147"/>
-      <c r="G1" s="147"/>
-      <c r="H1" s="147"/>
-      <c r="I1" s="147"/>
-      <c r="J1" s="147"/>
-      <c r="K1" s="147"/>
-      <c r="L1" s="147"/>
-      <c r="M1" s="147"/>
-      <c r="N1" s="148"/>
-    </row>
-    <row r="2" spans="1:29" s="1" customFormat="1" ht="16.5" thickBot="1">
-      <c r="A2" s="3" t="s">
+      <c r="B1" s="136"/>
+      <c r="C1" s="136"/>
+      <c r="D1" s="136"/>
+      <c r="E1" s="136"/>
+      <c r="F1" s="136"/>
+      <c r="G1" s="136"/>
+      <c r="H1" s="136"/>
+      <c r="I1" s="136"/>
+      <c r="J1" s="136"/>
+      <c r="K1" s="136"/>
+      <c r="L1" s="136"/>
+      <c r="M1" s="136"/>
+      <c r="N1" s="137"/>
+    </row>
+    <row r="2" spans="1:14" ht="16.2" thickBot="1">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="50" t="s">
-        <v>180</v>
-      </c>
-      <c r="M2" s="55" t="s">
+      <c r="L2" s="45" t="s">
         <v>179</v>
       </c>
-      <c r="N2" s="131" t="s">
-        <v>238</v>
-      </c>
-      <c r="O2"/>
-      <c r="P2"/>
-      <c r="Q2"/>
-      <c r="R2"/>
-      <c r="S2"/>
-      <c r="T2"/>
-      <c r="U2"/>
-      <c r="V2"/>
-      <c r="W2"/>
-      <c r="X2"/>
-      <c r="Y2"/>
-      <c r="Z2"/>
-      <c r="AA2"/>
-      <c r="AB2"/>
-      <c r="AC2"/>
-    </row>
-    <row r="3" spans="1:29" ht="15.75" thickBot="1">
-      <c r="A3" s="6">
+      <c r="M2" s="49" t="s">
+        <v>178</v>
+      </c>
+      <c r="N2" s="116" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="15" thickBot="1">
+      <c r="A3" s="5">
         <v>1</v>
       </c>
-      <c r="B3" s="149" t="s">
+      <c r="B3" s="132" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="83" t="s">
+      <c r="C3" s="74" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="129" t="s">
-        <v>237</v>
-      </c>
-      <c r="E3" s="84" t="s">
+      <c r="D3" s="114" t="s">
+        <v>236</v>
+      </c>
+      <c r="E3" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="84" t="s">
+      <c r="F3" s="75" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="84" t="s">
+      <c r="G3" s="75" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="85" t="s">
+      <c r="H3" s="76" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="86" t="s">
-        <v>18</v>
-      </c>
-      <c r="J3" s="84" t="s">
+      <c r="I3" s="77" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="75" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="87">
+      <c r="K3" s="78">
         <v>6</v>
       </c>
-      <c r="L3" s="87">
+      <c r="L3" s="78">
         <f>K3*6</f>
         <v>36</v>
       </c>
-      <c r="M3" s="88" t="s">
+      <c r="M3" s="79" t="s">
         <v>20</v>
       </c>
-      <c r="N3" s="130" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="4" spans="1:29" ht="15.75" thickBot="1">
-      <c r="A4" s="6">
+      <c r="N3" s="115" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="15" thickBot="1">
+      <c r="A4" s="5">
         <v>2</v>
       </c>
-      <c r="B4" s="150"/>
-      <c r="C4" s="93" t="s">
+      <c r="B4" s="133"/>
+      <c r="C4" s="84" t="s">
+        <v>204</v>
+      </c>
+      <c r="D4" s="103" t="s">
         <v>205</v>
       </c>
-      <c r="D4" s="115" t="s">
+      <c r="E4" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="47" t="s">
+        <v>203</v>
+      </c>
+      <c r="G4" s="47" t="s">
         <v>206</v>
       </c>
-      <c r="E4" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="53" t="s">
-        <v>204</v>
-      </c>
-      <c r="G4" s="53" t="s">
+      <c r="H4" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="H4" s="94" t="s">
+      <c r="I4" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" s="47" t="s">
         <v>208</v>
       </c>
-      <c r="I4" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="J4" s="53" t="s">
-        <v>209</v>
-      </c>
-      <c r="K4" s="7">
+      <c r="K4" s="6">
         <v>1</v>
       </c>
-      <c r="L4" s="7">
+      <c r="L4" s="6">
         <f t="shared" ref="L4:L5" si="0">K4*6</f>
         <v>6</v>
       </c>
-      <c r="M4" s="95" t="s">
+      <c r="M4" s="86" t="s">
         <v>20</v>
       </c>
-      <c r="N4" s="95"/>
-    </row>
-    <row r="5" spans="1:29" ht="15.75" thickBot="1">
-      <c r="A5" s="6">
+      <c r="N4" s="86"/>
+    </row>
+    <row r="5" spans="1:14" ht="15" thickBot="1">
+      <c r="A5" s="5">
         <v>3</v>
       </c>
-      <c r="B5" s="150"/>
-      <c r="C5" s="133" t="s">
+      <c r="B5" s="133"/>
+      <c r="C5" s="118" t="s">
+        <v>239</v>
+      </c>
+      <c r="D5" s="119" t="s">
+        <v>210</v>
+      </c>
+      <c r="E5" s="71" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="131" t="s">
+        <v>248</v>
+      </c>
+      <c r="G5" s="81" t="s">
+        <v>37</v>
+      </c>
+      <c r="H5" s="80" t="s">
         <v>240</v>
       </c>
-      <c r="D5" s="134" t="s">
-        <v>211</v>
-      </c>
-      <c r="E5" s="80" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="152" t="s">
-        <v>249</v>
-      </c>
-      <c r="G5" s="90" t="s">
-        <v>37</v>
-      </c>
-      <c r="H5" s="89" t="s">
-        <v>241</v>
-      </c>
-      <c r="I5" s="90" t="s">
-        <v>18</v>
-      </c>
-      <c r="J5" s="81" t="s">
-        <v>210</v>
-      </c>
-      <c r="K5" s="82">
+      <c r="I5" s="81" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" s="72" t="s">
+        <v>209</v>
+      </c>
+      <c r="K5" s="73">
         <v>2</v>
       </c>
-      <c r="L5" s="82">
+      <c r="L5" s="73">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="M5" s="91" t="s">
+      <c r="M5" s="82" t="s">
         <v>20</v>
       </c>
-      <c r="N5" s="132" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="6" spans="1:29" ht="15.75" thickBot="1">
-      <c r="A6" s="6">
+      <c r="N5" s="117" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="15" thickBot="1">
+      <c r="A6" s="5">
         <v>4</v>
       </c>
-      <c r="B6" s="150"/>
-      <c r="C6" s="34" t="s">
+      <c r="B6" s="133"/>
+      <c r="C6" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="27" t="s">
+      <c r="D6" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="27" t="s">
+      <c r="E6" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="27" t="s">
+      <c r="F6" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="27" t="s">
+      <c r="G6" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="96" t="s">
+      <c r="H6" s="87" t="s">
         <v>26</v>
       </c>
-      <c r="I6" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="J6" s="27" t="s">
+      <c r="I6" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="K6" s="7">
+      <c r="K6" s="6">
         <v>1</v>
       </c>
-      <c r="L6" s="7">
+      <c r="L6" s="6">
         <f t="shared" ref="L6:L42" si="1">K6*6</f>
         <v>6</v>
       </c>
-      <c r="M6" s="97" t="s">
+      <c r="M6" s="86" t="s">
         <v>20</v>
       </c>
-      <c r="N6" s="97"/>
-    </row>
-    <row r="7" spans="1:29" ht="15.75" thickBot="1">
-      <c r="A7" s="6">
+      <c r="N6" s="86"/>
+    </row>
+    <row r="7" spans="1:14" ht="15" thickBot="1">
+      <c r="A7" s="5">
         <v>5</v>
       </c>
-      <c r="B7" s="150"/>
-      <c r="C7" s="34" t="s">
+      <c r="B7" s="133"/>
+      <c r="C7" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="27" t="s">
+      <c r="D7" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="27" t="s">
+      <c r="E7" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="29" t="s">
+      <c r="F7" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="G7" s="27" t="s">
+      <c r="G7" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="H7" s="96" t="s">
+      <c r="H7" s="87" t="s">
         <v>32</v>
       </c>
-      <c r="I7" s="96" t="s">
+      <c r="I7" s="87" t="s">
         <v>33</v>
       </c>
-      <c r="J7" s="27" t="s">
+      <c r="J7" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="K7" s="7">
+      <c r="K7" s="6">
         <v>8</v>
       </c>
-      <c r="L7" s="7">
+      <c r="L7" s="6">
         <f t="shared" si="1"/>
         <v>48</v>
       </c>
-      <c r="M7" s="98" t="s">
+      <c r="M7" s="53" t="s">
         <v>20</v>
       </c>
-      <c r="N7" s="98"/>
-    </row>
-    <row r="8" spans="1:29" ht="15.75" thickBot="1">
-      <c r="A8" s="6">
+      <c r="N7" s="53"/>
+    </row>
+    <row r="8" spans="1:14" ht="15" thickBot="1">
+      <c r="A8" s="5">
         <v>6</v>
       </c>
-      <c r="B8" s="150"/>
-      <c r="C8" s="34" t="s">
+      <c r="B8" s="133"/>
+      <c r="C8" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="112" t="s">
-        <v>236</v>
-      </c>
-      <c r="E8" s="27" t="s">
+      <c r="D8" s="100" t="s">
+        <v>235</v>
+      </c>
+      <c r="E8" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="F8" s="29" t="s">
+      <c r="F8" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="G8" s="28" t="s">
+      <c r="G8" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="H8" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="I8" s="27" t="s">
+      <c r="I8" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="J8" s="27" t="s">
+      <c r="J8" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="K8" s="9">
+      <c r="K8" s="8">
         <v>3</v>
       </c>
-      <c r="L8" s="7">
+      <c r="L8" s="6">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="M8" s="57" t="s">
+      <c r="M8" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="N8" s="57"/>
-    </row>
-    <row r="9" spans="1:29" ht="15.75" thickBot="1">
-      <c r="A9" s="6">
+      <c r="N8" s="51"/>
+    </row>
+    <row r="9" spans="1:14" ht="15" thickBot="1">
+      <c r="A9" s="5">
         <v>7</v>
       </c>
-      <c r="B9" s="150"/>
-      <c r="C9" s="34" t="s">
+      <c r="B9" s="133"/>
+      <c r="C9" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="27" t="s">
+      <c r="D9" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="E9" s="27" t="s">
+      <c r="E9" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="27" t="s">
+      <c r="F9" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="G9" s="28" t="s">
+      <c r="G9" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="H9" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="I9" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="J9" s="27" t="s">
+      <c r="I9" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="K9" s="9">
+      <c r="K9" s="8">
         <v>1</v>
       </c>
-      <c r="L9" s="7">
+      <c r="L9" s="6">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M9" s="57" t="s">
+      <c r="M9" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="N9" s="57"/>
-    </row>
-    <row r="10" spans="1:29" ht="15.75" thickBot="1">
-      <c r="A10" s="6">
+      <c r="N9" s="51"/>
+    </row>
+    <row r="10" spans="1:14" ht="15" thickBot="1">
+      <c r="A10" s="5">
         <v>8</v>
       </c>
-      <c r="B10" s="150"/>
-      <c r="C10" s="34" t="s">
+      <c r="B10" s="133"/>
+      <c r="C10" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="D10" s="112" t="s">
-        <v>235</v>
-      </c>
-      <c r="E10" s="27" t="s">
+      <c r="D10" s="100" t="s">
+        <v>234</v>
+      </c>
+      <c r="E10" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="F10" s="27" t="s">
+      <c r="F10" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="G10" s="28" t="s">
+      <c r="G10" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="H10" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="I10" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="J10" s="27" t="s">
+      <c r="I10" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10" s="24" t="s">
         <v>47</v>
       </c>
-      <c r="K10" s="9">
+      <c r="K10" s="8">
         <v>3</v>
       </c>
-      <c r="L10" s="7">
+      <c r="L10" s="6">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="M10" s="57" t="s">
+      <c r="M10" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="N10" s="57"/>
-    </row>
-    <row r="11" spans="1:29" ht="15.75" thickBot="1">
-      <c r="A11" s="6">
+      <c r="N10" s="51"/>
+    </row>
+    <row r="11" spans="1:14" ht="15" thickBot="1">
+      <c r="A11" s="5">
         <v>9</v>
       </c>
-      <c r="B11" s="150"/>
-      <c r="C11" s="99" t="s">
+      <c r="B11" s="133"/>
+      <c r="C11" s="31" t="s">
+        <v>160</v>
+      </c>
+      <c r="D11" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="24" t="s">
         <v>161</v>
       </c>
-      <c r="D11" s="51" t="s">
-        <v>51</v>
-      </c>
-      <c r="E11" s="51" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11" s="51" t="s">
-        <v>162</v>
-      </c>
-      <c r="G11" s="28" t="s">
+      <c r="G11" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="H11" s="54" t="s">
-        <v>232</v>
-      </c>
-      <c r="I11" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="J11" s="27" t="s">
+      <c r="H11" s="48" t="s">
+        <v>231</v>
+      </c>
+      <c r="I11" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="J11" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="K11" s="9">
+      <c r="K11" s="8">
         <v>1</v>
       </c>
-      <c r="L11" s="7">
+      <c r="L11" s="6">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M11" s="56" t="s">
+      <c r="M11" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="N11" s="56"/>
-    </row>
-    <row r="12" spans="1:29" ht="15.75" thickBot="1">
-      <c r="A12" s="6">
+      <c r="N11" s="50"/>
+    </row>
+    <row r="12" spans="1:14" ht="15" thickBot="1">
+      <c r="A12" s="5">
         <v>10</v>
       </c>
-      <c r="B12" s="150"/>
-      <c r="C12" s="34" t="s">
+      <c r="B12" s="133"/>
+      <c r="C12" s="31" t="s">
+        <v>162</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" s="24" t="s">
         <v>163</v>
       </c>
-      <c r="D12" s="27" t="s">
-        <v>53</v>
-      </c>
-      <c r="E12" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="F12" s="27" t="s">
-        <v>164</v>
-      </c>
-      <c r="G12" s="28" t="s">
+      <c r="G12" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="H12" s="54" t="s">
-        <v>233</v>
-      </c>
-      <c r="I12" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="J12" s="27" t="s">
+      <c r="H12" s="48" t="s">
+        <v>232</v>
+      </c>
+      <c r="I12" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="J12" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="K12" s="9">
+      <c r="K12" s="8">
         <v>1</v>
       </c>
-      <c r="L12" s="7">
+      <c r="L12" s="6">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M12" s="56" t="s">
+      <c r="M12" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="N12" s="56"/>
-    </row>
-    <row r="13" spans="1:29" ht="15.75" thickBot="1">
-      <c r="A13" s="6">
+      <c r="N12" s="50"/>
+    </row>
+    <row r="13" spans="1:14" ht="15" thickBot="1">
+      <c r="A13" s="5">
         <v>11</v>
       </c>
-      <c r="B13" s="151"/>
-      <c r="C13" s="35" t="s">
+      <c r="B13" s="134"/>
+      <c r="C13" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="D13" s="30" t="s">
+      <c r="D13" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="E13" s="30" t="s">
+      <c r="E13" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="F13" s="30" t="s">
+      <c r="F13" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="G13" s="31" t="s">
+      <c r="G13" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="H13" s="12" t="s">
+      <c r="H13" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="I13" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="J13" s="30" t="s">
+      <c r="I13" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="J13" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="K13" s="12">
+      <c r="K13" s="11">
         <v>1</v>
       </c>
-      <c r="L13" s="10">
+      <c r="L13" s="9">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M13" s="100" t="s">
+      <c r="M13" s="88" t="s">
         <v>20</v>
       </c>
-      <c r="N13" s="100"/>
-    </row>
-    <row r="14" spans="1:29" ht="15.75" thickBot="1">
-      <c r="A14" s="6">
+      <c r="N13" s="88"/>
+    </row>
+    <row r="14" spans="1:14" ht="15" thickBot="1">
+      <c r="A14" s="5">
         <v>12</v>
       </c>
-      <c r="B14" s="150" t="s">
+      <c r="B14" s="133" t="s">
         <v>62</v>
       </c>
-      <c r="C14" s="101" t="s">
+      <c r="C14" s="89" t="s">
         <v>63</v>
       </c>
-      <c r="D14" s="32" t="s">
+      <c r="D14" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="E14" s="32" t="s">
+      <c r="E14" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="F14" s="32" t="s">
+      <c r="F14" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="G14" s="32" t="s">
+      <c r="G14" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="H14" s="15" t="s">
+      <c r="H14" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="I14" s="33" t="s">
-        <v>18</v>
-      </c>
-      <c r="J14" s="33" t="s">
+      <c r="I14" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="J14" s="30" t="s">
         <v>69</v>
       </c>
-      <c r="K14" s="15">
+      <c r="K14" s="14">
         <v>1</v>
       </c>
-      <c r="L14" s="102">
+      <c r="L14" s="90">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M14" s="103" t="s">
+      <c r="M14" s="91" t="s">
         <v>20</v>
       </c>
-      <c r="N14" s="103"/>
-    </row>
-    <row r="15" spans="1:29" ht="15.75" thickBot="1">
-      <c r="A15" s="6">
+      <c r="N14" s="91"/>
+    </row>
+    <row r="15" spans="1:14" ht="15" thickBot="1">
+      <c r="A15" s="5">
         <v>13</v>
       </c>
-      <c r="B15" s="150"/>
-      <c r="C15" s="34" t="s">
+      <c r="B15" s="133"/>
+      <c r="C15" s="31" t="s">
+        <v>214</v>
+      </c>
+      <c r="D15" s="100" t="s">
+        <v>213</v>
+      </c>
+      <c r="E15" s="47" t="s">
+        <v>212</v>
+      </c>
+      <c r="F15" s="47" t="s">
+        <v>211</v>
+      </c>
+      <c r="G15" s="47" t="s">
         <v>215</v>
       </c>
-      <c r="D15" s="112" t="s">
-        <v>214</v>
-      </c>
-      <c r="E15" s="53" t="s">
-        <v>213</v>
-      </c>
-      <c r="F15" s="53" t="s">
-        <v>212</v>
-      </c>
-      <c r="G15" s="53" t="s">
+      <c r="H15" s="92" t="s">
         <v>216</v>
       </c>
-      <c r="H15" s="104" t="s">
-        <v>217</v>
-      </c>
-      <c r="I15" s="54" t="s">
-        <v>18</v>
-      </c>
-      <c r="J15" s="54" t="s">
+      <c r="I15" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="J15" s="48" t="s">
         <v>69</v>
       </c>
-      <c r="K15" s="9">
+      <c r="K15" s="8">
         <v>1</v>
       </c>
-      <c r="L15" s="7">
+      <c r="L15" s="6">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M15" s="56" t="s">
+      <c r="M15" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="N15" s="56"/>
-    </row>
-    <row r="16" spans="1:29" ht="15.75" thickBot="1">
-      <c r="A16" s="6">
+      <c r="N15" s="50"/>
+    </row>
+    <row r="16" spans="1:14" ht="15" thickBot="1">
+      <c r="A16" s="5">
         <v>14</v>
       </c>
-      <c r="B16" s="150"/>
-      <c r="C16" s="93" t="s">
+      <c r="B16" s="133"/>
+      <c r="C16" s="84" t="s">
+        <v>228</v>
+      </c>
+      <c r="D16" s="100" t="s">
+        <v>227</v>
+      </c>
+      <c r="E16" s="47" t="s">
+        <v>226</v>
+      </c>
+      <c r="F16" s="47" t="s">
+        <v>225</v>
+      </c>
+      <c r="G16" s="47" t="s">
         <v>229</v>
       </c>
-      <c r="D16" s="112" t="s">
-        <v>228</v>
-      </c>
-      <c r="E16" s="53" t="s">
-        <v>227</v>
-      </c>
-      <c r="F16" s="53" t="s">
-        <v>226</v>
-      </c>
-      <c r="G16" s="53" t="s">
+      <c r="H16" s="92" t="s">
         <v>230</v>
       </c>
-      <c r="H16" s="104" t="s">
-        <v>231</v>
-      </c>
-      <c r="I16" s="54" t="s">
-        <v>18</v>
-      </c>
-      <c r="J16" s="54" t="s">
+      <c r="I16" s="48" t="s">
+        <v>18</v>
+      </c>
+      <c r="J16" s="48" t="s">
         <v>69</v>
       </c>
-      <c r="K16" s="9">
+      <c r="K16" s="8">
         <v>1</v>
       </c>
-      <c r="L16" s="7">
+      <c r="L16" s="6">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M16" s="56" t="s">
+      <c r="M16" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="N16" s="56"/>
-    </row>
-    <row r="17" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A17" s="6">
+      <c r="N16" s="50"/>
+    </row>
+    <row r="17" spans="1:14" ht="15" thickBot="1">
+      <c r="A17" s="5">
         <v>15</v>
       </c>
-      <c r="B17" s="150"/>
-      <c r="C17" s="105" t="s">
+      <c r="B17" s="133"/>
+      <c r="C17" s="93" t="s">
         <v>70</v>
       </c>
-      <c r="D17" s="113" t="s">
+      <c r="D17" s="101" t="s">
         <v>71</v>
       </c>
-      <c r="E17" s="67" t="s">
+      <c r="E17" s="60" t="s">
         <v>72</v>
       </c>
-      <c r="F17" s="67" t="s">
+      <c r="F17" s="60" t="s">
         <v>73</v>
       </c>
-      <c r="G17" s="67" t="s">
+      <c r="G17" s="60" t="s">
         <v>74</v>
       </c>
-      <c r="H17" s="68" t="s">
+      <c r="H17" s="61" t="s">
         <v>75</v>
       </c>
-      <c r="I17" s="68" t="s">
-        <v>18</v>
-      </c>
-      <c r="J17" s="68" t="s">
+      <c r="I17" s="61" t="s">
+        <v>18</v>
+      </c>
+      <c r="J17" s="61" t="s">
         <v>69</v>
       </c>
-      <c r="K17" s="63">
+      <c r="K17" s="56">
         <v>1</v>
       </c>
-      <c r="L17" s="106">
+      <c r="L17" s="94">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M17" s="107" t="s">
+      <c r="M17" s="95" t="s">
         <v>20</v>
       </c>
-      <c r="N17" s="107"/>
-    </row>
-    <row r="18" spans="1:14" ht="16.5" thickBot="1">
-      <c r="A18" s="6">
+      <c r="N17" s="95"/>
+    </row>
+    <row r="18" spans="1:14" ht="16.2" thickBot="1">
+      <c r="A18" s="5">
         <v>16</v>
       </c>
-      <c r="B18" s="92" t="s">
+      <c r="B18" s="83" t="s">
         <v>76</v>
       </c>
-      <c r="C18" s="71" t="s">
+      <c r="C18" s="64" t="s">
         <v>77</v>
       </c>
-      <c r="D18" s="114" t="s">
+      <c r="D18" s="102" t="s">
         <v>78</v>
       </c>
-      <c r="E18" s="72" t="s">
+      <c r="E18" s="65" t="s">
         <v>79</v>
       </c>
-      <c r="F18" s="72" t="s">
+      <c r="F18" s="65" t="s">
         <v>80</v>
       </c>
-      <c r="G18" s="73" t="s">
+      <c r="G18" s="66" t="s">
         <v>81</v>
       </c>
-      <c r="H18" s="73" t="s">
-        <v>18</v>
-      </c>
-      <c r="I18" s="72" t="s">
-        <v>18</v>
-      </c>
-      <c r="J18" s="73" t="s">
+      <c r="H18" s="66" t="s">
+        <v>18</v>
+      </c>
+      <c r="I18" s="65" t="s">
+        <v>18</v>
+      </c>
+      <c r="J18" s="66" t="s">
         <v>69</v>
       </c>
-      <c r="K18" s="69">
+      <c r="K18" s="62">
         <v>1</v>
       </c>
-      <c r="L18" s="108">
+      <c r="L18" s="96">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M18" s="70" t="s">
+      <c r="M18" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="N18" s="70"/>
-    </row>
-    <row r="19" spans="1:14" ht="30.75" thickBot="1">
-      <c r="A19" s="6">
+      <c r="N18" s="63"/>
+    </row>
+    <row r="19" spans="1:14" ht="29.4" thickBot="1">
+      <c r="A19" s="5">
         <v>17</v>
       </c>
-      <c r="B19" s="92" t="s">
+      <c r="B19" s="83" t="s">
+        <v>217</v>
+      </c>
+      <c r="C19" s="97" t="s">
+        <v>219</v>
+      </c>
+      <c r="D19" s="102" t="s">
         <v>218</v>
       </c>
-      <c r="C19" s="109" t="s">
+      <c r="E19" s="98" t="s">
         <v>220</v>
       </c>
-      <c r="D19" s="114" t="s">
-        <v>219</v>
-      </c>
-      <c r="E19" s="110" t="s">
+      <c r="F19" s="98" t="s">
         <v>221</v>
       </c>
-      <c r="F19" s="110" t="s">
+      <c r="G19" s="99" t="s">
         <v>222</v>
       </c>
-      <c r="G19" s="111" t="s">
+      <c r="H19" s="99" t="s">
         <v>223</v>
       </c>
-      <c r="H19" s="111" t="s">
+      <c r="I19" s="98" t="s">
         <v>224</v>
       </c>
-      <c r="I19" s="110" t="s">
-        <v>225</v>
-      </c>
-      <c r="J19" s="111" t="s">
+      <c r="J19" s="99" t="s">
         <v>69</v>
       </c>
-      <c r="K19" s="69">
+      <c r="K19" s="62">
         <v>1</v>
       </c>
-      <c r="L19" s="108">
+      <c r="L19" s="96">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M19" s="70" t="s">
+      <c r="M19" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="N19" s="70"/>
-    </row>
-    <row r="20" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A20" s="6">
-        <v>18</v>
-      </c>
-      <c r="B20" s="149" t="s">
+      <c r="N19" s="63"/>
+    </row>
+    <row r="20" spans="1:14" ht="15" thickBot="1">
+      <c r="A20" s="5">
+        <v>18</v>
+      </c>
+      <c r="B20" s="132" t="s">
         <v>82</v>
       </c>
-      <c r="C20" s="65" t="s">
+      <c r="C20" s="58" t="s">
+        <v>172</v>
+      </c>
+      <c r="D20" s="40" t="s">
         <v>173</v>
       </c>
-      <c r="D20" s="45" t="s">
+      <c r="E20" s="40" t="s">
         <v>174</v>
       </c>
-      <c r="E20" s="45" t="s">
+      <c r="F20" s="40" t="s">
+        <v>174</v>
+      </c>
+      <c r="G20" s="23" t="s">
         <v>175</v>
       </c>
-      <c r="F20" s="45" t="s">
-        <v>175</v>
-      </c>
-      <c r="G20" s="26" t="s">
+      <c r="H20" s="23" t="s">
         <v>176</v>
       </c>
-      <c r="H20" s="26" t="s">
-        <v>177</v>
-      </c>
-      <c r="I20" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="J20" s="26" t="s">
+      <c r="I20" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="J20" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="K20" s="14">
+      <c r="K20" s="13">
         <v>1</v>
       </c>
-      <c r="L20" s="13">
+      <c r="L20" s="12">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M20" s="66" t="s">
+      <c r="M20" s="59" t="s">
         <v>20</v>
       </c>
-      <c r="N20" s="66"/>
-    </row>
-    <row r="21" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A21" s="6">
+      <c r="N20" s="59"/>
+    </row>
+    <row r="21" spans="1:14" ht="15" thickBot="1">
+      <c r="A21" s="5">
         <v>19</v>
       </c>
-      <c r="B21" s="151"/>
-      <c r="C21" s="46" t="s">
+      <c r="B21" s="134"/>
+      <c r="C21" s="41" t="s">
         <v>83</v>
       </c>
-      <c r="D21" s="47" t="s">
+      <c r="D21" s="42" t="s">
         <v>84</v>
       </c>
-      <c r="E21" s="47" t="s">
+      <c r="E21" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="F21" s="47" t="s">
+      <c r="F21" s="42" t="s">
         <v>85</v>
       </c>
-      <c r="G21" s="47" t="s">
+      <c r="G21" s="42" t="s">
         <v>86</v>
       </c>
-      <c r="H21" s="48"/>
-      <c r="I21" s="48"/>
-      <c r="J21" s="47" t="s">
+      <c r="H21" s="43"/>
+      <c r="I21" s="43"/>
+      <c r="J21" s="42" t="s">
         <v>69</v>
       </c>
-      <c r="K21" s="48">
+      <c r="K21" s="43">
         <v>1</v>
       </c>
-      <c r="L21" s="11">
+      <c r="L21" s="10">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M21" s="49" t="s">
+      <c r="M21" s="44" t="s">
         <v>87</v>
       </c>
-      <c r="N21" s="49"/>
-    </row>
-    <row r="22" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A22" s="6">
+      <c r="N21" s="44"/>
+    </row>
+    <row r="22" spans="1:14" ht="15" thickBot="1">
+      <c r="A22" s="5">
         <v>20</v>
       </c>
-      <c r="B22" s="149" t="s">
+      <c r="B22" s="132" t="s">
         <v>88</v>
       </c>
-      <c r="C22" s="135" t="s">
+      <c r="C22" s="120" t="s">
         <v>89</v>
       </c>
-      <c r="D22" s="139" t="s">
-        <v>243</v>
-      </c>
-      <c r="E22" s="25" t="s">
+      <c r="D22" s="124" t="s">
+        <v>242</v>
+      </c>
+      <c r="E22" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="F22" s="25" t="s">
+      <c r="F22" s="22" t="s">
         <v>91</v>
       </c>
-      <c r="G22" s="26" t="s">
+      <c r="G22" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="H22" s="14" t="s">
+      <c r="H22" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="I22" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="J22" s="25" t="s">
+      <c r="I22" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="J22" s="22" t="s">
         <v>93</v>
       </c>
-      <c r="K22" s="136">
+      <c r="K22" s="121">
         <v>3</v>
       </c>
-      <c r="L22" s="136">
+      <c r="L22" s="121">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="M22" s="137" t="s">
+      <c r="M22" s="122" t="s">
         <v>20</v>
       </c>
-      <c r="N22" s="138"/>
-    </row>
-    <row r="23" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A23" s="6">
+      <c r="N22" s="123"/>
+    </row>
+    <row r="23" spans="1:14" ht="15" thickBot="1">
+      <c r="A23" s="5">
         <v>21</v>
       </c>
-      <c r="B23" s="150"/>
-      <c r="C23" s="116" t="s">
+      <c r="B23" s="133"/>
+      <c r="C23" s="104" t="s">
+        <v>164</v>
+      </c>
+      <c r="D23" s="109" t="s">
         <v>165</v>
       </c>
-      <c r="D23" s="122" t="s">
+      <c r="E23" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="F23" s="24" t="s">
         <v>166</v>
       </c>
-      <c r="E23" s="51" t="s">
-        <v>90</v>
-      </c>
-      <c r="F23" s="51" t="s">
+      <c r="G23" s="25" t="s">
+        <v>154</v>
+      </c>
+      <c r="H23" s="48" t="s">
+        <v>233</v>
+      </c>
+      <c r="I23" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="J23" s="47" t="s">
         <v>167</v>
       </c>
-      <c r="G23" s="28" t="s">
-        <v>155</v>
-      </c>
-      <c r="H23" s="54" t="s">
-        <v>234</v>
-      </c>
-      <c r="I23" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="J23" s="53" t="s">
-        <v>168</v>
-      </c>
-      <c r="K23" s="7">
+      <c r="K23" s="6">
         <v>1</v>
       </c>
-      <c r="L23" s="7">
+      <c r="L23" s="6">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M23" s="56" t="s">
-        <v>178</v>
-      </c>
-      <c r="N23" s="56"/>
-    </row>
-    <row r="24" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A24" s="6">
+      <c r="M23" s="50" t="s">
+        <v>177</v>
+      </c>
+      <c r="N23" s="50"/>
+    </row>
+    <row r="24" spans="1:14" ht="15" thickBot="1">
+      <c r="A24" s="5">
         <v>22</v>
       </c>
-      <c r="B24" s="150"/>
-      <c r="C24" s="117" t="s">
-        <v>193</v>
-      </c>
-      <c r="D24" s="123" t="s">
+      <c r="B24" s="133"/>
+      <c r="C24" s="105" t="s">
+        <v>192</v>
+      </c>
+      <c r="D24" s="110" t="s">
+        <v>185</v>
+      </c>
+      <c r="E24" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="F24" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="E24" s="51" t="s">
-        <v>90</v>
-      </c>
-      <c r="F24" s="118" t="s">
+      <c r="G24" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="G24" s="118" t="s">
+      <c r="H24" s="106" t="s">
         <v>188</v>
       </c>
-      <c r="H24" s="119" t="s">
-        <v>189</v>
-      </c>
-      <c r="I24" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="J24" s="53" t="s">
-        <v>199</v>
-      </c>
-      <c r="K24" s="7">
+      <c r="I24" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="J24" s="47" t="s">
+        <v>198</v>
+      </c>
+      <c r="K24" s="6">
         <v>1</v>
       </c>
-      <c r="L24" s="7">
+      <c r="L24" s="6">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M24" s="59" t="s">
+      <c r="M24" s="53" t="s">
         <v>20</v>
       </c>
-      <c r="N24" s="59"/>
-    </row>
-    <row r="25" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A25" s="6">
+      <c r="N24" s="53"/>
+    </row>
+    <row r="25" spans="1:14" ht="15" thickBot="1">
+      <c r="A25" s="5">
         <v>23</v>
       </c>
-      <c r="B25" s="150"/>
-      <c r="C25" s="117" t="s">
-        <v>194</v>
-      </c>
-      <c r="D25" s="123" t="s">
+      <c r="B25" s="133"/>
+      <c r="C25" s="105" t="s">
+        <v>193</v>
+      </c>
+      <c r="D25" s="110" t="s">
+        <v>189</v>
+      </c>
+      <c r="E25" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="F25" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="E25" s="51" t="s">
-        <v>90</v>
-      </c>
-      <c r="F25" s="118" t="s">
+      <c r="G25" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="H25" s="106" t="s">
         <v>191</v>
       </c>
-      <c r="G25" s="118" t="s">
-        <v>188</v>
-      </c>
-      <c r="H25" s="119" t="s">
-        <v>192</v>
-      </c>
-      <c r="I25" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="J25" s="53" t="s">
-        <v>200</v>
-      </c>
-      <c r="K25" s="7">
+      <c r="I25" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="J25" s="47" t="s">
+        <v>199</v>
+      </c>
+      <c r="K25" s="6">
         <v>1</v>
       </c>
-      <c r="L25" s="7">
+      <c r="L25" s="6">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M25" s="56" t="s">
+      <c r="M25" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="N25" s="56"/>
-    </row>
-    <row r="26" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A26" s="6">
+      <c r="N25" s="50"/>
+    </row>
+    <row r="26" spans="1:14" ht="15" thickBot="1">
+      <c r="A26" s="5">
         <v>24</v>
       </c>
-      <c r="B26" s="150"/>
-      <c r="C26" s="117" t="s">
+      <c r="B26" s="133"/>
+      <c r="C26" s="105" t="s">
+        <v>195</v>
+      </c>
+      <c r="D26" s="110" t="s">
         <v>196</v>
       </c>
-      <c r="D26" s="123" t="s">
+      <c r="E26" s="47" t="s">
+        <v>90</v>
+      </c>
+      <c r="F26" s="107" t="s">
+        <v>194</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="H26" s="108" t="s">
         <v>197</v>
       </c>
-      <c r="E26" s="53" t="s">
-        <v>90</v>
-      </c>
-      <c r="F26" s="120" t="s">
-        <v>195</v>
-      </c>
-      <c r="G26" s="118" t="s">
-        <v>188</v>
-      </c>
-      <c r="H26" s="121" t="s">
-        <v>198</v>
-      </c>
-      <c r="I26" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="J26" s="53" t="s">
-        <v>201</v>
-      </c>
-      <c r="K26" s="7">
+      <c r="I26" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="J26" s="47" t="s">
+        <v>200</v>
+      </c>
+      <c r="K26" s="6">
         <v>1</v>
       </c>
-      <c r="L26" s="7">
+      <c r="L26" s="6">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M26" s="56" t="s">
+      <c r="M26" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="N26" s="56"/>
-    </row>
-    <row r="27" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A27" s="6">
+      <c r="N26" s="50"/>
+    </row>
+    <row r="27" spans="1:14" ht="15" thickBot="1">
+      <c r="A27" s="5">
         <v>25</v>
       </c>
-      <c r="B27" s="150"/>
-      <c r="C27" s="140" t="s">
-        <v>247</v>
-      </c>
-      <c r="D27" s="141" t="s">
-        <v>203</v>
-      </c>
-      <c r="E27" s="142" t="s">
+      <c r="B27" s="133"/>
+      <c r="C27" s="125" t="s">
         <v>246</v>
       </c>
-      <c r="F27" s="143" t="s">
+      <c r="D27" s="126" t="s">
+        <v>202</v>
+      </c>
+      <c r="E27" s="127" t="s">
         <v>245</v>
       </c>
-      <c r="G27" s="143" t="s">
+      <c r="F27" s="128" t="s">
+        <v>244</v>
+      </c>
+      <c r="G27" s="128" t="s">
         <v>114</v>
       </c>
-      <c r="H27" s="144" t="s">
-        <v>244</v>
-      </c>
-      <c r="I27" s="80" t="s">
-        <v>18</v>
-      </c>
-      <c r="J27" s="81" t="s">
-        <v>202</v>
-      </c>
-      <c r="K27" s="82">
+      <c r="H27" s="129" t="s">
+        <v>243</v>
+      </c>
+      <c r="I27" s="71" t="s">
+        <v>18</v>
+      </c>
+      <c r="J27" s="72" t="s">
+        <v>201</v>
+      </c>
+      <c r="K27" s="73">
         <v>2</v>
       </c>
-      <c r="L27" s="82">
+      <c r="L27" s="73">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="M27" s="145" t="s">
+      <c r="M27" s="130" t="s">
         <v>20</v>
       </c>
-      <c r="N27" s="132" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A28" s="6">
+      <c r="N27" s="117" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="15" thickBot="1">
+      <c r="A28" s="5">
         <v>26</v>
       </c>
-      <c r="B28" s="150"/>
-      <c r="C28" s="34" t="s">
+      <c r="B28" s="133"/>
+      <c r="C28" s="31" t="s">
         <v>94</v>
       </c>
-      <c r="D28" s="7" t="s">
+      <c r="D28" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="E28" s="27" t="s">
+      <c r="E28" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="F28" s="27" t="s">
+      <c r="F28" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="G28" s="28" t="s">
+      <c r="G28" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="H28" s="9" t="s">
+      <c r="H28" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="I28" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="J28" s="27" t="s">
+      <c r="I28" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="J28" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="K28" s="7">
+      <c r="K28" s="6">
         <v>2</v>
       </c>
-      <c r="L28" s="8">
+      <c r="L28" s="7">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="M28" s="57" t="s">
+      <c r="M28" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="N28" s="57"/>
-    </row>
-    <row r="29" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A29" s="6">
+      <c r="N28" s="51"/>
+    </row>
+    <row r="29" spans="1:14" ht="15" thickBot="1">
+      <c r="A29" s="5">
         <v>27</v>
       </c>
-      <c r="B29" s="150"/>
-      <c r="C29" s="34" t="s">
+      <c r="B29" s="133"/>
+      <c r="C29" s="31" t="s">
         <v>99</v>
       </c>
-      <c r="D29" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="E29" s="27" t="s">
+      <c r="D29" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="E29" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="F29" s="27" t="s">
+      <c r="F29" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="G29" s="28" t="s">
+      <c r="G29" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="H29" s="9" t="s">
+      <c r="H29" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="I29" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="J29" s="27" t="s">
+      <c r="I29" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="J29" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="K29" s="7">
+      <c r="K29" s="6">
         <v>1</v>
       </c>
-      <c r="L29" s="8">
+      <c r="L29" s="7">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M29" s="57" t="s">
+      <c r="M29" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="N29" s="57"/>
-    </row>
-    <row r="30" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A30" s="6">
+      <c r="N29" s="51"/>
+    </row>
+    <row r="30" spans="1:14" ht="15" thickBot="1">
+      <c r="A30" s="5">
         <v>28</v>
       </c>
-      <c r="B30" s="150"/>
-      <c r="C30" s="34" t="s">
+      <c r="B30" s="133"/>
+      <c r="C30" s="31" t="s">
         <v>104</v>
       </c>
-      <c r="D30" s="27" t="s">
+      <c r="D30" s="24" t="s">
         <v>105</v>
       </c>
-      <c r="E30" s="27" t="s">
+      <c r="E30" s="24" t="s">
         <v>103</v>
       </c>
-      <c r="F30" s="29" t="s">
+      <c r="F30" s="26" t="s">
         <v>106</v>
       </c>
-      <c r="G30" s="28" t="s">
+      <c r="G30" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="H30" s="9" t="s">
+      <c r="H30" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="I30" s="28" t="s">
+      <c r="I30" s="25" t="s">
         <v>109</v>
       </c>
-      <c r="J30" s="27" t="s">
+      <c r="J30" s="24" t="s">
         <v>110</v>
       </c>
-      <c r="K30" s="7">
+      <c r="K30" s="6">
         <v>1</v>
       </c>
-      <c r="L30" s="8">
+      <c r="L30" s="7">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M30" s="57" t="s">
+      <c r="M30" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="N30" s="57"/>
-    </row>
-    <row r="31" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A31" s="6">
+      <c r="N30" s="51"/>
+    </row>
+    <row r="31" spans="1:14" ht="15" thickBot="1">
+      <c r="A31" s="5">
         <v>29</v>
       </c>
-      <c r="B31" s="150"/>
-      <c r="C31" s="34" t="s">
+      <c r="B31" s="133"/>
+      <c r="C31" s="31" t="s">
         <v>111</v>
       </c>
-      <c r="D31" s="27" t="s">
+      <c r="D31" s="24" t="s">
         <v>112</v>
       </c>
-      <c r="E31" s="27" t="s">
+      <c r="E31" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="F31" s="27" t="s">
+      <c r="F31" s="24" t="s">
         <v>113</v>
       </c>
-      <c r="G31" s="28" t="s">
+      <c r="G31" s="25" t="s">
         <v>114</v>
       </c>
-      <c r="H31" s="9" t="s">
+      <c r="H31" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="I31" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="J31" s="27" t="s">
+      <c r="I31" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="J31" s="24" t="s">
         <v>116</v>
       </c>
-      <c r="K31" s="7">
+      <c r="K31" s="6">
         <v>1</v>
       </c>
-      <c r="L31" s="8">
+      <c r="L31" s="7">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M31" s="57" t="s">
+      <c r="M31" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="N31" s="57"/>
-    </row>
-    <row r="32" spans="1:14" s="1" customFormat="1" ht="15.75" thickBot="1">
-      <c r="A32" s="6">
+      <c r="N31" s="51"/>
+    </row>
+    <row r="32" spans="1:14" ht="15" thickBot="1">
+      <c r="A32" s="5">
         <v>30</v>
       </c>
-      <c r="B32" s="151"/>
-      <c r="C32" s="35" t="s">
+      <c r="B32" s="134"/>
+      <c r="C32" s="32" t="s">
         <v>117</v>
       </c>
-      <c r="D32" s="10" t="s">
+      <c r="D32" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="E32" s="30" t="s">
+      <c r="E32" s="27" t="s">
         <v>90</v>
       </c>
-      <c r="F32" s="30" t="s">
+      <c r="F32" s="27" t="s">
         <v>119</v>
       </c>
-      <c r="G32" s="31" t="s">
+      <c r="G32" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="H32" s="12" t="s">
+      <c r="H32" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="I32" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="J32" s="30" t="s">
+      <c r="I32" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="J32" s="27" t="s">
         <v>121</v>
       </c>
-      <c r="K32" s="12">
+      <c r="K32" s="11">
         <v>8</v>
       </c>
-      <c r="L32" s="11">
+      <c r="L32" s="10">
         <f t="shared" si="1"/>
         <v>48</v>
       </c>
-      <c r="M32" s="74" t="s">
+      <c r="M32" s="67" t="s">
         <v>20</v>
       </c>
-      <c r="N32" s="74"/>
-    </row>
-    <row r="33" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A33" s="6">
+      <c r="N32" s="67"/>
+    </row>
+    <row r="33" spans="1:14" ht="15" thickBot="1">
+      <c r="A33" s="5">
         <v>31</v>
       </c>
-      <c r="B33" s="150" t="s">
+      <c r="B33" s="133" t="s">
         <v>122</v>
       </c>
-      <c r="C33" s="124" t="s">
-        <v>184</v>
-      </c>
-      <c r="D33" s="128" t="s">
+      <c r="C33" s="111" t="s">
+        <v>183</v>
+      </c>
+      <c r="D33" s="113" t="s">
         <v>123</v>
       </c>
-      <c r="E33" s="125" t="s">
+      <c r="E33" s="29" t="s">
+        <v>180</v>
+      </c>
+      <c r="F33" s="90" t="s">
         <v>181</v>
       </c>
-      <c r="F33" s="126" t="s">
+      <c r="G33" s="112" t="s">
         <v>182</v>
       </c>
-      <c r="G33" s="127" t="s">
-        <v>183</v>
-      </c>
-      <c r="H33" s="33" t="s">
-        <v>18</v>
-      </c>
-      <c r="I33" s="32" t="s">
-        <v>18</v>
-      </c>
-      <c r="J33" s="33" t="s">
+      <c r="H33" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="I33" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="J33" s="30" t="s">
         <v>69</v>
       </c>
-      <c r="K33" s="15">
+      <c r="K33" s="14">
         <v>1</v>
       </c>
-      <c r="L33" s="102">
+      <c r="L33" s="90">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M33" s="103" t="s">
+      <c r="M33" s="91" t="s">
         <v>20</v>
       </c>
-      <c r="N33" s="103"/>
-    </row>
-    <row r="34" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A34" s="6">
+      <c r="N33" s="91"/>
+    </row>
+    <row r="34" spans="1:14" ht="15" thickBot="1">
+      <c r="A34" s="5">
         <v>32</v>
       </c>
-      <c r="B34" s="150"/>
-      <c r="C34" s="34" t="s">
+      <c r="B34" s="133"/>
+      <c r="C34" s="31" t="s">
         <v>124</v>
       </c>
-      <c r="D34" s="27" t="s">
+      <c r="D34" s="24" t="s">
         <v>125</v>
       </c>
-      <c r="E34" s="27" t="s">
+      <c r="E34" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="F34" s="27" t="s">
+      <c r="F34" s="24" t="s">
         <v>127</v>
       </c>
-      <c r="G34" s="28" t="s">
+      <c r="G34" s="25" t="s">
         <v>128</v>
       </c>
-      <c r="H34" s="9" t="s">
+      <c r="H34" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="I34" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="J34" s="28" t="s">
+      <c r="I34" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="J34" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="K34" s="9">
+      <c r="K34" s="8">
         <v>1</v>
       </c>
-      <c r="L34" s="8">
+      <c r="L34" s="7">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M34" s="57" t="s">
+      <c r="M34" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="N34" s="57"/>
-    </row>
-    <row r="35" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A35" s="6">
+      <c r="N34" s="51"/>
+    </row>
+    <row r="35" spans="1:14" ht="15" thickBot="1">
+      <c r="A35" s="5">
         <v>33</v>
       </c>
-      <c r="B35" s="150"/>
-      <c r="C35" s="75" t="s">
+      <c r="B35" s="133"/>
+      <c r="C35" s="68" t="s">
+        <v>168</v>
+      </c>
+      <c r="D35" s="69" t="s">
+        <v>130</v>
+      </c>
+      <c r="E35" s="69" t="s">
         <v>169</v>
       </c>
-      <c r="D35" s="76" t="s">
-        <v>130</v>
-      </c>
-      <c r="E35" s="76" t="s">
+      <c r="F35" s="57" t="s">
+        <v>171</v>
+      </c>
+      <c r="G35" s="60" t="s">
         <v>170</v>
       </c>
-      <c r="F35" s="77" t="s">
-        <v>172</v>
-      </c>
-      <c r="G35" s="67" t="s">
-        <v>171</v>
-      </c>
-      <c r="H35" s="63"/>
-      <c r="I35" s="67" t="s">
-        <v>18</v>
-      </c>
-      <c r="J35" s="68" t="s">
+      <c r="H35" s="56"/>
+      <c r="I35" s="60" t="s">
+        <v>18</v>
+      </c>
+      <c r="J35" s="61" t="s">
         <v>131</v>
       </c>
-      <c r="K35" s="63">
+      <c r="K35" s="56">
         <v>1</v>
       </c>
-      <c r="L35" s="64">
+      <c r="L35" s="57">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M35" s="78" t="s">
+      <c r="M35" s="70" t="s">
         <v>87</v>
       </c>
-      <c r="N35" s="78"/>
-    </row>
-    <row r="36" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A36" s="6">
+      <c r="N35" s="139"/>
+    </row>
+    <row r="36" spans="1:14" ht="15" thickBot="1">
+      <c r="A36" s="5">
         <v>34</v>
       </c>
-      <c r="B36" s="149" t="s">
+      <c r="B36" s="132" t="s">
         <v>132</v>
       </c>
-      <c r="C36" s="36" t="s">
+      <c r="C36" s="74" t="s">
+        <v>249</v>
+      </c>
+      <c r="D36" s="75" t="s">
         <v>133</v>
       </c>
-      <c r="D36" s="37" t="s">
+      <c r="E36" s="75" t="s">
         <v>134</v>
       </c>
-      <c r="E36" s="37" t="s">
+      <c r="F36" s="75" t="s">
+        <v>134</v>
+      </c>
+      <c r="G36" s="75" t="s">
         <v>135</v>
       </c>
-      <c r="F36" s="37" t="s">
-        <v>135</v>
-      </c>
-      <c r="G36" s="37" t="s">
-        <v>136</v>
-      </c>
-      <c r="H36" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="I36" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="J36" s="37" t="s">
+      <c r="H36" s="75" t="s">
+        <v>18</v>
+      </c>
+      <c r="I36" s="75" t="s">
+        <v>18</v>
+      </c>
+      <c r="J36" s="75" t="s">
         <v>69</v>
       </c>
-      <c r="K36" s="17">
+      <c r="K36" s="78">
         <v>1</v>
       </c>
-      <c r="L36" s="13">
+      <c r="L36" s="78">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M36" s="79" t="s">
+      <c r="M36" s="138" t="s">
+        <v>136</v>
+      </c>
+      <c r="N36" s="141" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" ht="15" thickBot="1">
+      <c r="A37" s="5">
+        <v>35</v>
+      </c>
+      <c r="B37" s="133"/>
+      <c r="C37" s="33" t="s">
         <v>137</v>
       </c>
-      <c r="N36" s="79"/>
-    </row>
-    <row r="37" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A37" s="6">
-        <v>35</v>
-      </c>
-      <c r="B37" s="150"/>
-      <c r="C37" s="38" t="s">
+      <c r="D37" s="34" t="s">
         <v>138</v>
       </c>
-      <c r="D37" s="39" t="s">
+      <c r="E37" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="F37" s="34" t="s">
         <v>139</v>
       </c>
-      <c r="E37" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="F37" s="39" t="s">
+      <c r="G37" s="34" t="s">
         <v>140</v>
       </c>
-      <c r="G37" s="39" t="s">
+      <c r="H37" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="I37" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J37" s="35" t="s">
         <v>141</v>
       </c>
-      <c r="H37" s="39" t="s">
-        <v>18</v>
-      </c>
-      <c r="I37" s="39" t="s">
-        <v>18</v>
-      </c>
-      <c r="J37" s="40" t="s">
-        <v>142</v>
-      </c>
-      <c r="K37" s="18">
+      <c r="K37" s="16">
         <v>2</v>
       </c>
-      <c r="L37" s="8">
+      <c r="L37" s="7">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="M37" s="58" t="s">
+      <c r="M37" s="52" t="s">
+        <v>142</v>
+      </c>
+      <c r="N37" s="52"/>
+    </row>
+    <row r="38" spans="1:14" ht="15" thickBot="1">
+      <c r="A38" s="5">
+        <v>36</v>
+      </c>
+      <c r="B38" s="133"/>
+      <c r="C38" s="33" t="s">
         <v>143</v>
       </c>
-      <c r="N37" s="58"/>
-    </row>
-    <row r="38" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A38" s="6">
-        <v>36</v>
-      </c>
-      <c r="B38" s="150"/>
-      <c r="C38" s="38" t="s">
+      <c r="D38" s="34" t="s">
         <v>144</v>
       </c>
-      <c r="D38" s="39" t="s">
+      <c r="E38" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="F38" s="34" t="s">
         <v>145</v>
       </c>
-      <c r="E38" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="F38" s="39" t="s">
-        <v>146</v>
-      </c>
-      <c r="G38" s="39" t="s">
-        <v>136</v>
-      </c>
-      <c r="H38" s="39" t="s">
-        <v>18</v>
-      </c>
-      <c r="I38" s="39" t="s">
-        <v>18</v>
-      </c>
-      <c r="J38" s="40" t="s">
+      <c r="G38" s="34" t="s">
+        <v>135</v>
+      </c>
+      <c r="H38" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="I38" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="J38" s="35" t="s">
         <v>69</v>
       </c>
-      <c r="K38" s="18">
+      <c r="K38" s="16">
         <v>1</v>
       </c>
-      <c r="L38" s="8">
+      <c r="L38" s="7">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M38" s="58" t="s">
-        <v>137</v>
-      </c>
-      <c r="N38" s="58"/>
-    </row>
-    <row r="39" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A39" s="6">
+      <c r="M38" s="52" t="s">
+        <v>136</v>
+      </c>
+      <c r="N38" s="52"/>
+    </row>
+    <row r="39" spans="1:14" ht="15" thickBot="1">
+      <c r="A39" s="5">
         <v>37</v>
       </c>
-      <c r="B39" s="150"/>
-      <c r="C39" s="16" t="s">
+      <c r="B39" s="133"/>
+      <c r="C39" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="D39" s="24" t="s">
         <v>147</v>
       </c>
-      <c r="D39" s="27" t="s">
+      <c r="E39" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="F39" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="E39" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="F39" s="27" t="s">
+      <c r="G39" s="24" t="s">
         <v>149</v>
       </c>
-      <c r="G39" s="27" t="s">
-        <v>150</v>
-      </c>
-      <c r="H39" s="27" t="s">
-        <v>149</v>
-      </c>
-      <c r="I39" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="J39" s="28" t="s">
-        <v>142</v>
-      </c>
-      <c r="K39" s="7">
+      <c r="H39" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="I39" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="J39" s="25" t="s">
+        <v>141</v>
+      </c>
+      <c r="K39" s="6">
         <v>1</v>
       </c>
-      <c r="L39" s="8">
+      <c r="L39" s="7">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M39" s="59" t="s">
+      <c r="M39" s="53" t="s">
         <v>20</v>
       </c>
-      <c r="N39" s="59"/>
-    </row>
-    <row r="40" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A40" s="6">
+      <c r="N39" s="53"/>
+    </row>
+    <row r="40" spans="1:14" ht="15" thickBot="1">
+      <c r="A40" s="5">
         <v>38</v>
       </c>
-      <c r="B40" s="150"/>
-      <c r="C40" s="34" t="s">
+      <c r="B40" s="133"/>
+      <c r="C40" s="31" t="s">
+        <v>150</v>
+      </c>
+      <c r="D40" s="24" t="s">
         <v>151</v>
       </c>
-      <c r="D40" s="27" t="s">
+      <c r="E40" s="24" t="s">
         <v>152</v>
       </c>
-      <c r="E40" s="27" t="s">
+      <c r="F40" s="24" t="s">
         <v>153</v>
       </c>
-      <c r="F40" s="27" t="s">
+      <c r="G40" s="24" t="s">
         <v>154</v>
       </c>
-      <c r="G40" s="27" t="s">
+      <c r="H40" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="H40" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="I40" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="J40" s="28" t="s">
+      <c r="I40" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="J40" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="K40" s="9">
+      <c r="K40" s="8">
         <v>2</v>
       </c>
-      <c r="L40" s="8">
+      <c r="L40" s="7">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="M40" s="60" t="s">
+      <c r="M40" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="N40" s="60"/>
-    </row>
-    <row r="41" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A41" s="6">
+      <c r="N40" s="50"/>
+    </row>
+    <row r="41" spans="1:14" ht="15" thickBot="1">
+      <c r="A41" s="5">
         <v>39</v>
       </c>
-      <c r="B41" s="150"/>
-      <c r="C41" s="41" t="s">
+      <c r="B41" s="133"/>
+      <c r="C41" s="36" t="s">
+        <v>156</v>
+      </c>
+      <c r="D41" s="17"/>
+      <c r="E41" s="37" t="s">
         <v>157</v>
       </c>
-      <c r="D41" s="19"/>
-      <c r="E41" s="42" t="s">
-        <v>158</v>
-      </c>
-      <c r="F41" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="G41" s="19"/>
-      <c r="H41" s="19"/>
-      <c r="I41" s="19"/>
-      <c r="J41" s="19"/>
-      <c r="K41" s="19">
+      <c r="F41" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="G41" s="17"/>
+      <c r="H41" s="17"/>
+      <c r="I41" s="17"/>
+      <c r="J41" s="17"/>
+      <c r="K41" s="17">
         <v>5</v>
       </c>
-      <c r="L41" s="8">
+      <c r="L41" s="7">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
-      <c r="M41" s="61" t="s">
-        <v>18</v>
-      </c>
-      <c r="N41" s="61"/>
-    </row>
-    <row r="42" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A42" s="20">
+      <c r="M41" s="54" t="s">
+        <v>18</v>
+      </c>
+      <c r="N41" s="54"/>
+    </row>
+    <row r="42" spans="1:14" ht="15" thickBot="1">
+      <c r="A42" s="18">
         <v>40</v>
       </c>
-      <c r="B42" s="151"/>
-      <c r="C42" s="43" t="s">
+      <c r="B42" s="134"/>
+      <c r="C42" s="38" t="s">
+        <v>158</v>
+      </c>
+      <c r="D42" s="19"/>
+      <c r="E42" s="39" t="s">
         <v>159</v>
       </c>
-      <c r="D42" s="21"/>
-      <c r="E42" s="44" t="s">
-        <v>160</v>
-      </c>
-      <c r="F42" s="21" t="s">
-        <v>160</v>
-      </c>
-      <c r="G42" s="21"/>
-      <c r="H42" s="21"/>
-      <c r="I42" s="21"/>
-      <c r="J42" s="21"/>
-      <c r="K42" s="21">
+      <c r="F42" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="G42" s="19"/>
+      <c r="H42" s="19"/>
+      <c r="I42" s="19"/>
+      <c r="J42" s="19"/>
+      <c r="K42" s="19">
         <v>5</v>
       </c>
-      <c r="L42" s="11">
+      <c r="L42" s="10">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
-      <c r="M42" s="62" t="s">
-        <v>18</v>
-      </c>
-      <c r="N42" s="62"/>
+      <c r="M42" s="55" t="s">
+        <v>18</v>
+      </c>
+      <c r="N42" s="140"/>
     </row>
     <row r="43" spans="1:14">
       <c r="A43"/>
-      <c r="C43" s="22"/>
-      <c r="D43" s="22"/>
-      <c r="E43" s="22"/>
-      <c r="F43" s="22"/>
-      <c r="G43" s="22"/>
-      <c r="H43" s="22"/>
-      <c r="I43" s="22"/>
-      <c r="J43" s="22"/>
-      <c r="N43" s="24"/>
+      <c r="C43" s="20"/>
+      <c r="D43" s="20"/>
+      <c r="E43" s="20"/>
+      <c r="F43" s="20"/>
+      <c r="G43" s="20"/>
+      <c r="H43" s="20"/>
+      <c r="I43" s="20"/>
+      <c r="J43" s="20"/>
     </row>
     <row r="44" spans="1:14">
       <c r="A44"/>
-      <c r="C44" s="22"/>
-      <c r="D44" s="22"/>
-      <c r="E44" s="22"/>
-      <c r="F44" s="22"/>
-      <c r="G44" s="22"/>
-      <c r="H44" s="22"/>
-      <c r="I44" s="22"/>
-      <c r="J44" s="22"/>
+      <c r="C44" s="20"/>
+      <c r="D44" s="20"/>
+      <c r="E44" s="20"/>
+      <c r="F44" s="20"/>
+      <c r="G44" s="20"/>
+      <c r="H44" s="20"/>
+      <c r="I44" s="20"/>
+      <c r="J44" s="20"/>
     </row>
     <row r="45" spans="1:14">
       <c r="A45"/>
@@ -3927,8 +3917,8 @@
     </row>
     <row r="52" spans="1:14" ht="15.75" customHeight="1">
       <c r="A52"/>
-      <c r="M52" s="52"/>
-      <c r="N52" s="52"/>
+      <c r="M52" s="46"/>
+      <c r="N52" s="46"/>
     </row>
     <row r="53" spans="1:14">
       <c r="A53"/>
@@ -3946,10 +3936,10 @@
       <c r="A57"/>
     </row>
     <row r="58" spans="1:14">
-      <c r="H58" s="23"/>
+      <c r="H58" s="21"/>
     </row>
     <row r="59" spans="1:14">
-      <c r="H59" s="23"/>
+      <c r="H59" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/Deliverables/Interface_Board/BOM/NEW-6 Prototypes_Interface_Board.xlsx
+++ b/Deliverables/Interface_Board/BOM/NEW-6 Prototypes_Interface_Board.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25219"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25028"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\ChristianRaun-EthercatDesign\Deliverables\Interface_Board\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ChristianRaun-EthercatDesign\Deliverables\Interface_Board\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDF47179-0C58-4C13-A5D5-F912EB5D2053}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C78702D4-948A-4579-81A9-B272744D9726}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="255">
   <si>
     <t>Bill of Material (BOM) for Interface_Board</t>
   </si>
@@ -449,23 +449,10 @@
     <t>Aliexpress</t>
   </si>
   <si>
-    <t>10/100 BASE-TX RJ45 WITH LEDS_x000D_
-INTEGRATED MAGNETICS CONNECTOR</t>
-  </si>
-  <si>
     <t>J2, J3</t>
   </si>
   <si>
-    <t>SK07-111071ENL</t>
-  </si>
-  <si>
-    <t>SAK ELECTRONICS CO.,LTD</t>
-  </si>
-  <si>
     <t>----</t>
-  </si>
-  <si>
-    <t>Local Supplier</t>
   </si>
   <si>
     <t>CONN HEADER 4 POS 2.54mm SMD</t>
@@ -817,6 +804,30 @@
   <si>
     <t>Description added for number of pins</t>
   </si>
+  <si>
+    <t>QFN-36</t>
+  </si>
+  <si>
+    <t>SB1</t>
+  </si>
+  <si>
+    <t>P4, P5, P6, P7, P8</t>
+  </si>
+  <si>
+    <t>Through Hole Ethernet Connectors/Modular Connectors (RJ45 RJ11) ROHS</t>
+  </si>
+  <si>
+    <t>HY951180A</t>
+  </si>
+  <si>
+    <t>HANRUN</t>
+  </si>
+  <si>
+    <t>C34677</t>
+  </si>
+  <si>
+    <t>DO NOT MOUNT</t>
+  </si>
 </sst>
 </file>
 
@@ -825,12 +836,19 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.0000"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1025,6 +1043,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -1064,7 +1090,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="30">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -1459,26 +1485,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="142">
+  <cellXfs count="152">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1487,7 +1524,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1496,16 +1533,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1514,46 +1551,43 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="14" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1568,87 +1602,87 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="5" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="21" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="21" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="21" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="21" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="5" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="21" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="21" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="21" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="21" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="20" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="20" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="24" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="27" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="27" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="26" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1657,10 +1691,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="4" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="4" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
@@ -1669,13 +1703,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="25" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="25" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1687,43 +1721,43 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="6" borderId="20" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="6" borderId="21" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="15" fillId="6" borderId="20" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="6" borderId="21" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="16" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="16" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1732,10 +1766,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="23" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="23" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1744,73 +1778,70 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="25" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="25" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="26" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="26" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="24" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="10" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="15" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="23" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1819,62 +1850,96 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="20" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="20" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="21" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="28" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="29" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="21" xfId="1" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="28" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="29" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="21" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2154,43 +2219,43 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N59"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="6.109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="14.44140625" customWidth="1"/>
-    <col min="3" max="3" width="103.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="34.6640625" customWidth="1"/>
+    <col min="1" max="1" width="6.140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" customWidth="1"/>
+    <col min="3" max="3" width="70.7109375" customWidth="1"/>
+    <col min="4" max="4" width="34.7109375" customWidth="1"/>
     <col min="5" max="5" width="21" customWidth="1"/>
     <col min="6" max="6" width="29" customWidth="1"/>
-    <col min="7" max="7" width="26.33203125" customWidth="1"/>
-    <col min="8" max="8" width="15.33203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="21.5546875" customWidth="1"/>
+    <col min="7" max="7" width="26.28515625" customWidth="1"/>
+    <col min="8" max="8" width="15.28515625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="21.5703125" customWidth="1"/>
     <col min="10" max="10" width="7" customWidth="1"/>
-    <col min="11" max="11" width="21.88671875" customWidth="1"/>
-    <col min="12" max="12" width="14.109375" customWidth="1"/>
-    <col min="13" max="13" width="16.33203125" customWidth="1"/>
-    <col min="14" max="14" width="37.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.85546875" customWidth="1"/>
+    <col min="12" max="12" width="14.140625" customWidth="1"/>
+    <col min="13" max="13" width="16.28515625" customWidth="1"/>
+    <col min="14" max="14" width="37.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="16.2" thickBot="1">
-      <c r="A1" s="135" t="s">
+    <row r="1" spans="1:14" ht="16.5" thickBot="1">
+      <c r="A1" s="136" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="136"/>
-      <c r="C1" s="136"/>
-      <c r="D1" s="136"/>
-      <c r="E1" s="136"/>
-      <c r="F1" s="136"/>
-      <c r="G1" s="136"/>
-      <c r="H1" s="136"/>
-      <c r="I1" s="136"/>
-      <c r="J1" s="136"/>
-      <c r="K1" s="136"/>
-      <c r="L1" s="136"/>
-      <c r="M1" s="136"/>
-      <c r="N1" s="137"/>
-    </row>
-    <row r="2" spans="1:14" ht="16.2" thickBot="1">
+      <c r="B1" s="137"/>
+      <c r="C1" s="137"/>
+      <c r="D1" s="137"/>
+      <c r="E1" s="137"/>
+      <c r="F1" s="137"/>
+      <c r="G1" s="137"/>
+      <c r="H1" s="137"/>
+      <c r="I1" s="137"/>
+      <c r="J1" s="137"/>
+      <c r="K1" s="137"/>
+      <c r="L1" s="137"/>
+      <c r="M1" s="137"/>
+      <c r="N1" s="138"/>
+    </row>
+    <row r="2" spans="1:14" ht="16.5" thickBot="1">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -2224,89 +2289,89 @@
       <c r="K2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="45" t="s">
-        <v>179</v>
-      </c>
-      <c r="M2" s="49" t="s">
-        <v>178</v>
-      </c>
-      <c r="N2" s="116" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="15" thickBot="1">
+      <c r="L2" s="44" t="s">
+        <v>175</v>
+      </c>
+      <c r="M2" s="48" t="s">
+        <v>174</v>
+      </c>
+      <c r="N2" s="115" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="15.75" thickBot="1">
       <c r="A3" s="5">
         <v>1</v>
       </c>
-      <c r="B3" s="132" t="s">
+      <c r="B3" s="133" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="74" t="s">
+      <c r="C3" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="114" t="s">
-        <v>236</v>
-      </c>
-      <c r="E3" s="75" t="s">
+      <c r="D3" s="113" t="s">
+        <v>232</v>
+      </c>
+      <c r="E3" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="75" t="s">
+      <c r="F3" s="74" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="75" t="s">
+      <c r="G3" s="74" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="76" t="s">
+      <c r="H3" s="75" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="77" t="s">
+      <c r="I3" s="76" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="75" t="s">
+      <c r="J3" s="74" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="78">
+      <c r="K3" s="77">
         <v>6</v>
       </c>
-      <c r="L3" s="78">
+      <c r="L3" s="77">
         <f>K3*6</f>
         <v>36</v>
       </c>
-      <c r="M3" s="79" t="s">
+      <c r="M3" s="78" t="s">
         <v>20</v>
       </c>
-      <c r="N3" s="115" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="15" thickBot="1">
+      <c r="N3" s="114" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="15.75" thickBot="1">
       <c r="A4" s="5">
         <v>2</v>
       </c>
-      <c r="B4" s="133"/>
-      <c r="C4" s="84" t="s">
+      <c r="B4" s="134"/>
+      <c r="C4" s="83" t="s">
+        <v>200</v>
+      </c>
+      <c r="D4" s="102" t="s">
+        <v>201</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="46" t="s">
+        <v>199</v>
+      </c>
+      <c r="G4" s="46" t="s">
+        <v>202</v>
+      </c>
+      <c r="H4" s="84" t="s">
+        <v>203</v>
+      </c>
+      <c r="I4" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" s="46" t="s">
         <v>204</v>
-      </c>
-      <c r="D4" s="103" t="s">
-        <v>205</v>
-      </c>
-      <c r="E4" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="47" t="s">
-        <v>203</v>
-      </c>
-      <c r="G4" s="47" t="s">
-        <v>206</v>
-      </c>
-      <c r="H4" s="85" t="s">
-        <v>207</v>
-      </c>
-      <c r="I4" s="25" t="s">
-        <v>18</v>
-      </c>
-      <c r="J4" s="47" t="s">
-        <v>208</v>
       </c>
       <c r="K4" s="6">
         <v>1</v>
@@ -2315,81 +2380,81 @@
         <f t="shared" ref="L4:L5" si="0">K4*6</f>
         <v>6</v>
       </c>
-      <c r="M4" s="86" t="s">
+      <c r="M4" s="85" t="s">
         <v>20</v>
       </c>
-      <c r="N4" s="86"/>
-    </row>
-    <row r="5" spans="1:14" ht="15" thickBot="1">
+      <c r="N4" s="85"/>
+    </row>
+    <row r="5" spans="1:14" ht="15.75" thickBot="1">
       <c r="A5" s="5">
         <v>3</v>
       </c>
-      <c r="B5" s="133"/>
-      <c r="C5" s="118" t="s">
-        <v>239</v>
-      </c>
-      <c r="D5" s="119" t="s">
-        <v>210</v>
-      </c>
-      <c r="E5" s="71" t="s">
+      <c r="B5" s="134"/>
+      <c r="C5" s="116" t="s">
+        <v>235</v>
+      </c>
+      <c r="D5" s="117" t="s">
+        <v>206</v>
+      </c>
+      <c r="E5" s="70" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="131" t="s">
-        <v>248</v>
-      </c>
-      <c r="G5" s="81" t="s">
+      <c r="F5" s="129" t="s">
+        <v>244</v>
+      </c>
+      <c r="G5" s="80" t="s">
         <v>37</v>
       </c>
-      <c r="H5" s="80" t="s">
-        <v>240</v>
-      </c>
-      <c r="I5" s="81" t="s">
+      <c r="H5" s="79" t="s">
+        <v>236</v>
+      </c>
+      <c r="I5" s="80" t="s">
         <v>18</v>
       </c>
-      <c r="J5" s="72" t="s">
-        <v>209</v>
-      </c>
-      <c r="K5" s="73">
+      <c r="J5" s="71" t="s">
+        <v>205</v>
+      </c>
+      <c r="K5" s="72">
         <v>2</v>
       </c>
-      <c r="L5" s="73">
+      <c r="L5" s="72">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="M5" s="82" t="s">
+      <c r="M5" s="81" t="s">
         <v>20</v>
       </c>
-      <c r="N5" s="117" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="15" thickBot="1">
+      <c r="N5" s="150" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="15.75" thickBot="1">
       <c r="A6" s="5">
         <v>4</v>
       </c>
-      <c r="B6" s="133"/>
-      <c r="C6" s="31" t="s">
+      <c r="B6" s="134"/>
+      <c r="C6" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="24" t="s">
+      <c r="D6" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="E6" s="24" t="s">
+      <c r="E6" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="24" t="s">
+      <c r="F6" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="G6" s="24" t="s">
+      <c r="G6" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="87" t="s">
+      <c r="H6" s="86" t="s">
         <v>26</v>
       </c>
-      <c r="I6" s="25" t="s">
+      <c r="I6" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="J6" s="24" t="s">
+      <c r="J6" s="23" t="s">
         <v>27</v>
       </c>
       <c r="K6" s="6">
@@ -2399,38 +2464,38 @@
         <f t="shared" ref="L6:L42" si="1">K6*6</f>
         <v>6</v>
       </c>
-      <c r="M6" s="86" t="s">
+      <c r="M6" s="85" t="s">
         <v>20</v>
       </c>
-      <c r="N6" s="86"/>
-    </row>
-    <row r="7" spans="1:14" ht="15" thickBot="1">
+      <c r="N6" s="85"/>
+    </row>
+    <row r="7" spans="1:14" ht="15.75" thickBot="1">
       <c r="A7" s="5">
         <v>5</v>
       </c>
-      <c r="B7" s="133"/>
-      <c r="C7" s="31" t="s">
+      <c r="B7" s="134"/>
+      <c r="C7" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="24" t="s">
+      <c r="D7" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="24" t="s">
+      <c r="E7" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="26" t="s">
+      <c r="F7" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="G7" s="24" t="s">
+      <c r="G7" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="H7" s="87" t="s">
+      <c r="H7" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="I7" s="87" t="s">
+      <c r="I7" s="86" t="s">
         <v>33</v>
       </c>
-      <c r="J7" s="24" t="s">
+      <c r="J7" s="23" t="s">
         <v>34</v>
       </c>
       <c r="K7" s="6">
@@ -2440,38 +2505,38 @@
         <f t="shared" si="1"/>
         <v>48</v>
       </c>
-      <c r="M7" s="53" t="s">
+      <c r="M7" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="N7" s="53"/>
-    </row>
-    <row r="8" spans="1:14" ht="15" thickBot="1">
+      <c r="N7" s="52"/>
+    </row>
+    <row r="8" spans="1:14" ht="15.75" thickBot="1">
       <c r="A8" s="5">
         <v>6</v>
       </c>
-      <c r="B8" s="133"/>
-      <c r="C8" s="31" t="s">
+      <c r="B8" s="134"/>
+      <c r="C8" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="100" t="s">
-        <v>235</v>
-      </c>
-      <c r="E8" s="24" t="s">
+      <c r="D8" s="99" t="s">
+        <v>231</v>
+      </c>
+      <c r="E8" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="F8" s="26" t="s">
+      <c r="F8" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="G8" s="25" t="s">
+      <c r="G8" s="24" t="s">
         <v>37</v>
       </c>
       <c r="H8" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="I8" s="24" t="s">
+      <c r="I8" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="J8" s="24" t="s">
+      <c r="J8" s="23" t="s">
         <v>40</v>
       </c>
       <c r="K8" s="8">
@@ -2481,38 +2546,38 @@
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="M8" s="51" t="s">
+      <c r="M8" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="N8" s="51"/>
-    </row>
-    <row r="9" spans="1:14" ht="15" thickBot="1">
+      <c r="N8" s="50"/>
+    </row>
+    <row r="9" spans="1:14" ht="15.75" thickBot="1">
       <c r="A9" s="5">
         <v>7</v>
       </c>
-      <c r="B9" s="133"/>
-      <c r="C9" s="31" t="s">
+      <c r="B9" s="134"/>
+      <c r="C9" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="24" t="s">
+      <c r="D9" s="23" t="s">
         <v>42</v>
       </c>
-      <c r="E9" s="24" t="s">
+      <c r="E9" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="24" t="s">
+      <c r="F9" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="G9" s="25" t="s">
+      <c r="G9" s="24" t="s">
         <v>45</v>
       </c>
       <c r="H9" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="I9" s="25" t="s">
+      <c r="I9" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="J9" s="24" t="s">
+      <c r="J9" s="23" t="s">
         <v>47</v>
       </c>
       <c r="K9" s="8">
@@ -2522,38 +2587,38 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M9" s="51" t="s">
+      <c r="M9" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="N9" s="51"/>
-    </row>
-    <row r="10" spans="1:14" ht="15" thickBot="1">
+      <c r="N9" s="50"/>
+    </row>
+    <row r="10" spans="1:14" ht="15.75" thickBot="1">
       <c r="A10" s="5">
         <v>8</v>
       </c>
-      <c r="B10" s="133"/>
-      <c r="C10" s="31" t="s">
+      <c r="B10" s="134"/>
+      <c r="C10" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="D10" s="100" t="s">
-        <v>234</v>
-      </c>
-      <c r="E10" s="24" t="s">
+      <c r="D10" s="99" t="s">
+        <v>230</v>
+      </c>
+      <c r="E10" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="F10" s="24" t="s">
+      <c r="F10" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="G10" s="25" t="s">
+      <c r="G10" s="24" t="s">
         <v>45</v>
       </c>
       <c r="H10" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="I10" s="25" t="s">
+      <c r="I10" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="J10" s="24" t="s">
+      <c r="J10" s="23" t="s">
         <v>47</v>
       </c>
       <c r="K10" s="8">
@@ -2563,38 +2628,38 @@
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="M10" s="51" t="s">
+      <c r="M10" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="N10" s="51"/>
-    </row>
-    <row r="11" spans="1:14" ht="15" thickBot="1">
+      <c r="N10" s="50"/>
+    </row>
+    <row r="11" spans="1:14" ht="15.75" thickBot="1">
       <c r="A11" s="5">
         <v>9</v>
       </c>
-      <c r="B11" s="133"/>
-      <c r="C11" s="31" t="s">
-        <v>160</v>
-      </c>
-      <c r="D11" s="24" t="s">
+      <c r="B11" s="134"/>
+      <c r="C11" s="30" t="s">
+        <v>156</v>
+      </c>
+      <c r="D11" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="E11" s="24" t="s">
+      <c r="E11" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="F11" s="24" t="s">
-        <v>161</v>
-      </c>
-      <c r="G11" s="25" t="s">
+      <c r="F11" s="23" t="s">
+        <v>157</v>
+      </c>
+      <c r="G11" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="H11" s="48" t="s">
-        <v>231</v>
-      </c>
-      <c r="I11" s="25" t="s">
+      <c r="H11" s="47" t="s">
+        <v>227</v>
+      </c>
+      <c r="I11" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="J11" s="24" t="s">
+      <c r="J11" s="23" t="s">
         <v>52</v>
       </c>
       <c r="K11" s="8">
@@ -2604,38 +2669,38 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M11" s="50" t="s">
+      <c r="M11" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="N11" s="50"/>
-    </row>
-    <row r="12" spans="1:14" ht="15" thickBot="1">
+      <c r="N11" s="49"/>
+    </row>
+    <row r="12" spans="1:14" ht="15.75" thickBot="1">
       <c r="A12" s="5">
         <v>10</v>
       </c>
-      <c r="B12" s="133"/>
-      <c r="C12" s="31" t="s">
-        <v>162</v>
-      </c>
-      <c r="D12" s="24" t="s">
+      <c r="B12" s="134"/>
+      <c r="C12" s="30" t="s">
+        <v>158</v>
+      </c>
+      <c r="D12" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="E12" s="24" t="s">
+      <c r="E12" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="F12" s="24" t="s">
-        <v>163</v>
-      </c>
-      <c r="G12" s="25" t="s">
+      <c r="F12" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="G12" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="H12" s="48" t="s">
-        <v>232</v>
-      </c>
-      <c r="I12" s="25" t="s">
+      <c r="H12" s="47" t="s">
+        <v>228</v>
+      </c>
+      <c r="I12" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="J12" s="24" t="s">
+      <c r="J12" s="23" t="s">
         <v>54</v>
       </c>
       <c r="K12" s="8">
@@ -2645,38 +2710,38 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M12" s="50" t="s">
+      <c r="M12" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="N12" s="50"/>
-    </row>
-    <row r="13" spans="1:14" ht="15" thickBot="1">
+      <c r="N12" s="49"/>
+    </row>
+    <row r="13" spans="1:14" ht="15.75" thickBot="1">
       <c r="A13" s="5">
         <v>11</v>
       </c>
-      <c r="B13" s="134"/>
-      <c r="C13" s="32" t="s">
+      <c r="B13" s="135"/>
+      <c r="C13" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="D13" s="27" t="s">
+      <c r="D13" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="E13" s="27" t="s">
+      <c r="E13" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="F13" s="27" t="s">
+      <c r="F13" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="G13" s="28" t="s">
+      <c r="G13" s="27" t="s">
         <v>59</v>
       </c>
       <c r="H13" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="I13" s="28" t="s">
+      <c r="I13" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="J13" s="27" t="s">
+      <c r="J13" s="26" t="s">
         <v>61</v>
       </c>
       <c r="K13" s="11">
@@ -2686,81 +2751,81 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M13" s="88" t="s">
+      <c r="M13" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="N13" s="88"/>
-    </row>
-    <row r="14" spans="1:14" ht="15" thickBot="1">
+      <c r="N13" s="87"/>
+    </row>
+    <row r="14" spans="1:14" ht="15.75" thickBot="1">
       <c r="A14" s="5">
         <v>12</v>
       </c>
-      <c r="B14" s="133" t="s">
+      <c r="B14" s="134" t="s">
         <v>62</v>
       </c>
-      <c r="C14" s="89" t="s">
+      <c r="C14" s="88" t="s">
         <v>63</v>
       </c>
-      <c r="D14" s="29" t="s">
+      <c r="D14" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="E14" s="29" t="s">
+      <c r="E14" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="F14" s="29" t="s">
+      <c r="F14" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="G14" s="29" t="s">
+      <c r="G14" s="28" t="s">
         <v>67</v>
       </c>
       <c r="H14" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="I14" s="30" t="s">
+      <c r="I14" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="J14" s="30" t="s">
+      <c r="J14" s="29" t="s">
         <v>69</v>
       </c>
       <c r="K14" s="14">
         <v>1</v>
       </c>
-      <c r="L14" s="90">
+      <c r="L14" s="89">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M14" s="91" t="s">
+      <c r="M14" s="90" t="s">
         <v>20</v>
       </c>
-      <c r="N14" s="91"/>
-    </row>
-    <row r="15" spans="1:14" ht="15" thickBot="1">
+      <c r="N14" s="90"/>
+    </row>
+    <row r="15" spans="1:14" ht="15.75" thickBot="1">
       <c r="A15" s="5">
         <v>13</v>
       </c>
-      <c r="B15" s="133"/>
-      <c r="C15" s="31" t="s">
-        <v>214</v>
-      </c>
-      <c r="D15" s="100" t="s">
-        <v>213</v>
-      </c>
-      <c r="E15" s="47" t="s">
+      <c r="B15" s="134"/>
+      <c r="C15" s="30" t="s">
+        <v>210</v>
+      </c>
+      <c r="D15" s="99" t="s">
+        <v>209</v>
+      </c>
+      <c r="E15" s="46" t="s">
+        <v>208</v>
+      </c>
+      <c r="F15" s="46" t="s">
+        <v>207</v>
+      </c>
+      <c r="G15" s="46" t="s">
+        <v>211</v>
+      </c>
+      <c r="H15" s="91" t="s">
         <v>212</v>
       </c>
-      <c r="F15" s="47" t="s">
-        <v>211</v>
-      </c>
-      <c r="G15" s="47" t="s">
-        <v>215</v>
-      </c>
-      <c r="H15" s="92" t="s">
-        <v>216</v>
-      </c>
-      <c r="I15" s="48" t="s">
+      <c r="I15" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="J15" s="48" t="s">
+      <c r="J15" s="47" t="s">
         <v>69</v>
       </c>
       <c r="K15" s="8">
@@ -2770,38 +2835,38 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M15" s="50" t="s">
+      <c r="M15" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="N15" s="50"/>
-    </row>
-    <row r="16" spans="1:14" ht="15" thickBot="1">
+      <c r="N15" s="49"/>
+    </row>
+    <row r="16" spans="1:14" ht="15.75" thickBot="1">
       <c r="A16" s="5">
         <v>14</v>
       </c>
-      <c r="B16" s="133"/>
-      <c r="C16" s="84" t="s">
-        <v>228</v>
-      </c>
-      <c r="D16" s="100" t="s">
-        <v>227</v>
-      </c>
-      <c r="E16" s="47" t="s">
+      <c r="B16" s="134"/>
+      <c r="C16" s="83" t="s">
+        <v>224</v>
+      </c>
+      <c r="D16" s="99" t="s">
+        <v>223</v>
+      </c>
+      <c r="E16" s="46" t="s">
+        <v>222</v>
+      </c>
+      <c r="F16" s="46" t="s">
+        <v>221</v>
+      </c>
+      <c r="G16" s="46" t="s">
+        <v>225</v>
+      </c>
+      <c r="H16" s="91" t="s">
         <v>226</v>
       </c>
-      <c r="F16" s="47" t="s">
-        <v>225</v>
-      </c>
-      <c r="G16" s="47" t="s">
-        <v>229</v>
-      </c>
-      <c r="H16" s="92" t="s">
-        <v>230</v>
-      </c>
-      <c r="I16" s="48" t="s">
+      <c r="I16" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="J16" s="48" t="s">
+      <c r="J16" s="47" t="s">
         <v>69</v>
       </c>
       <c r="K16" s="8">
@@ -2811,167 +2876,167 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M16" s="50" t="s">
+      <c r="M16" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="N16" s="50"/>
-    </row>
-    <row r="17" spans="1:14" ht="15" thickBot="1">
+      <c r="N16" s="49"/>
+    </row>
+    <row r="17" spans="1:14" ht="15.75" thickBot="1">
       <c r="A17" s="5">
         <v>15</v>
       </c>
-      <c r="B17" s="133"/>
-      <c r="C17" s="93" t="s">
+      <c r="B17" s="134"/>
+      <c r="C17" s="92" t="s">
         <v>70</v>
       </c>
-      <c r="D17" s="101" t="s">
+      <c r="D17" s="100" t="s">
         <v>71</v>
       </c>
-      <c r="E17" s="60" t="s">
+      <c r="E17" s="59" t="s">
         <v>72</v>
       </c>
-      <c r="F17" s="60" t="s">
+      <c r="F17" s="59" t="s">
         <v>73</v>
       </c>
-      <c r="G17" s="60" t="s">
+      <c r="G17" s="59" t="s">
         <v>74</v>
       </c>
-      <c r="H17" s="61" t="s">
+      <c r="H17" s="60" t="s">
         <v>75</v>
       </c>
-      <c r="I17" s="61" t="s">
+      <c r="I17" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="J17" s="61" t="s">
+      <c r="J17" s="60" t="s">
         <v>69</v>
       </c>
-      <c r="K17" s="56">
+      <c r="K17" s="55">
         <v>1</v>
       </c>
-      <c r="L17" s="94">
+      <c r="L17" s="93">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M17" s="95" t="s">
+      <c r="M17" s="94" t="s">
         <v>20</v>
       </c>
-      <c r="N17" s="95"/>
-    </row>
-    <row r="18" spans="1:14" ht="16.2" thickBot="1">
+      <c r="N17" s="94"/>
+    </row>
+    <row r="18" spans="1:14" ht="16.5" thickBot="1">
       <c r="A18" s="5">
         <v>16</v>
       </c>
-      <c r="B18" s="83" t="s">
+      <c r="B18" s="82" t="s">
         <v>76</v>
       </c>
-      <c r="C18" s="64" t="s">
+      <c r="C18" s="63" t="s">
         <v>77</v>
       </c>
-      <c r="D18" s="102" t="s">
+      <c r="D18" s="101" t="s">
         <v>78</v>
       </c>
-      <c r="E18" s="65" t="s">
+      <c r="E18" s="64" t="s">
         <v>79</v>
       </c>
-      <c r="F18" s="65" t="s">
+      <c r="F18" s="64" t="s">
         <v>80</v>
       </c>
-      <c r="G18" s="66" t="s">
+      <c r="G18" s="65" t="s">
         <v>81</v>
       </c>
-      <c r="H18" s="66" t="s">
+      <c r="H18" s="65" t="s">
         <v>18</v>
       </c>
-      <c r="I18" s="65" t="s">
+      <c r="I18" s="64" t="s">
         <v>18</v>
       </c>
-      <c r="J18" s="66" t="s">
+      <c r="J18" s="65" t="s">
         <v>69</v>
       </c>
-      <c r="K18" s="62">
+      <c r="K18" s="61">
         <v>1</v>
       </c>
-      <c r="L18" s="96">
+      <c r="L18" s="95">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M18" s="63" t="s">
+      <c r="M18" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="N18" s="63"/>
-    </row>
-    <row r="19" spans="1:14" ht="29.4" thickBot="1">
+      <c r="N18" s="62"/>
+    </row>
+    <row r="19" spans="1:14" ht="30.75" thickBot="1">
       <c r="A19" s="5">
         <v>17</v>
       </c>
-      <c r="B19" s="83" t="s">
+      <c r="B19" s="82" t="s">
+        <v>213</v>
+      </c>
+      <c r="C19" s="96" t="s">
+        <v>215</v>
+      </c>
+      <c r="D19" s="101" t="s">
+        <v>214</v>
+      </c>
+      <c r="E19" s="97" t="s">
+        <v>216</v>
+      </c>
+      <c r="F19" s="97" t="s">
         <v>217</v>
       </c>
-      <c r="C19" s="97" t="s">
+      <c r="G19" s="98" t="s">
+        <v>218</v>
+      </c>
+      <c r="H19" s="98" t="s">
         <v>219</v>
       </c>
-      <c r="D19" s="102" t="s">
-        <v>218</v>
-      </c>
-      <c r="E19" s="98" t="s">
+      <c r="I19" s="97" t="s">
         <v>220</v>
       </c>
-      <c r="F19" s="98" t="s">
-        <v>221</v>
-      </c>
-      <c r="G19" s="99" t="s">
-        <v>222</v>
-      </c>
-      <c r="H19" s="99" t="s">
-        <v>223</v>
-      </c>
-      <c r="I19" s="98" t="s">
-        <v>224</v>
-      </c>
-      <c r="J19" s="99" t="s">
+      <c r="J19" s="98" t="s">
         <v>69</v>
       </c>
-      <c r="K19" s="62">
+      <c r="K19" s="61">
         <v>1</v>
       </c>
-      <c r="L19" s="96">
+      <c r="L19" s="95">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M19" s="63" t="s">
+      <c r="M19" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="N19" s="63"/>
-    </row>
-    <row r="20" spans="1:14" ht="15" thickBot="1">
+      <c r="N19" s="62"/>
+    </row>
+    <row r="20" spans="1:14" ht="15.75" thickBot="1">
       <c r="A20" s="5">
         <v>18</v>
       </c>
-      <c r="B20" s="132" t="s">
+      <c r="B20" s="133" t="s">
         <v>82</v>
       </c>
-      <c r="C20" s="58" t="s">
+      <c r="C20" s="57" t="s">
+        <v>168</v>
+      </c>
+      <c r="D20" s="39" t="s">
+        <v>169</v>
+      </c>
+      <c r="E20" s="148" t="s">
+        <v>43</v>
+      </c>
+      <c r="F20" s="39" t="s">
+        <v>170</v>
+      </c>
+      <c r="G20" s="22" t="s">
+        <v>171</v>
+      </c>
+      <c r="H20" s="22" t="s">
         <v>172</v>
       </c>
-      <c r="D20" s="40" t="s">
-        <v>173</v>
-      </c>
-      <c r="E20" s="40" t="s">
-        <v>174</v>
-      </c>
-      <c r="F20" s="40" t="s">
-        <v>174</v>
-      </c>
-      <c r="G20" s="23" t="s">
-        <v>175</v>
-      </c>
-      <c r="H20" s="23" t="s">
-        <v>176</v>
-      </c>
-      <c r="I20" s="22" t="s">
+      <c r="I20" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="J20" s="23" t="s">
+      <c r="J20" s="22" t="s">
         <v>69</v>
       </c>
       <c r="K20" s="13">
@@ -2981,119 +3046,119 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M20" s="59" t="s">
+      <c r="M20" s="58" t="s">
         <v>20</v>
       </c>
-      <c r="N20" s="59"/>
-    </row>
-    <row r="21" spans="1:14" ht="15" thickBot="1">
+      <c r="N20" s="58"/>
+    </row>
+    <row r="21" spans="1:14" ht="15.75" thickBot="1">
       <c r="A21" s="5">
         <v>19</v>
       </c>
-      <c r="B21" s="134"/>
-      <c r="C21" s="41" t="s">
+      <c r="B21" s="135"/>
+      <c r="C21" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="D21" s="42" t="s">
+      <c r="D21" s="41" t="s">
         <v>84</v>
       </c>
-      <c r="E21" s="42" t="s">
+      <c r="E21" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="F21" s="42" t="s">
+      <c r="F21" s="41" t="s">
         <v>85</v>
       </c>
-      <c r="G21" s="42" t="s">
+      <c r="G21" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="H21" s="43"/>
-      <c r="I21" s="43"/>
-      <c r="J21" s="42" t="s">
+      <c r="H21" s="42"/>
+      <c r="I21" s="42"/>
+      <c r="J21" s="41" t="s">
         <v>69</v>
       </c>
-      <c r="K21" s="43">
+      <c r="K21" s="42">
         <v>1</v>
       </c>
       <c r="L21" s="10">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M21" s="44" t="s">
+      <c r="M21" s="43" t="s">
         <v>87</v>
       </c>
-      <c r="N21" s="44"/>
-    </row>
-    <row r="22" spans="1:14" ht="15" thickBot="1">
+      <c r="N21" s="43"/>
+    </row>
+    <row r="22" spans="1:14" ht="15.75" thickBot="1">
       <c r="A22" s="5">
         <v>20</v>
       </c>
-      <c r="B22" s="132" t="s">
+      <c r="B22" s="133" t="s">
         <v>88</v>
       </c>
-      <c r="C22" s="120" t="s">
+      <c r="C22" s="118" t="s">
         <v>89</v>
       </c>
-      <c r="D22" s="124" t="s">
-        <v>242</v>
-      </c>
-      <c r="E22" s="22" t="s">
+      <c r="D22" s="122" t="s">
+        <v>238</v>
+      </c>
+      <c r="E22" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="F22" s="22" t="s">
+      <c r="F22" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="G22" s="23" t="s">
+      <c r="G22" s="22" t="s">
         <v>59</v>
       </c>
       <c r="H22" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="I22" s="22" t="s">
+      <c r="I22" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="J22" s="22" t="s">
+      <c r="J22" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="K22" s="121">
+      <c r="K22" s="119">
         <v>3</v>
       </c>
-      <c r="L22" s="121">
+      <c r="L22" s="119">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="M22" s="122" t="s">
+      <c r="M22" s="120" t="s">
         <v>20</v>
       </c>
-      <c r="N22" s="123"/>
-    </row>
-    <row r="23" spans="1:14" ht="15" thickBot="1">
+      <c r="N22" s="121"/>
+    </row>
+    <row r="23" spans="1:14" ht="15.75" thickBot="1">
       <c r="A23" s="5">
         <v>21</v>
       </c>
-      <c r="B23" s="133"/>
-      <c r="C23" s="104" t="s">
-        <v>164</v>
-      </c>
-      <c r="D23" s="109" t="s">
-        <v>165</v>
-      </c>
-      <c r="E23" s="24" t="s">
+      <c r="B23" s="134"/>
+      <c r="C23" s="103" t="s">
+        <v>160</v>
+      </c>
+      <c r="D23" s="108" t="s">
+        <v>161</v>
+      </c>
+      <c r="E23" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="F23" s="24" t="s">
-        <v>166</v>
-      </c>
-      <c r="G23" s="25" t="s">
-        <v>154</v>
-      </c>
-      <c r="H23" s="48" t="s">
-        <v>233</v>
-      </c>
-      <c r="I23" s="24" t="s">
+      <c r="F23" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="G23" s="24" t="s">
+        <v>150</v>
+      </c>
+      <c r="H23" s="47" t="s">
+        <v>229</v>
+      </c>
+      <c r="I23" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="J23" s="47" t="s">
-        <v>167</v>
+      <c r="J23" s="46" t="s">
+        <v>163</v>
       </c>
       <c r="K23" s="6">
         <v>1</v>
@@ -3102,39 +3167,39 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M23" s="50" t="s">
-        <v>177</v>
-      </c>
-      <c r="N23" s="50"/>
-    </row>
-    <row r="24" spans="1:14" ht="15" thickBot="1">
+      <c r="M23" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="N23" s="49"/>
+    </row>
+    <row r="24" spans="1:14" ht="15.75" thickBot="1">
       <c r="A24" s="5">
         <v>22</v>
       </c>
-      <c r="B24" s="133"/>
-      <c r="C24" s="105" t="s">
-        <v>192</v>
-      </c>
-      <c r="D24" s="110" t="s">
-        <v>185</v>
-      </c>
-      <c r="E24" s="24" t="s">
+      <c r="B24" s="134"/>
+      <c r="C24" s="104" t="s">
+        <v>188</v>
+      </c>
+      <c r="D24" s="109" t="s">
+        <v>181</v>
+      </c>
+      <c r="E24" s="23" t="s">
         <v>90</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="H24" s="106" t="s">
-        <v>188</v>
-      </c>
-      <c r="I24" s="24" t="s">
+        <v>183</v>
+      </c>
+      <c r="H24" s="105" t="s">
+        <v>184</v>
+      </c>
+      <c r="I24" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="J24" s="47" t="s">
-        <v>198</v>
+      <c r="J24" s="46" t="s">
+        <v>194</v>
       </c>
       <c r="K24" s="6">
         <v>1</v>
@@ -3143,39 +3208,39 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M24" s="53" t="s">
+      <c r="M24" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="N24" s="53"/>
-    </row>
-    <row r="25" spans="1:14" ht="15" thickBot="1">
+      <c r="N24" s="52"/>
+    </row>
+    <row r="25" spans="1:14" ht="15.75" thickBot="1">
       <c r="A25" s="5">
         <v>23</v>
       </c>
-      <c r="B25" s="133"/>
-      <c r="C25" s="105" t="s">
-        <v>193</v>
-      </c>
-      <c r="D25" s="110" t="s">
+      <c r="B25" s="134"/>
+      <c r="C25" s="104" t="s">
         <v>189</v>
       </c>
-      <c r="E25" s="24" t="s">
+      <c r="D25" s="109" t="s">
+        <v>185</v>
+      </c>
+      <c r="E25" s="23" t="s">
         <v>90</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="G25" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="H25" s="105" t="s">
         <v>187</v>
       </c>
-      <c r="H25" s="106" t="s">
-        <v>191</v>
-      </c>
-      <c r="I25" s="24" t="s">
+      <c r="I25" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="J25" s="47" t="s">
-        <v>199</v>
+      <c r="J25" s="46" t="s">
+        <v>195</v>
       </c>
       <c r="K25" s="6">
         <v>1</v>
@@ -3184,39 +3249,39 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M25" s="50" t="s">
+      <c r="M25" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="N25" s="50"/>
-    </row>
-    <row r="26" spans="1:14" ht="15" thickBot="1">
+      <c r="N25" s="49"/>
+    </row>
+    <row r="26" spans="1:14" ht="15.75" thickBot="1">
       <c r="A26" s="5">
         <v>24</v>
       </c>
-      <c r="B26" s="133"/>
-      <c r="C26" s="105" t="s">
-        <v>195</v>
-      </c>
-      <c r="D26" s="110" t="s">
+      <c r="B26" s="134"/>
+      <c r="C26" s="104" t="s">
+        <v>191</v>
+      </c>
+      <c r="D26" s="109" t="s">
+        <v>192</v>
+      </c>
+      <c r="E26" s="46" t="s">
+        <v>90</v>
+      </c>
+      <c r="F26" s="106" t="s">
+        <v>190</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="H26" s="107" t="s">
+        <v>193</v>
+      </c>
+      <c r="I26" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="J26" s="46" t="s">
         <v>196</v>
-      </c>
-      <c r="E26" s="47" t="s">
-        <v>90</v>
-      </c>
-      <c r="F26" s="107" t="s">
-        <v>194</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="H26" s="108" t="s">
-        <v>197</v>
-      </c>
-      <c r="I26" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="J26" s="47" t="s">
-        <v>200</v>
       </c>
       <c r="K26" s="6">
         <v>1</v>
@@ -3225,81 +3290,81 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M26" s="50" t="s">
+      <c r="M26" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="N26" s="50"/>
-    </row>
-    <row r="27" spans="1:14" ht="15" thickBot="1">
+      <c r="N26" s="49"/>
+    </row>
+    <row r="27" spans="1:14" ht="15.75" thickBot="1">
       <c r="A27" s="5">
         <v>25</v>
       </c>
-      <c r="B27" s="133"/>
-      <c r="C27" s="125" t="s">
-        <v>246</v>
-      </c>
-      <c r="D27" s="126" t="s">
-        <v>202</v>
-      </c>
-      <c r="E27" s="127" t="s">
-        <v>245</v>
-      </c>
-      <c r="F27" s="128" t="s">
-        <v>244</v>
-      </c>
-      <c r="G27" s="128" t="s">
+      <c r="B27" s="134"/>
+      <c r="C27" s="123" t="s">
+        <v>242</v>
+      </c>
+      <c r="D27" s="124" t="s">
+        <v>198</v>
+      </c>
+      <c r="E27" s="125" t="s">
+        <v>241</v>
+      </c>
+      <c r="F27" s="126" t="s">
+        <v>240</v>
+      </c>
+      <c r="G27" s="126" t="s">
         <v>114</v>
       </c>
-      <c r="H27" s="129" t="s">
-        <v>243</v>
-      </c>
-      <c r="I27" s="71" t="s">
+      <c r="H27" s="127" t="s">
+        <v>239</v>
+      </c>
+      <c r="I27" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="J27" s="72" t="s">
-        <v>201</v>
-      </c>
-      <c r="K27" s="73">
+      <c r="J27" s="71" t="s">
+        <v>197</v>
+      </c>
+      <c r="K27" s="72">
         <v>2</v>
       </c>
-      <c r="L27" s="73">
+      <c r="L27" s="72">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="M27" s="130" t="s">
+      <c r="M27" s="128" t="s">
         <v>20</v>
       </c>
-      <c r="N27" s="117" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" ht="15" thickBot="1">
+      <c r="N27" s="150" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="15.75" thickBot="1">
       <c r="A28" s="5">
         <v>26</v>
       </c>
-      <c r="B28" s="133"/>
-      <c r="C28" s="31" t="s">
+      <c r="B28" s="134"/>
+      <c r="C28" s="30" t="s">
         <v>94</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="E28" s="24" t="s">
+      <c r="E28" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="F28" s="24" t="s">
+      <c r="F28" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="G28" s="25" t="s">
+      <c r="G28" s="24" t="s">
         <v>59</v>
       </c>
       <c r="H28" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="I28" s="24" t="s">
+      <c r="I28" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="J28" s="24" t="s">
+      <c r="J28" s="23" t="s">
         <v>98</v>
       </c>
       <c r="K28" s="6">
@@ -3309,38 +3374,38 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="M28" s="51" t="s">
+      <c r="M28" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="N28" s="51"/>
-    </row>
-    <row r="29" spans="1:14" ht="15" thickBot="1">
+      <c r="N28" s="50"/>
+    </row>
+    <row r="29" spans="1:14" ht="15.75" thickBot="1">
       <c r="A29" s="5">
         <v>27</v>
       </c>
-      <c r="B29" s="133"/>
-      <c r="C29" s="31" t="s">
+      <c r="B29" s="134"/>
+      <c r="C29" s="30" t="s">
         <v>99</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="E29" s="24" t="s">
+        <v>180</v>
+      </c>
+      <c r="E29" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="F29" s="24" t="s">
+      <c r="F29" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="G29" s="25" t="s">
+      <c r="G29" s="24" t="s">
         <v>59</v>
       </c>
       <c r="H29" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="I29" s="24" t="s">
+      <c r="I29" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="J29" s="24" t="s">
+      <c r="J29" s="23" t="s">
         <v>102</v>
       </c>
       <c r="K29" s="6">
@@ -3350,38 +3415,38 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M29" s="51" t="s">
+      <c r="M29" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="N29" s="51"/>
-    </row>
-    <row r="30" spans="1:14" ht="15" thickBot="1">
+      <c r="N29" s="50"/>
+    </row>
+    <row r="30" spans="1:14" ht="15.75" thickBot="1">
       <c r="A30" s="5">
         <v>28</v>
       </c>
-      <c r="B30" s="133"/>
-      <c r="C30" s="31" t="s">
+      <c r="B30" s="134"/>
+      <c r="C30" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="D30" s="24" t="s">
+      <c r="D30" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="E30" s="24" t="s">
+      <c r="E30" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="F30" s="26" t="s">
+      <c r="F30" s="25" t="s">
         <v>106</v>
       </c>
-      <c r="G30" s="25" t="s">
+      <c r="G30" s="24" t="s">
         <v>107</v>
       </c>
       <c r="H30" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="I30" s="25" t="s">
+      <c r="I30" s="24" t="s">
         <v>109</v>
       </c>
-      <c r="J30" s="24" t="s">
+      <c r="J30" s="23" t="s">
         <v>110</v>
       </c>
       <c r="K30" s="6">
@@ -3391,38 +3456,38 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M30" s="51" t="s">
+      <c r="M30" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="N30" s="51"/>
-    </row>
-    <row r="31" spans="1:14" ht="15" thickBot="1">
+      <c r="N30" s="50"/>
+    </row>
+    <row r="31" spans="1:14" ht="15.75" thickBot="1">
       <c r="A31" s="5">
         <v>29</v>
       </c>
-      <c r="B31" s="133"/>
-      <c r="C31" s="31" t="s">
+      <c r="B31" s="134"/>
+      <c r="C31" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="D31" s="24" t="s">
+      <c r="D31" s="23" t="s">
         <v>112</v>
       </c>
-      <c r="E31" s="24" t="s">
+      <c r="E31" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="F31" s="24" t="s">
+      <c r="F31" s="23" t="s">
         <v>113</v>
       </c>
-      <c r="G31" s="25" t="s">
+      <c r="G31" s="24" t="s">
         <v>114</v>
       </c>
       <c r="H31" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="I31" s="24" t="s">
+      <c r="I31" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="J31" s="24" t="s">
+      <c r="J31" s="23" t="s">
         <v>116</v>
       </c>
       <c r="K31" s="6">
@@ -3432,38 +3497,38 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M31" s="51" t="s">
+      <c r="M31" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="N31" s="51"/>
-    </row>
-    <row r="32" spans="1:14" ht="15" thickBot="1">
+      <c r="N31" s="50"/>
+    </row>
+    <row r="32" spans="1:14" ht="15.75" thickBot="1">
       <c r="A32" s="5">
         <v>30</v>
       </c>
-      <c r="B32" s="134"/>
-      <c r="C32" s="32" t="s">
+      <c r="B32" s="135"/>
+      <c r="C32" s="31" t="s">
         <v>117</v>
       </c>
       <c r="D32" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="E32" s="27" t="s">
+      <c r="E32" s="26" t="s">
         <v>90</v>
       </c>
-      <c r="F32" s="27" t="s">
+      <c r="F32" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="G32" s="28" t="s">
+      <c r="G32" s="27" t="s">
         <v>59</v>
       </c>
       <c r="H32" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="I32" s="27" t="s">
+      <c r="I32" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="J32" s="27" t="s">
+      <c r="J32" s="26" t="s">
         <v>121</v>
       </c>
       <c r="K32" s="11">
@@ -3473,81 +3538,81 @@
         <f t="shared" si="1"/>
         <v>48</v>
       </c>
-      <c r="M32" s="67" t="s">
+      <c r="M32" s="66" t="s">
         <v>20</v>
       </c>
-      <c r="N32" s="67"/>
-    </row>
-    <row r="33" spans="1:14" ht="15" thickBot="1">
+      <c r="N32" s="66"/>
+    </row>
+    <row r="33" spans="1:14" ht="15.75" thickBot="1">
       <c r="A33" s="5">
         <v>31</v>
       </c>
-      <c r="B33" s="133" t="s">
+      <c r="B33" s="134" t="s">
         <v>122</v>
       </c>
-      <c r="C33" s="111" t="s">
-        <v>183</v>
-      </c>
-      <c r="D33" s="113" t="s">
+      <c r="C33" s="110" t="s">
+        <v>179</v>
+      </c>
+      <c r="D33" s="112" t="s">
         <v>123</v>
       </c>
-      <c r="E33" s="29" t="s">
-        <v>180</v>
-      </c>
-      <c r="F33" s="90" t="s">
-        <v>181</v>
-      </c>
-      <c r="G33" s="112" t="s">
-        <v>182</v>
-      </c>
-      <c r="H33" s="30" t="s">
+      <c r="E33" s="139" t="s">
+        <v>247</v>
+      </c>
+      <c r="F33" s="28" t="s">
+        <v>176</v>
+      </c>
+      <c r="G33" s="89" t="s">
+        <v>177</v>
+      </c>
+      <c r="H33" s="111" t="s">
+        <v>178</v>
+      </c>
+      <c r="I33" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="I33" s="29" t="s">
-        <v>18</v>
-      </c>
-      <c r="J33" s="30" t="s">
+      <c r="J33" s="29" t="s">
         <v>69</v>
       </c>
       <c r="K33" s="14">
         <v>1</v>
       </c>
-      <c r="L33" s="90">
+      <c r="L33" s="89">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M33" s="91" t="s">
+      <c r="M33" s="90" t="s">
         <v>20</v>
       </c>
-      <c r="N33" s="91"/>
-    </row>
-    <row r="34" spans="1:14" ht="15" thickBot="1">
+      <c r="N33" s="90"/>
+    </row>
+    <row r="34" spans="1:14" ht="15.75" thickBot="1">
       <c r="A34" s="5">
         <v>32</v>
       </c>
-      <c r="B34" s="133"/>
-      <c r="C34" s="31" t="s">
+      <c r="B34" s="134"/>
+      <c r="C34" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="D34" s="24" t="s">
+      <c r="D34" s="23" t="s">
         <v>125</v>
       </c>
-      <c r="E34" s="24" t="s">
+      <c r="E34" s="23" t="s">
         <v>126</v>
       </c>
-      <c r="F34" s="24" t="s">
+      <c r="F34" s="23" t="s">
         <v>127</v>
       </c>
-      <c r="G34" s="25" t="s">
+      <c r="G34" s="24" t="s">
         <v>128</v>
       </c>
       <c r="H34" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="I34" s="24" t="s">
+      <c r="I34" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="J34" s="25" t="s">
+      <c r="J34" s="24" t="s">
         <v>69</v>
       </c>
       <c r="K34" s="8">
@@ -3557,163 +3622,163 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M34" s="51" t="s">
+      <c r="M34" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="N34" s="51"/>
-    </row>
-    <row r="35" spans="1:14" ht="15" thickBot="1">
+      <c r="N34" s="50"/>
+    </row>
+    <row r="35" spans="1:14" ht="15.75" thickBot="1">
       <c r="A35" s="5">
         <v>33</v>
       </c>
-      <c r="B35" s="133"/>
-      <c r="C35" s="68" t="s">
-        <v>168</v>
-      </c>
-      <c r="D35" s="69" t="s">
+      <c r="B35" s="134"/>
+      <c r="C35" s="67" t="s">
+        <v>164</v>
+      </c>
+      <c r="D35" s="68" t="s">
         <v>130</v>
       </c>
-      <c r="E35" s="69" t="s">
-        <v>169</v>
-      </c>
-      <c r="F35" s="57" t="s">
-        <v>171</v>
-      </c>
-      <c r="G35" s="60" t="s">
-        <v>170</v>
-      </c>
-      <c r="H35" s="56"/>
-      <c r="I35" s="60" t="s">
+      <c r="E35" s="68" t="s">
+        <v>165</v>
+      </c>
+      <c r="F35" s="56" t="s">
+        <v>167</v>
+      </c>
+      <c r="G35" s="59" t="s">
+        <v>166</v>
+      </c>
+      <c r="H35" s="55"/>
+      <c r="I35" s="59" t="s">
         <v>18</v>
       </c>
-      <c r="J35" s="61" t="s">
+      <c r="J35" s="60" t="s">
         <v>131</v>
       </c>
-      <c r="K35" s="56">
+      <c r="K35" s="55">
         <v>1</v>
       </c>
-      <c r="L35" s="57">
+      <c r="L35" s="56">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M35" s="70" t="s">
+      <c r="M35" s="69" t="s">
         <v>87</v>
       </c>
-      <c r="N35" s="139"/>
-    </row>
-    <row r="36" spans="1:14" ht="15" thickBot="1">
+      <c r="N35" s="131"/>
+    </row>
+    <row r="36" spans="1:14" ht="15.75" thickBot="1">
       <c r="A36" s="5">
         <v>34</v>
       </c>
-      <c r="B36" s="132" t="s">
+      <c r="B36" s="133" t="s">
         <v>132</v>
       </c>
-      <c r="C36" s="74" t="s">
-        <v>249</v>
-      </c>
-      <c r="D36" s="75" t="s">
+      <c r="C36" s="73" t="s">
+        <v>245</v>
+      </c>
+      <c r="D36" s="74" t="s">
         <v>133</v>
       </c>
-      <c r="E36" s="75" t="s">
+      <c r="E36" s="143" t="s">
+        <v>43</v>
+      </c>
+      <c r="F36" s="74" t="s">
         <v>134</v>
       </c>
-      <c r="F36" s="75" t="s">
-        <v>134</v>
-      </c>
-      <c r="G36" s="75" t="s">
+      <c r="G36" s="74" t="s">
         <v>135</v>
       </c>
-      <c r="H36" s="75" t="s">
+      <c r="H36" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="I36" s="75" t="s">
+      <c r="I36" s="74" t="s">
         <v>18</v>
       </c>
-      <c r="J36" s="75" t="s">
+      <c r="J36" s="74" t="s">
         <v>69</v>
       </c>
-      <c r="K36" s="78">
+      <c r="K36" s="77">
         <v>1</v>
       </c>
-      <c r="L36" s="78">
+      <c r="L36" s="77">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M36" s="138" t="s">
+      <c r="M36" s="130" t="s">
         <v>136</v>
       </c>
-      <c r="N36" s="141" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" ht="15" thickBot="1">
+      <c r="N36" s="132" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" ht="15.75" thickBot="1">
       <c r="A37" s="5">
         <v>35</v>
       </c>
-      <c r="B37" s="133"/>
-      <c r="C37" s="33" t="s">
+      <c r="B37" s="134"/>
+      <c r="C37" s="140" t="s">
+        <v>250</v>
+      </c>
+      <c r="D37" s="145" t="s">
         <v>137</v>
       </c>
-      <c r="D37" s="34" t="s">
+      <c r="E37" s="144" t="s">
+        <v>43</v>
+      </c>
+      <c r="F37" s="142" t="s">
+        <v>251</v>
+      </c>
+      <c r="G37" s="146" t="s">
+        <v>252</v>
+      </c>
+      <c r="H37" s="146" t="s">
+        <v>253</v>
+      </c>
+      <c r="I37" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="J37" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="E37" s="34" t="s">
-        <v>43</v>
-      </c>
-      <c r="F37" s="34" t="s">
-        <v>139</v>
-      </c>
-      <c r="G37" s="34" t="s">
-        <v>140</v>
-      </c>
-      <c r="H37" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="I37" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="J37" s="35" t="s">
-        <v>141</v>
-      </c>
-      <c r="K37" s="16">
+      <c r="K37" s="6">
         <v>2</v>
       </c>
-      <c r="L37" s="7">
+      <c r="L37" s="6">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="M37" s="52" t="s">
-        <v>142</v>
+        <v>20</v>
       </c>
       <c r="N37" s="52"/>
     </row>
-    <row r="38" spans="1:14" ht="15" thickBot="1">
+    <row r="38" spans="1:14" ht="15.75" thickBot="1">
       <c r="A38" s="5">
         <v>36</v>
       </c>
-      <c r="B38" s="133"/>
-      <c r="C38" s="33" t="s">
-        <v>143</v>
-      </c>
-      <c r="D38" s="34" t="s">
-        <v>144</v>
-      </c>
-      <c r="E38" s="34" t="s">
+      <c r="B38" s="134"/>
+      <c r="C38" s="32" t="s">
+        <v>139</v>
+      </c>
+      <c r="D38" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="E38" s="33" t="s">
         <v>43</v>
       </c>
-      <c r="F38" s="34" t="s">
-        <v>145</v>
-      </c>
-      <c r="G38" s="34" t="s">
+      <c r="F38" s="33" t="s">
+        <v>141</v>
+      </c>
+      <c r="G38" s="33" t="s">
         <v>135</v>
       </c>
-      <c r="H38" s="34" t="s">
+      <c r="H38" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="I38" s="34" t="s">
+      <c r="I38" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="J38" s="35" t="s">
+      <c r="J38" s="34" t="s">
         <v>69</v>
       </c>
       <c r="K38" s="16">
@@ -3723,39 +3788,39 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M38" s="52" t="s">
+      <c r="M38" s="51" t="s">
         <v>136</v>
       </c>
-      <c r="N38" s="52"/>
-    </row>
-    <row r="39" spans="1:14" ht="15" thickBot="1">
+      <c r="N38" s="51"/>
+    </row>
+    <row r="39" spans="1:14" ht="15.75" thickBot="1">
       <c r="A39" s="5">
         <v>37</v>
       </c>
-      <c r="B39" s="133"/>
+      <c r="B39" s="134"/>
       <c r="C39" s="15" t="s">
-        <v>146</v>
-      </c>
-      <c r="D39" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="E39" s="24" t="s">
+        <v>142</v>
+      </c>
+      <c r="D39" s="23" t="s">
+        <v>143</v>
+      </c>
+      <c r="E39" s="23" t="s">
         <v>43</v>
       </c>
-      <c r="F39" s="24" t="s">
-        <v>148</v>
-      </c>
-      <c r="G39" s="24" t="s">
-        <v>149</v>
-      </c>
-      <c r="H39" s="24" t="s">
-        <v>148</v>
-      </c>
-      <c r="I39" s="24" t="s">
+      <c r="F39" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="G39" s="23" t="s">
+        <v>145</v>
+      </c>
+      <c r="H39" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="I39" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="J39" s="25" t="s">
-        <v>141</v>
+      <c r="J39" s="24" t="s">
+        <v>138</v>
       </c>
       <c r="K39" s="6">
         <v>1</v>
@@ -3764,38 +3829,38 @@
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="M39" s="53" t="s">
+      <c r="M39" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="N39" s="53"/>
-    </row>
-    <row r="40" spans="1:14" ht="15" thickBot="1">
+      <c r="N39" s="52"/>
+    </row>
+    <row r="40" spans="1:14" ht="15.75" thickBot="1">
       <c r="A40" s="5">
         <v>38</v>
       </c>
-      <c r="B40" s="133"/>
-      <c r="C40" s="31" t="s">
+      <c r="B40" s="134"/>
+      <c r="C40" s="30" t="s">
+        <v>146</v>
+      </c>
+      <c r="D40" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="E40" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="F40" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="G40" s="23" t="s">
         <v>150</v>
       </c>
-      <c r="D40" s="24" t="s">
+      <c r="H40" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="E40" s="24" t="s">
-        <v>152</v>
-      </c>
-      <c r="F40" s="24" t="s">
-        <v>153</v>
-      </c>
-      <c r="G40" s="24" t="s">
-        <v>154</v>
-      </c>
-      <c r="H40" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="I40" s="24" t="s">
+      <c r="I40" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="J40" s="25" t="s">
+      <c r="J40" s="24" t="s">
         <v>69</v>
       </c>
       <c r="K40" s="8">
@@ -3805,94 +3870,102 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="M40" s="50" t="s">
+      <c r="M40" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="N40" s="50"/>
-    </row>
-    <row r="41" spans="1:14" ht="15" thickBot="1">
+      <c r="N40" s="49"/>
+    </row>
+    <row r="41" spans="1:14" ht="15.75" thickBot="1">
       <c r="A41" s="5">
         <v>39</v>
       </c>
-      <c r="B41" s="133"/>
-      <c r="C41" s="36" t="s">
-        <v>156</v>
-      </c>
-      <c r="D41" s="17"/>
-      <c r="E41" s="37" t="s">
-        <v>157</v>
+      <c r="B41" s="134"/>
+      <c r="C41" s="35" t="s">
+        <v>152</v>
+      </c>
+      <c r="D41" s="141" t="s">
+        <v>248</v>
+      </c>
+      <c r="E41" s="36" t="s">
+        <v>153</v>
       </c>
       <c r="F41" s="17" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="G41" s="17"/>
       <c r="H41" s="17"/>
       <c r="I41" s="17"/>
       <c r="J41" s="17"/>
       <c r="K41" s="17">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L41" s="7">
         <f t="shared" si="1"/>
-        <v>30</v>
-      </c>
-      <c r="M41" s="54" t="s">
+        <v>6</v>
+      </c>
+      <c r="M41" s="53" t="s">
         <v>18</v>
       </c>
-      <c r="N41" s="54"/>
-    </row>
-    <row r="42" spans="1:14" ht="15" thickBot="1">
-      <c r="A42" s="18">
+      <c r="N41" s="149" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" ht="15.75" thickBot="1">
+      <c r="A42" s="5">
         <v>40</v>
       </c>
-      <c r="B42" s="134"/>
-      <c r="C42" s="38" t="s">
-        <v>158</v>
-      </c>
-      <c r="D42" s="19"/>
-      <c r="E42" s="39" t="s">
-        <v>159</v>
-      </c>
-      <c r="F42" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="G42" s="19"/>
-      <c r="H42" s="19"/>
-      <c r="I42" s="19"/>
-      <c r="J42" s="19"/>
-      <c r="K42" s="19">
+      <c r="B42" s="135"/>
+      <c r="C42" s="37" t="s">
+        <v>154</v>
+      </c>
+      <c r="D42" s="147" t="s">
+        <v>249</v>
+      </c>
+      <c r="E42" s="38" t="s">
+        <v>155</v>
+      </c>
+      <c r="F42" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="G42" s="18"/>
+      <c r="H42" s="18"/>
+      <c r="I42" s="18"/>
+      <c r="J42" s="18"/>
+      <c r="K42" s="18">
         <v>5</v>
       </c>
       <c r="L42" s="10">
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
-      <c r="M42" s="55" t="s">
+      <c r="M42" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="N42" s="140"/>
+      <c r="N42" s="151" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="43" spans="1:14">
       <c r="A43"/>
-      <c r="C43" s="20"/>
-      <c r="D43" s="20"/>
-      <c r="E43" s="20"/>
-      <c r="F43" s="20"/>
-      <c r="G43" s="20"/>
-      <c r="H43" s="20"/>
-      <c r="I43" s="20"/>
-      <c r="J43" s="20"/>
+      <c r="C43" s="19"/>
+      <c r="D43" s="19"/>
+      <c r="E43" s="19"/>
+      <c r="F43" s="19"/>
+      <c r="G43" s="19"/>
+      <c r="H43" s="19"/>
+      <c r="I43" s="19"/>
+      <c r="J43" s="19"/>
     </row>
     <row r="44" spans="1:14">
       <c r="A44"/>
-      <c r="C44" s="20"/>
-      <c r="D44" s="20"/>
-      <c r="E44" s="20"/>
-      <c r="F44" s="20"/>
-      <c r="G44" s="20"/>
-      <c r="H44" s="20"/>
-      <c r="I44" s="20"/>
-      <c r="J44" s="20"/>
+      <c r="C44" s="19"/>
+      <c r="D44" s="19"/>
+      <c r="E44" s="19"/>
+      <c r="F44" s="19"/>
+      <c r="G44" s="19"/>
+      <c r="H44" s="19"/>
+      <c r="I44" s="19"/>
+      <c r="J44" s="19"/>
     </row>
     <row r="45" spans="1:14">
       <c r="A45"/>
@@ -3917,8 +3990,8 @@
     </row>
     <row r="52" spans="1:14" ht="15.75" customHeight="1">
       <c r="A52"/>
-      <c r="M52" s="46"/>
-      <c r="N52" s="46"/>
+      <c r="M52" s="45"/>
+      <c r="N52" s="45"/>
     </row>
     <row r="53" spans="1:14">
       <c r="A53"/>
@@ -3936,10 +4009,10 @@
       <c r="A57"/>
     </row>
     <row r="58" spans="1:14">
-      <c r="H58" s="21"/>
+      <c r="H58" s="20"/>
     </row>
     <row r="59" spans="1:14">
-      <c r="H59" s="21"/>
+      <c r="H59" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -3951,7 +4024,7 @@
     <mergeCell ref="B22:B32"/>
     <mergeCell ref="B33:B35"/>
   </mergeCells>
-  <phoneticPr fontId="22" type="noConversion"/>
+  <phoneticPr fontId="23" type="noConversion"/>
   <conditionalFormatting sqref="M21:N21">
     <cfRule type="dataBar" priority="39">
       <dataBar>
@@ -4137,9 +4210,10 @@
     <hyperlink ref="M16" r:id="rId34" xr:uid="{E7A9FE43-2492-4F96-944F-8153D9DD3BC5}"/>
     <hyperlink ref="M5" r:id="rId35" xr:uid="{307763C7-77E9-4298-8365-93694DC5AA9D}"/>
     <hyperlink ref="M27" r:id="rId36" xr:uid="{57DF62BF-599B-4CBE-A3A7-7AFF81EE4B99}"/>
+    <hyperlink ref="M37" r:id="rId37" xr:uid="{1914B45F-070C-4E08-B2BC-BA04E54BEF9D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId37"/>
+  <pageSetup orientation="portrait" r:id="rId38"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
